--- a/premise/data/additional_inventories/lci-rail-freight.xlsx
+++ b/premise/data/additional_inventories/lci-rail-freight.xlsx
@@ -1358,15 +1358,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A08E695-FC79-4DF0-ACCB-3B3F78317B74}">
-  <dimension ref="A1:H943"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{2A08E695-FC79-4DF0-ACCB-3B3F78317B74}">
+  <dimension ref="A1:Z966"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="61.83203125" customWidth="1"/>
     <col min="2" max="2" width="11.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ns3:dyDescent="0.2">
       <c r="A1" t="s">
         <v>228</v>
       </c>
@@ -1374,7 +1374,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" ns3:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1382,7 +1382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ns3:dyDescent="0.2">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -1390,7 +1390,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" ns3:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1398,7 +1398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" ns3:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1406,7 +1406,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" ns3:dyDescent="0.2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -1414,7 +1414,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" ns3:dyDescent="0.2">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1422,7 +1422,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" ns3:dyDescent="0.2">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1430,12 +1430,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" ns3:dyDescent="0.2">
       <c r="A10" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" ns3:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>16</v>
       </c>
@@ -1461,7 +1461,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" ns3:dyDescent="0.2">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -1484,7 +1484,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" ns3:dyDescent="0.2">
       <c r="A13" t="s">
         <v>270</v>
       </c>
@@ -1507,7 +1507,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" ns3:dyDescent="0.2">
       <c r="A14" t="s">
         <v>266</v>
       </c>
@@ -1530,7 +1530,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" ns3:dyDescent="0.2">
       <c r="A15" t="s">
         <v>271</v>
       </c>
@@ -1553,7 +1553,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" ns3:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -1577,7 +1577,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" ns3:dyDescent="0.2">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -1601,7 +1601,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" ns3:dyDescent="0.2">
       <c r="A18" t="s">
         <v>1</v>
       </c>
@@ -1621,7 +1621,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" ns3:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>0</v>
       </c>
@@ -1629,7 +1629,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" ns3:dyDescent="0.2">
       <c r="A21" t="s">
         <v>2</v>
       </c>
@@ -1637,7 +1637,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" ns3:dyDescent="0.2">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -1645,7 +1645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" ns3:dyDescent="0.2">
       <c r="A23" t="s">
         <v>5</v>
       </c>
@@ -1653,7 +1653,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" ns3:dyDescent="0.2">
       <c r="A24" t="s">
         <v>7</v>
       </c>
@@ -1661,7 +1661,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" ns3:dyDescent="0.2">
       <c r="A25" t="s">
         <v>9</v>
       </c>
@@ -1669,7 +1669,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" ns3:dyDescent="0.2">
       <c r="A26" t="s">
         <v>10</v>
       </c>
@@ -1677,12 +1677,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" ns3:dyDescent="0.2">
       <c r="A27" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" ns3:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>16</v>
       </c>
@@ -1708,7 +1708,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" ns3:dyDescent="0.2">
       <c r="A29" t="s">
         <v>19</v>
       </c>
@@ -1731,7 +1731,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" ns3:dyDescent="0.2">
       <c r="A30" t="s">
         <v>40</v>
       </c>
@@ -1754,7 +1754,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" ns3:dyDescent="0.2">
       <c r="A31" t="s">
         <v>30</v>
       </c>
@@ -1778,7 +1778,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" ns3:dyDescent="0.2">
       <c r="A32" t="s">
         <v>33</v>
       </c>
@@ -1802,7 +1802,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8" ns3:dyDescent="0.2">
       <c r="A33" t="s">
         <v>37</v>
       </c>
@@ -1822,7 +1822,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:8" ns3:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>0</v>
       </c>
@@ -1830,7 +1830,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" ns3:dyDescent="0.2">
       <c r="A36" t="s">
         <v>2</v>
       </c>
@@ -1838,7 +1838,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:8" ns3:dyDescent="0.2">
       <c r="A37" t="s">
         <v>4</v>
       </c>
@@ -1846,7 +1846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" ns3:dyDescent="0.2">
       <c r="A38" t="s">
         <v>5</v>
       </c>
@@ -1854,7 +1854,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:8" ns3:dyDescent="0.2">
       <c r="A39" t="s">
         <v>7</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" ns3:dyDescent="0.2">
       <c r="A40" t="s">
         <v>9</v>
       </c>
@@ -1870,7 +1870,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:8" ns3:dyDescent="0.2">
       <c r="A41" t="s">
         <v>12</v>
       </c>
@@ -1878,12 +1878,12 @@
         <v>276</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8" ns3:dyDescent="0.2">
       <c r="A42" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:8" ns3:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>16</v>
       </c>
@@ -1909,7 +1909,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" ns3:dyDescent="0.2">
       <c r="A44" t="s">
         <v>19</v>
       </c>
@@ -1932,7 +1932,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:8" ns3:dyDescent="0.2">
       <c r="A45" t="s">
         <v>30</v>
       </c>
@@ -1956,7 +1956,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" ns3:dyDescent="0.2">
       <c r="A46" t="s">
         <v>33</v>
       </c>
@@ -1980,7 +1980,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:8" ns3:dyDescent="0.2">
       <c r="A47" t="s">
         <v>49</v>
       </c>
@@ -2003,7 +2003,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" ns3:dyDescent="0.2">
       <c r="A48" t="s">
         <v>52</v>
       </c>
@@ -2026,7 +2026,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:8" ns3:dyDescent="0.2">
       <c r="A49" t="s">
         <v>273</v>
       </c>
@@ -2049,7 +2049,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" ns3:dyDescent="0.2">
       <c r="A50" t="s">
         <v>56</v>
       </c>
@@ -2072,7 +2072,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:8" ns3:dyDescent="0.2">
       <c r="A51" t="s">
         <v>45</v>
       </c>
@@ -2092,7 +2092,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:8" ns3:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>0</v>
       </c>
@@ -2100,7 +2100,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8" ns3:dyDescent="0.2">
       <c r="A54" t="s">
         <v>2</v>
       </c>
@@ -2108,7 +2108,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:8" ns3:dyDescent="0.2">
       <c r="A55" t="s">
         <v>4</v>
       </c>
@@ -2116,7 +2116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:8" ns3:dyDescent="0.2">
       <c r="A56" t="s">
         <v>5</v>
       </c>
@@ -2124,7 +2124,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:8" ns3:dyDescent="0.2">
       <c r="A57" t="s">
         <v>7</v>
       </c>
@@ -2132,7 +2132,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:8" ns3:dyDescent="0.2">
       <c r="A58" t="s">
         <v>9</v>
       </c>
@@ -2140,12 +2140,12 @@
         <v>232</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:8" ns3:dyDescent="0.2">
       <c r="A59" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8" ns3:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>16</v>
       </c>
@@ -2171,7 +2171,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:8" ns3:dyDescent="0.2">
       <c r="A61" t="s">
         <v>62</v>
       </c>
@@ -2194,7 +2194,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:8" ns3:dyDescent="0.2">
       <c r="A62" t="s">
         <v>1</v>
       </c>
@@ -2217,7 +2217,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:8" ns3:dyDescent="0.2">
       <c r="A63" t="s">
         <v>67</v>
       </c>
@@ -2240,7 +2240,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:8" ns3:dyDescent="0.2">
       <c r="A64" t="s">
         <v>56</v>
       </c>
@@ -2263,7 +2263,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:8" ns3:dyDescent="0.2">
       <c r="A65" t="s">
         <v>68</v>
       </c>
@@ -2286,7 +2286,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:8" ns3:dyDescent="0.2">
       <c r="A66" t="s">
         <v>69</v>
       </c>
@@ -2309,7 +2309,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:8" ns3:dyDescent="0.2">
       <c r="A67" t="s">
         <v>72</v>
       </c>
@@ -2329,7 +2329,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" ns3:dyDescent="0.2">
       <c r="A68" t="s">
         <v>75</v>
       </c>
@@ -2349,7 +2349,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:8" ns3:dyDescent="0.2">
       <c r="A69" t="s">
         <v>77</v>
       </c>
@@ -2369,7 +2369,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:8" ns3:dyDescent="0.2">
       <c r="A70" t="s">
         <v>79</v>
       </c>
@@ -2389,7 +2389,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:8" ns3:dyDescent="0.2">
       <c r="A71" t="s">
         <v>81</v>
       </c>
@@ -2409,7 +2409,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:8" ns3:dyDescent="0.2">
       <c r="A72" t="s">
         <v>83</v>
       </c>
@@ -2429,7 +2429,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" ns3:dyDescent="0.2">
       <c r="A73" t="s">
         <v>85</v>
       </c>
@@ -2449,7 +2449,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:8" ns3:dyDescent="0.2">
       <c r="A74" t="s">
         <v>87</v>
       </c>
@@ -2469,7 +2469,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:8" ns3:dyDescent="0.2">
       <c r="A75" t="s">
         <v>88</v>
       </c>
@@ -2489,7 +2489,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:8" ns3:dyDescent="0.2">
       <c r="A76" t="s">
         <v>90</v>
       </c>
@@ -2509,7 +2509,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:8" ns3:dyDescent="0.2">
       <c r="A77" t="s">
         <v>92</v>
       </c>
@@ -2529,7 +2529,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:8" ns3:dyDescent="0.2">
       <c r="A78" t="s">
         <v>94</v>
       </c>
@@ -2549,7 +2549,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:8" ns3:dyDescent="0.2">
       <c r="A79" t="s">
         <v>96</v>
       </c>
@@ -2569,7 +2569,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:8" ns3:dyDescent="0.2">
       <c r="A80" t="s">
         <v>98</v>
       </c>
@@ -2589,7 +2589,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:8" ns3:dyDescent="0.2">
       <c r="A81" t="s">
         <v>100</v>
       </c>
@@ -2609,7 +2609,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:8" ns3:dyDescent="0.2">
       <c r="A82" t="s">
         <v>102</v>
       </c>
@@ -2629,7 +2629,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:8" ns3:dyDescent="0.2">
       <c r="A83" t="s">
         <v>104</v>
       </c>
@@ -2649,7 +2649,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:8" ns3:dyDescent="0.2">
       <c r="A84" t="s">
         <v>106</v>
       </c>
@@ -2669,7 +2669,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:8" ns3:dyDescent="0.2">
       <c r="A85" t="s">
         <v>108</v>
       </c>
@@ -2689,7 +2689,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:8" ns3:dyDescent="0.2">
       <c r="A86" t="s">
         <v>109</v>
       </c>
@@ -2709,7 +2709,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:8" ns3:dyDescent="0.2">
       <c r="A87" t="s">
         <v>111</v>
       </c>
@@ -2729,7 +2729,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:8" ns3:dyDescent="0.2">
       <c r="A88" t="s">
         <v>230</v>
       </c>
@@ -2749,7 +2749,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:8" ns3:dyDescent="0.2">
       <c r="A89" t="s">
         <v>113</v>
       </c>
@@ -2769,7 +2769,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:8" ns3:dyDescent="0.2">
       <c r="A90" t="s">
         <v>59</v>
       </c>
@@ -2789,7 +2789,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:8" ns3:dyDescent="0.2">
       <c r="A92" s="2" t="s">
         <v>0</v>
       </c>
@@ -2797,7 +2797,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:8" ns3:dyDescent="0.2">
       <c r="A93" t="s">
         <v>2</v>
       </c>
@@ -2805,7 +2805,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:8" ns3:dyDescent="0.2">
       <c r="A94" t="s">
         <v>4</v>
       </c>
@@ -2813,7 +2813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:8" ns3:dyDescent="0.2">
       <c r="A95" t="s">
         <v>5</v>
       </c>
@@ -2821,7 +2821,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:8" ns3:dyDescent="0.2">
       <c r="A96" t="s">
         <v>7</v>
       </c>
@@ -2829,7 +2829,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:8" ns3:dyDescent="0.2">
       <c r="A97" t="s">
         <v>9</v>
       </c>
@@ -2837,12 +2837,12 @@
         <v>232</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:8" ns3:dyDescent="0.2">
       <c r="A98" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:8" ns3:dyDescent="0.2">
       <c r="A99" s="2" t="s">
         <v>16</v>
       </c>
@@ -2868,7 +2868,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:8" ns3:dyDescent="0.2">
       <c r="A100" t="s">
         <v>62</v>
       </c>
@@ -2891,7 +2891,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:8" ns3:dyDescent="0.2">
       <c r="A101" t="s">
         <v>117</v>
       </c>
@@ -2914,7 +2914,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:8" ns3:dyDescent="0.2">
       <c r="A102" t="s">
         <v>37</v>
       </c>
@@ -2934,7 +2934,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:8" ns3:dyDescent="0.2">
       <c r="A103" t="s">
         <v>67</v>
       </c>
@@ -2957,7 +2957,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:8" ns3:dyDescent="0.2">
       <c r="A104" t="s">
         <v>56</v>
       </c>
@@ -2980,7 +2980,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:8" ns3:dyDescent="0.2">
       <c r="A105" t="s">
         <v>68</v>
       </c>
@@ -3003,7 +3003,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:8" ns3:dyDescent="0.2">
       <c r="A106" t="s">
         <v>69</v>
       </c>
@@ -3026,7 +3026,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:8" ns3:dyDescent="0.2">
       <c r="A107" t="s">
         <v>72</v>
       </c>
@@ -3046,7 +3046,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:8" ns3:dyDescent="0.2">
       <c r="A108" t="s">
         <v>75</v>
       </c>
@@ -3066,7 +3066,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:8" ns3:dyDescent="0.2">
       <c r="A109" t="s">
         <v>77</v>
       </c>
@@ -3086,7 +3086,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:8" ns3:dyDescent="0.2">
       <c r="A110" t="s">
         <v>79</v>
       </c>
@@ -3106,7 +3106,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:8" ns3:dyDescent="0.2">
       <c r="A111" t="s">
         <v>81</v>
       </c>
@@ -3126,7 +3126,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:8" ns3:dyDescent="0.2">
       <c r="A112" t="s">
         <v>83</v>
       </c>
@@ -3146,7 +3146,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:8" ns3:dyDescent="0.2">
       <c r="A113" t="s">
         <v>85</v>
       </c>
@@ -3166,7 +3166,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:8" ns3:dyDescent="0.2">
       <c r="A114" t="s">
         <v>87</v>
       </c>
@@ -3186,7 +3186,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:8" ns3:dyDescent="0.2">
       <c r="A115" t="s">
         <v>88</v>
       </c>
@@ -3206,7 +3206,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:8" ns3:dyDescent="0.2">
       <c r="A116" t="s">
         <v>90</v>
       </c>
@@ -3226,7 +3226,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:8" ns3:dyDescent="0.2">
       <c r="A117" t="s">
         <v>92</v>
       </c>
@@ -3246,7 +3246,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:8" ns3:dyDescent="0.2">
       <c r="A118" t="s">
         <v>94</v>
       </c>
@@ -3266,7 +3266,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:8" ns3:dyDescent="0.2">
       <c r="A119" t="s">
         <v>96</v>
       </c>
@@ -3286,7 +3286,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:8" ns3:dyDescent="0.2">
       <c r="A120" t="s">
         <v>98</v>
       </c>
@@ -3306,7 +3306,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:8" ns3:dyDescent="0.2">
       <c r="A121" t="s">
         <v>100</v>
       </c>
@@ -3326,7 +3326,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:8" ns3:dyDescent="0.2">
       <c r="A122" t="s">
         <v>102</v>
       </c>
@@ -3346,7 +3346,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:8" ns3:dyDescent="0.2">
       <c r="A123" t="s">
         <v>104</v>
       </c>
@@ -3366,7 +3366,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:8" ns3:dyDescent="0.2">
       <c r="A124" t="s">
         <v>106</v>
       </c>
@@ -3386,7 +3386,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:8" ns3:dyDescent="0.2">
       <c r="A125" t="s">
         <v>108</v>
       </c>
@@ -3406,7 +3406,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:8" ns3:dyDescent="0.2">
       <c r="A126" t="s">
         <v>109</v>
       </c>
@@ -3426,7 +3426,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:8" ns3:dyDescent="0.2">
       <c r="A127" t="s">
         <v>231</v>
       </c>
@@ -3446,7 +3446,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:8" ns3:dyDescent="0.2">
       <c r="A128" t="s">
         <v>111</v>
       </c>
@@ -3466,7 +3466,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:8" ns3:dyDescent="0.2">
       <c r="A129" t="s">
         <v>230</v>
       </c>
@@ -3486,7 +3486,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:8" ns3:dyDescent="0.2">
       <c r="A130" t="s">
         <v>113</v>
       </c>
@@ -3506,7 +3506,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:8" ns3:dyDescent="0.2">
       <c r="A131" t="s">
         <v>115</v>
       </c>
@@ -3526,7 +3526,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:8" ns3:dyDescent="0.2">
       <c r="A133" s="2" t="s">
         <v>0</v>
       </c>
@@ -3534,7 +3534,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:8" ns3:dyDescent="0.2">
       <c r="A134" t="s">
         <v>2</v>
       </c>
@@ -3542,7 +3542,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:8" ns3:dyDescent="0.2">
       <c r="A135" t="s">
         <v>4</v>
       </c>
@@ -3550,7 +3550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:8" ns3:dyDescent="0.2">
       <c r="A136" t="s">
         <v>5</v>
       </c>
@@ -3558,7 +3558,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:8" ns3:dyDescent="0.2">
       <c r="A137" t="s">
         <v>7</v>
       </c>
@@ -3566,7 +3566,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:8" ns3:dyDescent="0.2">
       <c r="A138" t="s">
         <v>9</v>
       </c>
@@ -3574,12 +3574,12 @@
         <v>232</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:8" ns3:dyDescent="0.2">
       <c r="A139" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:8" ns3:dyDescent="0.2">
       <c r="A140" s="2" t="s">
         <v>16</v>
       </c>
@@ -3605,7 +3605,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:8" ns3:dyDescent="0.2">
       <c r="A141" t="s">
         <v>62</v>
       </c>
@@ -3628,7 +3628,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:8" ns3:dyDescent="0.2">
       <c r="A142" t="s">
         <v>124</v>
       </c>
@@ -3651,7 +3651,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:8" ns3:dyDescent="0.2">
       <c r="A143" t="s">
         <v>45</v>
       </c>
@@ -3671,7 +3671,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:8" ns3:dyDescent="0.2">
       <c r="A144" t="s">
         <v>67</v>
       </c>
@@ -3694,7 +3694,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:8" ns3:dyDescent="0.2">
       <c r="A145" t="s">
         <v>56</v>
       </c>
@@ -3717,7 +3717,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:8" ns3:dyDescent="0.2">
       <c r="A146" t="s">
         <v>68</v>
       </c>
@@ -3740,7 +3740,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:8" ns3:dyDescent="0.2">
       <c r="A147" t="s">
         <v>69</v>
       </c>
@@ -3763,7 +3763,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:8" ns3:dyDescent="0.2">
       <c r="A148" t="s">
         <v>123</v>
       </c>
@@ -3783,7 +3783,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:8" ns3:dyDescent="0.2">
       <c r="A149" t="s">
         <v>277</v>
       </c>
@@ -3804,7 +3804,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:8" ns3:dyDescent="0.2">
       <c r="A151" s="2" t="s">
         <v>0</v>
       </c>
@@ -3812,7 +3812,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:8" ns3:dyDescent="0.2">
       <c r="A152" t="s">
         <v>2</v>
       </c>
@@ -3820,7 +3820,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:8" ns3:dyDescent="0.2">
       <c r="A153" t="s">
         <v>4</v>
       </c>
@@ -3828,7 +3828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:8" ns3:dyDescent="0.2">
       <c r="A154" t="s">
         <v>5</v>
       </c>
@@ -3836,7 +3836,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:8" ns3:dyDescent="0.2">
       <c r="A155" t="s">
         <v>7</v>
       </c>
@@ -3844,7 +3844,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:8" ns3:dyDescent="0.2">
       <c r="A156" t="s">
         <v>9</v>
       </c>
@@ -3852,12 +3852,12 @@
         <v>232</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:8" ns3:dyDescent="0.2">
       <c r="A157" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:8" ns3:dyDescent="0.2">
       <c r="A158" s="2" t="s">
         <v>16</v>
       </c>
@@ -3883,7 +3883,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:8" ns3:dyDescent="0.2">
       <c r="A159" t="s">
         <v>62</v>
       </c>
@@ -3906,7 +3906,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:8" ns3:dyDescent="0.2">
       <c r="A160" t="s">
         <v>1</v>
       </c>
@@ -3929,7 +3929,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:8" ns3:dyDescent="0.2">
       <c r="A161" t="s">
         <v>129</v>
       </c>
@@ -3952,7 +3952,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:8" ns3:dyDescent="0.2">
       <c r="A162" t="s">
         <v>56</v>
       </c>
@@ -3975,7 +3975,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:8" ns3:dyDescent="0.2">
       <c r="A163" t="s">
         <v>130</v>
       </c>
@@ -3998,7 +3998,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:8" ns3:dyDescent="0.2">
       <c r="A164" t="s">
         <v>69</v>
       </c>
@@ -4021,7 +4021,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:8" ns3:dyDescent="0.2">
       <c r="A165" t="s">
         <v>72</v>
       </c>
@@ -4041,7 +4041,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:8" ns3:dyDescent="0.2">
       <c r="A166" t="s">
         <v>75</v>
       </c>
@@ -4061,7 +4061,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:8" ns3:dyDescent="0.2">
       <c r="A167" t="s">
         <v>77</v>
       </c>
@@ -4081,7 +4081,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:8" ns3:dyDescent="0.2">
       <c r="A168" t="s">
         <v>79</v>
       </c>
@@ -4101,7 +4101,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:8" ns3:dyDescent="0.2">
       <c r="A169" t="s">
         <v>81</v>
       </c>
@@ -4121,7 +4121,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:8" ns3:dyDescent="0.2">
       <c r="A170" t="s">
         <v>83</v>
       </c>
@@ -4141,7 +4141,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:8" ns3:dyDescent="0.2">
       <c r="A171" t="s">
         <v>85</v>
       </c>
@@ -4161,7 +4161,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:8" ns3:dyDescent="0.2">
       <c r="A172" t="s">
         <v>87</v>
       </c>
@@ -4181,7 +4181,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:8" ns3:dyDescent="0.2">
       <c r="A173" t="s">
         <v>88</v>
       </c>
@@ -4201,7 +4201,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:8" ns3:dyDescent="0.2">
       <c r="A174" t="s">
         <v>90</v>
       </c>
@@ -4221,7 +4221,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:8" ns3:dyDescent="0.2">
       <c r="A175" t="s">
         <v>92</v>
       </c>
@@ -4241,7 +4241,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:8" ns3:dyDescent="0.2">
       <c r="A176" t="s">
         <v>94</v>
       </c>
@@ -4261,7 +4261,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:8" ns3:dyDescent="0.2">
       <c r="A177" t="s">
         <v>96</v>
       </c>
@@ -4281,7 +4281,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:8" ns3:dyDescent="0.2">
       <c r="A178" t="s">
         <v>98</v>
       </c>
@@ -4301,7 +4301,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:8" ns3:dyDescent="0.2">
       <c r="A179" t="s">
         <v>100</v>
       </c>
@@ -4321,7 +4321,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:8" ns3:dyDescent="0.2">
       <c r="A180" t="s">
         <v>102</v>
       </c>
@@ -4341,7 +4341,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:8" ns3:dyDescent="0.2">
       <c r="A181" t="s">
         <v>104</v>
       </c>
@@ -4361,7 +4361,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:8" ns3:dyDescent="0.2">
       <c r="A182" t="s">
         <v>106</v>
       </c>
@@ -4381,7 +4381,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:8" ns3:dyDescent="0.2">
       <c r="A183" t="s">
         <v>108</v>
       </c>
@@ -4401,7 +4401,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:8" ns3:dyDescent="0.2">
       <c r="A184" t="s">
         <v>109</v>
       </c>
@@ -4421,7 +4421,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:8" ns3:dyDescent="0.2">
       <c r="A185" t="s">
         <v>111</v>
       </c>
@@ -4441,7 +4441,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:8" ns3:dyDescent="0.2">
       <c r="A186" t="s">
         <v>230</v>
       </c>
@@ -4461,7 +4461,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:8" ns3:dyDescent="0.2">
       <c r="A187" t="s">
         <v>113</v>
       </c>
@@ -4481,7 +4481,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:8" ns3:dyDescent="0.2">
       <c r="A188" t="s">
         <v>59</v>
       </c>
@@ -4501,7 +4501,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:8" ns3:dyDescent="0.2">
       <c r="A190" s="2" t="s">
         <v>0</v>
       </c>
@@ -4509,7 +4509,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:8" ns3:dyDescent="0.2">
       <c r="A191" t="s">
         <v>2</v>
       </c>
@@ -4517,7 +4517,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:8" ns3:dyDescent="0.2">
       <c r="A192" t="s">
         <v>4</v>
       </c>
@@ -4525,7 +4525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:8" ns3:dyDescent="0.2">
       <c r="A193" t="s">
         <v>5</v>
       </c>
@@ -4533,7 +4533,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:8" ns3:dyDescent="0.2">
       <c r="A194" t="s">
         <v>7</v>
       </c>
@@ -4541,7 +4541,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:8" ns3:dyDescent="0.2">
       <c r="A195" t="s">
         <v>9</v>
       </c>
@@ -4549,12 +4549,12 @@
         <v>232</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:8" ns3:dyDescent="0.2">
       <c r="A196" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:8" ns3:dyDescent="0.2">
       <c r="A197" s="2" t="s">
         <v>16</v>
       </c>
@@ -4580,7 +4580,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:8" ns3:dyDescent="0.2">
       <c r="A198" t="s">
         <v>62</v>
       </c>
@@ -4603,7 +4603,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:8" ns3:dyDescent="0.2">
       <c r="A199" t="s">
         <v>117</v>
       </c>
@@ -4626,7 +4626,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:8" ns3:dyDescent="0.2">
       <c r="A200" t="s">
         <v>132</v>
       </c>
@@ -4649,7 +4649,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:8" ns3:dyDescent="0.2">
       <c r="A201" t="s">
         <v>37</v>
       </c>
@@ -4672,7 +4672,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:8" ns3:dyDescent="0.2">
       <c r="A202" t="s">
         <v>129</v>
       </c>
@@ -4695,7 +4695,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:8" ns3:dyDescent="0.2">
       <c r="A203" t="s">
         <v>56</v>
       </c>
@@ -4718,7 +4718,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:8" ns3:dyDescent="0.2">
       <c r="A204" t="s">
         <v>130</v>
       </c>
@@ -4741,7 +4741,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:8" ns3:dyDescent="0.2">
       <c r="A205" t="s">
         <v>69</v>
       </c>
@@ -4764,7 +4764,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:8" ns3:dyDescent="0.2">
       <c r="A206" t="s">
         <v>72</v>
       </c>
@@ -4784,7 +4784,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:8" ns3:dyDescent="0.2">
       <c r="A207" t="s">
         <v>75</v>
       </c>
@@ -4804,7 +4804,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:8" ns3:dyDescent="0.2">
       <c r="A208" t="s">
         <v>77</v>
       </c>
@@ -4824,7 +4824,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:8" ns3:dyDescent="0.2">
       <c r="A209" t="s">
         <v>79</v>
       </c>
@@ -4844,7 +4844,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:8" ns3:dyDescent="0.2">
       <c r="A210" t="s">
         <v>81</v>
       </c>
@@ -4864,7 +4864,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:8" ns3:dyDescent="0.2">
       <c r="A211" t="s">
         <v>83</v>
       </c>
@@ -4884,7 +4884,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:8" ns3:dyDescent="0.2">
       <c r="A212" t="s">
         <v>85</v>
       </c>
@@ -4904,7 +4904,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:8" ns3:dyDescent="0.2">
       <c r="A213" t="s">
         <v>87</v>
       </c>
@@ -4924,7 +4924,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:8" ns3:dyDescent="0.2">
       <c r="A214" t="s">
         <v>88</v>
       </c>
@@ -4944,7 +4944,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:8" ns3:dyDescent="0.2">
       <c r="A215" t="s">
         <v>90</v>
       </c>
@@ -4964,7 +4964,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:8" ns3:dyDescent="0.2">
       <c r="A216" t="s">
         <v>92</v>
       </c>
@@ -4984,7 +4984,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:8" ns3:dyDescent="0.2">
       <c r="A217" t="s">
         <v>94</v>
       </c>
@@ -5004,7 +5004,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:8" ns3:dyDescent="0.2">
       <c r="A218" t="s">
         <v>96</v>
       </c>
@@ -5024,7 +5024,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:8" ns3:dyDescent="0.2">
       <c r="A219" t="s">
         <v>98</v>
       </c>
@@ -5044,7 +5044,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:8" ns3:dyDescent="0.2">
       <c r="A220" t="s">
         <v>100</v>
       </c>
@@ -5064,7 +5064,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:8" ns3:dyDescent="0.2">
       <c r="A221" t="s">
         <v>102</v>
       </c>
@@ -5084,7 +5084,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:8" ns3:dyDescent="0.2">
       <c r="A222" t="s">
         <v>104</v>
       </c>
@@ -5104,7 +5104,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:8" ns3:dyDescent="0.2">
       <c r="A223" t="s">
         <v>106</v>
       </c>
@@ -5124,7 +5124,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:8" ns3:dyDescent="0.2">
       <c r="A224" t="s">
         <v>108</v>
       </c>
@@ -5144,7 +5144,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:8" ns3:dyDescent="0.2">
       <c r="A225" t="s">
         <v>109</v>
       </c>
@@ -5164,7 +5164,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:8" ns3:dyDescent="0.2">
       <c r="A226" t="s">
         <v>231</v>
       </c>
@@ -5184,7 +5184,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:8" ns3:dyDescent="0.2">
       <c r="A227" t="s">
         <v>111</v>
       </c>
@@ -5204,7 +5204,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:8" ns3:dyDescent="0.2">
       <c r="A228" t="s">
         <v>230</v>
       </c>
@@ -5224,7 +5224,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:8" ns3:dyDescent="0.2">
       <c r="A229" t="s">
         <v>113</v>
       </c>
@@ -5244,7 +5244,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:8" ns3:dyDescent="0.2">
       <c r="A230" t="s">
         <v>115</v>
       </c>
@@ -5264,7 +5264,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:8" ns3:dyDescent="0.2">
       <c r="A232" s="2" t="s">
         <v>0</v>
       </c>
@@ -5272,7 +5272,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:8" ns3:dyDescent="0.2">
       <c r="A233" t="s">
         <v>2</v>
       </c>
@@ -5280,7 +5280,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:8" ns3:dyDescent="0.2">
       <c r="A234" t="s">
         <v>4</v>
       </c>
@@ -5288,7 +5288,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:8" ns3:dyDescent="0.2">
       <c r="A235" t="s">
         <v>5</v>
       </c>
@@ -5296,7 +5296,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:8" ns3:dyDescent="0.2">
       <c r="A236" t="s">
         <v>7</v>
       </c>
@@ -5304,7 +5304,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:8" ns3:dyDescent="0.2">
       <c r="A237" t="s">
         <v>9</v>
       </c>
@@ -5312,12 +5312,12 @@
         <v>232</v>
       </c>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:8" ns3:dyDescent="0.2">
       <c r="A238" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:8" ns3:dyDescent="0.2">
       <c r="A239" s="2" t="s">
         <v>16</v>
       </c>
@@ -5343,7 +5343,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:8" ns3:dyDescent="0.2">
       <c r="A240" t="s">
         <v>62</v>
       </c>
@@ -5366,7 +5366,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:8" ns3:dyDescent="0.2">
       <c r="A241" t="s">
         <v>124</v>
       </c>
@@ -5389,7 +5389,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:8" ns3:dyDescent="0.2">
       <c r="A242" t="s">
         <v>45</v>
       </c>
@@ -5412,7 +5412,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:8" ns3:dyDescent="0.2">
       <c r="A243" t="s">
         <v>129</v>
       </c>
@@ -5435,7 +5435,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:8" ns3:dyDescent="0.2">
       <c r="A244" t="s">
         <v>56</v>
       </c>
@@ -5458,7 +5458,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:8" ns3:dyDescent="0.2">
       <c r="A245" t="s">
         <v>130</v>
       </c>
@@ -5481,7 +5481,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:8" ns3:dyDescent="0.2">
       <c r="A246" t="s">
         <v>69</v>
       </c>
@@ -5504,7 +5504,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:8" ns3:dyDescent="0.2">
       <c r="A247" t="s">
         <v>72</v>
       </c>
@@ -5524,7 +5524,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:8" ns3:dyDescent="0.2">
       <c r="A248" t="s">
         <v>75</v>
       </c>
@@ -5544,7 +5544,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:8" ns3:dyDescent="0.2">
       <c r="A249" t="s">
         <v>77</v>
       </c>
@@ -5564,7 +5564,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:8" ns3:dyDescent="0.2">
       <c r="A250" t="s">
         <v>79</v>
       </c>
@@ -5584,7 +5584,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:8" ns3:dyDescent="0.2">
       <c r="A251" t="s">
         <v>81</v>
       </c>
@@ -5604,7 +5604,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:8" ns3:dyDescent="0.2">
       <c r="A252" t="s">
         <v>83</v>
       </c>
@@ -5624,7 +5624,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:8" ns3:dyDescent="0.2">
       <c r="A253" t="s">
         <v>85</v>
       </c>
@@ -5644,7 +5644,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:8" ns3:dyDescent="0.2">
       <c r="A254" t="s">
         <v>87</v>
       </c>
@@ -5664,7 +5664,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:8" ns3:dyDescent="0.2">
       <c r="A255" t="s">
         <v>88</v>
       </c>
@@ -5684,7 +5684,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:8" ns3:dyDescent="0.2">
       <c r="A256" t="s">
         <v>90</v>
       </c>
@@ -5704,7 +5704,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:8" ns3:dyDescent="0.2">
       <c r="A257" t="s">
         <v>92</v>
       </c>
@@ -5724,7 +5724,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:8" ns3:dyDescent="0.2">
       <c r="A258" t="s">
         <v>94</v>
       </c>
@@ -5744,7 +5744,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:8" ns3:dyDescent="0.2">
       <c r="A259" t="s">
         <v>96</v>
       </c>
@@ -5764,7 +5764,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:8" ns3:dyDescent="0.2">
       <c r="A260" t="s">
         <v>98</v>
       </c>
@@ -5784,7 +5784,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:8" ns3:dyDescent="0.2">
       <c r="A261" t="s">
         <v>100</v>
       </c>
@@ -5804,7 +5804,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:8" ns3:dyDescent="0.2">
       <c r="A262" t="s">
         <v>102</v>
       </c>
@@ -5824,7 +5824,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:8" ns3:dyDescent="0.2">
       <c r="A263" t="s">
         <v>104</v>
       </c>
@@ -5844,7 +5844,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:8" ns3:dyDescent="0.2">
       <c r="A264" t="s">
         <v>106</v>
       </c>
@@ -5864,7 +5864,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:8" ns3:dyDescent="0.2">
       <c r="A265" t="s">
         <v>108</v>
       </c>
@@ -5884,7 +5884,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:8" ns3:dyDescent="0.2">
       <c r="A266" t="s">
         <v>109</v>
       </c>
@@ -5904,7 +5904,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:8" ns3:dyDescent="0.2">
       <c r="A267" t="s">
         <v>111</v>
       </c>
@@ -5924,7 +5924,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:8" ns3:dyDescent="0.2">
       <c r="A268" t="s">
         <v>230</v>
       </c>
@@ -5944,7 +5944,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:8" ns3:dyDescent="0.2">
       <c r="A269" t="s">
         <v>113</v>
       </c>
@@ -5964,7 +5964,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:8" ns3:dyDescent="0.2">
       <c r="A270" t="s">
         <v>123</v>
       </c>
@@ -5984,7 +5984,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:8" ns3:dyDescent="0.2">
       <c r="A272" s="2" t="s">
         <v>0</v>
       </c>
@@ -5992,7 +5992,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:8" ns3:dyDescent="0.2">
       <c r="A273" t="s">
         <v>2</v>
       </c>
@@ -6000,7 +6000,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:8" ns3:dyDescent="0.2">
       <c r="A274" t="s">
         <v>4</v>
       </c>
@@ -6008,7 +6008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:8" ns3:dyDescent="0.2">
       <c r="A275" t="s">
         <v>5</v>
       </c>
@@ -6016,7 +6016,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:8" ns3:dyDescent="0.2">
       <c r="A276" t="s">
         <v>7</v>
       </c>
@@ -6024,7 +6024,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:8" ns3:dyDescent="0.2">
       <c r="A277" t="s">
         <v>9</v>
       </c>
@@ -6032,12 +6032,12 @@
         <v>232</v>
       </c>
     </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:8" ns3:dyDescent="0.2">
       <c r="A278" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:8" ns3:dyDescent="0.2">
       <c r="A279" s="2" t="s">
         <v>16</v>
       </c>
@@ -6063,7 +6063,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:8" ns3:dyDescent="0.2">
       <c r="A280" t="s">
         <v>62</v>
       </c>
@@ -6086,7 +6086,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:8" ns3:dyDescent="0.2">
       <c r="A281" t="s">
         <v>1</v>
       </c>
@@ -6109,7 +6109,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:8" ns3:dyDescent="0.2">
       <c r="A282" t="s">
         <v>129</v>
       </c>
@@ -6132,7 +6132,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:8" ns3:dyDescent="0.2">
       <c r="A283" t="s">
         <v>56</v>
       </c>
@@ -6155,7 +6155,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:8" ns3:dyDescent="0.2">
       <c r="A284" t="s">
         <v>130</v>
       </c>
@@ -6178,7 +6178,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:8" ns3:dyDescent="0.2">
       <c r="A285" t="s">
         <v>69</v>
       </c>
@@ -6201,7 +6201,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:8" ns3:dyDescent="0.2">
       <c r="A286" t="s">
         <v>72</v>
       </c>
@@ -6221,7 +6221,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:8" ns3:dyDescent="0.2">
       <c r="A287" t="s">
         <v>75</v>
       </c>
@@ -6241,7 +6241,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:8" ns3:dyDescent="0.2">
       <c r="A288" t="s">
         <v>77</v>
       </c>
@@ -6261,7 +6261,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:8" ns3:dyDescent="0.2">
       <c r="A289" t="s">
         <v>79</v>
       </c>
@@ -6281,7 +6281,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:8" ns3:dyDescent="0.2">
       <c r="A290" t="s">
         <v>81</v>
       </c>
@@ -6301,7 +6301,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:8" ns3:dyDescent="0.2">
       <c r="A291" t="s">
         <v>83</v>
       </c>
@@ -6321,7 +6321,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:8" ns3:dyDescent="0.2">
       <c r="A292" t="s">
         <v>85</v>
       </c>
@@ -6341,7 +6341,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:8" ns3:dyDescent="0.2">
       <c r="A293" t="s">
         <v>87</v>
       </c>
@@ -6361,7 +6361,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:8" ns3:dyDescent="0.2">
       <c r="A294" t="s">
         <v>88</v>
       </c>
@@ -6381,7 +6381,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:8" ns3:dyDescent="0.2">
       <c r="A295" t="s">
         <v>90</v>
       </c>
@@ -6401,7 +6401,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:8" ns3:dyDescent="0.2">
       <c r="A296" t="s">
         <v>92</v>
       </c>
@@ -6421,7 +6421,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:8" ns3:dyDescent="0.2">
       <c r="A297" t="s">
         <v>94</v>
       </c>
@@ -6441,7 +6441,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:8" ns3:dyDescent="0.2">
       <c r="A298" t="s">
         <v>96</v>
       </c>
@@ -6461,7 +6461,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:8" ns3:dyDescent="0.2">
       <c r="A299" t="s">
         <v>98</v>
       </c>
@@ -6481,7 +6481,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:8" ns3:dyDescent="0.2">
       <c r="A300" t="s">
         <v>100</v>
       </c>
@@ -6501,7 +6501,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:8" ns3:dyDescent="0.2">
       <c r="A301" t="s">
         <v>102</v>
       </c>
@@ -6521,7 +6521,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:8" ns3:dyDescent="0.2">
       <c r="A302" t="s">
         <v>104</v>
       </c>
@@ -6541,7 +6541,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:8" ns3:dyDescent="0.2">
       <c r="A303" t="s">
         <v>106</v>
       </c>
@@ -6561,7 +6561,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:8" ns3:dyDescent="0.2">
       <c r="A304" t="s">
         <v>108</v>
       </c>
@@ -6581,7 +6581,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:8" ns3:dyDescent="0.2">
       <c r="A305" t="s">
         <v>109</v>
       </c>
@@ -6601,7 +6601,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:8" ns3:dyDescent="0.2">
       <c r="A306" t="s">
         <v>111</v>
       </c>
@@ -6621,7 +6621,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:8" ns3:dyDescent="0.2">
       <c r="A307" t="s">
         <v>230</v>
       </c>
@@ -6641,7 +6641,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:8" ns3:dyDescent="0.2">
       <c r="A308" t="s">
         <v>113</v>
       </c>
@@ -6661,7 +6661,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:8" ns3:dyDescent="0.2">
       <c r="A309" t="s">
         <v>59</v>
       </c>
@@ -6681,7 +6681,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="311" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:8" ns3:dyDescent="0.2">
       <c r="A311" s="2" t="s">
         <v>0</v>
       </c>
@@ -6689,7 +6689,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="312" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:8" ns3:dyDescent="0.2">
       <c r="A312" t="s">
         <v>2</v>
       </c>
@@ -6697,7 +6697,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="313" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:8" ns3:dyDescent="0.2">
       <c r="A313" t="s">
         <v>4</v>
       </c>
@@ -6705,7 +6705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="314" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:8" ns3:dyDescent="0.2">
       <c r="A314" t="s">
         <v>5</v>
       </c>
@@ -6713,7 +6713,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="315" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:8" ns3:dyDescent="0.2">
       <c r="A315" t="s">
         <v>7</v>
       </c>
@@ -6721,7 +6721,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="316" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:8" ns3:dyDescent="0.2">
       <c r="A316" t="s">
         <v>9</v>
       </c>
@@ -6729,12 +6729,12 @@
         <v>232</v>
       </c>
     </row>
-    <row r="317" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:8" ns3:dyDescent="0.2">
       <c r="A317" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="318" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:8" ns3:dyDescent="0.2">
       <c r="A318" s="2" t="s">
         <v>16</v>
       </c>
@@ -6760,7 +6760,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="319" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:8" ns3:dyDescent="0.2">
       <c r="A319" t="s">
         <v>62</v>
       </c>
@@ -6783,7 +6783,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="320" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:8" ns3:dyDescent="0.2">
       <c r="A320" t="s">
         <v>132</v>
       </c>
@@ -6806,7 +6806,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="321" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:8" ns3:dyDescent="0.2">
       <c r="A321" t="s">
         <v>37</v>
       </c>
@@ -6829,7 +6829,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="322" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:8" ns3:dyDescent="0.2">
       <c r="A322" t="s">
         <v>129</v>
       </c>
@@ -6852,7 +6852,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="323" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:8" ns3:dyDescent="0.2">
       <c r="A323" t="s">
         <v>56</v>
       </c>
@@ -6875,7 +6875,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="324" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:8" ns3:dyDescent="0.2">
       <c r="A324" t="s">
         <v>130</v>
       </c>
@@ -6898,7 +6898,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="325" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:8" ns3:dyDescent="0.2">
       <c r="A325" t="s">
         <v>69</v>
       </c>
@@ -6921,7 +6921,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="326" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:8" ns3:dyDescent="0.2">
       <c r="A326" t="s">
         <v>72</v>
       </c>
@@ -6941,7 +6941,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="327" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:8" ns3:dyDescent="0.2">
       <c r="A327" t="s">
         <v>75</v>
       </c>
@@ -6961,7 +6961,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="328" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:8" ns3:dyDescent="0.2">
       <c r="A328" t="s">
         <v>77</v>
       </c>
@@ -6981,7 +6981,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:8" ns3:dyDescent="0.2">
       <c r="A329" t="s">
         <v>79</v>
       </c>
@@ -7001,7 +7001,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="330" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:8" ns3:dyDescent="0.2">
       <c r="A330" t="s">
         <v>81</v>
       </c>
@@ -7021,7 +7021,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="331" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:8" ns3:dyDescent="0.2">
       <c r="A331" t="s">
         <v>83</v>
       </c>
@@ -7041,7 +7041,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="332" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:8" ns3:dyDescent="0.2">
       <c r="A332" t="s">
         <v>85</v>
       </c>
@@ -7061,7 +7061,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="333" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:8" ns3:dyDescent="0.2">
       <c r="A333" t="s">
         <v>87</v>
       </c>
@@ -7081,7 +7081,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="334" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:8" ns3:dyDescent="0.2">
       <c r="A334" t="s">
         <v>88</v>
       </c>
@@ -7101,7 +7101,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="335" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:8" ns3:dyDescent="0.2">
       <c r="A335" t="s">
         <v>90</v>
       </c>
@@ -7121,7 +7121,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="336" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:8" ns3:dyDescent="0.2">
       <c r="A336" t="s">
         <v>92</v>
       </c>
@@ -7141,7 +7141,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="337" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:8" ns3:dyDescent="0.2">
       <c r="A337" t="s">
         <v>94</v>
       </c>
@@ -7161,7 +7161,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="338" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:8" ns3:dyDescent="0.2">
       <c r="A338" t="s">
         <v>96</v>
       </c>
@@ -7181,7 +7181,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="339" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:8" ns3:dyDescent="0.2">
       <c r="A339" t="s">
         <v>98</v>
       </c>
@@ -7201,7 +7201,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="340" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:8" ns3:dyDescent="0.2">
       <c r="A340" t="s">
         <v>100</v>
       </c>
@@ -7221,7 +7221,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:8" ns3:dyDescent="0.2">
       <c r="A341" t="s">
         <v>102</v>
       </c>
@@ -7241,7 +7241,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="342" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:8" ns3:dyDescent="0.2">
       <c r="A342" t="s">
         <v>104</v>
       </c>
@@ -7261,7 +7261,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="343" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:8" ns3:dyDescent="0.2">
       <c r="A343" t="s">
         <v>106</v>
       </c>
@@ -7281,7 +7281,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="344" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:8" ns3:dyDescent="0.2">
       <c r="A344" t="s">
         <v>108</v>
       </c>
@@ -7301,7 +7301,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="345" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:8" ns3:dyDescent="0.2">
       <c r="A345" t="s">
         <v>109</v>
       </c>
@@ -7321,7 +7321,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="346" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:8" ns3:dyDescent="0.2">
       <c r="A346" t="s">
         <v>231</v>
       </c>
@@ -7341,7 +7341,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="347" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:8" ns3:dyDescent="0.2">
       <c r="A347" t="s">
         <v>111</v>
       </c>
@@ -7361,7 +7361,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="348" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:8" ns3:dyDescent="0.2">
       <c r="A348" t="s">
         <v>230</v>
       </c>
@@ -7381,7 +7381,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="349" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:8" ns3:dyDescent="0.2">
       <c r="A349" t="s">
         <v>113</v>
       </c>
@@ -7401,7 +7401,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="350" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:8" ns3:dyDescent="0.2">
       <c r="A350" t="s">
         <v>115</v>
       </c>
@@ -7421,7 +7421,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="352" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:8" ns3:dyDescent="0.2">
       <c r="A352" s="2" t="s">
         <v>0</v>
       </c>
@@ -7429,7 +7429,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="353" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:8" ns3:dyDescent="0.2">
       <c r="A353" t="s">
         <v>2</v>
       </c>
@@ -7437,7 +7437,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="354" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:8" ns3:dyDescent="0.2">
       <c r="A354" t="s">
         <v>4</v>
       </c>
@@ -7445,7 +7445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="355" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:8" ns3:dyDescent="0.2">
       <c r="A355" t="s">
         <v>5</v>
       </c>
@@ -7453,7 +7453,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="356" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:8" ns3:dyDescent="0.2">
       <c r="A356" t="s">
         <v>7</v>
       </c>
@@ -7461,7 +7461,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="357" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:8" ns3:dyDescent="0.2">
       <c r="A357" t="s">
         <v>9</v>
       </c>
@@ -7469,12 +7469,12 @@
         <v>232</v>
       </c>
     </row>
-    <row r="358" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:8" ns3:dyDescent="0.2">
       <c r="A358" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="359" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:8" ns3:dyDescent="0.2">
       <c r="A359" s="2" t="s">
         <v>16</v>
       </c>
@@ -7500,7 +7500,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="360" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:8" ns3:dyDescent="0.2">
       <c r="A360" t="s">
         <v>62</v>
       </c>
@@ -7523,7 +7523,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="361" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:8" ns3:dyDescent="0.2">
       <c r="A361" t="s">
         <v>124</v>
       </c>
@@ -7546,7 +7546,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="362" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:8" ns3:dyDescent="0.2">
       <c r="A362" t="s">
         <v>45</v>
       </c>
@@ -7569,7 +7569,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="363" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:8" ns3:dyDescent="0.2">
       <c r="A363" t="s">
         <v>129</v>
       </c>
@@ -7592,7 +7592,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="364" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:8" ns3:dyDescent="0.2">
       <c r="A364" t="s">
         <v>56</v>
       </c>
@@ -7615,7 +7615,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="365" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:8" ns3:dyDescent="0.2">
       <c r="A365" t="s">
         <v>130</v>
       </c>
@@ -7638,7 +7638,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="366" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:8" ns3:dyDescent="0.2">
       <c r="A366" t="s">
         <v>69</v>
       </c>
@@ -7661,7 +7661,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="367" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:8" ns3:dyDescent="0.2">
       <c r="A367" t="s">
         <v>72</v>
       </c>
@@ -7681,7 +7681,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="368" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:8" ns3:dyDescent="0.2">
       <c r="A368" t="s">
         <v>75</v>
       </c>
@@ -7701,7 +7701,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="369" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:8" ns3:dyDescent="0.2">
       <c r="A369" t="s">
         <v>77</v>
       </c>
@@ -7721,7 +7721,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="370" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:8" ns3:dyDescent="0.2">
       <c r="A370" t="s">
         <v>79</v>
       </c>
@@ -7741,7 +7741,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="371" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:8" ns3:dyDescent="0.2">
       <c r="A371" t="s">
         <v>81</v>
       </c>
@@ -7761,7 +7761,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="372" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:8" ns3:dyDescent="0.2">
       <c r="A372" t="s">
         <v>83</v>
       </c>
@@ -7781,7 +7781,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="373" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:8" ns3:dyDescent="0.2">
       <c r="A373" t="s">
         <v>85</v>
       </c>
@@ -7801,7 +7801,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="374" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:8" ns3:dyDescent="0.2">
       <c r="A374" t="s">
         <v>87</v>
       </c>
@@ -7821,7 +7821,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="375" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:8" ns3:dyDescent="0.2">
       <c r="A375" t="s">
         <v>88</v>
       </c>
@@ -7841,7 +7841,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="376" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:8" ns3:dyDescent="0.2">
       <c r="A376" t="s">
         <v>90</v>
       </c>
@@ -7861,7 +7861,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="377" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:8" ns3:dyDescent="0.2">
       <c r="A377" t="s">
         <v>92</v>
       </c>
@@ -7881,7 +7881,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="378" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:8" ns3:dyDescent="0.2">
       <c r="A378" t="s">
         <v>94</v>
       </c>
@@ -7901,7 +7901,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="379" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:8" ns3:dyDescent="0.2">
       <c r="A379" t="s">
         <v>96</v>
       </c>
@@ -7921,7 +7921,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="380" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:8" ns3:dyDescent="0.2">
       <c r="A380" t="s">
         <v>98</v>
       </c>
@@ -7941,7 +7941,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="381" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:8" ns3:dyDescent="0.2">
       <c r="A381" t="s">
         <v>100</v>
       </c>
@@ -7961,7 +7961,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="382" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:8" ns3:dyDescent="0.2">
       <c r="A382" t="s">
         <v>102</v>
       </c>
@@ -7981,7 +7981,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="383" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:8" ns3:dyDescent="0.2">
       <c r="A383" t="s">
         <v>104</v>
       </c>
@@ -8001,7 +8001,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="384" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:8" ns3:dyDescent="0.2">
       <c r="A384" t="s">
         <v>106</v>
       </c>
@@ -8021,7 +8021,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="385" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:8" ns3:dyDescent="0.2">
       <c r="A385" t="s">
         <v>108</v>
       </c>
@@ -8041,7 +8041,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="386" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:8" ns3:dyDescent="0.2">
       <c r="A386" t="s">
         <v>109</v>
       </c>
@@ -8061,7 +8061,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="387" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:8" ns3:dyDescent="0.2">
       <c r="A387" t="s">
         <v>111</v>
       </c>
@@ -8081,7 +8081,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="388" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:8" ns3:dyDescent="0.2">
       <c r="A388" t="s">
         <v>230</v>
       </c>
@@ -8101,7 +8101,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="389" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:8" ns3:dyDescent="0.2">
       <c r="A389" t="s">
         <v>113</v>
       </c>
@@ -8121,7 +8121,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="390" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:8" ns3:dyDescent="0.2">
       <c r="A390" t="s">
         <v>123</v>
       </c>
@@ -8141,7 +8141,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="392" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:8" ns3:dyDescent="0.2">
       <c r="A392" s="2" t="s">
         <v>0</v>
       </c>
@@ -8149,7 +8149,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="393" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:8" ns3:dyDescent="0.2">
       <c r="A393" t="s">
         <v>2</v>
       </c>
@@ -8157,7 +8157,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="394" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:8" ns3:dyDescent="0.2">
       <c r="A394" t="s">
         <v>4</v>
       </c>
@@ -8165,7 +8165,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="395" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:8" ns3:dyDescent="0.2">
       <c r="A395" t="s">
         <v>5</v>
       </c>
@@ -8173,7 +8173,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="396" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:8" ns3:dyDescent="0.2">
       <c r="A396" t="s">
         <v>7</v>
       </c>
@@ -8181,7 +8181,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="397" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:8" ns3:dyDescent="0.2">
       <c r="A397" t="s">
         <v>9</v>
       </c>
@@ -8189,12 +8189,12 @@
         <v>232</v>
       </c>
     </row>
-    <row r="398" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:8" ns3:dyDescent="0.2">
       <c r="A398" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="399" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:8" ns3:dyDescent="0.2">
       <c r="A399" s="2" t="s">
         <v>16</v>
       </c>
@@ -8220,7 +8220,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="400" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:8" ns3:dyDescent="0.2">
       <c r="A400" t="s">
         <v>62</v>
       </c>
@@ -8243,7 +8243,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="401" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:8" ns3:dyDescent="0.2">
       <c r="A401" t="s">
         <v>1</v>
       </c>
@@ -8266,7 +8266,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="402" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:8" ns3:dyDescent="0.2">
       <c r="A402" t="s">
         <v>129</v>
       </c>
@@ -8289,7 +8289,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="403" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:8" ns3:dyDescent="0.2">
       <c r="A403" t="s">
         <v>56</v>
       </c>
@@ -8312,7 +8312,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="404" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:8" ns3:dyDescent="0.2">
       <c r="A404" t="s">
         <v>130</v>
       </c>
@@ -8335,7 +8335,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="405" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:8" ns3:dyDescent="0.2">
       <c r="A405" t="s">
         <v>69</v>
       </c>
@@ -8358,7 +8358,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="406" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:8" ns3:dyDescent="0.2">
       <c r="A406" t="s">
         <v>72</v>
       </c>
@@ -8378,7 +8378,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="407" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:8" ns3:dyDescent="0.2">
       <c r="A407" t="s">
         <v>75</v>
       </c>
@@ -8398,7 +8398,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="408" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:8" ns3:dyDescent="0.2">
       <c r="A408" t="s">
         <v>77</v>
       </c>
@@ -8418,7 +8418,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="409" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:8" ns3:dyDescent="0.2">
       <c r="A409" t="s">
         <v>79</v>
       </c>
@@ -8438,7 +8438,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="410" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:8" ns3:dyDescent="0.2">
       <c r="A410" t="s">
         <v>81</v>
       </c>
@@ -8458,7 +8458,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="411" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:8" ns3:dyDescent="0.2">
       <c r="A411" t="s">
         <v>83</v>
       </c>
@@ -8478,7 +8478,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="412" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:8" ns3:dyDescent="0.2">
       <c r="A412" t="s">
         <v>85</v>
       </c>
@@ -8498,7 +8498,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="413" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:8" ns3:dyDescent="0.2">
       <c r="A413" t="s">
         <v>87</v>
       </c>
@@ -8518,7 +8518,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="414" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:8" ns3:dyDescent="0.2">
       <c r="A414" t="s">
         <v>88</v>
       </c>
@@ -8538,7 +8538,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="415" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:8" ns3:dyDescent="0.2">
       <c r="A415" t="s">
         <v>90</v>
       </c>
@@ -8558,7 +8558,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="416" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:8" ns3:dyDescent="0.2">
       <c r="A416" t="s">
         <v>92</v>
       </c>
@@ -8578,7 +8578,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="417" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:8" ns3:dyDescent="0.2">
       <c r="A417" t="s">
         <v>94</v>
       </c>
@@ -8598,7 +8598,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="418" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:8" ns3:dyDescent="0.2">
       <c r="A418" t="s">
         <v>96</v>
       </c>
@@ -8618,7 +8618,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="419" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:8" ns3:dyDescent="0.2">
       <c r="A419" t="s">
         <v>98</v>
       </c>
@@ -8638,7 +8638,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="420" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:8" ns3:dyDescent="0.2">
       <c r="A420" t="s">
         <v>100</v>
       </c>
@@ -8658,7 +8658,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="421" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:8" ns3:dyDescent="0.2">
       <c r="A421" t="s">
         <v>102</v>
       </c>
@@ -8678,7 +8678,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="422" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:8" ns3:dyDescent="0.2">
       <c r="A422" t="s">
         <v>104</v>
       </c>
@@ -8698,7 +8698,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="423" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:8" ns3:dyDescent="0.2">
       <c r="A423" t="s">
         <v>106</v>
       </c>
@@ -8718,7 +8718,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="424" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:8" ns3:dyDescent="0.2">
       <c r="A424" t="s">
         <v>108</v>
       </c>
@@ -8738,7 +8738,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="425" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:8" ns3:dyDescent="0.2">
       <c r="A425" t="s">
         <v>109</v>
       </c>
@@ -8758,7 +8758,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="426" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:8" ns3:dyDescent="0.2">
       <c r="A426" t="s">
         <v>111</v>
       </c>
@@ -8778,7 +8778,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="427" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:8" ns3:dyDescent="0.2">
       <c r="A427" t="s">
         <v>230</v>
       </c>
@@ -8798,7 +8798,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="428" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:8" ns3:dyDescent="0.2">
       <c r="A428" t="s">
         <v>113</v>
       </c>
@@ -8818,7 +8818,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="429" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:8" ns3:dyDescent="0.2">
       <c r="A429" t="s">
         <v>59</v>
       </c>
@@ -8838,7 +8838,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="431" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:8" ns3:dyDescent="0.2">
       <c r="A431" s="2" t="s">
         <v>0</v>
       </c>
@@ -8846,7 +8846,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="432" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:8" ns3:dyDescent="0.2">
       <c r="A432" t="s">
         <v>2</v>
       </c>
@@ -8854,7 +8854,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="433" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:8" ns3:dyDescent="0.2">
       <c r="A433" t="s">
         <v>4</v>
       </c>
@@ -8862,7 +8862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="434" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:8" ns3:dyDescent="0.2">
       <c r="A434" t="s">
         <v>5</v>
       </c>
@@ -8870,7 +8870,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="435" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:8" ns3:dyDescent="0.2">
       <c r="A435" t="s">
         <v>7</v>
       </c>
@@ -8878,7 +8878,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="436" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:8" ns3:dyDescent="0.2">
       <c r="A436" t="s">
         <v>9</v>
       </c>
@@ -8886,12 +8886,12 @@
         <v>232</v>
       </c>
     </row>
-    <row r="437" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:8" ns3:dyDescent="0.2">
       <c r="A437" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="438" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:8" ns3:dyDescent="0.2">
       <c r="A438" s="2" t="s">
         <v>16</v>
       </c>
@@ -8917,7 +8917,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="439" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:8" ns3:dyDescent="0.2">
       <c r="A439" t="s">
         <v>62</v>
       </c>
@@ -8940,7 +8940,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="440" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:8" ns3:dyDescent="0.2">
       <c r="A440" t="s">
         <v>142</v>
       </c>
@@ -8963,7 +8963,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="441" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:8" ns3:dyDescent="0.2">
       <c r="A441" t="s">
         <v>143</v>
       </c>
@@ -8986,7 +8986,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="442" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:8" ns3:dyDescent="0.2">
       <c r="A442" t="s">
         <v>37</v>
       </c>
@@ -9009,7 +9009,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="443" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:8" ns3:dyDescent="0.2">
       <c r="A443" t="s">
         <v>129</v>
       </c>
@@ -9032,7 +9032,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="444" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:8" ns3:dyDescent="0.2">
       <c r="A444" t="s">
         <v>56</v>
       </c>
@@ -9055,7 +9055,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="445" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:8" ns3:dyDescent="0.2">
       <c r="A445" t="s">
         <v>130</v>
       </c>
@@ -9078,7 +9078,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="446" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:8" ns3:dyDescent="0.2">
       <c r="A446" t="s">
         <v>69</v>
       </c>
@@ -9101,7 +9101,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="447" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:8" ns3:dyDescent="0.2">
       <c r="A447" t="s">
         <v>72</v>
       </c>
@@ -9121,7 +9121,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="448" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:8" ns3:dyDescent="0.2">
       <c r="A448" t="s">
         <v>75</v>
       </c>
@@ -9141,7 +9141,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="449" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:8" ns3:dyDescent="0.2">
       <c r="A449" t="s">
         <v>77</v>
       </c>
@@ -9161,7 +9161,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="450" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:8" ns3:dyDescent="0.2">
       <c r="A450" t="s">
         <v>79</v>
       </c>
@@ -9181,7 +9181,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="451" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:8" ns3:dyDescent="0.2">
       <c r="A451" t="s">
         <v>81</v>
       </c>
@@ -9201,7 +9201,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="452" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:8" ns3:dyDescent="0.2">
       <c r="A452" t="s">
         <v>83</v>
       </c>
@@ -9221,7 +9221,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="453" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:8" ns3:dyDescent="0.2">
       <c r="A453" t="s">
         <v>85</v>
       </c>
@@ -9241,7 +9241,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="454" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:8" ns3:dyDescent="0.2">
       <c r="A454" t="s">
         <v>87</v>
       </c>
@@ -9261,7 +9261,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="455" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:8" ns3:dyDescent="0.2">
       <c r="A455" t="s">
         <v>88</v>
       </c>
@@ -9281,7 +9281,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="456" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:8" ns3:dyDescent="0.2">
       <c r="A456" t="s">
         <v>90</v>
       </c>
@@ -9301,7 +9301,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="457" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:8" ns3:dyDescent="0.2">
       <c r="A457" t="s">
         <v>92</v>
       </c>
@@ -9321,7 +9321,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="458" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:8" ns3:dyDescent="0.2">
       <c r="A458" t="s">
         <v>94</v>
       </c>
@@ -9341,7 +9341,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="459" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:8" ns3:dyDescent="0.2">
       <c r="A459" t="s">
         <v>96</v>
       </c>
@@ -9361,7 +9361,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="460" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:8" ns3:dyDescent="0.2">
       <c r="A460" t="s">
         <v>98</v>
       </c>
@@ -9381,7 +9381,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="461" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:8" ns3:dyDescent="0.2">
       <c r="A461" t="s">
         <v>100</v>
       </c>
@@ -9401,7 +9401,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="462" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:8" ns3:dyDescent="0.2">
       <c r="A462" t="s">
         <v>102</v>
       </c>
@@ -9421,7 +9421,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="463" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:8" ns3:dyDescent="0.2">
       <c r="A463" t="s">
         <v>104</v>
       </c>
@@ -9441,7 +9441,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="464" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:8" ns3:dyDescent="0.2">
       <c r="A464" t="s">
         <v>106</v>
       </c>
@@ -9461,7 +9461,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="465" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:8" ns3:dyDescent="0.2">
       <c r="A465" t="s">
         <v>108</v>
       </c>
@@ -9481,7 +9481,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="466" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:8" ns3:dyDescent="0.2">
       <c r="A466" t="s">
         <v>109</v>
       </c>
@@ -9501,7 +9501,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="467" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:8" ns3:dyDescent="0.2">
       <c r="A467" t="s">
         <v>231</v>
       </c>
@@ -9521,7 +9521,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="468" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:8" ns3:dyDescent="0.2">
       <c r="A468" t="s">
         <v>111</v>
       </c>
@@ -9541,7 +9541,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="469" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:8" ns3:dyDescent="0.2">
       <c r="A469" t="s">
         <v>230</v>
       </c>
@@ -9561,7 +9561,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="470" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:8" ns3:dyDescent="0.2">
       <c r="A470" t="s">
         <v>113</v>
       </c>
@@ -9581,7 +9581,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="471" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:8" ns3:dyDescent="0.2">
       <c r="A471" t="s">
         <v>115</v>
       </c>
@@ -9601,7 +9601,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="473" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:8" ns3:dyDescent="0.2">
       <c r="A473" s="2" t="s">
         <v>0</v>
       </c>
@@ -9609,7 +9609,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="474" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:8" ns3:dyDescent="0.2">
       <c r="A474" t="s">
         <v>2</v>
       </c>
@@ -9617,7 +9617,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="475" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:8" ns3:dyDescent="0.2">
       <c r="A475" t="s">
         <v>4</v>
       </c>
@@ -9625,7 +9625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="476" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:8" ns3:dyDescent="0.2">
       <c r="A476" t="s">
         <v>5</v>
       </c>
@@ -9633,7 +9633,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="477" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:8" ns3:dyDescent="0.2">
       <c r="A477" t="s">
         <v>7</v>
       </c>
@@ -9641,7 +9641,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="478" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:8" ns3:dyDescent="0.2">
       <c r="A478" t="s">
         <v>9</v>
       </c>
@@ -9649,12 +9649,12 @@
         <v>232</v>
       </c>
     </row>
-    <row r="479" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:8" ns3:dyDescent="0.2">
       <c r="A479" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="480" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:8" ns3:dyDescent="0.2">
       <c r="A480" s="2" t="s">
         <v>16</v>
       </c>
@@ -9680,7 +9680,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="481" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:8" ns3:dyDescent="0.2">
       <c r="A481" t="s">
         <v>62</v>
       </c>
@@ -9703,7 +9703,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="482" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:8" ns3:dyDescent="0.2">
       <c r="A482" t="s">
         <v>124</v>
       </c>
@@ -9726,7 +9726,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="483" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:8" ns3:dyDescent="0.2">
       <c r="A483" t="s">
         <v>45</v>
       </c>
@@ -9749,7 +9749,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="484" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:8" ns3:dyDescent="0.2">
       <c r="A484" t="s">
         <v>129</v>
       </c>
@@ -9772,7 +9772,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="485" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:8" ns3:dyDescent="0.2">
       <c r="A485" t="s">
         <v>56</v>
       </c>
@@ -9795,7 +9795,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="486" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:8" ns3:dyDescent="0.2">
       <c r="A486" t="s">
         <v>130</v>
       </c>
@@ -9818,7 +9818,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="487" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:8" ns3:dyDescent="0.2">
       <c r="A487" t="s">
         <v>69</v>
       </c>
@@ -9841,7 +9841,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="488" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:8" ns3:dyDescent="0.2">
       <c r="A488" t="s">
         <v>72</v>
       </c>
@@ -9861,7 +9861,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="489" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:8" ns3:dyDescent="0.2">
       <c r="A489" t="s">
         <v>75</v>
       </c>
@@ -9881,7 +9881,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="490" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:8" ns3:dyDescent="0.2">
       <c r="A490" t="s">
         <v>77</v>
       </c>
@@ -9901,7 +9901,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="491" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:8" ns3:dyDescent="0.2">
       <c r="A491" t="s">
         <v>79</v>
       </c>
@@ -9921,7 +9921,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="492" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:8" ns3:dyDescent="0.2">
       <c r="A492" t="s">
         <v>81</v>
       </c>
@@ -9941,7 +9941,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="493" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:8" ns3:dyDescent="0.2">
       <c r="A493" t="s">
         <v>83</v>
       </c>
@@ -9961,7 +9961,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="494" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:8" ns3:dyDescent="0.2">
       <c r="A494" t="s">
         <v>85</v>
       </c>
@@ -9981,7 +9981,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="495" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:8" ns3:dyDescent="0.2">
       <c r="A495" t="s">
         <v>87</v>
       </c>
@@ -10001,7 +10001,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="496" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:8" ns3:dyDescent="0.2">
       <c r="A496" t="s">
         <v>88</v>
       </c>
@@ -10021,7 +10021,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="497" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:8" ns3:dyDescent="0.2">
       <c r="A497" t="s">
         <v>90</v>
       </c>
@@ -10041,7 +10041,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="498" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:8" ns3:dyDescent="0.2">
       <c r="A498" t="s">
         <v>92</v>
       </c>
@@ -10061,7 +10061,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="499" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:8" ns3:dyDescent="0.2">
       <c r="A499" t="s">
         <v>94</v>
       </c>
@@ -10081,7 +10081,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="500" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:8" ns3:dyDescent="0.2">
       <c r="A500" t="s">
         <v>96</v>
       </c>
@@ -10101,7 +10101,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="501" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:8" ns3:dyDescent="0.2">
       <c r="A501" t="s">
         <v>98</v>
       </c>
@@ -10121,7 +10121,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="502" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:8" ns3:dyDescent="0.2">
       <c r="A502" t="s">
         <v>100</v>
       </c>
@@ -10141,7 +10141,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="503" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:8" ns3:dyDescent="0.2">
       <c r="A503" t="s">
         <v>102</v>
       </c>
@@ -10161,7 +10161,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="504" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:8" ns3:dyDescent="0.2">
       <c r="A504" t="s">
         <v>104</v>
       </c>
@@ -10181,7 +10181,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="505" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:8" ns3:dyDescent="0.2">
       <c r="A505" t="s">
         <v>106</v>
       </c>
@@ -10201,7 +10201,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="506" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:8" ns3:dyDescent="0.2">
       <c r="A506" t="s">
         <v>108</v>
       </c>
@@ -10221,7 +10221,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="507" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:8" ns3:dyDescent="0.2">
       <c r="A507" t="s">
         <v>109</v>
       </c>
@@ -10241,7 +10241,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="508" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:8" ns3:dyDescent="0.2">
       <c r="A508" t="s">
         <v>111</v>
       </c>
@@ -10261,7 +10261,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="509" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:8" ns3:dyDescent="0.2">
       <c r="A509" t="s">
         <v>230</v>
       </c>
@@ -10281,7 +10281,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="510" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:8" ns3:dyDescent="0.2">
       <c r="A510" t="s">
         <v>113</v>
       </c>
@@ -10301,7 +10301,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="511" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:8" ns3:dyDescent="0.2">
       <c r="A511" t="s">
         <v>123</v>
       </c>
@@ -10321,7 +10321,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="513" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:8" ns3:dyDescent="0.2">
       <c r="A513" s="2" t="s">
         <v>0</v>
       </c>
@@ -10329,7 +10329,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="514" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:8" ns3:dyDescent="0.2">
       <c r="A514" t="s">
         <v>2</v>
       </c>
@@ -10337,7 +10337,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="515" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:8" ns3:dyDescent="0.2">
       <c r="A515" t="s">
         <v>4</v>
       </c>
@@ -10345,7 +10345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="516" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:8" ns3:dyDescent="0.2">
       <c r="A516" t="s">
         <v>5</v>
       </c>
@@ -10353,7 +10353,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="517" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:8" ns3:dyDescent="0.2">
       <c r="A517" t="s">
         <v>7</v>
       </c>
@@ -10361,7 +10361,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="518" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:8" ns3:dyDescent="0.2">
       <c r="A518" t="s">
         <v>9</v>
       </c>
@@ -10369,12 +10369,12 @@
         <v>232</v>
       </c>
     </row>
-    <row r="519" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:8" ns3:dyDescent="0.2">
       <c r="A519" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="520" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:8" ns3:dyDescent="0.2">
       <c r="A520" s="2" t="s">
         <v>16</v>
       </c>
@@ -10400,7 +10400,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="521" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:8" ns3:dyDescent="0.2">
       <c r="A521" t="s">
         <v>62</v>
       </c>
@@ -10423,7 +10423,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="522" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:8" ns3:dyDescent="0.2">
       <c r="A522" t="s">
         <v>1</v>
       </c>
@@ -10446,7 +10446,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="523" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:8" ns3:dyDescent="0.2">
       <c r="A523" t="s">
         <v>129</v>
       </c>
@@ -10469,7 +10469,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="524" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:8" ns3:dyDescent="0.2">
       <c r="A524" t="s">
         <v>56</v>
       </c>
@@ -10492,7 +10492,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="525" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:8" ns3:dyDescent="0.2">
       <c r="A525" t="s">
         <v>130</v>
       </c>
@@ -10515,7 +10515,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="526" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:8" ns3:dyDescent="0.2">
       <c r="A526" t="s">
         <v>69</v>
       </c>
@@ -10538,7 +10538,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="527" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:8" ns3:dyDescent="0.2">
       <c r="A527" t="s">
         <v>72</v>
       </c>
@@ -10558,7 +10558,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="528" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:8" ns3:dyDescent="0.2">
       <c r="A528" t="s">
         <v>75</v>
       </c>
@@ -10578,7 +10578,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="529" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:8" ns3:dyDescent="0.2">
       <c r="A529" t="s">
         <v>77</v>
       </c>
@@ -10598,7 +10598,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="530" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:8" ns3:dyDescent="0.2">
       <c r="A530" t="s">
         <v>79</v>
       </c>
@@ -10618,7 +10618,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="531" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:8" ns3:dyDescent="0.2">
       <c r="A531" t="s">
         <v>81</v>
       </c>
@@ -10638,7 +10638,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="532" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:8" ns3:dyDescent="0.2">
       <c r="A532" t="s">
         <v>83</v>
       </c>
@@ -10658,7 +10658,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="533" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:8" ns3:dyDescent="0.2">
       <c r="A533" t="s">
         <v>85</v>
       </c>
@@ -10678,7 +10678,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="534" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:8" ns3:dyDescent="0.2">
       <c r="A534" t="s">
         <v>87</v>
       </c>
@@ -10698,7 +10698,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="535" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:8" ns3:dyDescent="0.2">
       <c r="A535" t="s">
         <v>88</v>
       </c>
@@ -10718,7 +10718,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="536" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:8" ns3:dyDescent="0.2">
       <c r="A536" t="s">
         <v>90</v>
       </c>
@@ -10738,7 +10738,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="537" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:8" ns3:dyDescent="0.2">
       <c r="A537" t="s">
         <v>92</v>
       </c>
@@ -10758,7 +10758,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="538" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:8" ns3:dyDescent="0.2">
       <c r="A538" t="s">
         <v>94</v>
       </c>
@@ -10778,7 +10778,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="539" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:8" ns3:dyDescent="0.2">
       <c r="A539" t="s">
         <v>96</v>
       </c>
@@ -10798,7 +10798,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="540" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:8" ns3:dyDescent="0.2">
       <c r="A540" t="s">
         <v>98</v>
       </c>
@@ -10818,7 +10818,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="541" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:8" ns3:dyDescent="0.2">
       <c r="A541" t="s">
         <v>100</v>
       </c>
@@ -10838,7 +10838,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="542" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:8" ns3:dyDescent="0.2">
       <c r="A542" t="s">
         <v>102</v>
       </c>
@@ -10858,7 +10858,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="543" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:8" ns3:dyDescent="0.2">
       <c r="A543" t="s">
         <v>104</v>
       </c>
@@ -10878,7 +10878,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="544" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:8" ns3:dyDescent="0.2">
       <c r="A544" t="s">
         <v>106</v>
       </c>
@@ -10898,7 +10898,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="545" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:8" ns3:dyDescent="0.2">
       <c r="A545" t="s">
         <v>108</v>
       </c>
@@ -10918,7 +10918,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="546" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:8" ns3:dyDescent="0.2">
       <c r="A546" t="s">
         <v>109</v>
       </c>
@@ -10938,7 +10938,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="547" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:8" ns3:dyDescent="0.2">
       <c r="A547" t="s">
         <v>111</v>
       </c>
@@ -10958,7 +10958,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="548" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:8" ns3:dyDescent="0.2">
       <c r="A548" t="s">
         <v>230</v>
       </c>
@@ -10978,7 +10978,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="549" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:8" ns3:dyDescent="0.2">
       <c r="A549" t="s">
         <v>113</v>
       </c>
@@ -10998,7 +10998,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="550" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:8" ns3:dyDescent="0.2">
       <c r="A550" t="s">
         <v>59</v>
       </c>
@@ -11018,7 +11018,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="552" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:8" ns3:dyDescent="0.2">
       <c r="A552" s="2" t="s">
         <v>0</v>
       </c>
@@ -11026,7 +11026,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="553" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:8" ns3:dyDescent="0.2">
       <c r="A553" t="s">
         <v>2</v>
       </c>
@@ -11034,7 +11034,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="554" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:8" ns3:dyDescent="0.2">
       <c r="A554" t="s">
         <v>4</v>
       </c>
@@ -11042,7 +11042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="555" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:8" ns3:dyDescent="0.2">
       <c r="A555" t="s">
         <v>5</v>
       </c>
@@ -11050,7 +11050,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="556" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:8" ns3:dyDescent="0.2">
       <c r="A556" t="s">
         <v>7</v>
       </c>
@@ -11058,7 +11058,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="557" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:8" ns3:dyDescent="0.2">
       <c r="A557" t="s">
         <v>9</v>
       </c>
@@ -11066,12 +11066,12 @@
         <v>232</v>
       </c>
     </row>
-    <row r="558" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:8" ns3:dyDescent="0.2">
       <c r="A558" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="559" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:8" ns3:dyDescent="0.2">
       <c r="A559" s="2" t="s">
         <v>16</v>
       </c>
@@ -11097,7 +11097,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="560" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:8" ns3:dyDescent="0.2">
       <c r="A560" t="s">
         <v>62</v>
       </c>
@@ -11120,7 +11120,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="561" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:8" ns3:dyDescent="0.2">
       <c r="A561" t="s">
         <v>117</v>
       </c>
@@ -11143,7 +11143,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="562" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:8" ns3:dyDescent="0.2">
       <c r="A562" t="s">
         <v>132</v>
       </c>
@@ -11166,7 +11166,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="563" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:8" ns3:dyDescent="0.2">
       <c r="A563" t="s">
         <v>37</v>
       </c>
@@ -11189,7 +11189,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="564" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:8" ns3:dyDescent="0.2">
       <c r="A564" t="s">
         <v>129</v>
       </c>
@@ -11212,7 +11212,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="565" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:8" ns3:dyDescent="0.2">
       <c r="A565" t="s">
         <v>56</v>
       </c>
@@ -11235,7 +11235,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="566" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:8" ns3:dyDescent="0.2">
       <c r="A566" t="s">
         <v>130</v>
       </c>
@@ -11258,7 +11258,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="567" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:8" ns3:dyDescent="0.2">
       <c r="A567" t="s">
         <v>69</v>
       </c>
@@ -11281,7 +11281,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="568" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:8" ns3:dyDescent="0.2">
       <c r="A568" t="s">
         <v>72</v>
       </c>
@@ -11301,7 +11301,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="569" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:8" ns3:dyDescent="0.2">
       <c r="A569" t="s">
         <v>75</v>
       </c>
@@ -11321,7 +11321,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="570" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:8" ns3:dyDescent="0.2">
       <c r="A570" t="s">
         <v>77</v>
       </c>
@@ -11341,7 +11341,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="571" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:8" ns3:dyDescent="0.2">
       <c r="A571" t="s">
         <v>79</v>
       </c>
@@ -11361,7 +11361,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="572" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:8" ns3:dyDescent="0.2">
       <c r="A572" t="s">
         <v>81</v>
       </c>
@@ -11381,7 +11381,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="573" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:8" ns3:dyDescent="0.2">
       <c r="A573" t="s">
         <v>83</v>
       </c>
@@ -11401,7 +11401,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="574" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:8" ns3:dyDescent="0.2">
       <c r="A574" t="s">
         <v>85</v>
       </c>
@@ -11421,7 +11421,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="575" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:8" ns3:dyDescent="0.2">
       <c r="A575" t="s">
         <v>87</v>
       </c>
@@ -11441,7 +11441,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="576" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:8" ns3:dyDescent="0.2">
       <c r="A576" t="s">
         <v>88</v>
       </c>
@@ -11461,7 +11461,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="577" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:8" ns3:dyDescent="0.2">
       <c r="A577" t="s">
         <v>90</v>
       </c>
@@ -11481,7 +11481,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="578" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:8" ns3:dyDescent="0.2">
       <c r="A578" t="s">
         <v>92</v>
       </c>
@@ -11501,7 +11501,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="579" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:8" ns3:dyDescent="0.2">
       <c r="A579" t="s">
         <v>94</v>
       </c>
@@ -11521,7 +11521,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="580" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:8" ns3:dyDescent="0.2">
       <c r="A580" t="s">
         <v>96</v>
       </c>
@@ -11541,7 +11541,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="581" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:8" ns3:dyDescent="0.2">
       <c r="A581" t="s">
         <v>98</v>
       </c>
@@ -11561,7 +11561,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="582" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:8" ns3:dyDescent="0.2">
       <c r="A582" t="s">
         <v>100</v>
       </c>
@@ -11581,7 +11581,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="583" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:8" ns3:dyDescent="0.2">
       <c r="A583" t="s">
         <v>102</v>
       </c>
@@ -11601,7 +11601,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="584" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:8" ns3:dyDescent="0.2">
       <c r="A584" t="s">
         <v>104</v>
       </c>
@@ -11621,7 +11621,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="585" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:8" ns3:dyDescent="0.2">
       <c r="A585" t="s">
         <v>106</v>
       </c>
@@ -11641,7 +11641,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="586" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:8" ns3:dyDescent="0.2">
       <c r="A586" t="s">
         <v>108</v>
       </c>
@@ -11661,7 +11661,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="587" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:8" ns3:dyDescent="0.2">
       <c r="A587" t="s">
         <v>109</v>
       </c>
@@ -11681,7 +11681,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="588" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:8" ns3:dyDescent="0.2">
       <c r="A588" t="s">
         <v>231</v>
       </c>
@@ -11701,7 +11701,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="589" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:8" ns3:dyDescent="0.2">
       <c r="A589" t="s">
         <v>111</v>
       </c>
@@ -11721,7 +11721,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="590" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:8" ns3:dyDescent="0.2">
       <c r="A590" t="s">
         <v>230</v>
       </c>
@@ -11741,7 +11741,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="591" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:8" ns3:dyDescent="0.2">
       <c r="A591" t="s">
         <v>113</v>
       </c>
@@ -11761,7 +11761,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="592" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:8" ns3:dyDescent="0.2">
       <c r="A592" t="s">
         <v>115</v>
       </c>
@@ -11781,7 +11781,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="594" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:8" ns3:dyDescent="0.2">
       <c r="A594" s="2" t="s">
         <v>0</v>
       </c>
@@ -11789,7 +11789,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="595" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:8" ns3:dyDescent="0.2">
       <c r="A595" t="s">
         <v>2</v>
       </c>
@@ -11797,7 +11797,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="596" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:8" ns3:dyDescent="0.2">
       <c r="A596" t="s">
         <v>4</v>
       </c>
@@ -11805,7 +11805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="597" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:8" ns3:dyDescent="0.2">
       <c r="A597" t="s">
         <v>5</v>
       </c>
@@ -11813,7 +11813,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="598" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:8" ns3:dyDescent="0.2">
       <c r="A598" t="s">
         <v>7</v>
       </c>
@@ -11821,7 +11821,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="599" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:8" ns3:dyDescent="0.2">
       <c r="A599" t="s">
         <v>9</v>
       </c>
@@ -11829,12 +11829,12 @@
         <v>232</v>
       </c>
     </row>
-    <row r="600" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:8" ns3:dyDescent="0.2">
       <c r="A600" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="601" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:8" ns3:dyDescent="0.2">
       <c r="A601" s="2" t="s">
         <v>16</v>
       </c>
@@ -11860,7 +11860,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="602" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:8" ns3:dyDescent="0.2">
       <c r="A602" t="s">
         <v>62</v>
       </c>
@@ -11883,7 +11883,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="603" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:8" ns3:dyDescent="0.2">
       <c r="A603" t="s">
         <v>124</v>
       </c>
@@ -11906,7 +11906,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="604" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:8" ns3:dyDescent="0.2">
       <c r="A604" t="s">
         <v>45</v>
       </c>
@@ -11929,7 +11929,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="605" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:8" ns3:dyDescent="0.2">
       <c r="A605" t="s">
         <v>129</v>
       </c>
@@ -11952,7 +11952,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="606" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:8" ns3:dyDescent="0.2">
       <c r="A606" t="s">
         <v>56</v>
       </c>
@@ -11975,7 +11975,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="607" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:8" ns3:dyDescent="0.2">
       <c r="A607" t="s">
         <v>130</v>
       </c>
@@ -11998,7 +11998,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="608" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:8" ns3:dyDescent="0.2">
       <c r="A608" t="s">
         <v>69</v>
       </c>
@@ -12021,7 +12021,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="609" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:8" ns3:dyDescent="0.2">
       <c r="A609" t="s">
         <v>72</v>
       </c>
@@ -12041,7 +12041,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="610" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:8" ns3:dyDescent="0.2">
       <c r="A610" t="s">
         <v>75</v>
       </c>
@@ -12061,7 +12061,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="611" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:8" ns3:dyDescent="0.2">
       <c r="A611" t="s">
         <v>77</v>
       </c>
@@ -12081,7 +12081,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="612" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:8" ns3:dyDescent="0.2">
       <c r="A612" t="s">
         <v>79</v>
       </c>
@@ -12101,7 +12101,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="613" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:8" ns3:dyDescent="0.2">
       <c r="A613" t="s">
         <v>81</v>
       </c>
@@ -12121,7 +12121,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="614" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:8" ns3:dyDescent="0.2">
       <c r="A614" t="s">
         <v>83</v>
       </c>
@@ -12141,7 +12141,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="615" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:8" ns3:dyDescent="0.2">
       <c r="A615" t="s">
         <v>85</v>
       </c>
@@ -12161,7 +12161,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="616" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:8" ns3:dyDescent="0.2">
       <c r="A616" t="s">
         <v>87</v>
       </c>
@@ -12181,7 +12181,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="617" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:8" ns3:dyDescent="0.2">
       <c r="A617" t="s">
         <v>88</v>
       </c>
@@ -12201,7 +12201,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="618" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:8" ns3:dyDescent="0.2">
       <c r="A618" t="s">
         <v>90</v>
       </c>
@@ -12221,7 +12221,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="619" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:8" ns3:dyDescent="0.2">
       <c r="A619" t="s">
         <v>92</v>
       </c>
@@ -12241,7 +12241,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="620" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:8" ns3:dyDescent="0.2">
       <c r="A620" t="s">
         <v>94</v>
       </c>
@@ -12261,7 +12261,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="621" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:8" ns3:dyDescent="0.2">
       <c r="A621" t="s">
         <v>96</v>
       </c>
@@ -12281,7 +12281,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="622" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:8" ns3:dyDescent="0.2">
       <c r="A622" t="s">
         <v>98</v>
       </c>
@@ -12301,7 +12301,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="623" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:8" ns3:dyDescent="0.2">
       <c r="A623" t="s">
         <v>100</v>
       </c>
@@ -12321,7 +12321,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="624" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:8" ns3:dyDescent="0.2">
       <c r="A624" t="s">
         <v>102</v>
       </c>
@@ -12341,7 +12341,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="625" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:8" ns3:dyDescent="0.2">
       <c r="A625" t="s">
         <v>104</v>
       </c>
@@ -12361,7 +12361,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="626" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:8" ns3:dyDescent="0.2">
       <c r="A626" t="s">
         <v>106</v>
       </c>
@@ -12381,7 +12381,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="627" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:8" ns3:dyDescent="0.2">
       <c r="A627" t="s">
         <v>108</v>
       </c>
@@ -12401,7 +12401,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="628" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:8" ns3:dyDescent="0.2">
       <c r="A628" t="s">
         <v>109</v>
       </c>
@@ -12421,7 +12421,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="629" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:8" ns3:dyDescent="0.2">
       <c r="A629" t="s">
         <v>111</v>
       </c>
@@ -12441,7 +12441,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="630" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:8" ns3:dyDescent="0.2">
       <c r="A630" t="s">
         <v>230</v>
       </c>
@@ -12461,7 +12461,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="631" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:8" ns3:dyDescent="0.2">
       <c r="A631" t="s">
         <v>113</v>
       </c>
@@ -12481,7 +12481,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="632" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:8" ns3:dyDescent="0.2">
       <c r="A632" t="s">
         <v>123</v>
       </c>
@@ -12501,7 +12501,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="634" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:8" ns3:dyDescent="0.2">
       <c r="A634" s="2" t="s">
         <v>0</v>
       </c>
@@ -12509,7 +12509,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="635" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:8" ns3:dyDescent="0.2">
       <c r="A635" t="s">
         <v>2</v>
       </c>
@@ -12517,7 +12517,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="636" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:8" ns3:dyDescent="0.2">
       <c r="A636" t="s">
         <v>4</v>
       </c>
@@ -12525,7 +12525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="637" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:8" ns3:dyDescent="0.2">
       <c r="A637" t="s">
         <v>5</v>
       </c>
@@ -12533,7 +12533,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="638" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:8" ns3:dyDescent="0.2">
       <c r="A638" t="s">
         <v>7</v>
       </c>
@@ -12541,7 +12541,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="639" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:8" ns3:dyDescent="0.2">
       <c r="A639" t="s">
         <v>9</v>
       </c>
@@ -12549,12 +12549,12 @@
         <v>232</v>
       </c>
     </row>
-    <row r="640" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:8" ns3:dyDescent="0.2">
       <c r="A640" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="641" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:8" ns3:dyDescent="0.2">
       <c r="A641" s="2" t="s">
         <v>16</v>
       </c>
@@ -12580,7 +12580,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="642" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:8" ns3:dyDescent="0.2">
       <c r="A642" t="s">
         <v>233</v>
       </c>
@@ -12603,7 +12603,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="643" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:8" ns3:dyDescent="0.2">
       <c r="A643" t="s">
         <v>1</v>
       </c>
@@ -12626,7 +12626,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="644" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:8" ns3:dyDescent="0.2">
       <c r="A644" t="s">
         <v>129</v>
       </c>
@@ -12649,7 +12649,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="645" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:8" ns3:dyDescent="0.2">
       <c r="A645" t="s">
         <v>56</v>
       </c>
@@ -12672,7 +12672,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="646" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:8" ns3:dyDescent="0.2">
       <c r="A646" t="s">
         <v>130</v>
       </c>
@@ -12695,7 +12695,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="647" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:8" ns3:dyDescent="0.2">
       <c r="A647" t="s">
         <v>69</v>
       </c>
@@ -12718,7 +12718,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="648" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:8" ns3:dyDescent="0.2">
       <c r="A648" t="s">
         <v>72</v>
       </c>
@@ -12738,7 +12738,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="649" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:8" ns3:dyDescent="0.2">
       <c r="A649" t="s">
         <v>75</v>
       </c>
@@ -12758,7 +12758,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="650" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:8" ns3:dyDescent="0.2">
       <c r="A650" t="s">
         <v>77</v>
       </c>
@@ -12778,7 +12778,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="651" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:8" ns3:dyDescent="0.2">
       <c r="A651" t="s">
         <v>79</v>
       </c>
@@ -12798,7 +12798,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="652" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:8" ns3:dyDescent="0.2">
       <c r="A652" t="s">
         <v>81</v>
       </c>
@@ -12818,7 +12818,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="653" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:8" ns3:dyDescent="0.2">
       <c r="A653" t="s">
         <v>83</v>
       </c>
@@ -12838,7 +12838,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="654" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:8" ns3:dyDescent="0.2">
       <c r="A654" t="s">
         <v>85</v>
       </c>
@@ -12858,7 +12858,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="655" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:8" ns3:dyDescent="0.2">
       <c r="A655" t="s">
         <v>87</v>
       </c>
@@ -12878,7 +12878,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="656" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:8" ns3:dyDescent="0.2">
       <c r="A656" t="s">
         <v>88</v>
       </c>
@@ -12898,7 +12898,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="657" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:8" ns3:dyDescent="0.2">
       <c r="A657" t="s">
         <v>90</v>
       </c>
@@ -12918,7 +12918,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="658" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:8" ns3:dyDescent="0.2">
       <c r="A658" t="s">
         <v>92</v>
       </c>
@@ -12938,7 +12938,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="659" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:8" ns3:dyDescent="0.2">
       <c r="A659" t="s">
         <v>94</v>
       </c>
@@ -12958,7 +12958,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="660" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:8" ns3:dyDescent="0.2">
       <c r="A660" t="s">
         <v>96</v>
       </c>
@@ -12978,7 +12978,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="661" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:8" ns3:dyDescent="0.2">
       <c r="A661" t="s">
         <v>98</v>
       </c>
@@ -12998,7 +12998,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="662" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:8" ns3:dyDescent="0.2">
       <c r="A662" t="s">
         <v>100</v>
       </c>
@@ -13018,7 +13018,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="663" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:8" ns3:dyDescent="0.2">
       <c r="A663" t="s">
         <v>102</v>
       </c>
@@ -13038,7 +13038,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="664" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:8" ns3:dyDescent="0.2">
       <c r="A664" t="s">
         <v>104</v>
       </c>
@@ -13058,7 +13058,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="665" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:8" ns3:dyDescent="0.2">
       <c r="A665" t="s">
         <v>106</v>
       </c>
@@ -13078,7 +13078,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="666" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:8" ns3:dyDescent="0.2">
       <c r="A666" t="s">
         <v>108</v>
       </c>
@@ -13098,7 +13098,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="667" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:8" ns3:dyDescent="0.2">
       <c r="A667" t="s">
         <v>109</v>
       </c>
@@ -13118,7 +13118,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="668" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:8" ns3:dyDescent="0.2">
       <c r="A668" t="s">
         <v>111</v>
       </c>
@@ -13138,7 +13138,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="669" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:8" ns3:dyDescent="0.2">
       <c r="A669" t="s">
         <v>230</v>
       </c>
@@ -13158,7 +13158,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="670" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:8" ns3:dyDescent="0.2">
       <c r="A670" t="s">
         <v>113</v>
       </c>
@@ -13178,7 +13178,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="671" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:8" ns3:dyDescent="0.2">
       <c r="A671" t="s">
         <v>59</v>
       </c>
@@ -13198,7 +13198,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="673" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:8" ns3:dyDescent="0.2">
       <c r="A673" s="2" t="s">
         <v>0</v>
       </c>
@@ -13206,7 +13206,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="674" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:8" ns3:dyDescent="0.2">
       <c r="A674" t="s">
         <v>2</v>
       </c>
@@ -13214,7 +13214,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="675" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:8" ns3:dyDescent="0.2">
       <c r="A675" t="s">
         <v>4</v>
       </c>
@@ -13222,7 +13222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="676" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:8" ns3:dyDescent="0.2">
       <c r="A676" t="s">
         <v>5</v>
       </c>
@@ -13230,7 +13230,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="677" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:8" ns3:dyDescent="0.2">
       <c r="A677" t="s">
         <v>7</v>
       </c>
@@ -13238,7 +13238,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="678" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:8" ns3:dyDescent="0.2">
       <c r="A678" t="s">
         <v>9</v>
       </c>
@@ -13246,12 +13246,12 @@
         <v>232</v>
       </c>
     </row>
-    <row r="679" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:8" ns3:dyDescent="0.2">
       <c r="A679" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="680" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:8" ns3:dyDescent="0.2">
       <c r="A680" s="2" t="s">
         <v>16</v>
       </c>
@@ -13277,7 +13277,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="681" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:8" ns3:dyDescent="0.2">
       <c r="A681" t="s">
         <v>233</v>
       </c>
@@ -13300,7 +13300,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="682" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:8" ns3:dyDescent="0.2">
       <c r="A682" t="s">
         <v>142</v>
       </c>
@@ -13323,7 +13323,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="683" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:8" ns3:dyDescent="0.2">
       <c r="A683" t="s">
         <v>142</v>
       </c>
@@ -13346,7 +13346,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="684" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:8" ns3:dyDescent="0.2">
       <c r="A684" t="s">
         <v>142</v>
       </c>
@@ -13369,7 +13369,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="685" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:8" ns3:dyDescent="0.2">
       <c r="A685" t="s">
         <v>142</v>
       </c>
@@ -13392,7 +13392,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="686" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:8" ns3:dyDescent="0.2">
       <c r="A686" t="s">
         <v>142</v>
       </c>
@@ -13415,7 +13415,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="687" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:8" ns3:dyDescent="0.2">
       <c r="A687" t="s">
         <v>142</v>
       </c>
@@ -13438,7 +13438,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="688" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:8" ns3:dyDescent="0.2">
       <c r="A688" t="s">
         <v>142</v>
       </c>
@@ -13461,7 +13461,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="689" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:8" ns3:dyDescent="0.2">
       <c r="A689" t="s">
         <v>142</v>
       </c>
@@ -13484,7 +13484,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="690" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:8" ns3:dyDescent="0.2">
       <c r="A690" t="s">
         <v>142</v>
       </c>
@@ -13507,7 +13507,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="691" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:8" ns3:dyDescent="0.2">
       <c r="A691" t="s">
         <v>142</v>
       </c>
@@ -13530,7 +13530,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="692" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:8" ns3:dyDescent="0.2">
       <c r="A692" t="s">
         <v>142</v>
       </c>
@@ -13553,7 +13553,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="693" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:8" ns3:dyDescent="0.2">
       <c r="A693" t="s">
         <v>142</v>
       </c>
@@ -13576,7 +13576,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="694" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:8" ns3:dyDescent="0.2">
       <c r="A694" t="s">
         <v>142</v>
       </c>
@@ -13599,7 +13599,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="695" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:8" ns3:dyDescent="0.2">
       <c r="A695" t="s">
         <v>142</v>
       </c>
@@ -13622,7 +13622,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="696" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:8" ns3:dyDescent="0.2">
       <c r="A696" t="s">
         <v>142</v>
       </c>
@@ -13645,7 +13645,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="697" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:8" ns3:dyDescent="0.2">
       <c r="A697" t="s">
         <v>142</v>
       </c>
@@ -13668,7 +13668,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="698" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:8" ns3:dyDescent="0.2">
       <c r="A698" t="s">
         <v>142</v>
       </c>
@@ -13691,7 +13691,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="699" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:8" ns3:dyDescent="0.2">
       <c r="A699" t="s">
         <v>142</v>
       </c>
@@ -13714,7 +13714,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="700" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:8" ns3:dyDescent="0.2">
       <c r="A700" t="s">
         <v>142</v>
       </c>
@@ -13737,7 +13737,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="701" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:8" ns3:dyDescent="0.2">
       <c r="A701" t="s">
         <v>142</v>
       </c>
@@ -13760,7 +13760,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="702" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:8" ns3:dyDescent="0.2">
       <c r="A702" t="s">
         <v>142</v>
       </c>
@@ -13783,7 +13783,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="703" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:8" ns3:dyDescent="0.2">
       <c r="A703" t="s">
         <v>142</v>
       </c>
@@ -13806,7 +13806,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="704" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:8" ns3:dyDescent="0.2">
       <c r="A704" t="s">
         <v>142</v>
       </c>
@@ -13829,7 +13829,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="705" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:8" ns3:dyDescent="0.2">
       <c r="A705" t="s">
         <v>142</v>
       </c>
@@ -13852,7 +13852,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="706" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:8" ns3:dyDescent="0.2">
       <c r="A706" t="s">
         <v>142</v>
       </c>
@@ -13875,7 +13875,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="707" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:8" ns3:dyDescent="0.2">
       <c r="A707" t="s">
         <v>142</v>
       </c>
@@ -13898,7 +13898,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="708" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:8" ns3:dyDescent="0.2">
       <c r="A708" t="s">
         <v>142</v>
       </c>
@@ -13921,7 +13921,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="709" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:8" ns3:dyDescent="0.2">
       <c r="A709" t="s">
         <v>142</v>
       </c>
@@ -13944,7 +13944,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="710" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:8" ns3:dyDescent="0.2">
       <c r="A710" t="s">
         <v>142</v>
       </c>
@@ -13967,7 +13967,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="711" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:8" ns3:dyDescent="0.2">
       <c r="A711" t="s">
         <v>142</v>
       </c>
@@ -13990,7 +13990,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="712" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:8" ns3:dyDescent="0.2">
       <c r="A712" t="s">
         <v>142</v>
       </c>
@@ -14013,7 +14013,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="713" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:8" ns3:dyDescent="0.2">
       <c r="A713" t="s">
         <v>142</v>
       </c>
@@ -14036,7 +14036,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="714" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:8" ns3:dyDescent="0.2">
       <c r="A714" t="s">
         <v>142</v>
       </c>
@@ -14059,7 +14059,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="715" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:8" ns3:dyDescent="0.2">
       <c r="A715" t="s">
         <v>142</v>
       </c>
@@ -14082,7 +14082,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="716" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:8" ns3:dyDescent="0.2">
       <c r="A716" t="s">
         <v>142</v>
       </c>
@@ -14105,7 +14105,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="717" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:8" ns3:dyDescent="0.2">
       <c r="A717" t="s">
         <v>142</v>
       </c>
@@ -14128,7 +14128,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="718" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:8" ns3:dyDescent="0.2">
       <c r="A718" t="s">
         <v>142</v>
       </c>
@@ -14151,7 +14151,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="719" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:8" ns3:dyDescent="0.2">
       <c r="A719" t="s">
         <v>142</v>
       </c>
@@ -14174,7 +14174,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="720" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:8" ns3:dyDescent="0.2">
       <c r="A720" t="s">
         <v>142</v>
       </c>
@@ -14197,7 +14197,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="721" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:8" ns3:dyDescent="0.2">
       <c r="A721" t="s">
         <v>142</v>
       </c>
@@ -14220,7 +14220,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="722" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:8" ns3:dyDescent="0.2">
       <c r="A722" t="s">
         <v>142</v>
       </c>
@@ -14243,7 +14243,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="723" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:8" ns3:dyDescent="0.2">
       <c r="A723" t="s">
         <v>142</v>
       </c>
@@ -14266,7 +14266,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="724" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:8" ns3:dyDescent="0.2">
       <c r="A724" t="s">
         <v>142</v>
       </c>
@@ -14289,7 +14289,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="725" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:8" ns3:dyDescent="0.2">
       <c r="A725" t="s">
         <v>142</v>
       </c>
@@ -14312,7 +14312,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="726" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:8" ns3:dyDescent="0.2">
       <c r="A726" t="s">
         <v>142</v>
       </c>
@@ -14335,7 +14335,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="727" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:8" ns3:dyDescent="0.2">
       <c r="A727" t="s">
         <v>142</v>
       </c>
@@ -14358,7 +14358,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="728" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:8" ns3:dyDescent="0.2">
       <c r="A728" t="s">
         <v>142</v>
       </c>
@@ -14381,7 +14381,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="729" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:8" ns3:dyDescent="0.2">
       <c r="A729" t="s">
         <v>142</v>
       </c>
@@ -14404,7 +14404,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="730" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:8" ns3:dyDescent="0.2">
       <c r="A730" t="s">
         <v>142</v>
       </c>
@@ -14427,7 +14427,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="731" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:8" ns3:dyDescent="0.2">
       <c r="A731" t="s">
         <v>142</v>
       </c>
@@ -14450,7 +14450,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="732" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:8" ns3:dyDescent="0.2">
       <c r="A732" t="s">
         <v>142</v>
       </c>
@@ -14473,7 +14473,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="733" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:8" ns3:dyDescent="0.2">
       <c r="A733" t="s">
         <v>142</v>
       </c>
@@ -14496,7 +14496,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="734" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:8" ns3:dyDescent="0.2">
       <c r="A734" t="s">
         <v>142</v>
       </c>
@@ -14519,7 +14519,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="735" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:8" ns3:dyDescent="0.2">
       <c r="A735" t="s">
         <v>142</v>
       </c>
@@ -14542,7 +14542,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="736" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:8" ns3:dyDescent="0.2">
       <c r="A736" t="s">
         <v>142</v>
       </c>
@@ -14565,7 +14565,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="737" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:8" ns3:dyDescent="0.2">
       <c r="A737" t="s">
         <v>142</v>
       </c>
@@ -14588,7 +14588,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="738" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:8" ns3:dyDescent="0.2">
       <c r="A738" t="s">
         <v>142</v>
       </c>
@@ -14611,7 +14611,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="739" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:8" ns3:dyDescent="0.2">
       <c r="A739" t="s">
         <v>142</v>
       </c>
@@ -14634,7 +14634,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="740" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:8" ns3:dyDescent="0.2">
       <c r="A740" t="s">
         <v>142</v>
       </c>
@@ -14657,7 +14657,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="741" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:8" ns3:dyDescent="0.2">
       <c r="A741" t="s">
         <v>142</v>
       </c>
@@ -14680,7 +14680,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="742" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:8" ns3:dyDescent="0.2">
       <c r="A742" t="s">
         <v>142</v>
       </c>
@@ -14703,7 +14703,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="743" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:8" ns3:dyDescent="0.2">
       <c r="A743" t="s">
         <v>142</v>
       </c>
@@ -14726,7 +14726,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="744" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:8" ns3:dyDescent="0.2">
       <c r="A744" t="s">
         <v>142</v>
       </c>
@@ -14749,7 +14749,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="745" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:8" ns3:dyDescent="0.2">
       <c r="A745" t="s">
         <v>142</v>
       </c>
@@ -14772,7 +14772,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="746" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:8" ns3:dyDescent="0.2">
       <c r="A746" t="s">
         <v>142</v>
       </c>
@@ -14795,7 +14795,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="747" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:8" ns3:dyDescent="0.2">
       <c r="A747" t="s">
         <v>142</v>
       </c>
@@ -14818,7 +14818,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="748" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:8" ns3:dyDescent="0.2">
       <c r="A748" t="s">
         <v>142</v>
       </c>
@@ -14841,7 +14841,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="749" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:8" ns3:dyDescent="0.2">
       <c r="A749" t="s">
         <v>142</v>
       </c>
@@ -14864,7 +14864,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="750" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:8" ns3:dyDescent="0.2">
       <c r="A750" t="s">
         <v>143</v>
       </c>
@@ -14887,7 +14887,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="751" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:8" ns3:dyDescent="0.2">
       <c r="A751" t="s">
         <v>143</v>
       </c>
@@ -14910,7 +14910,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="752" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:8" ns3:dyDescent="0.2">
       <c r="A752" t="s">
         <v>143</v>
       </c>
@@ -14933,7 +14933,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="753" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:8" ns3:dyDescent="0.2">
       <c r="A753" t="s">
         <v>143</v>
       </c>
@@ -14956,7 +14956,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="754" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:8" ns3:dyDescent="0.2">
       <c r="A754" t="s">
         <v>143</v>
       </c>
@@ -14979,7 +14979,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="755" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:8" ns3:dyDescent="0.2">
       <c r="A755" t="s">
         <v>143</v>
       </c>
@@ -15002,7 +15002,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="756" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:8" ns3:dyDescent="0.2">
       <c r="A756" t="s">
         <v>143</v>
       </c>
@@ -15025,7 +15025,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="757" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:8" ns3:dyDescent="0.2">
       <c r="A757" t="s">
         <v>143</v>
       </c>
@@ -15048,7 +15048,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="758" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:8" ns3:dyDescent="0.2">
       <c r="A758" t="s">
         <v>143</v>
       </c>
@@ -15071,7 +15071,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="759" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:8" ns3:dyDescent="0.2">
       <c r="A759" t="s">
         <v>143</v>
       </c>
@@ -15094,7 +15094,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="760" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:8" ns3:dyDescent="0.2">
       <c r="A760" t="s">
         <v>143</v>
       </c>
@@ -15117,7 +15117,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="761" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:8" ns3:dyDescent="0.2">
       <c r="A761" t="s">
         <v>143</v>
       </c>
@@ -15140,7 +15140,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="762" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:8" ns3:dyDescent="0.2">
       <c r="A762" t="s">
         <v>143</v>
       </c>
@@ -15163,7 +15163,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="763" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:8" ns3:dyDescent="0.2">
       <c r="A763" t="s">
         <v>143</v>
       </c>
@@ -15186,7 +15186,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="764" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:8" ns3:dyDescent="0.2">
       <c r="A764" t="s">
         <v>143</v>
       </c>
@@ -15209,7 +15209,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="765" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:8" ns3:dyDescent="0.2">
       <c r="A765" t="s">
         <v>143</v>
       </c>
@@ -15232,7 +15232,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="766" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:8" ns3:dyDescent="0.2">
       <c r="A766" t="s">
         <v>143</v>
       </c>
@@ -15255,7 +15255,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="767" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:8" ns3:dyDescent="0.2">
       <c r="A767" t="s">
         <v>143</v>
       </c>
@@ -15278,7 +15278,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="768" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:8" ns3:dyDescent="0.2">
       <c r="A768" t="s">
         <v>143</v>
       </c>
@@ -15301,7 +15301,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="769" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:8" ns3:dyDescent="0.2">
       <c r="A769" t="s">
         <v>143</v>
       </c>
@@ -15324,7 +15324,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="770" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:8" ns3:dyDescent="0.2">
       <c r="A770" t="s">
         <v>143</v>
       </c>
@@ -15347,7 +15347,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="771" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:8" ns3:dyDescent="0.2">
       <c r="A771" t="s">
         <v>143</v>
       </c>
@@ -15370,7 +15370,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="772" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:8" ns3:dyDescent="0.2">
       <c r="A772" t="s">
         <v>143</v>
       </c>
@@ -15393,7 +15393,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="773" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:8" ns3:dyDescent="0.2">
       <c r="A773" t="s">
         <v>143</v>
       </c>
@@ -15416,7 +15416,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="774" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:8" ns3:dyDescent="0.2">
       <c r="A774" t="s">
         <v>143</v>
       </c>
@@ -15439,7 +15439,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="775" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="775" spans="1:8" ns3:dyDescent="0.2">
       <c r="A775" t="s">
         <v>143</v>
       </c>
@@ -15462,7 +15462,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="776" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="776" spans="1:8" ns3:dyDescent="0.2">
       <c r="A776" t="s">
         <v>143</v>
       </c>
@@ -15485,7 +15485,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="777" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="777" spans="1:8" ns3:dyDescent="0.2">
       <c r="A777" t="s">
         <v>143</v>
       </c>
@@ -15508,7 +15508,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="778" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:8" ns3:dyDescent="0.2">
       <c r="A778" t="s">
         <v>143</v>
       </c>
@@ -15531,7 +15531,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="779" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="779" spans="1:8" ns3:dyDescent="0.2">
       <c r="A779" t="s">
         <v>143</v>
       </c>
@@ -15554,7 +15554,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="780" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:8" ns3:dyDescent="0.2">
       <c r="A780" t="s">
         <v>143</v>
       </c>
@@ -15577,7 +15577,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="781" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="781" spans="1:8" ns3:dyDescent="0.2">
       <c r="A781" t="s">
         <v>143</v>
       </c>
@@ -15600,7 +15600,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="782" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="782" spans="1:8" ns3:dyDescent="0.2">
       <c r="A782" t="s">
         <v>143</v>
       </c>
@@ -15623,7 +15623,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="783" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:8" ns3:dyDescent="0.2">
       <c r="A783" t="s">
         <v>143</v>
       </c>
@@ -15646,7 +15646,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="784" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="784" spans="1:8" ns3:dyDescent="0.2">
       <c r="A784" t="s">
         <v>143</v>
       </c>
@@ -15669,7 +15669,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="785" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="785" spans="1:8" ns3:dyDescent="0.2">
       <c r="A785" t="s">
         <v>143</v>
       </c>
@@ -15692,7 +15692,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="786" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="786" spans="1:8" ns3:dyDescent="0.2">
       <c r="A786" t="s">
         <v>143</v>
       </c>
@@ -15715,7 +15715,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="787" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="787" spans="1:8" ns3:dyDescent="0.2">
       <c r="A787" t="s">
         <v>143</v>
       </c>
@@ -15738,7 +15738,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="788" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="788" spans="1:8" ns3:dyDescent="0.2">
       <c r="A788" t="s">
         <v>143</v>
       </c>
@@ -15761,7 +15761,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="789" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:8" ns3:dyDescent="0.2">
       <c r="A789" t="s">
         <v>143</v>
       </c>
@@ -15784,7 +15784,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="790" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="790" spans="1:8" ns3:dyDescent="0.2">
       <c r="A790" t="s">
         <v>143</v>
       </c>
@@ -15807,7 +15807,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="791" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="791" spans="1:8" ns3:dyDescent="0.2">
       <c r="A791" t="s">
         <v>143</v>
       </c>
@@ -15830,7 +15830,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="792" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="792" spans="1:8" ns3:dyDescent="0.2">
       <c r="A792" t="s">
         <v>143</v>
       </c>
@@ -15853,7 +15853,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="793" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="793" spans="1:8" ns3:dyDescent="0.2">
       <c r="A793" t="s">
         <v>143</v>
       </c>
@@ -15876,7 +15876,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="794" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="794" spans="1:8" ns3:dyDescent="0.2">
       <c r="A794" t="s">
         <v>143</v>
       </c>
@@ -15899,7 +15899,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="795" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="795" spans="1:8" ns3:dyDescent="0.2">
       <c r="A795" t="s">
         <v>143</v>
       </c>
@@ -15922,7 +15922,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="796" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="796" spans="1:8" ns3:dyDescent="0.2">
       <c r="A796" t="s">
         <v>143</v>
       </c>
@@ -15945,7 +15945,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="797" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="797" spans="1:8" ns3:dyDescent="0.2">
       <c r="A797" t="s">
         <v>143</v>
       </c>
@@ -15968,7 +15968,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="798" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="798" spans="1:8" ns3:dyDescent="0.2">
       <c r="A798" t="s">
         <v>143</v>
       </c>
@@ -15991,7 +15991,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="799" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="799" spans="1:8" ns3:dyDescent="0.2">
       <c r="A799" t="s">
         <v>143</v>
       </c>
@@ -16014,7 +16014,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="800" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="800" spans="1:8" ns3:dyDescent="0.2">
       <c r="A800" t="s">
         <v>143</v>
       </c>
@@ -16037,7 +16037,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="801" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="801" spans="1:8" ns3:dyDescent="0.2">
       <c r="A801" t="s">
         <v>143</v>
       </c>
@@ -16060,7 +16060,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="802" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="802" spans="1:8" ns3:dyDescent="0.2">
       <c r="A802" t="s">
         <v>143</v>
       </c>
@@ -16083,7 +16083,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="803" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="803" spans="1:8" ns3:dyDescent="0.2">
       <c r="A803" t="s">
         <v>143</v>
       </c>
@@ -16106,7 +16106,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="804" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="804" spans="1:8" ns3:dyDescent="0.2">
       <c r="A804" t="s">
         <v>143</v>
       </c>
@@ -16129,7 +16129,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="805" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="805" spans="1:8" ns3:dyDescent="0.2">
       <c r="A805" t="s">
         <v>143</v>
       </c>
@@ -16152,7 +16152,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="806" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="806" spans="1:8" ns3:dyDescent="0.2">
       <c r="A806" t="s">
         <v>143</v>
       </c>
@@ -16175,7 +16175,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="807" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="807" spans="1:8" ns3:dyDescent="0.2">
       <c r="A807" t="s">
         <v>143</v>
       </c>
@@ -16198,7 +16198,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="808" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="808" spans="1:8" ns3:dyDescent="0.2">
       <c r="A808" t="s">
         <v>143</v>
       </c>
@@ -16221,7 +16221,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="809" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="809" spans="1:8" ns3:dyDescent="0.2">
       <c r="A809" t="s">
         <v>143</v>
       </c>
@@ -16244,7 +16244,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="810" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="810" spans="1:8" ns3:dyDescent="0.2">
       <c r="A810" t="s">
         <v>143</v>
       </c>
@@ -16267,7 +16267,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="811" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="811" spans="1:8" ns3:dyDescent="0.2">
       <c r="A811" t="s">
         <v>143</v>
       </c>
@@ -16290,7 +16290,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="812" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="812" spans="1:8" ns3:dyDescent="0.2">
       <c r="A812" t="s">
         <v>143</v>
       </c>
@@ -16313,7 +16313,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="813" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="813" spans="1:8" ns3:dyDescent="0.2">
       <c r="A813" t="s">
         <v>143</v>
       </c>
@@ -16336,7 +16336,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="814" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="814" spans="1:8" ns3:dyDescent="0.2">
       <c r="A814" t="s">
         <v>143</v>
       </c>
@@ -16359,7 +16359,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="815" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="815" spans="1:8" ns3:dyDescent="0.2">
       <c r="A815" t="s">
         <v>143</v>
       </c>
@@ -16382,7 +16382,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="816" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="816" spans="1:8" ns3:dyDescent="0.2">
       <c r="A816" t="s">
         <v>143</v>
       </c>
@@ -16405,7 +16405,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="817" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="817" spans="1:8" ns3:dyDescent="0.2">
       <c r="A817" t="s">
         <v>143</v>
       </c>
@@ -16428,7 +16428,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="818" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="818" spans="1:8" ns3:dyDescent="0.2">
       <c r="A818" t="s">
         <v>117</v>
       </c>
@@ -16451,7 +16451,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="819" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="819" spans="1:8" ns3:dyDescent="0.2">
       <c r="A819" t="s">
         <v>117</v>
       </c>
@@ -16474,7 +16474,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="820" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="820" spans="1:8" ns3:dyDescent="0.2">
       <c r="A820" t="s">
         <v>117</v>
       </c>
@@ -16497,7 +16497,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="821" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="821" spans="1:8" ns3:dyDescent="0.2">
       <c r="A821" t="s">
         <v>132</v>
       </c>
@@ -16520,7 +16520,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="822" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="822" spans="1:8" ns3:dyDescent="0.2">
       <c r="A822" t="s">
         <v>132</v>
       </c>
@@ -16543,7 +16543,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="823" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="823" spans="1:8" ns3:dyDescent="0.2">
       <c r="A823" t="s">
         <v>132</v>
       </c>
@@ -16566,7 +16566,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="824" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="824" spans="1:8" ns3:dyDescent="0.2">
       <c r="A824" t="s">
         <v>37</v>
       </c>
@@ -16589,7 +16589,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="825" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="825" spans="1:8" ns3:dyDescent="0.2">
       <c r="A825" t="s">
         <v>129</v>
       </c>
@@ -16612,7 +16612,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="826" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="826" spans="1:8" ns3:dyDescent="0.2">
       <c r="A826" t="s">
         <v>56</v>
       </c>
@@ -16635,7 +16635,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="827" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="827" spans="1:8" ns3:dyDescent="0.2">
       <c r="A827" t="s">
         <v>130</v>
       </c>
@@ -16658,7 +16658,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="828" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="828" spans="1:8" ns3:dyDescent="0.2">
       <c r="A828" t="s">
         <v>69</v>
       </c>
@@ -16681,7 +16681,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="829" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="829" spans="1:8" ns3:dyDescent="0.2">
       <c r="A829" t="s">
         <v>72</v>
       </c>
@@ -16701,7 +16701,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="830" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="830" spans="1:8" ns3:dyDescent="0.2">
       <c r="A830" t="s">
         <v>75</v>
       </c>
@@ -16721,7 +16721,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="831" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="831" spans="1:8" ns3:dyDescent="0.2">
       <c r="A831" t="s">
         <v>77</v>
       </c>
@@ -16741,7 +16741,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="832" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="832" spans="1:8" ns3:dyDescent="0.2">
       <c r="A832" t="s">
         <v>79</v>
       </c>
@@ -16761,7 +16761,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="833" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="833" spans="1:8" ns3:dyDescent="0.2">
       <c r="A833" t="s">
         <v>81</v>
       </c>
@@ -16781,7 +16781,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="834" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="834" spans="1:8" ns3:dyDescent="0.2">
       <c r="A834" t="s">
         <v>83</v>
       </c>
@@ -16801,7 +16801,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="835" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="835" spans="1:8" ns3:dyDescent="0.2">
       <c r="A835" t="s">
         <v>85</v>
       </c>
@@ -16821,7 +16821,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="836" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="836" spans="1:8" ns3:dyDescent="0.2">
       <c r="A836" t="s">
         <v>87</v>
       </c>
@@ -16841,7 +16841,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="837" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="837" spans="1:8" ns3:dyDescent="0.2">
       <c r="A837" t="s">
         <v>88</v>
       </c>
@@ -16861,7 +16861,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="838" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="838" spans="1:8" ns3:dyDescent="0.2">
       <c r="A838" t="s">
         <v>90</v>
       </c>
@@ -16881,7 +16881,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="839" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="839" spans="1:8" ns3:dyDescent="0.2">
       <c r="A839" t="s">
         <v>92</v>
       </c>
@@ -16901,7 +16901,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="840" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="840" spans="1:8" ns3:dyDescent="0.2">
       <c r="A840" t="s">
         <v>94</v>
       </c>
@@ -16921,7 +16921,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="841" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="841" spans="1:8" ns3:dyDescent="0.2">
       <c r="A841" t="s">
         <v>96</v>
       </c>
@@ -16941,7 +16941,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="842" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="842" spans="1:8" ns3:dyDescent="0.2">
       <c r="A842" t="s">
         <v>98</v>
       </c>
@@ -16961,7 +16961,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="843" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="843" spans="1:8" ns3:dyDescent="0.2">
       <c r="A843" t="s">
         <v>100</v>
       </c>
@@ -16981,7 +16981,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="844" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="844" spans="1:8" ns3:dyDescent="0.2">
       <c r="A844" t="s">
         <v>102</v>
       </c>
@@ -17001,7 +17001,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="845" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="845" spans="1:8" ns3:dyDescent="0.2">
       <c r="A845" t="s">
         <v>104</v>
       </c>
@@ -17021,7 +17021,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="846" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="846" spans="1:8" ns3:dyDescent="0.2">
       <c r="A846" t="s">
         <v>106</v>
       </c>
@@ -17041,7 +17041,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="847" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="847" spans="1:8" ns3:dyDescent="0.2">
       <c r="A847" t="s">
         <v>108</v>
       </c>
@@ -17061,7 +17061,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="848" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="848" spans="1:8" ns3:dyDescent="0.2">
       <c r="A848" t="s">
         <v>109</v>
       </c>
@@ -17081,7 +17081,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="849" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="849" spans="1:8" ns3:dyDescent="0.2">
       <c r="A849" t="s">
         <v>231</v>
       </c>
@@ -17101,7 +17101,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="850" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="850" spans="1:8" ns3:dyDescent="0.2">
       <c r="A850" t="s">
         <v>111</v>
       </c>
@@ -17121,7 +17121,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="851" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="851" spans="1:8" ns3:dyDescent="0.2">
       <c r="A851" t="s">
         <v>230</v>
       </c>
@@ -17141,7 +17141,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="852" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="852" spans="1:8" ns3:dyDescent="0.2">
       <c r="A852" t="s">
         <v>113</v>
       </c>
@@ -17161,7 +17161,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="853" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="853" spans="1:8" ns3:dyDescent="0.2">
       <c r="A853" t="s">
         <v>115</v>
       </c>
@@ -17181,7 +17181,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="855" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="855" spans="1:8" ns3:dyDescent="0.2">
       <c r="A855" s="2" t="s">
         <v>0</v>
       </c>
@@ -17189,7 +17189,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="856" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="856" spans="1:8" ns3:dyDescent="0.2">
       <c r="A856" t="s">
         <v>2</v>
       </c>
@@ -17197,7 +17197,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="857" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="857" spans="1:8" ns3:dyDescent="0.2">
       <c r="A857" t="s">
         <v>4</v>
       </c>
@@ -17205,7 +17205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="858" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="858" spans="1:8" ns3:dyDescent="0.2">
       <c r="A858" t="s">
         <v>5</v>
       </c>
@@ -17213,7 +17213,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="859" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="859" spans="1:8" ns3:dyDescent="0.2">
       <c r="A859" t="s">
         <v>7</v>
       </c>
@@ -17221,7 +17221,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="860" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="860" spans="1:8" ns3:dyDescent="0.2">
       <c r="A860" t="s">
         <v>9</v>
       </c>
@@ -17229,12 +17229,12 @@
         <v>232</v>
       </c>
     </row>
-    <row r="861" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="861" spans="1:8" ns3:dyDescent="0.2">
       <c r="A861" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="862" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="862" spans="1:8" ns3:dyDescent="0.2">
       <c r="A862" s="2" t="s">
         <v>16</v>
       </c>
@@ -17260,7 +17260,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="863" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="863" spans="1:8" ns3:dyDescent="0.2">
       <c r="A863" t="s">
         <v>233</v>
       </c>
@@ -17283,7 +17283,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="864" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="864" spans="1:8" ns3:dyDescent="0.2">
       <c r="A864" t="s">
         <v>124</v>
       </c>
@@ -17306,7 +17306,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="865" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="865" spans="1:8" ns3:dyDescent="0.2">
       <c r="A865" t="s">
         <v>45</v>
       </c>
@@ -17329,7 +17329,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="866" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="866" spans="1:8" ns3:dyDescent="0.2">
       <c r="A866" t="s">
         <v>129</v>
       </c>
@@ -17352,7 +17352,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="867" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="867" spans="1:8" ns3:dyDescent="0.2">
       <c r="A867" t="s">
         <v>56</v>
       </c>
@@ -17375,7 +17375,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="868" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="868" spans="1:8" ns3:dyDescent="0.2">
       <c r="A868" t="s">
         <v>130</v>
       </c>
@@ -17398,7 +17398,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="869" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="869" spans="1:8" ns3:dyDescent="0.2">
       <c r="A869" t="s">
         <v>69</v>
       </c>
@@ -17421,7 +17421,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="870" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="870" spans="1:8" ns3:dyDescent="0.2">
       <c r="A870" t="s">
         <v>72</v>
       </c>
@@ -17441,7 +17441,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="871" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="871" spans="1:8" ns3:dyDescent="0.2">
       <c r="A871" t="s">
         <v>75</v>
       </c>
@@ -17461,7 +17461,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="872" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="872" spans="1:8" ns3:dyDescent="0.2">
       <c r="A872" t="s">
         <v>77</v>
       </c>
@@ -17481,7 +17481,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="873" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="873" spans="1:8" ns3:dyDescent="0.2">
       <c r="A873" t="s">
         <v>79</v>
       </c>
@@ -17501,7 +17501,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="874" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="874" spans="1:8" ns3:dyDescent="0.2">
       <c r="A874" t="s">
         <v>81</v>
       </c>
@@ -17521,7 +17521,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="875" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="875" spans="1:8" ns3:dyDescent="0.2">
       <c r="A875" t="s">
         <v>83</v>
       </c>
@@ -17541,7 +17541,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="876" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="876" spans="1:8" ns3:dyDescent="0.2">
       <c r="A876" t="s">
         <v>85</v>
       </c>
@@ -17561,7 +17561,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="877" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="877" spans="1:8" ns3:dyDescent="0.2">
       <c r="A877" t="s">
         <v>87</v>
       </c>
@@ -17581,7 +17581,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="878" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="878" spans="1:8" ns3:dyDescent="0.2">
       <c r="A878" t="s">
         <v>88</v>
       </c>
@@ -17601,7 +17601,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="879" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="879" spans="1:8" ns3:dyDescent="0.2">
       <c r="A879" t="s">
         <v>90</v>
       </c>
@@ -17621,7 +17621,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="880" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="880" spans="1:8" ns3:dyDescent="0.2">
       <c r="A880" t="s">
         <v>92</v>
       </c>
@@ -17641,7 +17641,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="881" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="881" spans="1:8" ns3:dyDescent="0.2">
       <c r="A881" t="s">
         <v>94</v>
       </c>
@@ -17661,7 +17661,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="882" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="882" spans="1:8" ns3:dyDescent="0.2">
       <c r="A882" t="s">
         <v>96</v>
       </c>
@@ -17681,7 +17681,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="883" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="883" spans="1:8" ns3:dyDescent="0.2">
       <c r="A883" t="s">
         <v>98</v>
       </c>
@@ -17701,7 +17701,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="884" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="884" spans="1:8" ns3:dyDescent="0.2">
       <c r="A884" t="s">
         <v>100</v>
       </c>
@@ -17721,7 +17721,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="885" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="885" spans="1:8" ns3:dyDescent="0.2">
       <c r="A885" t="s">
         <v>102</v>
       </c>
@@ -17741,7 +17741,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="886" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="886" spans="1:8" ns3:dyDescent="0.2">
       <c r="A886" t="s">
         <v>104</v>
       </c>
@@ -17761,7 +17761,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="887" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="887" spans="1:8" ns3:dyDescent="0.2">
       <c r="A887" t="s">
         <v>106</v>
       </c>
@@ -17781,7 +17781,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="888" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="888" spans="1:8" ns3:dyDescent="0.2">
       <c r="A888" t="s">
         <v>108</v>
       </c>
@@ -17801,7 +17801,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="889" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="889" spans="1:8" ns3:dyDescent="0.2">
       <c r="A889" t="s">
         <v>109</v>
       </c>
@@ -17821,7 +17821,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="890" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="890" spans="1:8" ns3:dyDescent="0.2">
       <c r="A890" t="s">
         <v>111</v>
       </c>
@@ -17841,7 +17841,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="891" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="891" spans="1:8" ns3:dyDescent="0.2">
       <c r="A891" t="s">
         <v>230</v>
       </c>
@@ -17861,7 +17861,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="892" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="892" spans="1:8" ns3:dyDescent="0.2">
       <c r="A892" t="s">
         <v>113</v>
       </c>
@@ -17881,7 +17881,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="893" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="893" spans="1:8" ns3:dyDescent="0.2">
       <c r="A893" t="s">
         <v>123</v>
       </c>
@@ -17901,7 +17901,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="895" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="895" spans="1:8" ht="16" ns3:dyDescent="0.2">
       <c r="A895" s="1" t="s">
         <v>0</v>
       </c>
@@ -17909,7 +17909,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="896" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="896" spans="1:8" ns3:dyDescent="0.2">
       <c r="A896" t="s">
         <v>2</v>
       </c>
@@ -17917,7 +17917,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="897" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="897" spans="1:8" ns3:dyDescent="0.2">
       <c r="A897" t="s">
         <v>4</v>
       </c>
@@ -17925,7 +17925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="898" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="898" spans="1:8" ns3:dyDescent="0.2">
       <c r="A898" t="s">
         <v>5</v>
       </c>
@@ -17933,7 +17933,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="899" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="899" spans="1:8" ns3:dyDescent="0.2">
       <c r="A899" t="s">
         <v>7</v>
       </c>
@@ -17941,7 +17941,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="900" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="900" spans="1:8" ns3:dyDescent="0.2">
       <c r="A900" t="s">
         <v>9</v>
       </c>
@@ -17949,7 +17949,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="901" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="901" spans="1:8" ns3:dyDescent="0.2">
       <c r="A901" t="s">
         <v>10</v>
       </c>
@@ -17957,7 +17957,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="902" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="902" spans="1:8" ns3:dyDescent="0.2">
       <c r="A902" t="s">
         <v>12</v>
       </c>
@@ -17965,12 +17965,12 @@
         <v>235</v>
       </c>
     </row>
-    <row r="903" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="903" spans="1:8" ht="16" ns3:dyDescent="0.2">
       <c r="A903" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="904" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="904" spans="1:8" ns3:dyDescent="0.2">
       <c r="A904" s="2" t="s">
         <v>16</v>
       </c>
@@ -17994,7 +17994,7 @@
       </c>
       <c r="H904" s="2"/>
     </row>
-    <row r="905" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="905" spans="1:8" ns3:dyDescent="0.2">
       <c r="A905" t="s">
         <v>236</v>
       </c>
@@ -18017,7 +18017,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="906" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="906" spans="1:8" ns3:dyDescent="0.2">
       <c r="A906" t="s">
         <v>238</v>
       </c>
@@ -18040,7 +18040,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="907" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="907" spans="1:8" ns3:dyDescent="0.2">
       <c r="A907" t="s">
         <v>239</v>
       </c>
@@ -18057,7 +18057,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="908" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="908" spans="1:8" ns3:dyDescent="0.2">
       <c r="A908" t="s">
         <v>241</v>
       </c>
@@ -18080,7 +18080,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="909" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="909" spans="1:8" ns3:dyDescent="0.2">
       <c r="A909" t="s">
         <v>243</v>
       </c>
@@ -18103,7 +18103,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="910" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="910" spans="1:8" ns3:dyDescent="0.2">
       <c r="A910" t="s">
         <v>246</v>
       </c>
@@ -18126,7 +18126,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="911" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="911" spans="1:8" ns3:dyDescent="0.2">
       <c r="A911" t="s">
         <v>247</v>
       </c>
@@ -18143,7 +18143,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="912" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="912" spans="1:8" ns3:dyDescent="0.2">
       <c r="A912" t="s">
         <v>81</v>
       </c>
@@ -18160,7 +18160,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="913" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="913" spans="1:7" ns3:dyDescent="0.2">
       <c r="A913" t="s">
         <v>109</v>
       </c>
@@ -18177,7 +18177,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="914" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="914" spans="1:7" ns3:dyDescent="0.2">
       <c r="A914" t="s">
         <v>94</v>
       </c>
@@ -18194,7 +18194,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="915" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="915" spans="1:7" ns3:dyDescent="0.2">
       <c r="A915" t="s">
         <v>248</v>
       </c>
@@ -18217,7 +18217,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="916" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="916" spans="1:7" ns3:dyDescent="0.2">
       <c r="A916" t="s">
         <v>250</v>
       </c>
@@ -18234,7 +18234,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="917" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="917" spans="1:7" ns3:dyDescent="0.2">
       <c r="A917" t="s">
         <v>79</v>
       </c>
@@ -18251,7 +18251,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="918" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="918" spans="1:7" ns3:dyDescent="0.2">
       <c r="A918" t="s">
         <v>253</v>
       </c>
@@ -18268,7 +18268,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="919" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="919" spans="1:7" ns3:dyDescent="0.2">
       <c r="A919" t="s">
         <v>255</v>
       </c>
@@ -18285,7 +18285,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="920" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="920" spans="1:7" ns3:dyDescent="0.2">
       <c r="A920" t="s">
         <v>257</v>
       </c>
@@ -18302,7 +18302,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="921" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="921" spans="1:7" ns3:dyDescent="0.2">
       <c r="A921" t="s">
         <v>258</v>
       </c>
@@ -18325,7 +18325,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="922" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="922" spans="1:7" ns3:dyDescent="0.2">
       <c r="A922" t="s">
         <v>260</v>
       </c>
@@ -18348,7 +18348,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="923" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="923" spans="1:7" ns3:dyDescent="0.2">
       <c r="A923" t="s">
         <v>262</v>
       </c>
@@ -18365,7 +18365,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="924" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="924" spans="1:7" ns3:dyDescent="0.2">
       <c r="A924" t="s">
         <v>263</v>
       </c>
@@ -18388,7 +18388,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="925" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="925" spans="1:7" ns3:dyDescent="0.2">
       <c r="A925" t="s">
         <v>100</v>
       </c>
@@ -18405,7 +18405,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="926" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="926" spans="1:7" ns3:dyDescent="0.2">
       <c r="A926" t="s">
         <v>266</v>
       </c>
@@ -18428,7 +18428,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="927" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="927" spans="1:7" ns3:dyDescent="0.2">
       <c r="A927" t="s">
         <v>264</v>
       </c>
@@ -18451,7 +18451,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="929" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="929" spans="1:8" ht="16" ns3:dyDescent="0.2">
       <c r="A929" s="1" t="s">
         <v>0</v>
       </c>
@@ -18459,7 +18459,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="930" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="930" spans="1:8" ns3:dyDescent="0.2">
       <c r="A930" t="s">
         <v>2</v>
       </c>
@@ -18467,7 +18467,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="931" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="931" spans="1:8" ns3:dyDescent="0.2">
       <c r="A931" t="s">
         <v>4</v>
       </c>
@@ -18475,7 +18475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="932" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="932" spans="1:8" ns3:dyDescent="0.2">
       <c r="A932" t="s">
         <v>5</v>
       </c>
@@ -18483,7 +18483,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="933" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="933" spans="1:8" ns3:dyDescent="0.2">
       <c r="A933" t="s">
         <v>7</v>
       </c>
@@ -18491,7 +18491,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="934" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="934" spans="1:8" ns3:dyDescent="0.2">
       <c r="A934" t="s">
         <v>9</v>
       </c>
@@ -18499,7 +18499,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="935" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="935" spans="1:8" ns3:dyDescent="0.2">
       <c r="A935" t="s">
         <v>10</v>
       </c>
@@ -18507,7 +18507,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="936" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="936" spans="1:8" ns3:dyDescent="0.2">
       <c r="A936" t="s">
         <v>12</v>
       </c>
@@ -18515,12 +18515,12 @@
         <v>267</v>
       </c>
     </row>
-    <row r="937" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="937" spans="1:8" ht="16" ns3:dyDescent="0.2">
       <c r="A937" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="938" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="938" spans="1:8" ns3:dyDescent="0.2">
       <c r="A938" s="2" t="s">
         <v>16</v>
       </c>
@@ -18544,7 +18544,7 @@
       </c>
       <c r="H938" s="2"/>
     </row>
-    <row r="939" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="939" spans="1:8" ns3:dyDescent="0.2">
       <c r="A939" t="s">
         <v>238</v>
       </c>
@@ -18567,7 +18567,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="940" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="940" spans="1:8" ns3:dyDescent="0.2">
       <c r="A940" t="s">
         <v>270</v>
       </c>
@@ -18590,7 +18590,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="941" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="941" spans="1:8" ns3:dyDescent="0.2">
       <c r="A941" t="s">
         <v>243</v>
       </c>
@@ -18613,7 +18613,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="942" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="942" spans="1:8" ns3:dyDescent="0.2">
       <c r="A942" t="s">
         <v>260</v>
       </c>
@@ -18636,7 +18636,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="943" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="943" spans="1:8" ns3:dyDescent="0.2">
       <c r="A943" t="s">
         <v>268</v>
       </c>
@@ -18659,8 +18659,526 @@
         <v>268</v>
       </c>
     </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>Fuel tank, compressed hydrogen gas, 700bar, with aluminium liner</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>hydrogen tank</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>Retained legacy truck component; preserves the master-branch dry-mass and electricity correction. Dry-mass correction, 2026-10-10. Evangelisti et al. (2017), doi:10.1016/j.jclepro.2016.11.159, supplementary Hydrogen tank (Scenario S17). Supplement: https://ars.els-cdn.com/content/image/1-s2.0-S0959652616320212-mmc1.docx. SHA256: ca9470c504f61ef58e2e5cc3cad8c06d6cecf17073074ac2ce19dca3678ac49d. Normalize all listed material and processing quantities by 113.169 kg of listed dry materials, not the legacy 93 kg denominator. The main text, scenario labels and supplementary output masses are inconsistent. The difference between nominal output and listed material mass is approximately stored hydrogen, but this interpretation is not explicit in the paper. Dry mass is an explicit modelling boundary, not an assumed missing material. Processing services do not add material mass. Preserve published material ratios and existing supplier proxies, including AlLi for aluminium; these are not validated as current vehicle specifications. Electricity is published in MJ: divide by 3.6 to obtain kWh. Restored in the rail inventory after shared-component consolidation; rail and final-energy kilogram requirements are unchanged. Carbon fibre uses the current canonical regional-truck component supplier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B949">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>700-bar hydrogen tank with aluminium (Type III) liner. Reference output: 1 kg dry tank assembly including tank balance of plant, excluding stored hydrogen. Source listed dry materials total 113.169 kg per assembly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>inventory provenance</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>{"schema version": 1, "role": "retained legacy component", "original workbook": "lci-trucks.xlsx", "original workbook sha256": "0b39c6311dc71dd13254a62901260e23747205cdd4f8871f952c1e77f4128fba", "source database version": "3.9", "model generation version": "not recorded in original workbook", "boundary": "Retained for compatibility on the ecoinvent 3.7 import basis; preserves the 2026-10-10 dry-mass and manufacturing-energy correction. Not regenerated by carculator_truck.", "metadata updated": "2026-10-14", "correction source revision": "ff79a88d0e7fc85f116cbe8387a458ac824e94b6", "corrected source workbook sha256": "e4a4b581c35c08e5a9f18a37cdd7bf6306172fd68234c43390bffc0779a7e3ca", "restored from revision": "83b9c0ae76db37b473233dce090bcbda22b9b67b", "restored in": "lci-rail-freight.xlsx", "restoration reason": "The shared-component consolidation removed this supplier while hydrogen rail and final-energy consumers retained their kilogram inputs. Restore the corrected Type III recipe, preserving consumer quantities."}</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>Evangelisti et al. 2017, doi: 10.1016/j.jclepro.2016.11.159</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E955" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F955" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G955" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H955" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I955" t="inlineStr">
+        <is>
+          <t>uncertainty type</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>market group for electricity, low voltage</t>
+        </is>
+      </c>
+      <c r="B956">
+        <v>0.04030844724851034</v>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>ENTSO-E</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F956" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G956" t="inlineStr">
+        <is>
+          <t>electricity, low voltage</t>
+        </is>
+      </c>
+      <c r="H956" t="inlineStr">
+        <is>
+          <t>16.422 MJ / 3.6 MJ/kWh / 113.169 kg dry assembly = 0.0403084472485 kWh/kg. Evangelisti et al. (2017), supplementary Hydrogen tank (Scenario S17). Preserve existing supplier proxy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>metal working, average for chromium steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="B957">
+        <v>0.0935856992639327</v>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F957" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G957" t="inlineStr">
+        <is>
+          <t>metal working, average for chromium steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="H957" t="inlineStr">
+        <is>
+          <t>(10.591) kg / 113.169 kg dry assembly = 0.0935856992639 kg/kg. Processing service; excluded from material mass balance. Evangelisti et al. (2017), supplementary Hydrogen tank (Scenario S17). Preserve existing supplier proxy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>market for steel, chromium steel 18/8</t>
+        </is>
+      </c>
+      <c r="B958">
+        <v>0.0935856992639327</v>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F958" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G958" t="inlineStr">
+        <is>
+          <t>steel, chromium steel 18/8</t>
+        </is>
+      </c>
+      <c r="H958" t="inlineStr">
+        <is>
+          <t>(10.591) kg / 113.169 kg dry assembly = 0.0935856992639 kg/kg. Material input. Evangelisti et al. (2017), supplementary Hydrogen tank (Scenario S17). Preserve existing supplier proxy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>epoxy resin production, liquid</t>
+        </is>
+      </c>
+      <c r="B959">
+        <v>0.2628811777076762</v>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F959" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G959" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="H959" t="inlineStr">
+        <is>
+          <t>(29.75) kg / 113.169 kg dry assembly = 0.262881177708 kg/kg. Material input. Evangelisti et al. (2017), supplementary Hydrogen tank (Scenario S17). Preserve existing supplier proxy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>carbon fiber production, weaved, at factory, carculator regional truck 2020</t>
+        </is>
+      </c>
+      <c r="B960">
+        <v>0.1756046267087277</v>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F960" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G960" t="inlineStr">
+        <is>
+          <t>carbon fiber, weaved</t>
+        </is>
+      </c>
+      <c r="H960" t="inlineStr">
+        <is>
+          <t>(19.873) kg / 113.169 kg dry assembly = 0.175604626709 kg/kg. Material input. Evangelisti et al. (2017), supplementary Hydrogen tank (Scenario S17). Preserve existing supplier proxy. Linked to the retained canonical regional-truck component supplier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>Fuel tank, compressed hydrogen gas, 700bar, with aluminium liner</t>
+        </is>
+      </c>
+      <c r="B961">
+        <v>1</v>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F961" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G961" t="inlineStr">
+        <is>
+          <t>hydrogen tank</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>market for sheet rolling, aluminium</t>
+        </is>
+      </c>
+      <c r="B962">
+        <v>0.3154574132492114</v>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F962" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G962" t="inlineStr">
+        <is>
+          <t>sheet rolling, aluminium</t>
+        </is>
+      </c>
+      <c r="H962" t="inlineStr">
+        <is>
+          <t>(35.7) kg / 113.169 kg dry assembly = 0.315457413249 kg/kg. Processing service; excluded from material mass balance. Evangelisti et al. (2017), supplementary Hydrogen tank (Scenario S17). Preserve existing supplier proxy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>market for aluminium alloy, AlLi</t>
+        </is>
+      </c>
+      <c r="B963">
+        <v>0.377497371188223</v>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F963" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G963" t="inlineStr">
+        <is>
+          <t>aluminium alloy, AlLi</t>
+        </is>
+      </c>
+      <c r="H963" t="inlineStr">
+        <is>
+          <t>(35.7 + 7.021) kg / 113.169 kg dry assembly = 0.377497371188 kg/kg. Material input. Evangelisti et al. (2017), supplementary Hydrogen tank (Scenario S17). Preserve existing supplier proxy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>market for glass fibre</t>
+        </is>
+      </c>
+      <c r="B964">
+        <v>0.04942166140904311</v>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F964" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G964" t="inlineStr">
+        <is>
+          <t>glass fibre</t>
+        </is>
+      </c>
+      <c r="H964" t="inlineStr">
+        <is>
+          <t>(5.593) kg / 113.169 kg dry assembly = 0.049421661409 kg/kg. Material input. Evangelisti et al. (2017), supplementary Hydrogen tank (Scenario S17). Preserve existing supplier proxy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>market for polyurethane, flexible foam</t>
+        </is>
+      </c>
+      <c r="B965">
+        <v>0.04100946372239748</v>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F965" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G965" t="inlineStr">
+        <is>
+          <t>polyurethane, flexible foam</t>
+        </is>
+      </c>
+      <c r="H965" t="inlineStr">
+        <is>
+          <t>(4.641) kg / 113.169 kg dry assembly = 0.0410094637224 kg/kg. Material input. Evangelisti et al. (2017), supplementary Hydrogen tank (Scenario S17). Preserve existing supplier proxy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="966"/>
   </sheetData>
-  <autoFilter ref="A1:H983" xr:uid="{2A08E695-FC79-4DF0-ACCB-3B3F78317B74}"/>
+  <autoFilter ref="A1:H983" ns2:uid="{2A08E695-FC79-4DF0-ACCB-3B3F78317B74}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>

--- a/premise/data/additional_inventories/lci-rail-freight.xlsx
+++ b/premise/data/additional_inventories/lci-rail-freight.xlsx
@@ -18974,7 +18974,7 @@
     <row r="960">
       <c r="A960" t="inlineStr">
         <is>
-          <t>carbon fiber production, weaved, at factory, carculator regional truck 2020</t>
+          <t xml:space="preserve">carbon fiber production, weaved, at factory</t>
         </is>
       </c>
       <c r="B960">
@@ -18997,12 +18997,13 @@
       </c>
       <c r="G960" t="inlineStr">
         <is>
-          <t>carbon fiber, weaved</t>
+          <t xml:space="preserve">carbon fiber, weaved</t>
         </is>
       </c>
       <c r="H960" t="inlineStr">
         <is>
-          <t>(19.873) kg / 113.169 kg dry assembly = 0.175604626709 kg/kg. Material input. Evangelisti et al. (2017), supplementary Hydrogen tank (Scenario S17). Preserve existing supplier proxy. Linked to the retained canonical regional-truck component supplier.</t>
+          <t xml:space="preserve">(19.873) kg / 113.169 kg dry assembly = 0.175604626709 kg/kg. Material input. Evangelisti et al. (2017), supplementary Hydrogen tank (Scenario S17). Preserve existing supplier proxy. Linked to the retained canonical regional-truck component supplier.
+Shared component reuse (2026-10-16): original model supplier 'carbon fiber production, weaved, at factory, carculator regional truck 2020' uses the existing canonical recipe in lci-carbon-fiber.xlsx; its quantities and uncertainty are retained.</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-rail-freight.xlsx
+++ b/premise/data/additional_inventories/lci-rail-freight.xlsx
@@ -1359,7 +1359,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{2A08E695-FC79-4DF0-ACCB-3B3F78317B74}">
-  <dimension ref="A1:Z966"/>
+  <dimension ref="A1:Z1001"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="61.83203125" customWidth="1"/>
@@ -1554,8 +1554,10 @@
       </c>
     </row>
     <row r="16" spans="1:8" ns3:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>30</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>electric motor, asynchronous traction, engineering reference</t>
+        </is>
       </c>
       <c r="B16">
         <f>24*53</f>
@@ -1570,11 +1572,20 @@
       <c r="F16" t="s">
         <v>20</v>
       </c>
-      <c r="G16" t="s">
-        <v>31</v>
-      </c>
-      <c r="H16" t="s">
-        <v>32</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>electric motor, asynchronous traction, engineering reference</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>APPROVED ASYNCHRONOUS TRACTION ENGINEERING REFERENCE, item19, 2026-10-18. Hsieh etal2026 DOI10.1007/s11367-026-02610-7, SI FigureS7 IM2 and TableS11; ABB2017 Re460 asynchronous traction https://library.e.abb.com/public/bfe91c518ff94330a3c591b4bbeb8b6a/65-69%201m6073_EN_72dpi.pdf. Use the IM2 Cu-stator/Al-rotor induction design: source FigureS7 rounded masspercent Al37.4, electricalsteel46.3, Cu10.0, lowalloysteel3.93, coating/insulation2.42 (sum100.05). Divide these full-composition shares by100.05 to resolve rounding. TableS11 individual masses differ somewhat from the figure (source62.9kg motor); this reference explicitly adopts the complete figure composition, not a claim that both tables close exactly. No permanent magnets or Nd/Dy magnet-processing inputs are included by design; this does not prove zero rare-earth flows in upstream supply. Represent electrical steel as a3.2percentSi engineering alloy, assuming75percentSi ferrosilicon plus low-alloy steel balance, with sheet rolling; source source-specific steel grade, lamination scrap and non-oriented processing remain proxies. Coating uses epoxy resin; source electrical insulation is not fully specified. Generic metal working plus1kWh/kg final assembly electricity are explicit engineering process assumptions (sensitivity.3-3kWh/kg), not measured rail-motor factory data. Retain original rail installed motor masses, service lifetimes and per-MJ allocations; replace only the permanent-magnet passenger-car manufacturing composition. IM2 is a100kW passenger-car study extrapolated perkg to rail, not a rail-rated thermal/mechanical design. Rail nameplate/mass, actual motor efficiency, bearings/rotor fabrication losses, maintenance and EOL coverage remain gaps. No train chassis/track added. Rewire three source locomotive motor inputs and all explicit train/tram final-energy motor inputs; road vehicle motors remain unchanged. Align existing service-to-locomotive input product labels to their actual supplier reference products so the real scoped normalization can resolve the source production links; amounts and lifetime allocation are unchanged.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+ecoinvent inventory for 1 unit (max. power output 100kW, 53kg). The power output at wheel is 4x 600kW, so 2,400kW (Vossloh Rail Vehicles, 2012). This equals 24 ecoinvent equivalents.
+The motors lifetime is assumed to equal the lifetime of the locomotive (40 years). Exact information on motors, including their lifetime is not available as locomotivve motors are produced to fit the vehicle and its power requirement. ABB (2017) mentiones that electric motors were still in good condition at the time of overhaul/maintainance after 20 years and the locomotive was prepared to run another 20 years. Material and energy requirements for maintainace of the motor are not considered.
+ABB (2017). IGBT converters extend life of Re460 locomotives. Retrieved on April, 6, 2024, from: https://library.e.abb.com/public/bfe91c518ff94330a3c591b4bbeb8b6a/65-69%201m6073_EN_72dpi.pdf?x-sign=opZfNERrVHhA5Ti99s4UxUeA3lIqHQkHDxt5CPVCyqbrd2RFMCmG94YZ6PDJII6i
+Vossloh Rail Vehicles (2012). UKlight diesel-electric locomotive. Retrieved from archieved version on April, 8, 2024, from https://web.archive.org/web/20140429192021/http://www.vossloh-innotrans.com/media/downloads/pdfs/vrv/Vossloh_UKLIGHT_us.pdf, orginial version archieved on April, 29, 2014, from https://www.vossloh.com/de/produkte-und-loesungen/innotrans/media/downloads/pdfs/vrv/Vossloh_UKLIGHT_us.pdf</t>
+        </is>
       </c>
     </row>
     <row r="17" spans="1:8" ns3:dyDescent="0.2">
@@ -1755,8 +1766,10 @@
       </c>
     </row>
     <row r="31" spans="1:8" ns3:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>30</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>electric motor, asynchronous traction, engineering reference</t>
+        </is>
       </c>
       <c r="B31">
         <f>70*53</f>
@@ -1771,11 +1784,24 @@
       <c r="F31" t="s">
         <v>20</v>
       </c>
-      <c r="G31" t="s">
-        <v>31</v>
-      </c>
-      <c r="H31" t="s">
-        <v>43</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>electric motor, asynchronous traction, engineering reference</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">APPROVED ASYNCHRONOUS TRACTION ENGINEERING REFERENCE, item19, 2026-10-18. Hsieh etal2026 DOI10.1007/s11367-026-02610-7, SI FigureS7 IM2 and TableS11; ABB2017 Re460 asynchronous traction https://library.e.abb.com/public/bfe91c518ff94330a3c591b4bbeb8b6a/65-69%201m6073_EN_72dpi.pdf. Use the IM2 Cu-stator/Al-rotor induction design: source FigureS7 rounded masspercent Al37.4, electricalsteel46.3, Cu10.0, lowalloysteel3.93, coating/insulation2.42 (sum100.05). Divide these full-composition shares by100.05 to resolve rounding. TableS11 individual masses differ somewhat from the figure (source62.9kg motor); this reference explicitly adopts the complete figure composition, not a claim that both tables close exactly. No permanent magnets or Nd/Dy magnet-processing inputs are included by design; this does not prove zero rare-earth flows in upstream supply. Represent electrical steel as a3.2percentSi engineering alloy, assuming75percentSi ferrosilicon plus low-alloy steel balance, with sheet rolling; source source-specific steel grade, lamination scrap and non-oriented processing remain proxies. Coating uses epoxy resin; source electrical insulation is not fully specified. Generic metal working plus1kWh/kg final assembly electricity are explicit engineering process assumptions (sensitivity.3-3kWh/kg), not measured rail-motor factory data. Retain original rail installed motor masses, service lifetimes and per-MJ allocations; replace only the permanent-magnet passenger-car manufacturing composition. IM2 is a100kW passenger-car study extrapolated perkg to rail, not a rail-rated thermal/mechanical design. Rail nameplate/mass, actual motor efficiency, bearings/rotor fabrication losses, maintenance and EOL coverage remain gaps. No train chassis/track added. Rewire three source locomotive motor inputs and all explicit train/tram final-energy motor inputs; road vehicle motors remain unchanged. Align existing service-to-locomotive input product labels to their actual supplier reference products so the real scoped normalization can resolve the source production links; amounts and lifetime allocation are unchanged.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+ecoinvent inventory for 1 unit (max. power output 100kW, 53kg). The Borderline CC 1500 AC_15kV_M_3500, used in the renovated Re460 lcomotive (ABB, 2018a), has an output at wheel of 3.5 MW. This equals 35 units of electric motors for passenger cars (assuming a similar material composition of the ecoinvent inventory compared to the electric motor used in the locomotive). To generate a total power of max. 6.1 MW, two converters are used as also seen in the videographic sources showing the modernization of the locomotive (ABB Schweiz, 2020). This equals 70 units of ecoinvent inventories (electric motor, for passenger car) necessary to propel the locomotive. This equals a weight of 3,710 kg, which is comparable to the weight/power ratio of other heavy duty electric motors produced by ABB, like the AMXE200L (ABB, 2022). Efficiency of the motors is therefore assumed to be approx. 87% (=6,100/7,000).
+The motors lifetime is assumed to equal the lifetime of the locomotive (40 years). Exact information on motors, including their lifetime is not available as locomotivve motors are produced to fit the vehicle and its power requirement. ABB (2017) mentiones that electric motors were still in good condition at the time of overhaul/maintainance after 20 years and the locomotive was prepared to run another 20 years. Material and energy requirements for maintainace of the motor are not considered.
+ABB (2017). IGBT converters extend life of Re460 locomotives. Retrieved on April, 6, 2024, from: https://library.e.abb.com/public/bfe91c518ff94330a3c591b4bbeb8b6a/65-69%201m6073_EN_72dpi.pdf?x-sign=opZfNERrVHhA5Ti99s4UxUeA3lIqHQkHDxt5CPVCyqbrd2RFMCmG94YZ6PDJII6i
+ABB (2018a) BORDLINE CC1500 AC_15kV- Product information. Retrieved on March, 21, 2024 from https://search.abb.com/library/Download.aspx?DocumentID=3BHS340076%20ZAB%20E04&amp;LanguageCode=en&amp;DocumentPartId=&amp;Action=Launch
+ABB (2022) Motors for heavy electric vehicles (catalog) - AMXE series. retrieved on April, 6, 2024, from https://search.abb.com/library/Download.aspx?DocumentID=9AAU00000000036&amp;LanguageCode=en&amp;DocumentPartId=&amp;Action=Launch
+ABB Schweiz (2020). Class Re 460 modernization program of Swiss Federal Railways SBB. Available at: https://www.youtube.com/watch?v=EqeFXbjETlA
+Hitachi (2022). RESIBLOC® Rail traction transformers. Available at: https://publisher.hitachienergy.com/preview?DocumentID=9AKK107992A2005&amp;LanguageCode=en&amp;DocumentPartId=&amp;Action=launch&amp;DocumentRevisionId=C
+</t>
+        </is>
       </c>
     </row>
     <row r="32" spans="1:8" ns3:dyDescent="0.2">
@@ -1933,8 +1959,10 @@
       </c>
     </row>
     <row r="45" spans="1:8" ns3:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>30</v>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>electric motor, asynchronous traction, engineering reference</t>
+        </is>
       </c>
       <c r="B45">
         <f>25*53</f>
@@ -1949,11 +1977,20 @@
       <c r="F45" t="s">
         <v>20</v>
       </c>
-      <c r="G45" t="s">
-        <v>31</v>
-      </c>
-      <c r="H45" t="s">
-        <v>47</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>electric motor, asynchronous traction, engineering reference</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>APPROVED ASYNCHRONOUS TRACTION ENGINEERING REFERENCE, item19, 2026-10-18. Hsieh etal2026 DOI10.1007/s11367-026-02610-7, SI FigureS7 IM2 and TableS11; ABB2017 Re460 asynchronous traction https://library.e.abb.com/public/bfe91c518ff94330a3c591b4bbeb8b6a/65-69%201m6073_EN_72dpi.pdf. Use the IM2 Cu-stator/Al-rotor induction design: source FigureS7 rounded masspercent Al37.4, electricalsteel46.3, Cu10.0, lowalloysteel3.93, coating/insulation2.42 (sum100.05). Divide these full-composition shares by100.05 to resolve rounding. TableS11 individual masses differ somewhat from the figure (source62.9kg motor); this reference explicitly adopts the complete figure composition, not a claim that both tables close exactly. No permanent magnets or Nd/Dy magnet-processing inputs are included by design; this does not prove zero rare-earth flows in upstream supply. Represent electrical steel as a3.2percentSi engineering alloy, assuming75percentSi ferrosilicon plus low-alloy steel balance, with sheet rolling; source source-specific steel grade, lamination scrap and non-oriented processing remain proxies. Coating uses epoxy resin; source electrical insulation is not fully specified. Generic metal working plus1kWh/kg final assembly electricity are explicit engineering process assumptions (sensitivity.3-3kWh/kg), not measured rail-motor factory data. Retain original rail installed motor masses, service lifetimes and per-MJ allocations; replace only the permanent-magnet passenger-car manufacturing composition. IM2 is a100kW passenger-car study extrapolated perkg to rail, not a rail-rated thermal/mechanical design. Rail nameplate/mass, actual motor efficiency, bearings/rotor fabrication losses, maintenance and EOL coverage remain gaps. No train chassis/track added. Rewire three source locomotive motor inputs and all explicit train/tram final-energy motor inputs; road vehicle motors remain unchanged. Align existing service-to-locomotive input product labels to their actual supplier reference products so the real scoped normalization can resolve the source production links; amounts and lifetime allocation are unchanged.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+ecoinvent inventory for 1 unit (max. power output 100kW, 53kg). The maximum power output the electric motors have to deal with is 2,500kW for the respective sizing of the HFC system, according to Knibbe et al. (2023). This equals 25 ecoinvent inventory equivalents, assuming comparable compositions of the ecoinvent inventory and locomotive traction motors.
+The motors lifetime is assumed to equal the lifetime of the locomotive (40 years). Exact information on motors, including their lifetime is not available as locomotivve motors are produced to fit the vehicle and its power requirement. ABB (2017) mentiones that electric motors were still in good condition at the time of overhaul/maintainance after 20 years and the locomotive was prepared to run another 20 years. Material and energy requirements for maintainace of the motor are not considered.
+ABB (2017). IGBT converters extend life of Re460 locomotives. Retrieved on April, 6, 2024, from: https://library.e.abb.com/public/bfe91c518ff94330a3c591b4bbeb8b6a/65-69%201m6073_EN_72dpi.pdf?x-sign=opZfNERrVHhA5Ti99s4UxUeA3lIqHQkHDxt5CPVCyqbrd2RFMCmG94YZ6PDJII6i
+Knibbe, R., Harding, D., Burton, J., Cooper, E., Amir Zadeh, Z., Sagulenko, M., Meehan, P. A., &amp; Buckley, R. (2023). Optimal battery and hydrogen fuel cell sizing in heavy-haul locomotives. Journal of Energy Storage, 71, 108090. https://doi.org/10.1016/j.est.2023.108090</t>
+        </is>
       </c>
     </row>
     <row r="46" spans="1:8" ns3:dyDescent="0.2">
@@ -2210,11 +2247,17 @@
       <c r="F62" t="s">
         <v>20</v>
       </c>
-      <c r="G62" t="s">
-        <v>65</v>
-      </c>
-      <c r="H62" t="s">
-        <v>66</v>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>locomotive diesel-electric</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Rail source linking consistency, item19: reference product now exactly matches its existing locomotive production supplier; numerical service and lifetime allocation unchanged.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+taken from ecoinvent, "transport, freight train, diesel</t>
+        </is>
       </c>
     </row>
     <row r="63" spans="1:8" ns3:dyDescent="0.2">
@@ -2930,8 +2973,15 @@
       <c r="F102" t="s">
         <v>20</v>
       </c>
-      <c r="G102" t="s">
-        <v>121</v>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>locomotive electric, catenary</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Rail source linking consistency, item19: reference product now exactly matches its existing locomotive production supplier; numerical service and lifetime allocation unchanged.</t>
+        </is>
       </c>
     </row>
     <row r="103" spans="1:8" ns3:dyDescent="0.2">
@@ -3667,8 +3717,15 @@
       <c r="F143" t="s">
         <v>20</v>
       </c>
-      <c r="G143" t="s">
-        <v>126</v>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>locomotive fuel cell, hydrogen</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Rail source linking consistency, item19: reference product now exactly matches its existing locomotive production supplier; numerical service and lifetime allocation unchanged.</t>
+        </is>
       </c>
     </row>
     <row r="144" spans="1:8" ns3:dyDescent="0.2">
@@ -3922,11 +3979,17 @@
       <c r="F160" t="s">
         <v>20</v>
       </c>
-      <c r="G160" t="s">
-        <v>65</v>
-      </c>
-      <c r="H160" t="s">
-        <v>128</v>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>locomotive diesel-electric</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Rail source linking consistency, item19: reference product now exactly matches its existing locomotive production supplier; numerical service and lifetime allocation unchanged.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+taken from ecoinvent "transport, freight train, diesel - IN"</t>
+        </is>
       </c>
     </row>
     <row r="161" spans="1:8" ns3:dyDescent="0.2">
@@ -4665,11 +4728,17 @@
       <c r="F201" t="s">
         <v>20</v>
       </c>
-      <c r="G201" t="s">
-        <v>121</v>
-      </c>
-      <c r="H201" t="s">
-        <v>134</v>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>locomotive electric, catenary</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Rail source linking consistency, item19: reference product now exactly matches its existing locomotive production supplier; numerical service and lifetime allocation unchanged.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+taken from ecoinvent process "transport, freight train, electricity - IN"</t>
+        </is>
       </c>
     </row>
     <row r="202" spans="1:8" ns3:dyDescent="0.2">
@@ -5405,11 +5474,17 @@
       <c r="F242" t="s">
         <v>20</v>
       </c>
-      <c r="G242" t="s">
-        <v>65</v>
-      </c>
-      <c r="H242" t="s">
-        <v>135</v>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>locomotive fuel cell, hydrogen</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>Rail source linking consistency, item19: reference product now exactly matches its existing locomotive production supplier; numerical service and lifetime allocation unchanged.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+taken from ecoinvent "transport, freight train, diesel - IN", as the hydrogen locomotive has similar output power as the diesel-electric train, and it is assumed that diesel trains can used for retrofitting HFC-systems</t>
+        </is>
       </c>
     </row>
     <row r="243" spans="1:8" ns3:dyDescent="0.2">
@@ -6102,11 +6177,17 @@
       <c r="F281" t="s">
         <v>20</v>
       </c>
-      <c r="G281" t="s">
-        <v>65</v>
-      </c>
-      <c r="H281" t="s">
-        <v>137</v>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>locomotive diesel-electric</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>Rail source linking consistency, item19: reference product now exactly matches its existing locomotive production supplier; numerical service and lifetime allocation unchanged.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+taken from ecoinvent inventor "transport, frieght train, diesel - CN"</t>
+        </is>
       </c>
     </row>
     <row r="282" spans="1:8" ns3:dyDescent="0.2">
@@ -6822,11 +6903,17 @@
       <c r="F321" t="s">
         <v>20</v>
       </c>
-      <c r="G321" t="s">
-        <v>65</v>
-      </c>
-      <c r="H321" t="s">
-        <v>138</v>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>locomotive electric, catenary</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>Rail source linking consistency, item19: reference product now exactly matches its existing locomotive production supplier; numerical service and lifetime allocation unchanged.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+taken from ecoinvent inventor "transport, frieght train, electricity - CN"</t>
+        </is>
       </c>
     </row>
     <row r="322" spans="1:8" ns3:dyDescent="0.2">
@@ -7562,11 +7649,17 @@
       <c r="F362" t="s">
         <v>20</v>
       </c>
-      <c r="G362" t="s">
-        <v>65</v>
-      </c>
-      <c r="H362" t="s">
-        <v>139</v>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>locomotive fuel cell, hydrogen</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>Rail source linking consistency, item19: reference product now exactly matches its existing locomotive production supplier; numerical service and lifetime allocation unchanged.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+taken from ecoinvent inventor "transport, frieght train, diesel - CN", as the hydrogen locomotive has similar output power as the diesel-electric train, and it is assumed that diesel trains can used for retrofitting HFC-systems</t>
+        </is>
       </c>
     </row>
     <row r="363" spans="1:8" ns3:dyDescent="0.2">
@@ -8259,11 +8352,17 @@
       <c r="F401" t="s">
         <v>20</v>
       </c>
-      <c r="G401" t="s">
-        <v>65</v>
-      </c>
-      <c r="H401" t="s">
-        <v>141</v>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>locomotive diesel-electric</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>Rail source linking consistency, item19: reference product now exactly matches its existing locomotive production supplier; numerical service and lifetime allocation unchanged.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+taken from ecoinvent inventory "transport, freight train, diesel - ZA"</t>
+        </is>
       </c>
     </row>
     <row r="402" spans="1:8" ns3:dyDescent="0.2">
@@ -9002,11 +9101,17 @@
       <c r="F442" t="s">
         <v>20</v>
       </c>
-      <c r="G442" t="s">
-        <v>65</v>
-      </c>
-      <c r="H442" t="s">
-        <v>144</v>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>locomotive electric, catenary</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>Rail source linking consistency, item19: reference product now exactly matches its existing locomotive production supplier; numerical service and lifetime allocation unchanged.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+taken from ecoinvent inventory "transport, freight train, electricity - ZA"</t>
+        </is>
       </c>
     </row>
     <row r="443" spans="1:8" ns3:dyDescent="0.2">
@@ -9742,11 +9847,17 @@
       <c r="F483" t="s">
         <v>20</v>
       </c>
-      <c r="G483" t="s">
-        <v>65</v>
-      </c>
-      <c r="H483" t="s">
-        <v>145</v>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>locomotive fuel cell, hydrogen</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>Rail source linking consistency, item19: reference product now exactly matches its existing locomotive production supplier; numerical service and lifetime allocation unchanged.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+taken from ecoinvent inventory "transport, freight train, diesel - ZA", as the hydrogen locomotive has similar output power as the diesel-electric train, and it is assumed that diesel trains can used for retrofitting HFC-systems</t>
+        </is>
       </c>
     </row>
     <row r="484" spans="1:8" ns3:dyDescent="0.2">
@@ -10439,11 +10550,17 @@
       <c r="F522" t="s">
         <v>20</v>
       </c>
-      <c r="G522" t="s">
-        <v>65</v>
-      </c>
-      <c r="H522" t="s">
-        <v>149</v>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>locomotive diesel-electric</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>Rail source linking consistency, item19: reference product now exactly matches its existing locomotive production supplier; numerical service and lifetime allocation unchanged.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+taken from ecoinvent inventory "transport, freight train, diesel - US"</t>
+        </is>
       </c>
     </row>
     <row r="523" spans="1:8" ns3:dyDescent="0.2">
@@ -11182,11 +11299,17 @@
       <c r="F563" t="s">
         <v>20</v>
       </c>
-      <c r="G563" t="s">
-        <v>65</v>
-      </c>
-      <c r="H563" t="s">
-        <v>149</v>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>locomotive electric, catenary</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>Rail source linking consistency, item19: reference product now exactly matches its existing locomotive production supplier; numerical service and lifetime allocation unchanged.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+taken from ecoinvent inventory "transport, freight train, diesel - US"</t>
+        </is>
       </c>
     </row>
     <row r="564" spans="1:8" ns3:dyDescent="0.2">
@@ -11922,11 +12045,17 @@
       <c r="F604" t="s">
         <v>20</v>
       </c>
-      <c r="G604" t="s">
-        <v>65</v>
-      </c>
-      <c r="H604" t="s">
-        <v>152</v>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>locomotive fuel cell, hydrogen</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>Rail source linking consistency, item19: reference product now exactly matches its existing locomotive production supplier; numerical service and lifetime allocation unchanged.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+taken from ecoinvent inventory "transport, freight train, diesel - US" as the hydrogen locomotive has similar output power as the diesel-electric train, and it is assumed that diesel trains can used for retrofitting HFC-systems</t>
+        </is>
       </c>
     </row>
     <row r="605" spans="1:8" ns3:dyDescent="0.2">
@@ -12619,11 +12748,17 @@
       <c r="F643" t="s">
         <v>20</v>
       </c>
-      <c r="G643" t="s">
-        <v>65</v>
-      </c>
-      <c r="H643" t="s">
-        <v>153</v>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>locomotive diesel-electric</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>Rail source linking consistency, item19: reference product now exactly matches its existing locomotive production supplier; numerical service and lifetime allocation unchanged.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+taken from ecoinvent inventory "transport, freight train, diesel - RoW"</t>
+        </is>
       </c>
     </row>
     <row r="644" spans="1:8" ns3:dyDescent="0.2">
@@ -16582,11 +16717,17 @@
       <c r="F824" t="s">
         <v>20</v>
       </c>
-      <c r="G824" t="s">
-        <v>65</v>
-      </c>
-      <c r="H824" t="s">
-        <v>226</v>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>locomotive electric, catenary</t>
+        </is>
+      </c>
+      <c r="H824" t="inlineStr">
+        <is>
+          <t>Rail source linking consistency, item19: reference product now exactly matches its existing locomotive production supplier; numerical service and lifetime allocation unchanged.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+taken from ecoinvent inventory "transport, freight train, electricity - RoW"</t>
+        </is>
       </c>
     </row>
     <row r="825" spans="1:8" ns3:dyDescent="0.2">
@@ -17322,11 +17463,17 @@
       <c r="F865" t="s">
         <v>20</v>
       </c>
-      <c r="G865" t="s">
-        <v>65</v>
-      </c>
-      <c r="H865" t="s">
-        <v>227</v>
+      <c r="G865" t="inlineStr">
+        <is>
+          <t>locomotive fuel cell, hydrogen</t>
+        </is>
+      </c>
+      <c r="H865" t="inlineStr">
+        <is>
+          <t>Rail source linking consistency, item19: reference product now exactly matches its existing locomotive production supplier; numerical service and lifetime allocation unchanged.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+taken from ecoinvent inventory "transport, freight train, diesel - RoW" as the hydrogen locomotive has similar output power as the diesel-electric train, and it is assumed that diesel trains can used for retrofitting HFC-systems</t>
+        </is>
       </c>
     </row>
     <row r="866" spans="1:8" ns3:dyDescent="0.2">
@@ -19178,6 +19325,688 @@
       </c>
     </row>
     <row r="966"/>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>non-oriented electrical steel, engineering alloy reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B970">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>non-oriented electrical steel, engineering alloy reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>Hsieh etal2026 DOI10.1007/s11367-026-02610-7, SI FigureS7 IM2 and TableS11; ABB2017 Re460 asynchronous traction https://library.e.abb.com/public/bfe91c518ff94330a3c591b4bbeb8b6a/65-69%201m6073_EN_72dpi.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>APPROVED ASYNCHRONOUS TRACTION ENGINEERING REFERENCE, item19, 2026-10-18. Hsieh etal2026 DOI10.1007/s11367-026-02610-7, SI FigureS7 IM2 and TableS11; ABB2017 Re460 asynchronous traction https://library.e.abb.com/public/bfe91c518ff94330a3c591b4bbeb8b6a/65-69%201m6073_EN_72dpi.pdf. Use the IM2 Cu-stator/Al-rotor induction design: source FigureS7 rounded masspercent Al37.4, electricalsteel46.3, Cu10.0, lowalloysteel3.93, coating/insulation2.42 (sum100.05). Divide these full-composition shares by100.05 to resolve rounding. TableS11 individual masses differ somewhat from the figure (source62.9kg motor); this reference explicitly adopts the complete figure composition, not a claim that both tables close exactly. No permanent magnets or Nd/Dy magnet-processing inputs are included by design; this does not prove zero rare-earth flows in upstream supply. Represent electrical steel as a3.2percentSi engineering alloy, assuming75percentSi ferrosilicon plus low-alloy steel balance, with sheet rolling; source source-specific steel grade, lamination scrap and non-oriented processing remain proxies. Coating uses epoxy resin; source electrical insulation is not fully specified. Generic metal working plus1kWh/kg final assembly electricity are explicit engineering process assumptions (sensitivity.3-3kWh/kg), not measured rail-motor factory data. Retain original rail installed motor masses, service lifetimes and per-MJ allocations; replace only the permanent-magnet passenger-car manufacturing composition. IM2 is a100kW passenger-car study extrapolated perkg to rail, not a rail-rated thermal/mechanical design. Rail nameplate/mass, actual motor efficiency, bearings/rotor fabrication losses, maintenance and EOL coverage remain gaps. No train chassis/track added. Rewire three source locomotive motor inputs and all explicit train/tram final-energy motor inputs; road vehicle motors remain unchanged. Align existing service-to-locomotive input product labels to their actual supplier reference products so the real scoped normalization can resolve the source production links; amounts and lifetime allocation are unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E976" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F976" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G976" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H976" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>non-oriented electrical steel, engineering alloy reference</t>
+        </is>
+      </c>
+      <c r="B977">
+        <v>1</v>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F977" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G977" t="inlineStr">
+        <is>
+          <t>non-oriented electrical steel, engineering alloy reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B978">
+        <v>0.9573333333333334</v>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F978" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G978" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>market for ferrosilicon</t>
+        </is>
+      </c>
+      <c r="B979">
+        <v>0.042666666666666665</v>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F979" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G979" t="inlineStr">
+        <is>
+          <t>ferrosilicon</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>sheet rolling, steel</t>
+        </is>
+      </c>
+      <c r="B980">
+        <v>1</v>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F980" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G980" t="inlineStr">
+        <is>
+          <t>sheet rolling, steel</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>electric motor, asynchronous traction, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B985">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>electric motor, asynchronous traction, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>Hsieh etal2026 DOI10.1007/s11367-026-02610-7, SI FigureS7 IM2 and TableS11; ABB2017 Re460 asynchronous traction https://library.e.abb.com/public/bfe91c518ff94330a3c591b4bbeb8b6a/65-69%201m6073_EN_72dpi.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>APPROVED ASYNCHRONOUS TRACTION ENGINEERING REFERENCE, item19, 2026-10-18. Hsieh etal2026 DOI10.1007/s11367-026-02610-7, SI FigureS7 IM2 and TableS11; ABB2017 Re460 asynchronous traction https://library.e.abb.com/public/bfe91c518ff94330a3c591b4bbeb8b6a/65-69%201m6073_EN_72dpi.pdf. Use the IM2 Cu-stator/Al-rotor induction design: source FigureS7 rounded masspercent Al37.4, electricalsteel46.3, Cu10.0, lowalloysteel3.93, coating/insulation2.42 (sum100.05). Divide these full-composition shares by100.05 to resolve rounding. TableS11 individual masses differ somewhat from the figure (source62.9kg motor); this reference explicitly adopts the complete figure composition, not a claim that both tables close exactly. No permanent magnets or Nd/Dy magnet-processing inputs are included by design; this does not prove zero rare-earth flows in upstream supply. Represent electrical steel as a3.2percentSi engineering alloy, assuming75percentSi ferrosilicon plus low-alloy steel balance, with sheet rolling; source source-specific steel grade, lamination scrap and non-oriented processing remain proxies. Coating uses epoxy resin; source electrical insulation is not fully specified. Generic metal working plus1kWh/kg final assembly electricity are explicit engineering process assumptions (sensitivity.3-3kWh/kg), not measured rail-motor factory data. Retain original rail installed motor masses, service lifetimes and per-MJ allocations; replace only the permanent-magnet passenger-car manufacturing composition. IM2 is a100kW passenger-car study extrapolated perkg to rail, not a rail-rated thermal/mechanical design. Rail nameplate/mass, actual motor efficiency, bearings/rotor fabrication losses, maintenance and EOL coverage remain gaps. No train chassis/track added. Rewire three source locomotive motor inputs and all explicit train/tram final-energy motor inputs; road vehicle motors remain unchanged. Align existing service-to-locomotive input product labels to their actual supplier reference products so the real scoped normalization can resolve the source production links; amounts and lifetime allocation are unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E991" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F991" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G991" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H991" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>electric motor, asynchronous traction, engineering reference</t>
+        </is>
+      </c>
+      <c r="B992">
+        <v>1</v>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F992" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G992" t="inlineStr">
+        <is>
+          <t>electric motor, asynchronous traction, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B993">
+        <v>0.37381309345327335</v>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F993" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G993" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>non-oriented electrical steel, engineering alloy reference</t>
+        </is>
+      </c>
+      <c r="B994">
+        <v>0.4627686156921539</v>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F994" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G994" t="inlineStr">
+        <is>
+          <t>non-oriented electrical steel, engineering alloy reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B995">
+        <v>0.09995002498750626</v>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F995" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G995" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B996">
+        <v>0.039280359820089955</v>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F996" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G996" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>market for epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="B997">
+        <v>0.02418790604697651</v>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F997" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G997" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="B998">
+        <v>0.37381309345327335</v>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F998" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G998" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="B999">
+        <v>0.09995002498750626</v>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F999" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G999" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="B1000">
+        <v>0.5020489755122438</v>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1000" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1000" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1001">
+        <v>1</v>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>Europe without Switzerland</t>
+        </is>
+      </c>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1001" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1001" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H983" ns2:uid="{2A08E695-FC79-4DF0-ACCB-3B3F78317B74}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/premise/data/additional_inventories/lci-rail-freight.xlsx
+++ b/premise/data/additional_inventories/lci-rail-freight.xlsx
@@ -1359,7 +1359,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{2A08E695-FC79-4DF0-ACCB-3B3F78317B74}">
-  <dimension ref="A1:Z1001"/>
+  <dimension ref="A1:Z1045"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="61.83203125" customWidth="1"/>
@@ -1426,8 +1426,19 @@
       <c r="A9" t="s">
         <v>10</v>
       </c>
-      <c r="B9" t="s">
-        <v>11</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">APPROVED RAIL CONVERTER ENGINEERING REFERENCE, item25, 2026-10-18. ABB2024 ACS6080 PEP ABBG-00712-V01.01-EN, marked Draft/Public, page7, https://library.e.abb.com/public/f0dd73990f0242ab9a0e88dbf6090edd/PEP_EPD_ACS6080_33AXD10002395301_RevA_EN_05122024.pdf; ABB BORDLINE masses/power retained from existing rail sources. Infineon FZ1500R33HE3 datasheet construction reference https://www.infineon.com/assets/row/public/documents/60/49/infineon-fz1500r33he3-datasheet-en.pdf. Replace the mass-scaled4.5kg car battery-voltage converter with an explicit medium-voltage AC-drive-based reference, not a measured BORDLINE BOM. ABB2024 draft PEP gives14583kg including packaging:steel43.4%,Cu20.4%,Al2.25%,GFRP1.7%,otherplastics0.4%,electroniccomponents12.9%,wood13.7%,other5.25%. Percentages sum100. Treat wood as packaging and exclude it from installed reference mass:hardware fraction0.863. Perkg installed converter divide other category fractions by0.863; purchase packaging wood0.137/0.863kg additionally. Source is an18MW industrial AC drive, not a rail-qualified product: composition transfer to BORDLINE is an explicit engineering analogue, with source installed masses and power/lifetime counts unchanged. Assume electronic component mass70%film capacitors,25%power semiconductor modules,5%populated control boards. These fractions are design assumptions; sensitivity capacitor50-80%, module10-40%, board2-10%, constrained to100%. Generic Pb-free through-hole board retains upstream precious metals; no zero-gold assumption. Illustrative power module retained recipe:Cu50%,Al10%,alumina20%,PPS10%,silicone8%,silicon die2%. Represent die fabrication by existing fabricated-IC-wafer service using300um silicon thickness and2330kg/m3 density:0.02/(2330*0.0003)m2/kgmodule. This wafer and power-module composition are engineering proxies, not Infineon material declarations or verified rail die technology. Module assembly1kWh/kg assumed. Film capacitor proxy includes its own constituent materials once. Other5.25%/0.863=6.08343% installed hardware mass remains compositionally UNRESOLVED and is not silently converted into zero metal or an arbitrary PCB. Known retained material coverage93.91657%; trace-metal completeness is not claimed.100%retention reference plus generic metal-working/1kWh final assembly perkg; yields, cooling coolant, additional cabling, end-of-life and rail qualification remain gaps. Do not infer corrected system gold totals before rebuilding and sensitivity analysis. No passenger/freight service denominator change in this commit.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+market for locomotive (ecoinvent) is based on Frischknecht et al. (1996). This study only consideres materials of the catenary electric locomotive RE 460 (~84t, years of construction 1991-1996), operated by the SBB in CH. Electrical components are not considered. This equals a electric locomotives base components without the electrical equipment (= power tracktion). Therfore additional components are added to the inventory to represent a diesel locomotive (ICE, generator, fuel tank, transformer, inverter, electric motors). As a reference diesel-electric locomotive the UKlight (Vossloh Rail Vehicles, 2012), as it is supplied by ABB (also supllying the Re460) and is similar in size (85t) to the Re460 (84t). The UKlight from Vossloh Rail Vehicles operates on 2,800 kW max. power with a starting tractive effort of 317 kN and a max speed of 160 km/h. This makes it comparable to the electric alternative Re460 with a tractive effort of 300 kN, although having a higher max. power of 6,100 kW and higher max. speed of 230 km/h. The two vehicles are still assumed to be comparable alternatives as freight rail transport does not operate on high velocities. 
+Electrical components taken from ABB (2018b).
+Average lifetime is assumed to be similar to the electric counterpart, namly 40 years with 9.6 million km Frischknecht et al. (1996). Assuming an average speed of 40 kmh (approx. 25 mph, based on Statista (2024)) equals a drivingtime of 240,000 h over the lifetime of the locomotive.
+ABB (2018b). Bordline CC1500 DE - Product information. Retrieved March 23, 2024, from  https://search.abb.com/library/Download.aspx?DocumentID=3BHS340077%20ZAB%20E01&amp;LanguageCode=en&amp;DocumentPartId=&amp;Action=Launch
+Frischknecht R., Bollens U., Bosshart S., Ciot M., Ciseri L., Doka G., Dones R., Gantner U. and Hischier R. (1996) Ökoinventare von Energiesystemen: Grundlagen für den ökologischen Vergleich von Energiesystemen und den Einbezug von Energiesystemen in Ökobilanzen für die Schweiz
+Statista  (n.d.).Union Pacific: Average train speed 2022. Retrieved April 3, 2024, from https://www.statista.com/statistics/547745/average-train-speed-union-pacific-railroad/
+Vossloh Rail Vehicles (2012). UKlight diesel-electric locomotive. Retrieved from archieved version on April, 8, 2024, from https://web.archive.org/web/20140429192021/http://www.vossloh-innotrans.com/media/downloads/pdfs/vrv/Vossloh_UKLIGHT_us.pdf, orginial version archieved on April, 29, 2014, from https://www.vossloh.com/de/produkte-und-loesungen/innotrans/media/downloads/pdfs/vrv/Vossloh_UKLIGHT_us.pdf
+</t>
+        </is>
       </c>
     </row>
     <row r="10" spans="1:8" ns3:dyDescent="0.2">
@@ -1589,8 +1600,10 @@
       </c>
     </row>
     <row r="17" spans="1:8" ns3:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>33</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>traction converter, medium-voltage rail engineering reference</t>
+        </is>
       </c>
       <c r="B17">
         <f>1013.33333333333*4.5</f>
@@ -1605,8 +1618,10 @@
       <c r="F17" t="s">
         <v>20</v>
       </c>
-      <c r="G17" t="s">
-        <v>34</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>traction converter, medium-voltage rail engineering reference</t>
+        </is>
       </c>
       <c r="H17" t="s">
         <v>35</v>
@@ -1684,8 +1699,17 @@
       <c r="A26" t="s">
         <v>10</v>
       </c>
-      <c r="B26" t="s">
-        <v>39</v>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">APPROVED RAIL CONVERTER ENGINEERING REFERENCE, item25, 2026-10-18. ABB2024 ACS6080 PEP ABBG-00712-V01.01-EN, marked Draft/Public, page7, https://library.e.abb.com/public/f0dd73990f0242ab9a0e88dbf6090edd/PEP_EPD_ACS6080_33AXD10002395301_RevA_EN_05122024.pdf; ABB BORDLINE masses/power retained from existing rail sources. Infineon FZ1500R33HE3 datasheet construction reference https://www.infineon.com/assets/row/public/documents/60/49/infineon-fz1500r33he3-datasheet-en.pdf. Replace the mass-scaled4.5kg car battery-voltage converter with an explicit medium-voltage AC-drive-based reference, not a measured BORDLINE BOM. ABB2024 draft PEP gives14583kg including packaging:steel43.4%,Cu20.4%,Al2.25%,GFRP1.7%,otherplastics0.4%,electroniccomponents12.9%,wood13.7%,other5.25%. Percentages sum100. Treat wood as packaging and exclude it from installed reference mass:hardware fraction0.863. Perkg installed converter divide other category fractions by0.863; purchase packaging wood0.137/0.863kg additionally. Source is an18MW industrial AC drive, not a rail-qualified product: composition transfer to BORDLINE is an explicit engineering analogue, with source installed masses and power/lifetime counts unchanged. Assume electronic component mass70%film capacitors,25%power semiconductor modules,5%populated control boards. These fractions are design assumptions; sensitivity capacitor50-80%, module10-40%, board2-10%, constrained to100%. Generic Pb-free through-hole board retains upstream precious metals; no zero-gold assumption. Illustrative power module retained recipe:Cu50%,Al10%,alumina20%,PPS10%,silicone8%,silicon die2%. Represent die fabrication by existing fabricated-IC-wafer service using300um silicon thickness and2330kg/m3 density:0.02/(2330*0.0003)m2/kgmodule. This wafer and power-module composition are engineering proxies, not Infineon material declarations or verified rail die technology. Module assembly1kWh/kg assumed. Film capacitor proxy includes its own constituent materials once. Other5.25%/0.863=6.08343% installed hardware mass remains compositionally UNRESOLVED and is not silently converted into zero metal or an arbitrary PCB. Known retained material coverage93.91657%; trace-metal completeness is not claimed.100%retention reference plus generic metal-working/1kWh final assembly perkg; yields, cooling coolant, additional cabling, end-of-life and rail qualification remain gaps. Do not infer corrected system gold totals before rebuilding and sensitivity analysis. No passenger/freight service denominator change in this commit.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+market for locomotive (ecoinvent) is based on Frischknecht et al. (1996). This study only consideres materials of the catenary electric locomotive RE 460 (~84t, years of construction 1991-1996, 6,100 kW max. power, 300 kN max. tractive effort), operated by the SBB in CH. Electrical components are not considered. This equals a electric locomotives base components without the electrical equipment (= power tracktion). Therfore additional components are added to the inventory to represent a electric locomotive (transformer, electric motor, converter). Electrical components taken from ABB (2018a).
+Average Lifetime is 40 years with 9.6 million km. Assuming an average speed of 40 kmh (approx. 25 mph, based on Statista (2024)) equals a drivingtime of 240,000 h over the lifetime of the locomotive.
+ABB (2018a). Bordline CC1500 AC_15kV - Product information. Retrieved March 23, 2024, from  https://search.abb.com/library/Download.aspx?DocumentID=3BHS340076%20ZAB%20E04&amp;LanguageCode=en&amp;DocumentPartId=&amp;Action=Launch
+Frischknecht R., Bollens U., Bosshart S., Ciot M., Ciseri L., Doka G., Dones R., Gantner U. and Hischier R. (1996) Ökoinventare von Energiesystemen: Grundlagen für den ökologischen Vergleich von Energiesystemen und den Einbezug von Energiesystemen in Ökobilanzen für die Schweiz
+Statista  (n.d.).Union Pacific: Average train speed 2022. Retrieved April 3, 2024, from https://www.statista.com/statistics/547745/average-train-speed-union-pacific-railroad/
+</t>
+        </is>
       </c>
     </row>
     <row r="27" spans="1:8" ns3:dyDescent="0.2">
@@ -1805,8 +1829,10 @@
       </c>
     </row>
     <row r="32" spans="1:8" ns3:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>33</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>traction converter, medium-voltage rail engineering reference</t>
+        </is>
       </c>
       <c r="B32">
         <f>2302.22222222222*4.5</f>
@@ -1821,8 +1847,10 @@
       <c r="F32" t="s">
         <v>20</v>
       </c>
-      <c r="G32" t="s">
-        <v>34</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>traction converter, medium-voltage rail engineering reference</t>
+        </is>
       </c>
       <c r="H32" t="s">
         <v>44</v>
@@ -1900,8 +1928,20 @@
       <c r="A41" t="s">
         <v>12</v>
       </c>
-      <c r="B41" t="s">
-        <v>276</v>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">APPROVED RAIL CONVERTER ENGINEERING REFERENCE, item25, 2026-10-18. ABB2024 ACS6080 PEP ABBG-00712-V01.01-EN, marked Draft/Public, page7, https://library.e.abb.com/public/f0dd73990f0242ab9a0e88dbf6090edd/PEP_EPD_ACS6080_33AXD10002395301_RevA_EN_05122024.pdf; ABB BORDLINE masses/power retained from existing rail sources. Infineon FZ1500R33HE3 datasheet construction reference https://www.infineon.com/assets/row/public/documents/60/49/infineon-fz1500r33he3-datasheet-en.pdf. Replace the mass-scaled4.5kg car battery-voltage converter with an explicit medium-voltage AC-drive-based reference, not a measured BORDLINE BOM. ABB2024 draft PEP gives14583kg including packaging:steel43.4%,Cu20.4%,Al2.25%,GFRP1.7%,otherplastics0.4%,electroniccomponents12.9%,wood13.7%,other5.25%. Percentages sum100. Treat wood as packaging and exclude it from installed reference mass:hardware fraction0.863. Perkg installed converter divide other category fractions by0.863; purchase packaging wood0.137/0.863kg additionally. Source is an18MW industrial AC drive, not a rail-qualified product: composition transfer to BORDLINE is an explicit engineering analogue, with source installed masses and power/lifetime counts unchanged. Assume electronic component mass70%film capacitors,25%power semiconductor modules,5%populated control boards. These fractions are design assumptions; sensitivity capacitor50-80%, module10-40%, board2-10%, constrained to100%. Generic Pb-free through-hole board retains upstream precious metals; no zero-gold assumption. Illustrative power module retained recipe:Cu50%,Al10%,alumina20%,PPS10%,silicone8%,silicon die2%. Represent die fabrication by existing fabricated-IC-wafer service using300um silicon thickness and2330kg/m3 density:0.02/(2330*0.0003)m2/kgmodule. This wafer and power-module composition are engineering proxies, not Infineon material declarations or verified rail die technology. Module assembly1kWh/kg assumed. Film capacitor proxy includes its own constituent materials once. Other5.25%/0.863=6.08343% installed hardware mass remains compositionally UNRESOLVED and is not silently converted into zero metal or an arbitrary PCB. Known retained material coverage93.91657%; trace-metal completeness is not claimed.100%retention reference plus generic metal-working/1kWh final assembly perkg; yields, cooling coolant, additional cabling, end-of-life and rail qualification remain gaps. Do not infer corrected system gold totals before rebuilding and sensitivity analysis. No passenger/freight service denominator change in this commit.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+market for locomotive (ecoinvent) is based on Frischknecht et al. (1996). This study only consideres materials of the catenary electric locomotive RE 460, operated by the SBB in CH. Electrical components are not considered. This equals a electric locomotives base components without the electrical equipment (= power traction). Therefore additional components are added to the inventory to represent a fuel cell, hydrogen locomotive (electric motor, converter, fuel cell, fuel tank, battery cell). It is assumed that diesel-electric locomotives will be retrofitted with fuel cell system or that hydrogen driven locomotives operate similarly to diesel locomotives. Electrical components taken from ABB (2018b).
+The HFC-battery system is sized to be able to produce a max. power output of 2,500 kW (Knibbe et al., 2023). As this power output is similar to the diesel-electric locomotive UKlight (Vossloh Rail Vehicles, 2012) of 2,800 kW it is assumed that the HFC-locomotive will have a comparable tractive effort of below 300 kN. This makes it a viable alternative to the electric, catenary or diesel-electric counter part.
+Average Lifetime is 40 years with 9.6 million km. Assuming an average speed of 40 kmh (approx. 25 mph, based on Statista (2024)) equals a drivingtime of 240,000 h over the lifetime of the locomotive.
+ABB (2018b). Bordline CC1500 DE - Product information. Retrieved March 23, 2024, from  https://search.abb.com/library/Download.aspx?DocumentID=3BHS340077%20ZAB%20E01&amp;LanguageCode=en&amp;DocumentPartId=&amp;Action=Launch
+Frischknecht R., Bollens U., Bosshart S., Ciot M., Ciseri L., Doka G., Dones R., Gantner U. and Hischier R. (1996) Ökoinventare von Energiesystemen: Grundlagen für den ökologischen Vergleich von Energiesystemen und den Einbezug von Energiesystemen in Ökobilanzen für die Schweiz
+Knibbe, R., Harding, D., Burton, J., Cooper, E., Amir Zadeh, Z., Sagulenko, M., Meehan, P. A., &amp; Buckley, R. (2023). Optimal battery and hydrogen fuel cell sizing in heavy-haul locomotives. Journal of Energy Storage, 71, 108090. https://doi.org/10.1016/j.est.2023.108090
+Statista  (n.d.).Union Pacific: Average train speed 2022. Retrieved April 3, 2024, from https://www.statista.com/statistics/547745/average-train-speed-union-pacific-railroad/
+Vossloh Rail Vehicles (2012). UKlight diesel-electric locomotive. Retrieved from archieved version on April, 8, 2024, from https://web.archive.org/web/20140429192021/http://www.vossloh-innotrans.com/media/downloads/pdfs/vrv/Vossloh_UKLIGHT_us.pdf, orginial version archieved on April, 29, 2014, from https://www.vossloh.com/de/produkte-und-loesungen/innotrans/media/downloads/pdfs/vrv/Vossloh_UKLIGHT_us.pdf
+</t>
+        </is>
       </c>
     </row>
     <row r="42" spans="1:8" ns3:dyDescent="0.2">
@@ -1994,8 +2034,10 @@
       </c>
     </row>
     <row r="46" spans="1:8" ns3:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>33</v>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>traction converter, medium-voltage rail engineering reference</t>
+        </is>
       </c>
       <c r="B46">
         <f>506.666666666667*4.5</f>
@@ -2010,8 +2052,10 @@
       <c r="F46" t="s">
         <v>20</v>
       </c>
-      <c r="G46" t="s">
-        <v>34</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>traction converter, medium-voltage rail engineering reference</t>
+        </is>
       </c>
       <c r="H46" t="s">
         <v>48</v>
@@ -20004,6 +20048,928 @@
       <c r="G1001" t="inlineStr">
         <is>
           <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>power semiconductor module, rail converter engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1006">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>power semiconductor module, rail converter engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>ABB2024 ACS6080 PEP ABBG-00712-V01.01-EN, marked Draft/Public, page7, https://library.e.abb.com/public/f0dd73990f0242ab9a0e88dbf6090edd/PEP_EPD_ACS6080_33AXD10002395301_RevA_EN_05122024.pdf; ABB BORDLINE masses/power retained from existing rail sources. Infineon FZ1500R33HE3 datasheet construction reference https://www.infineon.com/assets/row/public/documents/60/49/infineon-fz1500r33he3-datasheet-en.pdf.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>APPROVED RAIL CONVERTER ENGINEERING REFERENCE, item25, 2026-10-18. ABB2024 ACS6080 PEP ABBG-00712-V01.01-EN, marked Draft/Public, page7, https://library.e.abb.com/public/f0dd73990f0242ab9a0e88dbf6090edd/PEP_EPD_ACS6080_33AXD10002395301_RevA_EN_05122024.pdf; ABB BORDLINE masses/power retained from existing rail sources. Infineon FZ1500R33HE3 datasheet construction reference https://www.infineon.com/assets/row/public/documents/60/49/infineon-fz1500r33he3-datasheet-en.pdf. Replace the mass-scaled4.5kg car battery-voltage converter with an explicit medium-voltage AC-drive-based reference, not a measured BORDLINE BOM. ABB2024 draft PEP gives14583kg including packaging:steel43.4%,Cu20.4%,Al2.25%,GFRP1.7%,otherplastics0.4%,electroniccomponents12.9%,wood13.7%,other5.25%. Percentages sum100. Treat wood as packaging and exclude it from installed reference mass:hardware fraction0.863. Perkg installed converter divide other category fractions by0.863; purchase packaging wood0.137/0.863kg additionally. Source is an18MW industrial AC drive, not a rail-qualified product: composition transfer to BORDLINE is an explicit engineering analogue, with source installed masses and power/lifetime counts unchanged. Assume electronic component mass70%film capacitors,25%power semiconductor modules,5%populated control boards. These fractions are design assumptions; sensitivity capacitor50-80%, module10-40%, board2-10%, constrained to100%. Generic Pb-free through-hole board retains upstream precious metals; no zero-gold assumption. Illustrative power module retained recipe:Cu50%,Al10%,alumina20%,PPS10%,silicone8%,silicon die2%. Represent die fabrication by existing fabricated-IC-wafer service using300um silicon thickness and2330kg/m3 density:0.02/(2330*0.0003)m2/kgmodule. This wafer and power-module composition are engineering proxies, not Infineon material declarations or verified rail die technology. Module assembly1kWh/kg assumed. Film capacitor proxy includes its own constituent materials once. Other5.25%/0.863=6.08343% installed hardware mass remains compositionally UNRESOLVED and is not silently converted into zero metal or an arbitrary PCB. Known retained material coverage93.91657%; trace-metal completeness is not claimed.100%retention reference plus generic metal-working/1kWh final assembly perkg; yields, cooling coolant, additional cabling, end-of-life and rail qualification remain gaps. Do not infer corrected system gold totals before rebuilding and sensitivity analysis. No passenger/freight service denominator change in this commit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1012" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1012" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1012" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1012" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1012" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>power semiconductor module, rail converter engineering reference</t>
+        </is>
+      </c>
+      <c r="B1013">
+        <v>1</v>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1013" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1013" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1013" t="inlineStr">
+        <is>
+          <t>power semiconductor module, rail converter engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B1014">
+        <v>0.5</v>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1014" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1014" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1014" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B1015">
+        <v>0.1</v>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1015" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1015" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>market for aluminium oxide, non-metallurgical</t>
+        </is>
+      </c>
+      <c r="B1016">
+        <v>0.2</v>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1016" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1016" t="inlineStr">
+        <is>
+          <t>aluminium oxide, non-metallurgical</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>market for polyphenylene sulfide</t>
+        </is>
+      </c>
+      <c r="B1017">
+        <v>0.1</v>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1017" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1017" t="inlineStr">
+        <is>
+          <t>polyphenylene sulfide</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>market for silicone product</t>
+        </is>
+      </c>
+      <c r="B1018">
+        <v>0.08</v>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1018" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1018" t="inlineStr">
+        <is>
+          <t>silicone product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>market for wafer, fabricated, for integrated circuit</t>
+        </is>
+      </c>
+      <c r="B1019">
+        <v>0.028612303290414882</v>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>square meter</t>
+        </is>
+      </c>
+      <c r="F1019" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1019" t="inlineStr">
+        <is>
+          <t>wafer, fabricated, for integrated circuit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1020">
+        <v>1</v>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1020" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1020" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>traction converter, medium-voltage rail engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1025">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>traction converter, medium-voltage rail engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>ABB2024 ACS6080 PEP ABBG-00712-V01.01-EN, marked Draft/Public, page7, https://library.e.abb.com/public/f0dd73990f0242ab9a0e88dbf6090edd/PEP_EPD_ACS6080_33AXD10002395301_RevA_EN_05122024.pdf; ABB BORDLINE masses/power retained from existing rail sources. Infineon FZ1500R33HE3 datasheet construction reference https://www.infineon.com/assets/row/public/documents/60/49/infineon-fz1500r33he3-datasheet-en.pdf.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>APPROVED RAIL CONVERTER ENGINEERING REFERENCE, item25, 2026-10-18. ABB2024 ACS6080 PEP ABBG-00712-V01.01-EN, marked Draft/Public, page7, https://library.e.abb.com/public/f0dd73990f0242ab9a0e88dbf6090edd/PEP_EPD_ACS6080_33AXD10002395301_RevA_EN_05122024.pdf; ABB BORDLINE masses/power retained from existing rail sources. Infineon FZ1500R33HE3 datasheet construction reference https://www.infineon.com/assets/row/public/documents/60/49/infineon-fz1500r33he3-datasheet-en.pdf. Replace the mass-scaled4.5kg car battery-voltage converter with an explicit medium-voltage AC-drive-based reference, not a measured BORDLINE BOM. ABB2024 draft PEP gives14583kg including packaging:steel43.4%,Cu20.4%,Al2.25%,GFRP1.7%,otherplastics0.4%,electroniccomponents12.9%,wood13.7%,other5.25%. Percentages sum100. Treat wood as packaging and exclude it from installed reference mass:hardware fraction0.863. Perkg installed converter divide other category fractions by0.863; purchase packaging wood0.137/0.863kg additionally. Source is an18MW industrial AC drive, not a rail-qualified product: composition transfer to BORDLINE is an explicit engineering analogue, with source installed masses and power/lifetime counts unchanged. Assume electronic component mass70%film capacitors,25%power semiconductor modules,5%populated control boards. These fractions are design assumptions; sensitivity capacitor50-80%, module10-40%, board2-10%, constrained to100%. Generic Pb-free through-hole board retains upstream precious metals; no zero-gold assumption. Illustrative power module retained recipe:Cu50%,Al10%,alumina20%,PPS10%,silicone8%,silicon die2%. Represent die fabrication by existing fabricated-IC-wafer service using300um silicon thickness and2330kg/m3 density:0.02/(2330*0.0003)m2/kgmodule. This wafer and power-module composition are engineering proxies, not Infineon material declarations or verified rail die technology. Module assembly1kWh/kg assumed. Film capacitor proxy includes its own constituent materials once. Other5.25%/0.863=6.08343% installed hardware mass remains compositionally UNRESOLVED and is not silently converted into zero metal or an arbitrary PCB. Known retained material coverage93.91657%; trace-metal completeness is not claimed.100%retention reference plus generic metal-working/1kWh final assembly perkg; yields, cooling coolant, additional cabling, end-of-life and rail qualification remain gaps. Do not infer corrected system gold totals before rebuilding and sensitivity analysis. No passenger/freight service denominator change in this commit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1031" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1031" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1031" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1031" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>traction converter, medium-voltage rail engineering reference</t>
+        </is>
+      </c>
+      <c r="B1032">
+        <v>1</v>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1032" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1032" t="inlineStr">
+        <is>
+          <t>traction converter, medium-voltage rail engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B1033">
+        <v>0.5028968713789108</v>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1033" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1033" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B1034">
+        <v>0.23638470451911933</v>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1034" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1034" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B1035">
+        <v>0.026071842410196985</v>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1035" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1035" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>market for glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+      <c r="B1036">
+        <v>0.01969872537659328</v>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1036" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1036" t="inlineStr">
+        <is>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>market for polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="B1037">
+        <v>0.004634994206257242</v>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1037" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1037" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>market for capacitor, film type, for through-hole mounting</t>
+        </is>
+      </c>
+      <c r="B1038">
+        <v>0.10463499420625723</v>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1038" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1038" t="inlineStr">
+        <is>
+          <t>capacitor, film type, for through-hole mounting</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>power semiconductor module, rail converter engineering reference</t>
+        </is>
+      </c>
+      <c r="B1039">
+        <v>0.037369640787949014</v>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1039" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1039" t="inlineStr">
+        <is>
+          <t>power semiconductor module, rail converter engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>market for printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+      <c r="B1040">
+        <v>0.0074739281575898035</v>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1040" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1040" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1040" t="inlineStr">
+        <is>
+          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>market for sawnwood, board, softwood, raw, dried (u=10%)</t>
+        </is>
+      </c>
+      <c r="B1041">
+        <v>0.0003174971031286211</v>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>Europe without Switzerland</t>
+        </is>
+      </c>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>cubic meter</t>
+        </is>
+      </c>
+      <c r="F1041" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1041" t="inlineStr">
+        <is>
+          <t>sawnwood, board, softwood, raw, dried (u=10%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1042">
+        <v>1</v>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1042" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1042" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="B1043">
+        <v>0.5028968713789108</v>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1043" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1043" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="B1044">
+        <v>0.23638470451911933</v>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1044" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1044" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1044" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="B1045">
+        <v>0.026071842410196985</v>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1045" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1045" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1045" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-rail-freight.xlsx
+++ b/premise/data/additional_inventories/lci-rail-freight.xlsx
@@ -1930,7 +1930,9 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">APPROVED RAIL CONVERTER ENGINEERING REFERENCE, item25, 2026-10-18. ABB2024 ACS6080 PEP ABBG-00712-V01.01-EN, marked Draft/Public, page7, https://library.e.abb.com/public/f0dd73990f0242ab9a0e88dbf6090edd/PEP_EPD_ACS6080_33AXD10002395301_RevA_EN_05122024.pdf; ABB BORDLINE masses/power retained from existing rail sources. Infineon FZ1500R33HE3 datasheet construction reference https://www.infineon.com/assets/row/public/documents/60/49/infineon-fz1500r33he3-datasheet-en.pdf. Replace the mass-scaled4.5kg car battery-voltage converter with an explicit medium-voltage AC-drive-based reference, not a measured BORDLINE BOM. ABB2024 draft PEP gives14583kg including packaging:steel43.4%,Cu20.4%,Al2.25%,GFRP1.7%,otherplastics0.4%,electroniccomponents12.9%,wood13.7%,other5.25%. Percentages sum100. Treat wood as packaging and exclude it from installed reference mass:hardware fraction0.863. Perkg installed converter divide other category fractions by0.863; purchase packaging wood0.137/0.863kg additionally. Source is an18MW industrial AC drive, not a rail-qualified product: composition transfer to BORDLINE is an explicit engineering analogue, with source installed masses and power/lifetime counts unchanged. Assume electronic component mass70%film capacitors,25%power semiconductor modules,5%populated control boards. These fractions are design assumptions; sensitivity capacitor50-80%, module10-40%, board2-10%, constrained to100%. Generic Pb-free through-hole board retains upstream precious metals; no zero-gold assumption. Illustrative power module retained recipe:Cu50%,Al10%,alumina20%,PPS10%,silicone8%,silicon die2%. Represent die fabrication by existing fabricated-IC-wafer service using300um silicon thickness and2330kg/m3 density:0.02/(2330*0.0003)m2/kgmodule. This wafer and power-module composition are engineering proxies, not Infineon material declarations or verified rail die technology. Module assembly1kWh/kg assumed. Film capacitor proxy includes its own constituent materials once. Other5.25%/0.863=6.08343% installed hardware mass remains compositionally UNRESOLVED and is not silently converted into zero metal or an arbitrary PCB. Known retained material coverage93.91657%; trace-metal completeness is not claimed.100%retention reference plus generic metal-working/1kWh final assembly perkg; yields, cooling coolant, additional cabling, end-of-life and rail qualification remain gaps. Do not infer corrected system gold totals before rebuilding and sensitivity analysis. No passenger/freight service denominator change in this commit.
+          <t xml:space="preserve">APPROVED SINGLE RAIL FUEL-CELL REPLACEMENT BUDGET, item29, 2026-10-18. Knibbe2023 DOI10.1016/j.est.2023.108090, owner rail reference860kW/30000hstack and240000hoperation; Stropnik2022 DOI10.1016/j.ijhydene.2022.04.011 BoP20000h. Existing owner buys860kW*240000/30000=6880kW-equivalent system sets. Generic assembly additionally buys20000/3800=5.2631579stacks, yielding42.105stack sets over owner life. Introduce rail-specific assembly per1kWe owner set:one existing generic manufactured stack (not generic lifetime assembly) and30000/20000=1.5genericBoP units. Therefore owner lifetime has8stacksets and12BoPsets, each budget applied once.30000h railstack life is the existing heavy-haul engineering assumption, not a demonstrated lightvehicle stack endurance; retain it explicitly rather than silently importing3800h. BoP20000h is a source-based engineering durability proxy; fractional1.5 is expected lifetime attribution, not an instantaneous1.5BoP installation. Stack and BoP manufacture/source grades/size proxies remain unchanged; generic stack remains eligible for existing future catalyst updates. No new platinum loading or primary/secondary curve. Heavy-haul power/duty/passenger representativeness, storage and battery design remain separate gaps. Existing860kW and6880owner quantity retained; the explicit final-energy hydrogen passenger-rail purchase relinked; other rail service inherits its locomotive supplier so old cached assembly identity cannot persist.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED RAIL CONVERTER ENGINEERING REFERENCE, item25, 2026-10-18. ABB2024 ACS6080 PEP ABBG-00712-V01.01-EN, marked Draft/Public, page7, https://library.e.abb.com/public/f0dd73990f0242ab9a0e88dbf6090edd/PEP_EPD_ACS6080_33AXD10002395301_RevA_EN_05122024.pdf; ABB BORDLINE masses/power retained from existing rail sources. Infineon FZ1500R33HE3 datasheet construction reference https://www.infineon.com/assets/row/public/documents/60/49/infineon-fz1500r33he3-datasheet-en.pdf. Replace the mass-scaled4.5kg car battery-voltage converter with an explicit medium-voltage AC-drive-based reference, not a measured BORDLINE BOM. ABB2024 draft PEP gives14583kg including packaging:steel43.4%,Cu20.4%,Al2.25%,GFRP1.7%,otherplastics0.4%,electroniccomponents12.9%,wood13.7%,other5.25%. Percentages sum100. Treat wood as packaging and exclude it from installed reference mass:hardware fraction0.863. Perkg installed converter divide other category fractions by0.863; purchase packaging wood0.137/0.863kg additionally. Source is an18MW industrial AC drive, not a rail-qualified product: composition transfer to BORDLINE is an explicit engineering analogue, with source installed masses and power/lifetime counts unchanged. Assume electronic component mass70%film capacitors,25%power semiconductor modules,5%populated control boards. These fractions are design assumptions; sensitivity capacitor50-80%, module10-40%, board2-10%, constrained to100%. Generic Pb-free through-hole board retains upstream precious metals; no zero-gold assumption. Illustrative power module retained recipe:Cu50%,Al10%,alumina20%,PPS10%,silicone8%,silicon die2%. Represent die fabrication by existing fabricated-IC-wafer service using300um silicon thickness and2330kg/m3 density:0.02/(2330*0.0003)m2/kgmodule. This wafer and power-module composition are engineering proxies, not Infineon material declarations or verified rail die technology. Module assembly1kWh/kg assumed. Film capacitor proxy includes its own constituent materials once. Other5.25%/0.863=6.08343% installed hardware mass remains compositionally UNRESOLVED and is not silently converted into zero metal or an arbitrary PCB. Known retained material coverage93.91657%; trace-metal completeness is not claimed.100%retention reference plus generic metal-working/1kWh final assembly perkg; yields, cooling coolant, additional cabling, end-of-life and rail qualification remain gaps. Do not infer corrected system gold totals before rebuilding and sensitivity analysis. No passenger/freight service denominator change in this commit.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 market for locomotive (ecoinvent) is based on Frischknecht et al. (1996). This study only consideres materials of the catenary electric locomotive RE 460, operated by the SBB in CH. Electrical components are not considered. This equals a electric locomotives base components without the electrical equipment (= power traction). Therefore additional components are added to the inventory to represent a fuel cell, hydrogen locomotive (electric motor, converter, fuel cell, fuel tank, battery cell). It is assumed that diesel-electric locomotives will be retrofitted with fuel cell system or that hydrogen driven locomotives operate similarly to diesel locomotives. Electrical components taken from ABB (2018b).
 The HFC-battery system is sized to be able to produce a max. power output of 2,500 kW (Knibbe et al., 2023). As this power output is similar to the diesel-electric locomotive UKlight (Vossloh Rail Vehicles, 2012) of 2,800 kW it is assumed that the HFC-locomotive will have a comparable tractive effort of below 300 kN. This makes it a viable alternative to the electric, catenary or diesel-electric counter part.
@@ -2062,8 +2064,10 @@
       </c>
     </row>
     <row r="47" spans="1:8" ns3:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>49</v>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>fuel cell system assembly, rail30kh stack engineering reference</t>
+        </is>
       </c>
       <c r="B47">
         <v>6880</v>
@@ -2077,11 +2081,15 @@
       <c r="F47" t="s">
         <v>20</v>
       </c>
-      <c r="G47" t="s">
-        <v>50</v>
-      </c>
-      <c r="H47" t="s">
-        <v>51</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>fuel cell system assembly, rail30kh stack engineering reference</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>APPROVED SINGLE RAIL FUEL-CELL REPLACEMENT BUDGET, item29, 2026-10-18. Knibbe2023 DOI10.1016/j.est.2023.108090, owner rail reference860kW/30000hstack and240000hoperation; Stropnik2022 DOI10.1016/j.ijhydene.2022.04.011 BoP20000h. Existing owner buys860kW*240000/30000=6880kW-equivalent system sets. Generic assembly additionally buys20000/3800=5.2631579stacks, yielding42.105stack sets over owner life. Introduce rail-specific assembly per1kWe owner set:one existing generic manufactured stack (not generic lifetime assembly) and30000/20000=1.5genericBoP units. Therefore owner lifetime has8stacksets and12BoPsets, each budget applied once.30000h railstack life is the existing heavy-haul engineering assumption, not a demonstrated lightvehicle stack endurance; retain it explicitly rather than silently importing3800h. BoP20000h is a source-based engineering durability proxy; fractional1.5 is expected lifetime attribution, not an instantaneous1.5BoP installation. Stack and BoP manufacture/source grades/size proxies remain unchanged; generic stack remains eligible for existing future catalyst updates. No new platinum loading or primary/secondary curve. Heavy-haul power/duty/passenger representativeness, storage and battery design remain separate gaps. Existing860kW and6880owner quantity retained; the explicit final-energy hydrogen passenger-rail purchase relinked; other rail service inherits its locomotive supplier so old cached assembly identity cannot persist.</t>
+        </is>
       </c>
     </row>
     <row r="48" spans="1:8" ns3:dyDescent="0.2">

--- a/premise/data/additional_inventories/lci-rail-freight.xlsx
+++ b/premise/data/additional_inventories/lci-rail-freight.xlsx
@@ -1930,7 +1930,9 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">APPROVED SINGLE RAIL FUEL-CELL REPLACEMENT BUDGET, item29, 2026-10-18. Knibbe2023 DOI10.1016/j.est.2023.108090, owner rail reference860kW/30000hstack and240000hoperation; Stropnik2022 DOI10.1016/j.ijhydene.2022.04.011 BoP20000h. Existing owner buys860kW*240000/30000=6880kW-equivalent system sets. Generic assembly additionally buys20000/3800=5.2631579stacks, yielding42.105stack sets over owner life. Introduce rail-specific assembly per1kWe owner set:one existing generic manufactured stack (not generic lifetime assembly) and30000/20000=1.5genericBoP units. Therefore owner lifetime has8stacksets and12BoPsets, each budget applied once.30000h railstack life is the existing heavy-haul engineering assumption, not a demonstrated lightvehicle stack endurance; retain it explicitly rather than silently importing3800h. BoP20000h is a source-based engineering durability proxy; fractional1.5 is expected lifetime attribution, not an instantaneous1.5BoP installation. Stack and BoP manufacture/source grades/size proxies remain unchanged; generic stack remains eligible for existing future catalyst updates. No new platinum loading or primary/secondary curve. Heavy-haul power/duty/passenger representativeness, storage and battery design remain separate gaps. Existing860kW and6880owner quantity retained; the explicit final-energy hydrogen passenger-rail purchase relinked; other rail service inherits its locomotive supplier so old cached assembly identity cannot persist.
+          <t xml:space="preserve">APPROVED HYDROGEN-RAIL COMPLETE LFP CAPACITY REFERENCE, issue33, 2026-10-18. Knibbe2023 DOI10.1016/j.est.2023.108090,3.6MWhLFP/860kWreference and133Wh/kgpack; Dai2018 public LFP non-cell material proportions https://publications.anl.gov/anlpubs/2018/10/146906.pdf Table8. Replace old whole-pack23.5kWh/165kg conversion purchased as bareNMC622cells with a complete3.6MWhLFP reference. Referencepack133Wh/kg =&gt;27067.66917293233kg installed; existing40year/15year lifetime convention gives9600kWh manufactured and treated, not annual procurement.15years remains an engineering calendar assumption, not demonstrated rail LFP cycle life; sensitivity10-20years and source-specific duty/aging remains required. At860kW total stored energy/power=4.186h; battery peakpower and simultaneous fuel-cell duty are not proven by this ratio. Per1kWh:6.25kg cells at existing160Wh/kgcell reference. Assume modular100kWh subsystems, each112series-equivalent3.2V LFPcells at279.017857Ah; series/parallel arrangement and thermal ratings are a design reference, not measured locomotive architecture. One existing6.668kg LFP monitoring/central-controls package per100kWh; other retained mass uses Dai non-electronic module/pack material proportions including50/50glycol/water. This hardware geometry/control allocation is an explicit engineering transfer. Complete pack mass/cellcapacity/control+waste close together. Controls package already treats its6.668kg, so local battery waste excludes that mass; no duplicate EOL. Source cell manufacturing chemistry, electronics-specific materials and thermal duty remain proxies; source133Wh/kg is not certification of this constructed BOM. Existing rail inventory had fixed barecell mass over time; this dedicated fixed-reference provider retains that temporal boundary and is outside generic road density-learning markets. No future LFP electrode evolution is claimed. No locomotive body, tender or track added. Rail source and explicit passenger-energy link are both changed.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED SINGLE RAIL FUEL-CELL REPLACEMENT BUDGET, item29, 2026-10-18. Knibbe2023 DOI10.1016/j.est.2023.108090, owner rail reference860kW/30000hstack and240000hoperation; Stropnik2022 DOI10.1016/j.ijhydene.2022.04.011 BoP20000h. Existing owner buys860kW*240000/30000=6880kW-equivalent system sets. Generic assembly additionally buys20000/3800=5.2631579stacks, yielding42.105stack sets over owner life. Introduce rail-specific assembly per1kWe owner set:one existing generic manufactured stack (not generic lifetime assembly) and30000/20000=1.5genericBoP units. Therefore owner lifetime has8stacksets and12BoPsets, each budget applied once.30000h railstack life is the existing heavy-haul engineering assumption, not a demonstrated lightvehicle stack endurance; retain it explicitly rather than silently importing3800h. BoP20000h is a source-based engineering durability proxy; fractional1.5 is expected lifetime attribution, not an instantaneous1.5BoP installation. Stack and BoP manufacture/source grades/size proxies remain unchanged; generic stack remains eligible for existing future catalyst updates. No new platinum loading or primary/secondary curve. Heavy-haul power/duty/passenger representativeness, storage and battery design remain separate gaps. Existing860kW and6880owner quantity retained; the explicit final-energy hydrogen passenger-rail purchase relinked; other rail service inherits its locomotive supplier so old cached assembly identity cannot persist.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED RAIL CONVERTER ENGINEERING REFERENCE, item25, 2026-10-18. ABB2024 ACS6080 PEP ABBG-00712-V01.01-EN, marked Draft/Public, page7, https://library.e.abb.com/public/f0dd73990f0242ab9a0e88dbf6090edd/PEP_EPD_ACS6080_33AXD10002395301_RevA_EN_05122024.pdf; ABB BORDLINE masses/power retained from existing rail sources. Infineon FZ1500R33HE3 datasheet construction reference https://www.infineon.com/assets/row/public/documents/60/49/infineon-fz1500r33he3-datasheet-en.pdf. Replace the mass-scaled4.5kg car battery-voltage converter with an explicit medium-voltage AC-drive-based reference, not a measured BORDLINE BOM. ABB2024 draft PEP gives14583kg including packaging:steel43.4%,Cu20.4%,Al2.25%,GFRP1.7%,otherplastics0.4%,electroniccomponents12.9%,wood13.7%,other5.25%. Percentages sum100. Treat wood as packaging and exclude it from installed reference mass:hardware fraction0.863. Perkg installed converter divide other category fractions by0.863; purchase packaging wood0.137/0.863kg additionally. Source is an18MW industrial AC drive, not a rail-qualified product: composition transfer to BORDLINE is an explicit engineering analogue, with source installed masses and power/lifetime counts unchanged. Assume electronic component mass70%film capacitors,25%power semiconductor modules,5%populated control boards. These fractions are design assumptions; sensitivity capacitor50-80%, module10-40%, board2-10%, constrained to100%. Generic Pb-free through-hole board retains upstream precious metals; no zero-gold assumption. Illustrative power module retained recipe:Cu50%,Al10%,alumina20%,PPS10%,silicone8%,silicon die2%. Represent die fabrication by existing fabricated-IC-wafer service using300um silicon thickness and2330kg/m3 density:0.02/(2330*0.0003)m2/kgmodule. This wafer and power-module composition are engineering proxies, not Infineon material declarations or verified rail die technology. Module assembly1kWh/kg assumed. Film capacitor proxy includes its own constituent materials once. Other5.25%/0.863=6.08343% installed hardware mass remains compositionally UNRESOLVED and is not silently converted into zero metal or an arbitrary PCB. Known retained material coverage93.91657%; trace-metal completeness is not claimed.100%retention reference plus generic metal-working/1kWh final assembly perkg; yields, cooling coolant, additional cabling, end-of-life and rail qualification remain gaps. Do not infer corrected system gold totals before rebuilding and sensitivity analysis. No passenger/freight service denominator change in this commit.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -2116,26 +2118,34 @@
       </c>
     </row>
     <row r="49" spans="1:8" ns3:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>273</v>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>battery capacity, hydrogen rail, LFP engineering reference</t>
+        </is>
       </c>
       <c r="B49">
-        <v>67404.255319148942</v>
+        <v>9600.0</v>
       </c>
       <c r="C49" t="s">
         <v>3</v>
       </c>
-      <c r="D49" t="s">
-        <v>24</v>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
       </c>
       <c r="F49" t="s">
         <v>20</v>
       </c>
-      <c r="G49" t="s">
-        <v>274</v>
-      </c>
-      <c r="H49" t="s">
-        <v>55</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>battery capacity, hydrogen rail, LFP engineering reference</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>APPROVED HYDROGEN-RAIL COMPLETE LFP CAPACITY REFERENCE, issue33, 2026-10-18. Knibbe2023 DOI10.1016/j.est.2023.108090,3.6MWhLFP/860kWreference and133Wh/kgpack; Dai2018 public LFP non-cell material proportions https://publications.anl.gov/anlpubs/2018/10/146906.pdf Table8. Replace old whole-pack23.5kWh/165kg conversion purchased as bareNMC622cells with a complete3.6MWhLFP reference. Referencepack133Wh/kg =&gt;27067.66917293233kg installed; existing40year/15year lifetime convention gives9600kWh manufactured and treated, not annual procurement.15years remains an engineering calendar assumption, not demonstrated rail LFP cycle life; sensitivity10-20years and source-specific duty/aging remains required. At860kW total stored energy/power=4.186h; battery peakpower and simultaneous fuel-cell duty are not proven by this ratio. Per1kWh:6.25kg cells at existing160Wh/kgcell reference. Assume modular100kWh subsystems, each112series-equivalent3.2V LFPcells at279.017857Ah; series/parallel arrangement and thermal ratings are a design reference, not measured locomotive architecture. One existing6.668kg LFP monitoring/central-controls package per100kWh; other retained mass uses Dai non-electronic module/pack material proportions including50/50glycol/water. This hardware geometry/control allocation is an explicit engineering transfer. Complete pack mass/cellcapacity/control+waste close together. Controls package already treats its6.668kg, so local battery waste excludes that mass; no duplicate EOL. Source cell manufacturing chemistry, electronics-specific materials and thermal duty remain proxies; source133Wh/kg is not certification of this constructed BOM. Existing rail inventory had fixed barecell mass over time; this dedicated fixed-reference provider retains that temporal boundary and is outside generic road density-learning markets. No future LFP electrode evolution is claimed. No locomotive body, tender or track added. Rail source and explicit passenger-energy link are both changed.</t>
+        </is>
       </c>
     </row>
     <row r="50" spans="1:8" ns3:dyDescent="0.2">

--- a/premise/data/additional_inventories/lci-rail-freight.xlsx
+++ b/premise/data/additional_inventories/lci-rail-freight.xlsx
@@ -1359,7 +1359,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{2A08E695-FC79-4DF0-ACCB-3B3F78317B74}">
-  <dimension ref="A1:Z1045"/>
+  <dimension ref="A1:Z1111"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="61.83203125" customWidth="1"/>
@@ -1930,7 +1930,9 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">APPROVED HYDROGEN-RAIL COMPLETE LFP CAPACITY REFERENCE, issue33, 2026-10-18. Knibbe2023 DOI10.1016/j.est.2023.108090,3.6MWhLFP/860kWreference and133Wh/kgpack; Dai2018 public LFP non-cell material proportions https://publications.anl.gov/anlpubs/2018/10/146906.pdf Table8. Replace old whole-pack23.5kWh/165kg conversion purchased as bareNMC622cells with a complete3.6MWhLFP reference. Referencepack133Wh/kg =&gt;27067.66917293233kg installed; existing40year/15year lifetime convention gives9600kWh manufactured and treated, not annual procurement.15years remains an engineering calendar assumption, not demonstrated rail LFP cycle life; sensitivity10-20years and source-specific duty/aging remains required. At860kW total stored energy/power=4.186h; battery peakpower and simultaneous fuel-cell duty are not proven by this ratio. Per1kWh:6.25kg cells at existing160Wh/kgcell reference. Assume modular100kWh subsystems, each112series-equivalent3.2V LFPcells at279.017857Ah; series/parallel arrangement and thermal ratings are a design reference, not measured locomotive architecture. One existing6.668kg LFP monitoring/central-controls package per100kWh; other retained mass uses Dai non-electronic module/pack material proportions including50/50glycol/water. This hardware geometry/control allocation is an explicit engineering transfer. Complete pack mass/cellcapacity/control+waste close together. Controls package already treats its6.668kg, so local battery waste excludes that mass; no duplicate EOL. Source cell manufacturing chemistry, electronics-specific materials and thermal duty remain proxies; source133Wh/kg is not certification of this constructed BOM. Existing rail inventory had fixed barecell mass over time; this dedicated fixed-reference provider retains that temporal boundary and is outside generic road density-learning markets. No future LFP electrode evolution is claimed. No locomotive body, tender or track added. Rail source and explicit passenger-energy link are both changed.
+          <t xml:space="preserve">APPROVED RAIL-SPECIFIC700BAR STORAGE/LIFE REFERENCE, issue69,2026-10-18. FCH2RAIL D1.5 railstorage investigation,DLR2021,AnnexBTable20, https://elib.dlr.de/145010/1/FCH2RAIL_D1.5.pdf :TypeIII70MPaTPED surveyreference8.3kgH2,2048x455mm,333Loutervolume,179kgINCLUDINGgas =&gt;170.7kgdry. Supplier surveyreference is not a certifiedcompleteheavyhaullocomotive design. Preserve current700barworkingpressure and40yearrailmanufacturinghorizon; do not forcepassenger350barorroadbus/truckvessels intoheavyhaul. Existing30323.845714kg cumulativecar-TypeIIIproxy was4sets over40years,with93kgdry/5.6kgH2. Its impliedinstalledgas=oldmass/4*5.6/93=456.488kg. Retain thisimpliedenergy budget as explicitengineeringreference because no route-specificrefuellingrange is documented; not infergasinventory fromlifetimefuelthroughput. Select55surveycylinders*8.3=456.5kgH2capacity,roundingup only0.012kg. Sourcepreserved860kW/.06185kgH2perkWhe implies8.582hfullpower before reserve; actualroute/peakduty,reserveandrefilling range remainunvalidated. Keep10yearvessellife/foursets as existing conservativeassumption,NOT manufacturerlifecertificate;test10-20years ratherthan invent a lifetime saving. Cylinder dry170.7 excludes8.3kgfuel. MaterialBOMunpublished:6mmAl linerat2700kg/m3 overcapsulearea2*pi*outerradius*length,2kgstainlessbosses,2kgPAprotection,remainingCF/epoxy at60/40vol%(1800/1200kg/m3),69.2308wt%fiber. Outerdiametergeometry,linerthickness,actualalloy/fiber andpressurequalification areengineeringassumptions,not a certifiedpressurevessel design.95%materialretention withmatchingprocesswaste and1kWh/kgforming/curing reference; wovenfiber is filamentwindingmanufacturingproxy. Installedvesseldrymass9388.5kg. Dedicatedsharedrack500kg(one40yearset,80%ordinary steel/20%Al) and100kgvalve/manifold/controls(two20yearsets:50stainless,5Cu,5brass,10PA,29.5Al,0.5auxinterfaceboard) are explicitmountingassumptions; no wholelocomotive,tenderchassis ortrack added. Lifetimevesselmanufacture220units,one rack,twoBoPsets are inside oneunit oflifetimeenergy-equipmentreference. Qtyone atlocomotiveproduction,not count220again in perMJadapter. Nominalinstalledstorageenvelope55*.333=18.315m3beforemounting; availablelocomotive/tenderpackaging is unresolved and not asserted tofit. Preserveexistingroad/railoperatingfuel andcompression path;700barpressureunchanged,no unsubstantiatedcompressionenergy saving. Originalrangeandbodyenergy notresimulated. EOL remainswholevehicleboundary,pressurespecificcylinderrecovery gap,no credits. Refreshstoredhydrogenpassengerrailcoefficients andindependentlynormalizefreightrailservices.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED HYDROGEN-RAIL COMPLETE LFP CAPACITY REFERENCE, issue33, 2026-10-18. Knibbe2023 DOI10.1016/j.est.2023.108090,3.6MWhLFP/860kWreference and133Wh/kgpack; Dai2018 public LFP non-cell material proportions https://publications.anl.gov/anlpubs/2018/10/146906.pdf Table8. Replace old whole-pack23.5kWh/165kg conversion purchased as bareNMC622cells with a complete3.6MWhLFP reference. Referencepack133Wh/kg =&gt;27067.66917293233kg installed; existing40year/15year lifetime convention gives9600kWh manufactured and treated, not annual procurement.15years remains an engineering calendar assumption, not demonstrated rail LFP cycle life; sensitivity10-20years and source-specific duty/aging remains required. At860kW total stored energy/power=4.186h; battery peakpower and simultaneous fuel-cell duty are not proven by this ratio. Per1kWh:6.25kg cells at existing160Wh/kgcell reference. Assume modular100kWh subsystems, each112series-equivalent3.2V LFPcells at279.017857Ah; series/parallel arrangement and thermal ratings are a design reference, not measured locomotive architecture. One existing6.668kg LFP monitoring/central-controls package per100kWh; other retained mass uses Dai non-electronic module/pack material proportions including50/50glycol/water. This hardware geometry/control allocation is an explicit engineering transfer. Complete pack mass/cellcapacity/control+waste close together. Controls package already treats its6.668kg, so local battery waste excludes that mass; no duplicate EOL. Source cell manufacturing chemistry, electronics-specific materials and thermal duty remain proxies; source133Wh/kg is not certification of this constructed BOM. Existing rail inventory had fixed barecell mass over time; this dedicated fixed-reference provider retains that temporal boundary and is outside generic road density-learning markets. No future LFP electrode evolution is claimed. No locomotive body, tender or track added. Rail source and explicit passenger-energy link are both changed.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED SINGLE RAIL FUEL-CELL REPLACEMENT BUDGET, item29, 2026-10-18. Knibbe2023 DOI10.1016/j.est.2023.108090, owner rail reference860kW/30000hstack and240000hoperation; Stropnik2022 DOI10.1016/j.ijhydene.2022.04.011 BoP20000h. Existing owner buys860kW*240000/30000=6880kW-equivalent system sets. Generic assembly additionally buys20000/3800=5.2631579stacks, yielding42.105stack sets over owner life. Introduce rail-specific assembly per1kWe owner set:one existing generic manufactured stack (not generic lifetime assembly) and30000/20000=1.5genericBoP units. Therefore owner lifetime has8stacksets and12BoPsets, each budget applied once.30000h railstack life is the existing heavy-haul engineering assumption, not a demonstrated lightvehicle stack endurance; retain it explicitly rather than silently importing3800h. BoP20000h is a source-based engineering durability proxy; fractional1.5 is expected lifetime attribution, not an instantaneous1.5BoP installation. Stack and BoP manufacture/source grades/size proxies remain unchanged; generic stack remains eligible for existing future catalyst updates. No new platinum loading or primary/secondary curve. Heavy-haul power/duty/passenger representativeness, storage and battery design remain separate gaps. Existing860kW and6880owner quantity retained; the explicit final-energy hydrogen passenger-rail purchase relinked; other rail service inherits its locomotive supplier so old cached assembly identity cannot persist.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -2095,26 +2097,36 @@
       </c>
     </row>
     <row r="48" spans="1:8" ns3:dyDescent="0.2">
-      <c r="A48" t="s">
-        <v>52</v>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>hydrogen fuel tank system, rail700bar lifetime reference</t>
+        </is>
       </c>
       <c r="B48">
-        <v>30323.845714285719</v>
-      </c>
-      <c r="C48" t="s">
-        <v>23</v>
-      </c>
-      <c r="D48" t="s">
-        <v>24</v>
+        <v>1</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
       </c>
       <c r="F48" t="s">
         <v>20</v>
       </c>
-      <c r="G48" t="s">
-        <v>53</v>
-      </c>
-      <c r="H48" t="s">
-        <v>54</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>hydrogen fuel tank system, rail700bar lifetime reference</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>APPROVED RAIL-SPECIFIC700BAR STORAGE/LIFE REFERENCE, issue69,2026-10-18. FCH2RAIL D1.5 railstorage investigation,DLR2021,AnnexBTable20, https://elib.dlr.de/145010/1/FCH2RAIL_D1.5.pdf :TypeIII70MPaTPED surveyreference8.3kgH2,2048x455mm,333Loutervolume,179kgINCLUDINGgas =&gt;170.7kgdry. Supplier surveyreference is not a certifiedcompleteheavyhaullocomotive design. Preserve current700barworkingpressure and40yearrailmanufacturinghorizon; do not forcepassenger350barorroadbus/truckvessels intoheavyhaul. Existing30323.845714kg cumulativecar-TypeIIIproxy was4sets over40years,with93kgdry/5.6kgH2. Its impliedinstalledgas=oldmass/4*5.6/93=456.488kg. Retain thisimpliedenergy budget as explicitengineeringreference because no route-specificrefuellingrange is documented; not infergasinventory fromlifetimefuelthroughput. Select55surveycylinders*8.3=456.5kgH2capacity,roundingup only0.012kg. Sourcepreserved860kW/.06185kgH2perkWhe implies8.582hfullpower before reserve; actualroute/peakduty,reserveandrefilling range remainunvalidated. Keep10yearvessellife/foursets as existing conservativeassumption,NOT manufacturerlifecertificate;test10-20years ratherthan invent a lifetime saving. Cylinder dry170.7 excludes8.3kgfuel. MaterialBOMunpublished:6mmAl linerat2700kg/m3 overcapsulearea2*pi*outerradius*length,2kgstainlessbosses,2kgPAprotection,remainingCF/epoxy at60/40vol%(1800/1200kg/m3),69.2308wt%fiber. Outerdiametergeometry,linerthickness,actualalloy/fiber andpressurequalification areengineeringassumptions,not a certifiedpressurevessel design.95%materialretention withmatchingprocesswaste and1kWh/kgforming/curing reference; wovenfiber is filamentwindingmanufacturingproxy. Installedvesseldrymass9388.5kg. Dedicatedsharedrack500kg(one40yearset,80%ordinary steel/20%Al) and100kgvalve/manifold/controls(two20yearsets:50stainless,5Cu,5brass,10PA,29.5Al,0.5auxinterfaceboard) are explicitmountingassumptions; no wholelocomotive,tenderchassis ortrack added. Lifetimevesselmanufacture220units,one rack,twoBoPsets are inside oneunit oflifetimeenergy-equipmentreference. Qtyone atlocomotiveproduction,not count220again in perMJadapter. Nominalinstalledstorageenvelope55*.333=18.315m3beforemounting; availablelocomotive/tenderpackaging is unresolved and not asserted tofit. Preserveexistingroad/railoperatingfuel andcompression path;700barpressureunchanged,no unsubstantiatedcompressionenergy saving. Originalrangeandbodyenergy notresimulated. EOL remainswholevehicleboundary,pressurespecificcylinderrecovery gap,no credits. Refreshstoredhydrogenpassengerrailcoefficients andindependentlynormalizefreightrailservices.</t>
+        </is>
       </c>
     </row>
     <row r="49" spans="1:8" ns3:dyDescent="0.2">
@@ -20988,6 +21000,1320 @@
       <c r="G1045" t="inlineStr">
         <is>
           <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>hydrogen fuel tank, rail700bar TypeIII cylinder, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1050">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>hydrogen fuel tank, rail700bar TypeIII cylinder, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>FCH2RAIL D1.5 railstorage investigation,DLR2021,AnnexBTable20, https://elib.dlr.de/145010/1/FCH2RAIL_D1.5.pdf :TypeIII70MPaTPED surveyreference8.3kgH2,2048x455mm,333Loutervolume,179kgINCLUDINGgas =&gt;170.7kgdry. Supplier surveyreference is not a certifiedcompleteheavyhaullocomotive design.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>APPROVED RAIL-SPECIFIC700BAR STORAGE/LIFE REFERENCE, issue69,2026-10-18. FCH2RAIL D1.5 railstorage investigation,DLR2021,AnnexBTable20, https://elib.dlr.de/145010/1/FCH2RAIL_D1.5.pdf :TypeIII70MPaTPED surveyreference8.3kgH2,2048x455mm,333Loutervolume,179kgINCLUDINGgas =&gt;170.7kgdry. Supplier surveyreference is not a certifiedcompleteheavyhaullocomotive design. Preserve current700barworkingpressure and40yearrailmanufacturinghorizon; do not forcepassenger350barorroadbus/truckvessels intoheavyhaul. Existing30323.845714kg cumulativecar-TypeIIIproxy was4sets over40years,with93kgdry/5.6kgH2. Its impliedinstalledgas=oldmass/4*5.6/93=456.488kg. Retain thisimpliedenergy budget as explicitengineeringreference because no route-specificrefuellingrange is documented; not infergasinventory fromlifetimefuelthroughput. Select55surveycylinders*8.3=456.5kgH2capacity,roundingup only0.012kg. Sourcepreserved860kW/.06185kgH2perkWhe implies8.582hfullpower before reserve; actualroute/peakduty,reserveandrefilling range remainunvalidated. Keep10yearvessellife/foursets as existing conservativeassumption,NOT manufacturerlifecertificate;test10-20years ratherthan invent a lifetime saving. Cylinder dry170.7 excludes8.3kgfuel. MaterialBOMunpublished:6mmAl linerat2700kg/m3 overcapsulearea2*pi*outerradius*length,2kgstainlessbosses,2kgPAprotection,remainingCF/epoxy at60/40vol%(1800/1200kg/m3),69.2308wt%fiber. Outerdiametergeometry,linerthickness,actualalloy/fiber andpressurequalification areengineeringassumptions,not a certifiedpressurevessel design.95%materialretention withmatchingprocesswaste and1kWh/kgforming/curing reference; wovenfiber is filamentwindingmanufacturingproxy. Installedvesseldrymass9388.5kg. Dedicatedsharedrack500kg(one40yearset,80%ordinary steel/20%Al) and100kgvalve/manifold/controls(two20yearsets:50stainless,5Cu,5brass,10PA,29.5Al,0.5auxinterfaceboard) are explicitmountingassumptions; no wholelocomotive,tenderchassis ortrack added. Lifetimevesselmanufacture220units,one rack,twoBoPsets are inside oneunit oflifetimeenergy-equipmentreference. Qtyone atlocomotiveproduction,not count220again in perMJadapter. Nominalinstalledstorageenvelope55*.333=18.315m3beforemounting; availablelocomotive/tenderpackaging is unresolved and not asserted tofit. Preserveexistingroad/railoperatingfuel andcompression path;700barpressureunchanged,no unsubstantiatedcompressionenergy saving. Originalrangeandbodyenergy notresimulated. EOL remainswholevehicleboundary,pressurespecificcylinderrecovery gap,no credits. Refreshstoredhydrogenpassengerrailcoefficients andindependentlynormalizefreightrailservices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1056" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1056" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1056" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1056" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1056" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1056" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>hydrogen fuel tank, rail700bar TypeIII cylinder, engineering reference</t>
+        </is>
+      </c>
+      <c r="B1057">
+        <v>1</v>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1057" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1057" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1057" t="inlineStr">
+        <is>
+          <t>hydrogen fuel tank, rail700bar TypeIII cylinder, engineering reference</t>
+        </is>
+      </c>
+      <c r="I1057" t="inlineStr">
+        <is>
+          <t>hydrogen fuel tank, rail700bar TypeIII cylinder, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B1058">
+        <v>49.92092580294951</v>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1058" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1058" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1058" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I1058" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>carbon fiber production, weaved, at factory</t>
+        </is>
+      </c>
+      <c r="B1059">
+        <v>86.92114043601472</v>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1059" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1059" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1059" t="inlineStr">
+        <is>
+          <t>carbon fiber, weaved</t>
+        </is>
+      </c>
+      <c r="I1059" t="inlineStr">
+        <is>
+          <t>carbon fiber, weaved</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>market for epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="B1060">
+        <v>38.63161797156208</v>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1060" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1060" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1060" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="I1060" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>market for steel, chromium steel 18/8</t>
+        </is>
+      </c>
+      <c r="B1061">
+        <v>2.1052631578947367</v>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1061" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1061" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1061" t="inlineStr">
+        <is>
+          <t>steel, chromium steel 18/8</t>
+        </is>
+      </c>
+      <c r="I1061" t="inlineStr">
+        <is>
+          <t>steel, chromium steel 18/8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>market for nylon 6</t>
+        </is>
+      </c>
+      <c r="B1062">
+        <v>2.1052631578947367</v>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1062" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1062" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1062" t="inlineStr">
+        <is>
+          <t>nylon 6</t>
+        </is>
+      </c>
+      <c r="I1062" t="inlineStr">
+        <is>
+          <t>nylon 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B1063">
+        <v>-8.98421052631578</v>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1063" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1063" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1063" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I1063" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1064">
+        <v>170.7</v>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1064" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1064" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1064" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I1064" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>hydrogen fuel tank, rail mounting rack, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1069">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>hydrogen fuel tank, rail mounting rack, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>FCH2RAIL D1.5 railstorage investigation,DLR2021,AnnexBTable20, https://elib.dlr.de/145010/1/FCH2RAIL_D1.5.pdf :TypeIII70MPaTPED surveyreference8.3kgH2,2048x455mm,333Loutervolume,179kgINCLUDINGgas =&gt;170.7kgdry. Supplier surveyreference is not a certifiedcompleteheavyhaullocomotive design.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>APPROVED RAIL-SPECIFIC700BAR STORAGE/LIFE REFERENCE, issue69,2026-10-18. FCH2RAIL D1.5 railstorage investigation,DLR2021,AnnexBTable20, https://elib.dlr.de/145010/1/FCH2RAIL_D1.5.pdf :TypeIII70MPaTPED surveyreference8.3kgH2,2048x455mm,333Loutervolume,179kgINCLUDINGgas =&gt;170.7kgdry. Supplier surveyreference is not a certifiedcompleteheavyhaullocomotive design. Preserve current700barworkingpressure and40yearrailmanufacturinghorizon; do not forcepassenger350barorroadbus/truckvessels intoheavyhaul. Existing30323.845714kg cumulativecar-TypeIIIproxy was4sets over40years,with93kgdry/5.6kgH2. Its impliedinstalledgas=oldmass/4*5.6/93=456.488kg. Retain thisimpliedenergy budget as explicitengineeringreference because no route-specificrefuellingrange is documented; not infergasinventory fromlifetimefuelthroughput. Select55surveycylinders*8.3=456.5kgH2capacity,roundingup only0.012kg. Sourcepreserved860kW/.06185kgH2perkWhe implies8.582hfullpower before reserve; actualroute/peakduty,reserveandrefilling range remainunvalidated. Keep10yearvessellife/foursets as existing conservativeassumption,NOT manufacturerlifecertificate;test10-20years ratherthan invent a lifetime saving. Cylinder dry170.7 excludes8.3kgfuel. MaterialBOMunpublished:6mmAl linerat2700kg/m3 overcapsulearea2*pi*outerradius*length,2kgstainlessbosses,2kgPAprotection,remainingCF/epoxy at60/40vol%(1800/1200kg/m3),69.2308wt%fiber. Outerdiametergeometry,linerthickness,actualalloy/fiber andpressurequalification areengineeringassumptions,not a certifiedpressurevessel design.95%materialretention withmatchingprocesswaste and1kWh/kgforming/curing reference; wovenfiber is filamentwindingmanufacturingproxy. Installedvesseldrymass9388.5kg. Dedicatedsharedrack500kg(one40yearset,80%ordinary steel/20%Al) and100kgvalve/manifold/controls(two20yearsets:50stainless,5Cu,5brass,10PA,29.5Al,0.5auxinterfaceboard) are explicitmountingassumptions; no wholelocomotive,tenderchassis ortrack added. Lifetimevesselmanufacture220units,one rack,twoBoPsets are inside oneunit oflifetimeenergy-equipmentreference. Qtyone atlocomotiveproduction,not count220again in perMJadapter. Nominalinstalledstorageenvelope55*.333=18.315m3beforemounting; availablelocomotive/tenderpackaging is unresolved and not asserted tofit. Preserveexistingroad/railoperatingfuel andcompression path;700barpressureunchanged,no unsubstantiatedcompressionenergy saving. Originalrangeandbodyenergy notresimulated. EOL remainswholevehicleboundary,pressurespecificcylinderrecovery gap,no credits. Refreshstoredhydrogenpassengerrailcoefficients andindependentlynormalizefreightrailservices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1075" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1075" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1075" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1075" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1075" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1075" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>hydrogen fuel tank, rail mounting rack, engineering reference</t>
+        </is>
+      </c>
+      <c r="B1076">
+        <v>1</v>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1076" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1076" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1076" t="inlineStr">
+        <is>
+          <t>hydrogen fuel tank, rail mounting rack, engineering reference</t>
+        </is>
+      </c>
+      <c r="I1076" t="inlineStr">
+        <is>
+          <t>hydrogen fuel tank, rail mounting rack, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B1077">
+        <v>400</v>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1077" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1077" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1077" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I1077" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B1078">
+        <v>100</v>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1078" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1078" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1078" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I1078" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>hydrogen fuel tank, rail shared valves and controls, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1083">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>hydrogen fuel tank, rail shared valves and controls, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>FCH2RAIL D1.5 railstorage investigation,DLR2021,AnnexBTable20, https://elib.dlr.de/145010/1/FCH2RAIL_D1.5.pdf :TypeIII70MPaTPED surveyreference8.3kgH2,2048x455mm,333Loutervolume,179kgINCLUDINGgas =&gt;170.7kgdry. Supplier surveyreference is not a certifiedcompleteheavyhaullocomotive design.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>APPROVED RAIL-SPECIFIC700BAR STORAGE/LIFE REFERENCE, issue69,2026-10-18. FCH2RAIL D1.5 railstorage investigation,DLR2021,AnnexBTable20, https://elib.dlr.de/145010/1/FCH2RAIL_D1.5.pdf :TypeIII70MPaTPED surveyreference8.3kgH2,2048x455mm,333Loutervolume,179kgINCLUDINGgas =&gt;170.7kgdry. Supplier surveyreference is not a certifiedcompleteheavyhaullocomotive design. Preserve current700barworkingpressure and40yearrailmanufacturinghorizon; do not forcepassenger350barorroadbus/truckvessels intoheavyhaul. Existing30323.845714kg cumulativecar-TypeIIIproxy was4sets over40years,with93kgdry/5.6kgH2. Its impliedinstalledgas=oldmass/4*5.6/93=456.488kg. Retain thisimpliedenergy budget as explicitengineeringreference because no route-specificrefuellingrange is documented; not infergasinventory fromlifetimefuelthroughput. Select55surveycylinders*8.3=456.5kgH2capacity,roundingup only0.012kg. Sourcepreserved860kW/.06185kgH2perkWhe implies8.582hfullpower before reserve; actualroute/peakduty,reserveandrefilling range remainunvalidated. Keep10yearvessellife/foursets as existing conservativeassumption,NOT manufacturerlifecertificate;test10-20years ratherthan invent a lifetime saving. Cylinder dry170.7 excludes8.3kgfuel. MaterialBOMunpublished:6mmAl linerat2700kg/m3 overcapsulearea2*pi*outerradius*length,2kgstainlessbosses,2kgPAprotection,remainingCF/epoxy at60/40vol%(1800/1200kg/m3),69.2308wt%fiber. Outerdiametergeometry,linerthickness,actualalloy/fiber andpressurequalification areengineeringassumptions,not a certifiedpressurevessel design.95%materialretention withmatchingprocesswaste and1kWh/kgforming/curing reference; wovenfiber is filamentwindingmanufacturingproxy. Installedvesseldrymass9388.5kg. Dedicatedsharedrack500kg(one40yearset,80%ordinary steel/20%Al) and100kgvalve/manifold/controls(two20yearsets:50stainless,5Cu,5brass,10PA,29.5Al,0.5auxinterfaceboard) are explicitmountingassumptions; no wholelocomotive,tenderchassis ortrack added. Lifetimevesselmanufacture220units,one rack,twoBoPsets are inside oneunit oflifetimeenergy-equipmentreference. Qtyone atlocomotiveproduction,not count220again in perMJadapter. Nominalinstalledstorageenvelope55*.333=18.315m3beforemounting; availablelocomotive/tenderpackaging is unresolved and not asserted tofit. Preserveexistingroad/railoperatingfuel andcompression path;700barpressureunchanged,no unsubstantiatedcompressionenergy saving. Originalrangeandbodyenergy notresimulated. EOL remainswholevehicleboundary,pressurespecificcylinderrecovery gap,no credits. Refreshstoredhydrogenpassengerrailcoefficients andindependentlynormalizefreightrailservices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1089" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1089" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1089" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1089" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1089" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1089" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>hydrogen fuel tank, rail shared valves and controls, engineering reference</t>
+        </is>
+      </c>
+      <c r="B1090">
+        <v>1</v>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1090" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1090" t="inlineStr">
+        <is>
+          <t>hydrogen fuel tank, rail shared valves and controls, engineering reference</t>
+        </is>
+      </c>
+      <c r="I1090" t="inlineStr">
+        <is>
+          <t>hydrogen fuel tank, rail shared valves and controls, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>market for steel, chromium steel 18/8</t>
+        </is>
+      </c>
+      <c r="B1091">
+        <v>50</v>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1091" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1091" t="inlineStr">
+        <is>
+          <t>steel, chromium steel 18/8</t>
+        </is>
+      </c>
+      <c r="I1091" t="inlineStr">
+        <is>
+          <t>steel, chromium steel 18/8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B1092">
+        <v>5</v>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1092" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1092" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I1092" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>market for brass</t>
+        </is>
+      </c>
+      <c r="B1093">
+        <v>5</v>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1093" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1093" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1093" t="inlineStr">
+        <is>
+          <t>brass</t>
+        </is>
+      </c>
+      <c r="I1093" t="inlineStr">
+        <is>
+          <t>brass</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>market for nylon 6</t>
+        </is>
+      </c>
+      <c r="B1094">
+        <v>10</v>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1094" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1094" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1094" t="inlineStr">
+        <is>
+          <t>nylon 6</t>
+        </is>
+      </c>
+      <c r="I1094" t="inlineStr">
+        <is>
+          <t>nylon 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B1095">
+        <v>29.5</v>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1095" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1095" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1095" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I1095" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+        </is>
+      </c>
+      <c r="B1096">
+        <v>0.5</v>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1096" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1096" t="inlineStr">
+        <is>
+          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+        </is>
+      </c>
+      <c r="I1096" t="inlineStr">
+        <is>
+          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>hydrogen fuel tank system, rail700bar lifetime reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>hydrogen fuel tank system, rail700bar lifetime reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>FCH2RAIL D1.5 railstorage investigation,DLR2021,AnnexBTable20, https://elib.dlr.de/145010/1/FCH2RAIL_D1.5.pdf :TypeIII70MPaTPED surveyreference8.3kgH2,2048x455mm,333Loutervolume,179kgINCLUDINGgas =&gt;170.7kgdry. Supplier surveyreference is not a certifiedcompleteheavyhaullocomotive design.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>APPROVED RAIL-SPECIFIC700BAR STORAGE/LIFE REFERENCE, issue69,2026-10-18. FCH2RAIL D1.5 railstorage investigation,DLR2021,AnnexBTable20, https://elib.dlr.de/145010/1/FCH2RAIL_D1.5.pdf :TypeIII70MPaTPED surveyreference8.3kgH2,2048x455mm,333Loutervolume,179kgINCLUDINGgas =&gt;170.7kgdry. Supplier surveyreference is not a certifiedcompleteheavyhaullocomotive design. Preserve current700barworkingpressure and40yearrailmanufacturinghorizon; do not forcepassenger350barorroadbus/truckvessels intoheavyhaul. Existing30323.845714kg cumulativecar-TypeIIIproxy was4sets over40years,with93kgdry/5.6kgH2. Its impliedinstalledgas=oldmass/4*5.6/93=456.488kg. Retain thisimpliedenergy budget as explicitengineeringreference because no route-specificrefuellingrange is documented; not infergasinventory fromlifetimefuelthroughput. Select55surveycylinders*8.3=456.5kgH2capacity,roundingup only0.012kg. Sourcepreserved860kW/.06185kgH2perkWhe implies8.582hfullpower before reserve; actualroute/peakduty,reserveandrefilling range remainunvalidated. Keep10yearvessellife/foursets as existing conservativeassumption,NOT manufacturerlifecertificate;test10-20years ratherthan invent a lifetime saving. Cylinder dry170.7 excludes8.3kgfuel. MaterialBOMunpublished:6mmAl linerat2700kg/m3 overcapsulearea2*pi*outerradius*length,2kgstainlessbosses,2kgPAprotection,remainingCF/epoxy at60/40vol%(1800/1200kg/m3),69.2308wt%fiber. Outerdiametergeometry,linerthickness,actualalloy/fiber andpressurequalification areengineeringassumptions,not a certifiedpressurevessel design.95%materialretention withmatchingprocesswaste and1kWh/kgforming/curing reference; wovenfiber is filamentwindingmanufacturingproxy. Installedvesseldrymass9388.5kg. Dedicatedsharedrack500kg(one40yearset,80%ordinary steel/20%Al) and100kgvalve/manifold/controls(two20yearsets:50stainless,5Cu,5brass,10PA,29.5Al,0.5auxinterfaceboard) are explicitmountingassumptions; no wholelocomotive,tenderchassis ortrack added. Lifetimevesselmanufacture220units,one rack,twoBoPsets are inside oneunit oflifetimeenergy-equipmentreference. Qtyone atlocomotiveproduction,not count220again in perMJadapter. Nominalinstalledstorageenvelope55*.333=18.315m3beforemounting; availablelocomotive/tenderpackaging is unresolved and not asserted tofit. Preserveexistingroad/railoperatingfuel andcompression path;700barpressureunchanged,no unsubstantiatedcompressionenergy saving. Originalrangeandbodyenergy notresimulated. EOL remainswholevehicleboundary,pressurespecificcylinderrecovery gap,no credits. Refreshstoredhydrogenpassengerrailcoefficients andindependentlynormalizefreightrailservices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1107" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1107" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1107" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1107" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1107" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1107" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>hydrogen fuel tank system, rail700bar lifetime reference</t>
+        </is>
+      </c>
+      <c r="B1108">
+        <v>1</v>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1108" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1108" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1108" t="inlineStr">
+        <is>
+          <t>hydrogen fuel tank system, rail700bar lifetime reference</t>
+        </is>
+      </c>
+      <c r="I1108" t="inlineStr">
+        <is>
+          <t>hydrogen fuel tank system, rail700bar lifetime reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>hydrogen fuel tank, rail700bar TypeIII cylinder, engineering reference</t>
+        </is>
+      </c>
+      <c r="B1109">
+        <v>220</v>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1109" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1109" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1109" t="inlineStr">
+        <is>
+          <t>hydrogen fuel tank, rail700bar TypeIII cylinder, engineering reference</t>
+        </is>
+      </c>
+      <c r="I1109" t="inlineStr">
+        <is>
+          <t>hydrogen fuel tank, rail700bar TypeIII cylinder, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>hydrogen fuel tank, rail mounting rack, engineering reference</t>
+        </is>
+      </c>
+      <c r="B1110">
+        <v>1</v>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1110" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1110" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1110" t="inlineStr">
+        <is>
+          <t>hydrogen fuel tank, rail mounting rack, engineering reference</t>
+        </is>
+      </c>
+      <c r="I1110" t="inlineStr">
+        <is>
+          <t>hydrogen fuel tank, rail mounting rack, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>hydrogen fuel tank, rail shared valves and controls, engineering reference</t>
+        </is>
+      </c>
+      <c r="B1111">
+        <v>2</v>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1111" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1111" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1111" t="inlineStr">
+        <is>
+          <t>hydrogen fuel tank, rail shared valves and controls, engineering reference</t>
+        </is>
+      </c>
+      <c r="I1111" t="inlineStr">
+        <is>
+          <t>hydrogen fuel tank, rail shared valves and controls, engineering reference</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-rail-freight.xlsx
+++ b/premise/data/additional_inventories/lci-rail-freight.xlsx
@@ -1359,7 +1359,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{2A08E695-FC79-4DF0-ACCB-3B3F78317B74}">
-  <dimension ref="A1:Z1111"/>
+  <dimension ref="A1:Z1157"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="61.83203125" customWidth="1"/>
@@ -1428,7 +1428,9 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">APPROVED RAIL CONVERTER ENGINEERING REFERENCE, item25, 2026-10-18. ABB2024 ACS6080 PEP ABBG-00712-V01.01-EN, marked Draft/Public, page7, https://library.e.abb.com/public/f0dd73990f0242ab9a0e88dbf6090edd/PEP_EPD_ACS6080_33AXD10002395301_RevA_EN_05122024.pdf; ABB BORDLINE masses/power retained from existing rail sources. Infineon FZ1500R33HE3 datasheet construction reference https://www.infineon.com/assets/row/public/documents/60/49/infineon-fz1500r33he3-datasheet-en.pdf. Replace the mass-scaled4.5kg car battery-voltage converter with an explicit medium-voltage AC-drive-based reference, not a measured BORDLINE BOM. ABB2024 draft PEP gives14583kg including packaging:steel43.4%,Cu20.4%,Al2.25%,GFRP1.7%,otherplastics0.4%,electroniccomponents12.9%,wood13.7%,other5.25%. Percentages sum100. Treat wood as packaging and exclude it from installed reference mass:hardware fraction0.863. Perkg installed converter divide other category fractions by0.863; purchase packaging wood0.137/0.863kg additionally. Source is an18MW industrial AC drive, not a rail-qualified product: composition transfer to BORDLINE is an explicit engineering analogue, with source installed masses and power/lifetime counts unchanged. Assume electronic component mass70%film capacitors,25%power semiconductor modules,5%populated control boards. These fractions are design assumptions; sensitivity capacitor50-80%, module10-40%, board2-10%, constrained to100%. Generic Pb-free through-hole board retains upstream precious metals; no zero-gold assumption. Illustrative power module retained recipe:Cu50%,Al10%,alumina20%,PPS10%,silicone8%,silicon die2%. Represent die fabrication by existing fabricated-IC-wafer service using300um silicon thickness and2330kg/m3 density:0.02/(2330*0.0003)m2/kgmodule. This wafer and power-module composition are engineering proxies, not Infineon material declarations or verified rail die technology. Module assembly1kWh/kg assumed. Film capacitor proxy includes its own constituent materials once. Other5.25%/0.863=6.08343% installed hardware mass remains compositionally UNRESOLVED and is not silently converted into zero metal or an arbitrary PCB. Known retained material coverage93.91657%; trace-metal completeness is not claimed.100%retention reference plus generic metal-working/1kWh final assembly perkg; yields, cooling coolant, additional cabling, end-of-life and rail qualification remain gaps. Do not infer corrected system gold totals before rebuilding and sensitivity analysis. No passenger/freight service denominator change in this commit.
+          <t xml:space="preserve">APPROVED RAIL GENERATOR FUNCTION AND RATING, issue104,2026-10-18. ABB NMG catalogue9AKK2017109096:page10 continuous60Hz40C,pf0.8,NMG0500DD04 DAPI 3590kVA/2872kW at460V;page17 net7050kg,gross7730kg. OldNMG0450DD04 at460V60Hz is2072kW,not2.8MW. https://search.abb.com/library/Download.aspx?DocumentID=9AKK2017109096&amp;LanguageCode=en&amp;DocumentPartId=&amp;Action=Launch . Material analogue:ABB AMG0900 5125kVA11kV EPD2000 pages2-3,https://library.e.abb.com/public/2bb39d909d618031c1256d63003c5c76/EPD%20for%20AMG%20900.pdf . Use kg/product column; kg/kVA column is visibly misaligned. Existing locomotive buys4410kg of unspecified passive electronics as a generator proxy; native mixture assigns153.468kg tantalum-capacitor packages,NOT elementalTa. Replace with7050kg of a dedicated synchronous powertrain-generator engineering reference. Selected industrial model rated2872kW is sufficient for the stated2800kW duty at460V/60Hz/pf0.8. This is not a rail-qualified UKlight generator or proof of compatible BORDLINE DC-link voltage:actual rail speed/voltage,rectification,EMC,cooling and mass require project-specific verification. Source mass is not scaled linearly fromkVA. Keep original40year generator allocation as a service assumption; EPD25year operation is not transferred as measured rail life. Test mass4410/7050/9000kg and20-40year service; keep operating diesel demand unchanged. Material composition is transferred PERkg from the much heavier,11kV medium-speed AMG0900,not claimed a published NMG BOM:kg/product={'electricalsteel': 7120.0, 'steel': 10900.0, 'forgedsteel': 5323.0, 'Al': 13.0, 'Cu': 2461.0, 'insulation': 155.0, 'resin': 225.0, 'paint': 40.0},installed total26237kg excluding800kg wood. Reserve1kg of the7050kg budget for an explicit analog excitation/AVR material reference; scale the remaining7049kg by these normalized fractions. The1kg AVR partition is an engineering allocation,not manufacturer traceability. Electricalsteel uses the existing3.2%Si reference;other/forgedsteel generic lowalloy feed,insulation glassfibre,impregnation epoxy,paint alkyd are stated material proxies. Existing electricalsteel rolling stays in its supplier;do not add a second generic metalworking energy package. EPD manufacturing40122kWh electricity and9659kWh heat per26237kg provide an aggregate factory-energy reference perkg,not operating losses. Potential factory/service overlap,forging details,lamination yield and actual coating remain gaps. AVR reference1kg contains0.05m2 unmountedPWB at assumed3.08kg/m2,6glassdiodes at0.596g,50gchoke,30gfilmcapacitor,10gmetalfilmresistors,5gSMTtransistors,100gCu,400gAl,100gepoxy andremainingsteel. This is an explicit analog material budget,not validated excitation circuit or a universal zeroTa/PM claim. Wound-field generator excitation is represented by the winding material budget;no unsupported full-machine permanent magnets. Full7050kg generator goes once toWEEE;AVR has no extra disposal. Native WEEE treatment is a proxy,not recoveryshare analysis. Gross-minus-net680kg shipping-package composition unresolved and excluded from installed mass;do not assign it invented metals. Rewire six passenger-train perMJ copies and provenance with unchanged lifetime-energy denominator;source generator kg increases7050/4410. Traction converter,motor,engine,tank,chassis and track unchanged. Only existing rail/final-energy workbooks;no runtime or native edits.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED RAIL CONVERTER ENGINEERING REFERENCE, item25, 2026-10-18. ABB2024 ACS6080 PEP ABBG-00712-V01.01-EN, marked Draft/Public, page7, https://library.e.abb.com/public/f0dd73990f0242ab9a0e88dbf6090edd/PEP_EPD_ACS6080_33AXD10002395301_RevA_EN_05122024.pdf; ABB BORDLINE masses/power retained from existing rail sources. Infineon FZ1500R33HE3 datasheet construction reference https://www.infineon.com/assets/row/public/documents/60/49/infineon-fz1500r33he3-datasheet-en.pdf. Replace the mass-scaled4.5kg car battery-voltage converter with an explicit medium-voltage AC-drive-based reference, not a measured BORDLINE BOM. ABB2024 draft PEP gives14583kg including packaging:steel43.4%,Cu20.4%,Al2.25%,GFRP1.7%,otherplastics0.4%,electroniccomponents12.9%,wood13.7%,other5.25%. Percentages sum100. Treat wood as packaging and exclude it from installed reference mass:hardware fraction0.863. Perkg installed converter divide other category fractions by0.863; purchase packaging wood0.137/0.863kg additionally. Source is an18MW industrial AC drive, not a rail-qualified product: composition transfer to BORDLINE is an explicit engineering analogue, with source installed masses and power/lifetime counts unchanged. Assume electronic component mass70%film capacitors,25%power semiconductor modules,5%populated control boards. These fractions are design assumptions; sensitivity capacitor50-80%, module10-40%, board2-10%, constrained to100%. Generic Pb-free through-hole board retains upstream precious metals; no zero-gold assumption. Illustrative power module retained recipe:Cu50%,Al10%,alumina20%,PPS10%,silicone8%,silicon die2%. Represent die fabrication by existing fabricated-IC-wafer service using300um silicon thickness and2330kg/m3 density:0.02/(2330*0.0003)m2/kgmodule. This wafer and power-module composition are engineering proxies, not Infineon material declarations or verified rail die technology. Module assembly1kWh/kg assumed. Film capacitor proxy includes its own constituent materials once. Other5.25%/0.863=6.08343% installed hardware mass remains compositionally UNRESOLVED and is not silently converted into zero metal or an arbitrary PCB. Known retained material coverage93.91657%; trace-metal completeness is not claimed.100%retention reference plus generic metal-working/1kWh final assembly perkg; yields, cooling coolant, additional cabling, end-of-life and rail qualification remain gaps. Do not infer corrected system gold totals before rebuilding and sensitivity analysis. No passenger/freight service denominator change in this commit.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 market for locomotive (ecoinvent) is based on Frischknecht et al. (1996). This study only consideres materials of the catenary electric locomotive RE 460 (~84t, years of construction 1991-1996), operated by the SBB in CH. Electrical components are not considered. This equals a electric locomotives base components without the electrical equipment (= power tracktion). Therfore additional components are added to the inventory to represent a diesel locomotive (ICE, generator, fuel tank, transformer, inverter, electric motors). As a reference diesel-electric locomotive the UKlight (Vossloh Rail Vehicles, 2012), as it is supplied by ABB (also supllying the Re460) and is similar in size (85t) to the Re460 (84t). The UKlight from Vossloh Rail Vehicles operates on 2,800 kW max. power with a starting tractive effort of 317 kN and a max speed of 160 km/h. This makes it comparable to the electric alternative Re460 with a tractive effort of 300 kN, although having a higher max. power of 6,100 kW and higher max. speed of 230 km/h. The two vehicles are still assumed to be comparable alternatives as freight rail transport does not operate on high velocities. 
 Electrical components taken from ABB (2018b).
@@ -1491,8 +1493,10 @@
       <c r="G12" t="s">
         <v>21</v>
       </c>
-      <c r="H12" t="s">
-        <v>22</v>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>APPROVED RAIL GENERATOR FUNCTION AND RATING, issue104,2026-10-18. ABB NMG catalogue9AKK2017109096:page10 continuous60Hz40C,pf0.8,NMG0500DD04 DAPI 3590kVA/2872kW at460V;page17 net7050kg,gross7730kg. OldNMG0450DD04 at460V60Hz is2072kW,not2.8MW. https://search.abb.com/library/Download.aspx?DocumentID=9AKK2017109096&amp;LanguageCode=en&amp;DocumentPartId=&amp;Action=Launch . Material analogue:ABB AMG0900 5125kVA11kV EPD2000 pages2-3,https://library.e.abb.com/public/2bb39d909d618031c1256d63003c5c76/EPD%20for%20AMG%20900.pdf . Use kg/product column; kg/kVA column is visibly misaligned. Existing locomotive buys4410kg of unspecified passive electronics as a generator proxy; native mixture assigns153.468kg tantalum-capacitor packages,NOT elementalTa. Replace with7050kg of a dedicated synchronous powertrain-generator engineering reference. Selected industrial model rated2872kW is sufficient for the stated2800kW duty at460V/60Hz/pf0.8. This is not a rail-qualified UKlight generator or proof of compatible BORDLINE DC-link voltage:actual rail speed/voltage,rectification,EMC,cooling and mass require project-specific verification. Source mass is not scaled linearly fromkVA. Keep original40year generator allocation as a service assumption; EPD25year operation is not transferred as measured rail life. Test mass4410/7050/9000kg and20-40year service; keep operating diesel demand unchanged. Material composition is transferred PERkg from the much heavier,11kV medium-speed AMG0900,not claimed a published NMG BOM:kg/product={'electricalsteel': 7120.0, 'steel': 10900.0, 'forgedsteel': 5323.0, 'Al': 13.0, 'Cu': 2461.0, 'insulation': 155.0, 'resin': 225.0, 'paint': 40.0},installed total26237kg excluding800kg wood. Reserve1kg of the7050kg budget for an explicit analog excitation/AVR material reference; scale the remaining7049kg by these normalized fractions. The1kg AVR partition is an engineering allocation,not manufacturer traceability. Electricalsteel uses the existing3.2%Si reference;other/forgedsteel generic lowalloy feed,insulation glassfibre,impregnation epoxy,paint alkyd are stated material proxies. Existing electricalsteel rolling stays in its supplier;do not add a second generic metalworking energy package. EPD manufacturing40122kWh electricity and9659kWh heat per26237kg provide an aggregate factory-energy reference perkg,not operating losses. Potential factory/service overlap,forging details,lamination yield and actual coating remain gaps. AVR reference1kg contains0.05m2 unmountedPWB at assumed3.08kg/m2,6glassdiodes at0.596g,50gchoke,30gfilmcapacitor,10gmetalfilmresistors,5gSMTtransistors,100gCu,400gAl,100gepoxy andremainingsteel. This is an explicit analog material budget,not validated excitation circuit or a universal zeroTa/PM claim. Wound-field generator excitation is represented by the winding material budget;no unsupported full-machine permanent magnets. Full7050kg generator goes once toWEEE;AVR has no extra disposal. Native WEEE treatment is a proxy,not recoveryshare analysis. Gross-minus-net680kg shipping-package composition unresolved and excluded from installed mass;do not assign it invented metals. Rewire six passenger-train perMJ copies and provenance with unchanged lifetime-energy denominator;source generator kg increases7050/4410. Traction converter,motor,engine,tank,chassis and track unchanged. Only existing rail/final-energy workbooks;no runtime or native edits.</t>
+        </is>
       </c>
     </row>
     <row r="13" spans="1:8" ns3:dyDescent="0.2">
@@ -1542,14 +1546,18 @@
       </c>
     </row>
     <row r="15" spans="1:8" ns3:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>271</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>rail powertrain generator, synchronous engineering reference</t>
+        </is>
       </c>
       <c r="B15">
-        <v>4410</v>
-      </c>
-      <c r="C15" t="s">
-        <v>3</v>
+        <v>7050.0</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="D15" t="s">
         <v>24</v>
@@ -1557,8 +1565,10 @@
       <c r="F15" t="s">
         <v>20</v>
       </c>
-      <c r="G15" t="s">
-        <v>272</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>rail powertrain generator, synchronous engineering reference</t>
+        </is>
       </c>
       <c r="H15" t="s">
         <v>29</v>
@@ -22317,6 +22327,1118 @@
         </is>
       </c>
     </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>rail generator analog excitation controller, engineering material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1116">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>rail generator analog excitation controller, engineering material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>ABB NMG catalogue9AKK2017109096:page10 continuous60Hz40C,pf0.8,NMG0500DD04 DAPI 3590kVA/2872kW at460V;page17 net7050kg,gross7730kg. OldNMG0450DD04 at460V60Hz is2072kW,not2.8MW. https://search.abb.com/library/Download.aspx?DocumentID=9AKK2017109096&amp;LanguageCode=en&amp;DocumentPartId=&amp;Action=Launch . Material analogue:ABB AMG0900 5125kVA11kV EPD2000 pages2-3,https://library.e.abb.com/public/2bb39d909d618031c1256d63003c5c76/EPD%20for%20AMG%20900.pdf . Use kg/product column; kg/kVA column is visibly misaligned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>APPROVED RAIL GENERATOR FUNCTION AND RATING, issue104,2026-10-18. ABB NMG catalogue9AKK2017109096:page10 continuous60Hz40C,pf0.8,NMG0500DD04 DAPI 3590kVA/2872kW at460V;page17 net7050kg,gross7730kg. OldNMG0450DD04 at460V60Hz is2072kW,not2.8MW. https://search.abb.com/library/Download.aspx?DocumentID=9AKK2017109096&amp;LanguageCode=en&amp;DocumentPartId=&amp;Action=Launch . Material analogue:ABB AMG0900 5125kVA11kV EPD2000 pages2-3,https://library.e.abb.com/public/2bb39d909d618031c1256d63003c5c76/EPD%20for%20AMG%20900.pdf . Use kg/product column; kg/kVA column is visibly misaligned. Existing locomotive buys4410kg of unspecified passive electronics as a generator proxy; native mixture assigns153.468kg tantalum-capacitor packages,NOT elementalTa. Replace with7050kg of a dedicated synchronous powertrain-generator engineering reference. Selected industrial model rated2872kW is sufficient for the stated2800kW duty at460V/60Hz/pf0.8. This is not a rail-qualified UKlight generator or proof of compatible BORDLINE DC-link voltage:actual rail speed/voltage,rectification,EMC,cooling and mass require project-specific verification. Source mass is not scaled linearly fromkVA. Keep original40year generator allocation as a service assumption; EPD25year operation is not transferred as measured rail life. Test mass4410/7050/9000kg and20-40year service; keep operating diesel demand unchanged. Material composition is transferred PERkg from the much heavier,11kV medium-speed AMG0900,not claimed a published NMG BOM:kg/product={'electricalsteel': 7120.0, 'steel': 10900.0, 'forgedsteel': 5323.0, 'Al': 13.0, 'Cu': 2461.0, 'insulation': 155.0, 'resin': 225.0, 'paint': 40.0},installed total26237kg excluding800kg wood. Reserve1kg of the7050kg budget for an explicit analog excitation/AVR material reference; scale the remaining7049kg by these normalized fractions. The1kg AVR partition is an engineering allocation,not manufacturer traceability. Electricalsteel uses the existing3.2%Si reference;other/forgedsteel generic lowalloy feed,insulation glassfibre,impregnation epoxy,paint alkyd are stated material proxies. Existing electricalsteel rolling stays in its supplier;do not add a second generic metalworking energy package. EPD manufacturing40122kWh electricity and9659kWh heat per26237kg provide an aggregate factory-energy reference perkg,not operating losses. Potential factory/service overlap,forging details,lamination yield and actual coating remain gaps. AVR reference1kg contains0.05m2 unmountedPWB at assumed3.08kg/m2,6glassdiodes at0.596g,50gchoke,30gfilmcapacitor,10gmetalfilmresistors,5gSMTtransistors,100gCu,400gAl,100gepoxy andremainingsteel. This is an explicit analog material budget,not validated excitation circuit or a universal zeroTa/PM claim. Wound-field generator excitation is represented by the winding material budget;no unsupported full-machine permanent magnets. Full7050kg generator goes once toWEEE;AVR has no extra disposal. Native WEEE treatment is a proxy,not recoveryshare analysis. Gross-minus-net680kg shipping-package composition unresolved and excluded from installed mass;do not assign it invented metals. Rewire six passenger-train perMJ copies and provenance with unchanged lifetime-energy denominator;source generator kg increases7050/4410. Traction converter,motor,engine,tank,chassis and track unchanged. Only existing rail/final-energy workbooks;no runtime or native edits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1122" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1122" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1122" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1122" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1122" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1122" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>rail generator analog excitation controller, engineering material reference</t>
+        </is>
+      </c>
+      <c r="B1123">
+        <v>1</v>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1123" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1123" t="inlineStr">
+        <is>
+          <t>rail generator analog excitation controller, engineering material reference</t>
+        </is>
+      </c>
+      <c r="I1123" t="inlineStr">
+        <is>
+          <t>rail generator analog excitation controller, engineering material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>market for printed wiring board, for surface mounting, Pb free surface</t>
+        </is>
+      </c>
+      <c r="B1124">
+        <v>0.05</v>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1124" t="inlineStr">
+        <is>
+          <t>square meter</t>
+        </is>
+      </c>
+      <c r="F1124" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1124" t="inlineStr">
+        <is>
+          <t>printed wiring board, for surface mounting, Pb free surface</t>
+        </is>
+      </c>
+      <c r="I1124" t="inlineStr">
+        <is>
+          <t>printed wiring board, for surface mounting, Pb free surface</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>market for diode, glass-, for through-hole mounting</t>
+        </is>
+      </c>
+      <c r="B1125">
+        <v>0.0035759999999999998</v>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1125" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1125" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1125" t="inlineStr">
+        <is>
+          <t>diode, glass-, for through-hole mounting</t>
+        </is>
+      </c>
+      <c r="I1125" t="inlineStr">
+        <is>
+          <t>diode, glass-, for through-hole mounting</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>market for inductor, ring core choke type</t>
+        </is>
+      </c>
+      <c r="B1126">
+        <v>0.05</v>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1126" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1126" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1126" t="inlineStr">
+        <is>
+          <t>inductor, ring core choke type</t>
+        </is>
+      </c>
+      <c r="I1126" t="inlineStr">
+        <is>
+          <t>inductor, ring core choke type</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>market for capacitor, film type, for through-hole mounting</t>
+        </is>
+      </c>
+      <c r="B1127">
+        <v>0.03</v>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1127" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1127" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1127" t="inlineStr">
+        <is>
+          <t>capacitor, film type, for through-hole mounting</t>
+        </is>
+      </c>
+      <c r="I1127" t="inlineStr">
+        <is>
+          <t>capacitor, film type, for through-hole mounting</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>market for resistor, metal film type, through-hole mounting</t>
+        </is>
+      </c>
+      <c r="B1128">
+        <v>0.01</v>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1128" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1128" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1128" t="inlineStr">
+        <is>
+          <t>resistor, metal film type, through-hole mounting</t>
+        </is>
+      </c>
+      <c r="I1128" t="inlineStr">
+        <is>
+          <t>resistor, metal film type, through-hole mounting</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>market for transistor, surface-mounted</t>
+        </is>
+      </c>
+      <c r="B1129">
+        <v>0.005</v>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1129" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1129" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1129" t="inlineStr">
+        <is>
+          <t>transistor, surface-mounted</t>
+        </is>
+      </c>
+      <c r="I1129" t="inlineStr">
+        <is>
+          <t>transistor, surface-mounted</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B1130">
+        <v>0.1</v>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1130" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1130" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1130" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I1130" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B1131">
+        <v>0.4</v>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1131" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1131" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1131" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I1131" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>market for epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="B1132">
+        <v>0.1</v>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1132" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1132" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1132" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="I1132" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B1133">
+        <v>0.14742399999999986</v>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1133" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1133" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1133" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I1133" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1134">
+        <v>1</v>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1134" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1134" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1134" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I1134" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>rail powertrain generator, synchronous engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1139">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>rail powertrain generator, synchronous engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>ABB NMG catalogue9AKK2017109096:page10 continuous60Hz40C,pf0.8,NMG0500DD04 DAPI 3590kVA/2872kW at460V;page17 net7050kg,gross7730kg. OldNMG0450DD04 at460V60Hz is2072kW,not2.8MW. https://search.abb.com/library/Download.aspx?DocumentID=9AKK2017109096&amp;LanguageCode=en&amp;DocumentPartId=&amp;Action=Launch . Material analogue:ABB AMG0900 5125kVA11kV EPD2000 pages2-3,https://library.e.abb.com/public/2bb39d909d618031c1256d63003c5c76/EPD%20for%20AMG%20900.pdf . Use kg/product column; kg/kVA column is visibly misaligned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>APPROVED RAIL GENERATOR FUNCTION AND RATING, issue104,2026-10-18. ABB NMG catalogue9AKK2017109096:page10 continuous60Hz40C,pf0.8,NMG0500DD04 DAPI 3590kVA/2872kW at460V;page17 net7050kg,gross7730kg. OldNMG0450DD04 at460V60Hz is2072kW,not2.8MW. https://search.abb.com/library/Download.aspx?DocumentID=9AKK2017109096&amp;LanguageCode=en&amp;DocumentPartId=&amp;Action=Launch . Material analogue:ABB AMG0900 5125kVA11kV EPD2000 pages2-3,https://library.e.abb.com/public/2bb39d909d618031c1256d63003c5c76/EPD%20for%20AMG%20900.pdf . Use kg/product column; kg/kVA column is visibly misaligned. Existing locomotive buys4410kg of unspecified passive electronics as a generator proxy; native mixture assigns153.468kg tantalum-capacitor packages,NOT elementalTa. Replace with7050kg of a dedicated synchronous powertrain-generator engineering reference. Selected industrial model rated2872kW is sufficient for the stated2800kW duty at460V/60Hz/pf0.8. This is not a rail-qualified UKlight generator or proof of compatible BORDLINE DC-link voltage:actual rail speed/voltage,rectification,EMC,cooling and mass require project-specific verification. Source mass is not scaled linearly fromkVA. Keep original40year generator allocation as a service assumption; EPD25year operation is not transferred as measured rail life. Test mass4410/7050/9000kg and20-40year service; keep operating diesel demand unchanged. Material composition is transferred PERkg from the much heavier,11kV medium-speed AMG0900,not claimed a published NMG BOM:kg/product={'electricalsteel': 7120.0, 'steel': 10900.0, 'forgedsteel': 5323.0, 'Al': 13.0, 'Cu': 2461.0, 'insulation': 155.0, 'resin': 225.0, 'paint': 40.0},installed total26237kg excluding800kg wood. Reserve1kg of the7050kg budget for an explicit analog excitation/AVR material reference; scale the remaining7049kg by these normalized fractions. The1kg AVR partition is an engineering allocation,not manufacturer traceability. Electricalsteel uses the existing3.2%Si reference;other/forgedsteel generic lowalloy feed,insulation glassfibre,impregnation epoxy,paint alkyd are stated material proxies. Existing electricalsteel rolling stays in its supplier;do not add a second generic metalworking energy package. EPD manufacturing40122kWh electricity and9659kWh heat per26237kg provide an aggregate factory-energy reference perkg,not operating losses. Potential factory/service overlap,forging details,lamination yield and actual coating remain gaps. AVR reference1kg contains0.05m2 unmountedPWB at assumed3.08kg/m2,6glassdiodes at0.596g,50gchoke,30gfilmcapacitor,10gmetalfilmresistors,5gSMTtransistors,100gCu,400gAl,100gepoxy andremainingsteel. This is an explicit analog material budget,not validated excitation circuit or a universal zeroTa/PM claim. Wound-field generator excitation is represented by the winding material budget;no unsupported full-machine permanent magnets. Full7050kg generator goes once toWEEE;AVR has no extra disposal. Native WEEE treatment is a proxy,not recoveryshare analysis. Gross-minus-net680kg shipping-package composition unresolved and excluded from installed mass;do not assign it invented metals. Rewire six passenger-train perMJ copies and provenance with unchanged lifetime-energy denominator;source generator kg increases7050/4410. Traction converter,motor,engine,tank,chassis and track unchanged. Only existing rail/final-energy workbooks;no runtime or native edits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1145" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1145" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1145" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1145" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1145" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1145" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>rail powertrain generator, synchronous engineering reference</t>
+        </is>
+      </c>
+      <c r="B1146">
+        <v>1</v>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1146" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1146" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1146" t="inlineStr">
+        <is>
+          <t>rail powertrain generator, synchronous engineering reference</t>
+        </is>
+      </c>
+      <c r="I1146" t="inlineStr">
+        <is>
+          <t>rail powertrain generator, synchronous engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>non-oriented electrical steel, engineering alloy reference</t>
+        </is>
+      </c>
+      <c r="B1147">
+        <v>0.2713339966810987</v>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1147" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1147" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1147" t="inlineStr">
+        <is>
+          <t>non-oriented electrical steel, engineering alloy reference</t>
+        </is>
+      </c>
+      <c r="I1147" t="inlineStr">
+        <is>
+          <t>non-oriented electrical steel, engineering alloy reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B1148">
+        <v>0.6182375601344753</v>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1148" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1148" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1148" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I1148" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B1149">
+        <v>0.0004954131961873992</v>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1149" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1149" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1149" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I1149" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B1150">
+        <v>0.09378552890901458</v>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1150" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1150" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1150" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I1150" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>market for glass fibre</t>
+        </is>
+      </c>
+      <c r="B1151">
+        <v>0.00590684964684976</v>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1151" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1151" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1151" t="inlineStr">
+        <is>
+          <t>glass fibre</t>
+        </is>
+      </c>
+      <c r="I1151" t="inlineStr">
+        <is>
+          <t>glass fibre</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>market for epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="B1152">
+        <v>0.00857445916478191</v>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1152" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1152" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1152" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="I1152" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>market for alkyd paint, white, without solvent, in 60% solution state</t>
+        </is>
+      </c>
+      <c r="B1153">
+        <v>0.0015243482959612284</v>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1153" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1153" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1153" t="inlineStr">
+        <is>
+          <t>alkyd paint, white, without solvent, in 60% solution state</t>
+        </is>
+      </c>
+      <c r="I1153" t="inlineStr">
+        <is>
+          <t>alkyd paint, white, without solvent, in 60% solution state</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>rail generator analog excitation controller, engineering material reference</t>
+        </is>
+      </c>
+      <c r="B1154">
+        <v>0.00014184397163120567</v>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1154" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1154" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1154" t="inlineStr">
+        <is>
+          <t>rail generator analog excitation controller, engineering material reference</t>
+        </is>
+      </c>
+      <c r="I1154" t="inlineStr">
+        <is>
+          <t>rail generator analog excitation controller, engineering material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1155">
+        <v>1.529214468117544</v>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1155" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1155" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1155" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I1155" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B1156">
+        <v>1.3253192057018715</v>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1156" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F1156" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1156" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I1156" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>market for waste electric and electronic equipment</t>
+        </is>
+      </c>
+      <c r="B1157">
+        <v>-1</v>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1157" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1157" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1157" t="inlineStr">
+        <is>
+          <t>waste electric and electronic equipment</t>
+        </is>
+      </c>
+      <c r="I1157" t="inlineStr">
+        <is>
+          <t>waste electric and electronic equipment</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H983" ns2:uid="{2A08E695-FC79-4DF0-ACCB-3B3F78317B74}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/premise/data/additional_inventories/lci-rail-freight.xlsx
+++ b/premise/data/additional_inventories/lci-rail-freight.xlsx
@@ -18184,8 +18184,12 @@
       <c r="A901" t="s">
         <v>10</v>
       </c>
-      <c r="B901" t="s">
-        <v>234</v>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>APPROVED RAIL ENGINE ALUMINIUM IDENTITY, issue105,2026-10-18. Wolff et al.2020, DOI10.3390/su12135396, original supplementary Production/Components/Engine.xlsx and Diesel Tank.xlsx. https://mdpi-res.com/d_attachment/sustainability/sustainability-12-05396/article_deploy/sustainability-12-05396-s001.zip . Source Engine.xlsx Sheet1 B8=171kg aluminium/B3=1140kg engine=.15kg/kg. Apply alreadyapproved truck correction ad6bb596 to this separately active rail copy. Replace unsupported specialtyAlLi by ordinary cast-alloy market at unchanged.15kg/kg;castalloy is an engineering material-class proxy,not sourcecertifiedAlSi grade or proofallpartsarecast. Native AlLi includes unsupported lithium/silver supply. Preserve engine mass9593.181818181818kg/locomotive,all buyer/perMJ coefficients,other ingredients,services andenergy. Source oldplastic.45kg/kg remains separate issue106;this identity correction alone does not close the1.405kg/kg material sum. Keep alloy uncertainty,purity,yields andfuturedesign gaps explicit;no elementarycomposition,primary/secondaryshare orrecoverycredit assumed. Existing workbookonly,no runtime/native edits.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Wolff et al. 2020, Sustainability, DOI: 10.3390/su12135396</t>
+        </is>
       </c>
     </row>
     <row r="902" spans="1:8" ns3:dyDescent="0.2">
@@ -18223,7 +18227,11 @@
       <c r="G904" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H904" s="2"/>
+      <c r="H904" s="2" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
     </row>
     <row r="905" spans="1:8" ns3:dyDescent="0.2">
       <c r="A905" t="s">
@@ -18247,6 +18255,11 @@
       <c r="G905" t="s">
         <v>237</v>
       </c>
+      <c r="H905" t="inlineStr">
+        <is>
+          <t>APPROVED RAIL ENGINE ALUMINIUM IDENTITY, issue105,2026-10-18. Wolff et al.2020, DOI10.3390/su12135396, original supplementary Production/Components/Engine.xlsx and Diesel Tank.xlsx. https://mdpi-res.com/d_attachment/sustainability/sustainability-12-05396/article_deploy/sustainability-12-05396-s001.zip . Source Engine.xlsx Sheet1 B8=171kg aluminium/B3=1140kg engine=.15kg/kg. Apply alreadyapproved truck correction ad6bb596 to this separately active rail copy. Replace unsupported specialtyAlLi by ordinary cast-alloy market at unchanged.15kg/kg;castalloy is an engineering material-class proxy,not sourcecertifiedAlSi grade or proofallpartsarecast. Native AlLi includes unsupported lithium/silver supply. Preserve engine mass9593.181818181818kg/locomotive,all buyer/perMJ coefficients,other ingredients,services andenergy. Source oldplastic.45kg/kg remains separate issue106;this identity correction alone does not close the1.405kg/kg material sum. Keep alloy uncertainty,purity,yields andfuturedesign gaps explicit;no elementarycomposition,primary/secondaryshare orrecoverycredit assumed. Existing workbookonly,no runtime/native edits.</t>
+        </is>
+      </c>
     </row>
     <row r="906" spans="1:8" ns3:dyDescent="0.2">
       <c r="A906" t="s">
@@ -18557,14 +18570,18 @@
       </c>
     </row>
     <row r="922" spans="1:7" ns3:dyDescent="0.2">
-      <c r="A922" t="s">
-        <v>260</v>
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>market for aluminium, cast alloy</t>
+        </is>
       </c>
       <c r="B922">
         <v>0.15</v>
       </c>
-      <c r="C922" t="s">
-        <v>3</v>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="D922" t="s">
         <v>24</v>
@@ -18575,8 +18592,15 @@
       <c r="F922" t="s">
         <v>20</v>
       </c>
-      <c r="G922" t="s">
-        <v>261</v>
+      <c r="G922" t="inlineStr">
+        <is>
+          <t>aluminium, cast alloy</t>
+        </is>
+      </c>
+      <c r="H922" t="inlineStr">
+        <is>
+          <t>APPROVED RAIL ENGINE ALUMINIUM IDENTITY, issue105,2026-10-18. Wolff et al.2020, DOI10.3390/su12135396, original supplementary Production/Components/Engine.xlsx and Diesel Tank.xlsx. https://mdpi-res.com/d_attachment/sustainability/sustainability-12-05396/article_deploy/sustainability-12-05396-s001.zip . Source Engine.xlsx Sheet1 B8=171kg aluminium/B3=1140kg engine=.15kg/kg. Apply alreadyapproved truck correction ad6bb596 to this separately active rail copy. Replace unsupported specialtyAlLi by ordinary cast-alloy market at unchanged.15kg/kg;castalloy is an engineering material-class proxy,not sourcecertifiedAlSi grade or proofallpartsarecast. Native AlLi includes unsupported lithium/silver supply. Preserve engine mass9593.181818181818kg/locomotive,all buyer/perMJ coefficients,other ingredients,services andenergy. Source oldplastic.45kg/kg remains separate issue106;this identity correction alone does not close the1.405kg/kg material sum. Keep alloy uncertainty,purity,yields andfuturedesign gaps explicit;no elementarycomposition,primary/secondaryshare orrecoverycredit assumed. Existing workbookonly,no runtime/native edits.</t>
+        </is>
       </c>
     </row>
     <row r="923" spans="1:7" ns3:dyDescent="0.2">

--- a/premise/data/additional_inventories/lci-rail-freight.xlsx
+++ b/premise/data/additional_inventories/lci-rail-freight.xlsx
@@ -18186,7 +18186,9 @@
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>APPROVED RAIL ENGINE ALUMINIUM IDENTITY, issue105,2026-10-18. Wolff et al.2020, DOI10.3390/su12135396, original supplementary Production/Components/Engine.xlsx and Diesel Tank.xlsx. https://mdpi-res.com/d_attachment/sustainability/sustainability-12-05396/article_deploy/sustainability-12-05396-s001.zip . Source Engine.xlsx Sheet1 B8=171kg aluminium/B3=1140kg engine=.15kg/kg. Apply alreadyapproved truck correction ad6bb596 to this separately active rail copy. Replace unsupported specialtyAlLi by ordinary cast-alloy market at unchanged.15kg/kg;castalloy is an engineering material-class proxy,not sourcecertifiedAlSi grade or proofallpartsarecast. Native AlLi includes unsupported lithium/silver supply. Preserve engine mass9593.181818181818kg/locomotive,all buyer/perMJ coefficients,other ingredients,services andenergy. Source oldplastic.45kg/kg remains separate issue106;this identity correction alone does not close the1.405kg/kg material sum. Keep alloy uncertainty,purity,yields andfuturedesign gaps explicit;no elementarycomposition,primary/secondaryshare orrecoverycredit assumed. Existing workbookonly,no runtime/native edits.
+          <t>APPROVED RAIL ENGINE PLASTIC SOURCE DOSE, issue106,2026-10-18. Wolff et al.2020, DOI10.3390/su12135396, original supplementary Production/Components/Engine.xlsx and Diesel Tank.xlsx. https://mdpi-res.com/d_attachment/sustainability/sustainability-12-05396/article_deploy/sustainability-12-05396-s001.zip . Engine.xlsx B9/B3=51.3/1140=.045kg plastic/kg engine;separate railcopy retained.45kg/kg after truckcopy wasfixed in38b99e4d. Correctonlythisdose to.045kg/kg. Currentmaterialsum1.405 becomes1kg/kg exactly with its retained decimal coefficients. Keep previouslyapproved ordinarycastAl.15kg/kg;othermetal/rubberfeeds unchanged. Sourceplastic isgeneric;retainedphenolicresin is an unverified chemistryproxy,not sourcedphenolic grade. Preserve manufacturingenergy/services,9593.181818181818kg installedengine reference andalllifetimes/perMJ buyers. This doesnotvalidate rail-specificengineefficiency,mass,power/life ormanufacturing/emissionyield;no artificialrenormalizationofothermaterials,recoverycredit orprimary/secondaryshares. Supersedesissue105 pendingplasticwarning. Existingworkbookonly.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED RAIL ENGINE ALUMINIUM IDENTITY, issue105,2026-10-18. Wolff et al.2020, DOI10.3390/su12135396, original supplementary Production/Components/Engine.xlsx and Diesel Tank.xlsx. https://mdpi-res.com/d_attachment/sustainability/sustainability-12-05396/article_deploy/sustainability-12-05396-s001.zip . Source Engine.xlsx Sheet1 B8=171kg aluminium/B3=1140kg engine=.15kg/kg. Apply alreadyapproved truck correction ad6bb596 to this separately active rail copy. Replace unsupported specialtyAlLi by ordinary cast-alloy market at unchanged.15kg/kg;castalloy is an engineering material-class proxy,not sourcecertifiedAlSi grade or proofallpartsarecast. Native AlLi includes unsupported lithium/silver supply. Preserve engine mass9593.181818181818kg/locomotive,all buyer/perMJ coefficients,other ingredients,services andenergy. Source oldplastic.45kg/kg remains separate issue106;this identity correction alone does not close the1.405kg/kg material sum. Keep alloy uncertainty,purity,yields andfuturedesign gaps explicit;no elementarycomposition,primary/secondaryshare orrecoverycredit assumed. Existing workbookonly,no runtime/native edits.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 Wolff et al. 2020, Sustainability, DOI: 10.3390/su12135396</t>
         </is>
@@ -18257,7 +18259,7 @@
       </c>
       <c r="H905" t="inlineStr">
         <is>
-          <t>APPROVED RAIL ENGINE ALUMINIUM IDENTITY, issue105,2026-10-18. Wolff et al.2020, DOI10.3390/su12135396, original supplementary Production/Components/Engine.xlsx and Diesel Tank.xlsx. https://mdpi-res.com/d_attachment/sustainability/sustainability-12-05396/article_deploy/sustainability-12-05396-s001.zip . Source Engine.xlsx Sheet1 B8=171kg aluminium/B3=1140kg engine=.15kg/kg. Apply alreadyapproved truck correction ad6bb596 to this separately active rail copy. Replace unsupported specialtyAlLi by ordinary cast-alloy market at unchanged.15kg/kg;castalloy is an engineering material-class proxy,not sourcecertifiedAlSi grade or proofallpartsarecast. Native AlLi includes unsupported lithium/silver supply. Preserve engine mass9593.181818181818kg/locomotive,all buyer/perMJ coefficients,other ingredients,services andenergy. Source oldplastic.45kg/kg remains separate issue106;this identity correction alone does not close the1.405kg/kg material sum. Keep alloy uncertainty,purity,yields andfuturedesign gaps explicit;no elementarycomposition,primary/secondaryshare orrecoverycredit assumed. Existing workbookonly,no runtime/native edits.</t>
+          <t>APPROVED RAIL ENGINE PLASTIC SOURCE DOSE, issue106,2026-10-18. Wolff et al.2020, DOI10.3390/su12135396, original supplementary Production/Components/Engine.xlsx and Diesel Tank.xlsx. https://mdpi-res.com/d_attachment/sustainability/sustainability-12-05396/article_deploy/sustainability-12-05396-s001.zip . Engine.xlsx B9/B3=51.3/1140=.045kg plastic/kg engine;separate railcopy retained.45kg/kg after truckcopy wasfixed in38b99e4d. Correctonlythisdose to.045kg/kg. Currentmaterialsum1.405 becomes1kg/kg exactly with its retained decimal coefficients. Keep previouslyapproved ordinarycastAl.15kg/kg;othermetal/rubberfeeds unchanged. Sourceplastic isgeneric;retainedphenolicresin is an unverified chemistryproxy,not sourcedphenolic grade. Preserve manufacturingenergy/services,9593.181818181818kg installedengine reference andalllifetimes/perMJ buyers. This doesnotvalidate rail-specificengineefficiency,mass,power/life ormanufacturing/emissionyield;no artificialrenormalizationofothermaterials,recoverycredit orprimary/secondaryshares. Supersedesissue105 pendingplasticwarning. Existingworkbookonly.</t>
         </is>
       </c>
     </row>
@@ -18688,7 +18690,7 @@
         <v>264</v>
       </c>
       <c r="B927">
-        <v>0.45</v>
+        <v>0.045</v>
       </c>
       <c r="C927" t="s">
         <v>23</v>
@@ -18704,6 +18706,11 @@
       </c>
       <c r="G927" t="s">
         <v>265</v>
+      </c>
+      <c r="H927" t="inlineStr">
+        <is>
+          <t>APPROVED RAIL ENGINE PLASTIC SOURCE DOSE, issue106,2026-10-18. Wolff et al.2020, DOI10.3390/su12135396, original supplementary Production/Components/Engine.xlsx and Diesel Tank.xlsx. https://mdpi-res.com/d_attachment/sustainability/sustainability-12-05396/article_deploy/sustainability-12-05396-s001.zip . Engine.xlsx B9/B3=51.3/1140=.045kg plastic/kg engine;separate railcopy retained.45kg/kg after truckcopy wasfixed in38b99e4d. Correctonlythisdose to.045kg/kg. Currentmaterialsum1.405 becomes1kg/kg exactly with its retained decimal coefficients. Keep previouslyapproved ordinarycastAl.15kg/kg;othermetal/rubberfeeds unchanged. Sourceplastic isgeneric;retainedphenolicresin is an unverified chemistryproxy,not sourcedphenolic grade. Preserve manufacturingenergy/services,9593.181818181818kg installedengine reference andalllifetimes/perMJ buyers. This doesnotvalidate rail-specificengineefficiency,mass,power/life ormanufacturing/emissionyield;no artificialrenormalizationofothermaterials,recoverycredit orprimary/secondaryshares. Supersedesissue105 pendingplasticwarning. Existingworkbookonly.</t>
+        </is>
       </c>
     </row>
     <row r="929" spans="1:8" ht="16" ns3:dyDescent="0.2">

--- a/premise/data/additional_inventories/lci-rail-freight.xlsx
+++ b/premise/data/additional_inventories/lci-rail-freight.xlsx
@@ -18765,8 +18765,12 @@
       <c r="A935" t="s">
         <v>10</v>
       </c>
-      <c r="B935" t="s">
-        <v>234</v>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>APPROVED RAIL DIESEL TANK ALUMINIUM IDENTITY, issue107,2026-10-18. Wolff et al.2020, DOI10.3390/su12135396, original supplementary Production/Components/Engine.xlsx and Diesel Tank.xlsx. https://mdpi-res.com/d_attachment/sustainability/sustainability-12-05396/article_deploy/sustainability-12-05396-s001.zip . Source specifiesemptyaluminiumtank withnospecialtyAlLi grade. Reuse approvedtrucktank ordinarywroughtalloyreference at1kg/kg finishedtank; no inventedlithium/silveralloyrequirement. Wroughtmarketmix is a formingcompatibleproxy,notverifiedexacttankalloy/retainedelementalcomposition. Keep91.16651797151124kg adoptedrail tankreference,source5000litre sizinganalogy,othermanufacturingenergy/servicesandallperMJ/lifetimeallocation. Welding5m/kg remainsseparateissue108. Do notinfernewmetalyield,EOLcredit orprimary/secondaryshare. No runtime/native changes;existingrailworkbookonly.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Wolff et al. 2020, Sustainability, DOI: 10.3390/su12135396</t>
+        </is>
       </c>
     </row>
     <row r="936" spans="1:8" ns3:dyDescent="0.2">
@@ -18804,7 +18808,11 @@
       <c r="G938" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H938" s="2"/>
+      <c r="H938" s="2" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
     </row>
     <row r="939" spans="1:8" ns3:dyDescent="0.2">
       <c r="A939" t="s">
@@ -18828,6 +18836,11 @@
       <c r="G939" t="s">
         <v>238</v>
       </c>
+      <c r="H939" t="inlineStr">
+        <is>
+          <t>APPROVED RAIL DIESEL TANK ALUMINIUM IDENTITY, issue107,2026-10-18. Wolff et al.2020, DOI10.3390/su12135396, original supplementary Production/Components/Engine.xlsx and Diesel Tank.xlsx. https://mdpi-res.com/d_attachment/sustainability/sustainability-12-05396/article_deploy/sustainability-12-05396-s001.zip . Source specifiesemptyaluminiumtank withnospecialtyAlLi grade. Reuse approvedtrucktank ordinarywroughtalloyreference at1kg/kg finishedtank; no inventedlithium/silveralloyrequirement. Wroughtmarketmix is a formingcompatibleproxy,notverifiedexacttankalloy/retainedelementalcomposition. Keep91.16651797151124kg adoptedrail tankreference,source5000litre sizinganalogy,othermanufacturingenergy/servicesandallperMJ/lifetimeallocation. Welding5m/kg remainsseparateissue108. Do notinfernewmetalyield,EOLcredit orprimary/secondaryshare. No runtime/native changes;existingrailworkbookonly.</t>
+        </is>
+      </c>
     </row>
     <row r="940" spans="1:8" ns3:dyDescent="0.2">
       <c r="A940" t="s">
@@ -18876,14 +18889,18 @@
       </c>
     </row>
     <row r="942" spans="1:8" ns3:dyDescent="0.2">
-      <c r="A942" t="s">
-        <v>260</v>
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
       </c>
       <c r="B942">
         <v>1</v>
       </c>
-      <c r="C942" t="s">
-        <v>3</v>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="D942" t="s">
         <v>24</v>
@@ -18894,8 +18911,15 @@
       <c r="F942" t="s">
         <v>20</v>
       </c>
-      <c r="G942" t="s">
-        <v>261</v>
+      <c r="G942" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="H942" t="inlineStr">
+        <is>
+          <t>APPROVED RAIL DIESEL TANK ALUMINIUM IDENTITY, issue107,2026-10-18. Wolff et al.2020, DOI10.3390/su12135396, original supplementary Production/Components/Engine.xlsx and Diesel Tank.xlsx. https://mdpi-res.com/d_attachment/sustainability/sustainability-12-05396/article_deploy/sustainability-12-05396-s001.zip . Source specifiesemptyaluminiumtank withnospecialtyAlLi grade. Reuse approvedtrucktank ordinarywroughtalloyreference at1kg/kg finishedtank; no inventedlithium/silveralloyrequirement. Wroughtmarketmix is a formingcompatibleproxy,notverifiedexacttankalloy/retainedelementalcomposition. Keep91.16651797151124kg adoptedrail tankreference,source5000litre sizinganalogy,othermanufacturingenergy/servicesandallperMJ/lifetimeallocation. Welding5m/kg remainsseparateissue108. Do notinfernewmetalyield,EOLcredit orprimary/secondaryshare. No runtime/native changes;existingrailworkbookonly.</t>
+        </is>
       </c>
     </row>
     <row r="943" spans="1:8" ns3:dyDescent="0.2">

--- a/premise/data/additional_inventories/lci-rail-freight.xlsx
+++ b/premise/data/additional_inventories/lci-rail-freight.xlsx
@@ -18767,7 +18767,9 @@
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t>APPROVED RAIL DIESEL TANK ALUMINIUM IDENTITY, issue107,2026-10-18. Wolff et al.2020, DOI10.3390/su12135396, original supplementary Production/Components/Engine.xlsx and Diesel Tank.xlsx. https://mdpi-res.com/d_attachment/sustainability/sustainability-12-05396/article_deploy/sustainability-12-05396-s001.zip . Source specifiesemptyaluminiumtank withnospecialtyAlLi grade. Reuse approvedtrucktank ordinarywroughtalloyreference at1kg/kg finishedtank; no inventedlithium/silveralloyrequirement. Wroughtmarketmix is a formingcompatibleproxy,notverifiedexacttankalloy/retainedelementalcomposition. Keep91.16651797151124kg adoptedrail tankreference,source5000litre sizinganalogy,othermanufacturingenergy/servicesandallperMJ/lifetimeallocation. Welding5m/kg remainsseparateissue108. Do notinfernewmetalyield,EOLcredit orprimary/secondaryshare. No runtime/native changes;existingrailworkbookonly.
+          <t>APPROVED RAIL TANK WELDING NORMALIZATION, issue108,2026-10-18. Wolff et al.2020, DOI10.3390/su12135396, original supplementary Production/Components/Engine.xlsx and Diesel Tank.xlsx. https://mdpi-res.com/d_attachment/sustainability/sustainability-12-05396/article_deploy/sustainability-12-05396-s001.zip . DieselTank.xlsx Sheet1 B6=51.7kg drytwo-tankassembly,B11=5m arcwelding perassembly. Railcopy produces1kg drytank butretained5m/kg. Correctto5/51.7=0.09671179883945841m/kg,matchingapprovedtruckcopy778aa04d. This restores thehistoricalroad-tank manufacturinganalogy; it isnot a measuredseamdesign forthe adopted5000litre locomotive tank. Weldingdistanceexpertinterviewandlinearperkgtransferremainuncertain. Keep91.16651797151124kg railtank,supplierunit/location,ordinarywroughtAl feed,metalworking,electricity andalllifetime/perMJ doses unchanged. Source-batch5m backcalculatesat51.7kg;nominalrailtank nowuses8.816877946954666m ratherthan455.8325898575562m. Otherenergy/mass/prospectivegradeassumptions remainseparate. No native/runtime changes;existingworkbookonly.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED RAIL DIESEL TANK ALUMINIUM IDENTITY, issue107,2026-10-18. Wolff et al.2020, DOI10.3390/su12135396, original supplementary Production/Components/Engine.xlsx and Diesel Tank.xlsx. https://mdpi-res.com/d_attachment/sustainability/sustainability-12-05396/article_deploy/sustainability-12-05396-s001.zip . Source specifiesemptyaluminiumtank withnospecialtyAlLi grade. Reuse approvedtrucktank ordinarywroughtalloyreference at1kg/kg finishedtank; no inventedlithium/silveralloyrequirement. Wroughtmarketmix is a formingcompatibleproxy,notverifiedexacttankalloy/retainedelementalcomposition. Keep91.16651797151124kg adoptedrail tankreference,source5000litre sizinganalogy,othermanufacturingenergy/servicesandallperMJ/lifetimeallocation. Welding5m/kg remainsseparateissue108. Do notinfernewmetalyield,EOLcredit orprimary/secondaryshare. No runtime/native changes;existingrailworkbookonly.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 Wolff et al. 2020, Sustainability, DOI: 10.3390/su12135396</t>
         </is>
@@ -18838,7 +18840,7 @@
       </c>
       <c r="H939" t="inlineStr">
         <is>
-          <t>APPROVED RAIL DIESEL TANK ALUMINIUM IDENTITY, issue107,2026-10-18. Wolff et al.2020, DOI10.3390/su12135396, original supplementary Production/Components/Engine.xlsx and Diesel Tank.xlsx. https://mdpi-res.com/d_attachment/sustainability/sustainability-12-05396/article_deploy/sustainability-12-05396-s001.zip . Source specifiesemptyaluminiumtank withnospecialtyAlLi grade. Reuse approvedtrucktank ordinarywroughtalloyreference at1kg/kg finishedtank; no inventedlithium/silveralloyrequirement. Wroughtmarketmix is a formingcompatibleproxy,notverifiedexacttankalloy/retainedelementalcomposition. Keep91.16651797151124kg adoptedrail tankreference,source5000litre sizinganalogy,othermanufacturingenergy/servicesandallperMJ/lifetimeallocation. Welding5m/kg remainsseparateissue108. Do notinfernewmetalyield,EOLcredit orprimary/secondaryshare. No runtime/native changes;existingrailworkbookonly.</t>
+          <t>APPROVED RAIL TANK WELDING NORMALIZATION, issue108,2026-10-18. Wolff et al.2020, DOI10.3390/su12135396, original supplementary Production/Components/Engine.xlsx and Diesel Tank.xlsx. https://mdpi-res.com/d_attachment/sustainability/sustainability-12-05396/article_deploy/sustainability-12-05396-s001.zip . DieselTank.xlsx Sheet1 B6=51.7kg drytwo-tankassembly,B11=5m arcwelding perassembly. Railcopy produces1kg drytank butretained5m/kg. Correctto5/51.7=0.09671179883945841m/kg,matchingapprovedtruckcopy778aa04d. This restores thehistoricalroad-tank manufacturinganalogy; it isnot a measuredseamdesign forthe adopted5000litre locomotive tank. Weldingdistanceexpertinterviewandlinearperkgtransferremainuncertain. Keep91.16651797151124kg railtank,supplierunit/location,ordinarywroughtAl feed,metalworking,electricity andalllifetime/perMJ doses unchanged. Source-batch5m backcalculatesat51.7kg;nominalrailtank nowuses8.816877946954666m ratherthan455.8325898575562m. Otherenergy/mass/prospectivegradeassumptions remainseparate. No native/runtime changes;existingworkbookonly.</t>
         </is>
       </c>
     </row>
@@ -18927,7 +18929,7 @@
         <v>268</v>
       </c>
       <c r="B943">
-        <v>5</v>
+        <v>0.09671179883945841</v>
       </c>
       <c r="C943" t="s">
         <v>23</v>
@@ -18943,6 +18945,11 @@
       </c>
       <c r="G943" t="s">
         <v>268</v>
+      </c>
+      <c r="H943" t="inlineStr">
+        <is>
+          <t>APPROVED RAIL TANK WELDING NORMALIZATION, issue108,2026-10-18. Wolff et al.2020, DOI10.3390/su12135396, original supplementary Production/Components/Engine.xlsx and Diesel Tank.xlsx. https://mdpi-res.com/d_attachment/sustainability/sustainability-12-05396/article_deploy/sustainability-12-05396-s001.zip . DieselTank.xlsx Sheet1 B6=51.7kg drytwo-tankassembly,B11=5m arcwelding perassembly. Railcopy produces1kg drytank butretained5m/kg. Correctto5/51.7=0.09671179883945841m/kg,matchingapprovedtruckcopy778aa04d. This restores thehistoricalroad-tank manufacturinganalogy; it isnot a measuredseamdesign forthe adopted5000litre locomotive tank. Weldingdistanceexpertinterviewandlinearperkgtransferremainuncertain. Keep91.16651797151124kg railtank,supplierunit/location,ordinarywroughtAl feed,metalworking,electricity andalllifetime/perMJ doses unchanged. Source-batch5m backcalculatesat51.7kg;nominalrailtank nowuses8.816877946954666m ratherthan455.8325898575562m. Otherenergy/mass/prospectivegradeassumptions remainseparate. No native/runtime changes;existingworkbookonly.</t>
+        </is>
       </c>
     </row>
     <row r="944">

--- a/premise/data/additional_inventories/lci-rail-freight.xlsx
+++ b/premise/data/additional_inventories/lci-rail-freight.xlsx
@@ -1428,7 +1428,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">APPROVED RAIL GENERATOR FUNCTION AND RATING, issue104,2026-10-18. ABB NMG catalogue9AKK2017109096:page10 continuous60Hz40C,pf0.8,NMG0500DD04 DAPI 3590kVA/2872kW at460V;page17 net7050kg,gross7730kg. OldNMG0450DD04 at460V60Hz is2072kW,not2.8MW. https://search.abb.com/library/Download.aspx?DocumentID=9AKK2017109096&amp;LanguageCode=en&amp;DocumentPartId=&amp;Action=Launch . Material analogue:ABB AMG0900 5125kVA11kV EPD2000 pages2-3,https://library.e.abb.com/public/2bb39d909d618031c1256d63003c5c76/EPD%20for%20AMG%20900.pdf . Use kg/product column; kg/kVA column is visibly misaligned. Existing locomotive buys4410kg of unspecified passive electronics as a generator proxy; native mixture assigns153.468kg tantalum-capacitor packages,NOT elementalTa. Replace with7050kg of a dedicated synchronous powertrain-generator engineering reference. Selected industrial model rated2872kW is sufficient for the stated2800kW duty at460V/60Hz/pf0.8. This is not a rail-qualified UKlight generator or proof of compatible BORDLINE DC-link voltage:actual rail speed/voltage,rectification,EMC,cooling and mass require project-specific verification. Source mass is not scaled linearly fromkVA. Keep original40year generator allocation as a service assumption; EPD25year operation is not transferred as measured rail life. Test mass4410/7050/9000kg and20-40year service; keep operating diesel demand unchanged. Material composition is transferred PERkg from the much heavier,11kV medium-speed AMG0900,not claimed a published NMG BOM:kg/product={'electricalsteel': 7120.0, 'steel': 10900.0, 'forgedsteel': 5323.0, 'Al': 13.0, 'Cu': 2461.0, 'insulation': 155.0, 'resin': 225.0, 'paint': 40.0},installed total26237kg excluding800kg wood. Reserve1kg of the7050kg budget for an explicit analog excitation/AVR material reference; scale the remaining7049kg by these normalized fractions. The1kg AVR partition is an engineering allocation,not manufacturer traceability. Electricalsteel uses the existing3.2%Si reference;other/forgedsteel generic lowalloy feed,insulation glassfibre,impregnation epoxy,paint alkyd are stated material proxies. Existing electricalsteel rolling stays in its supplier;do not add a second generic metalworking energy package. EPD manufacturing40122kWh electricity and9659kWh heat per26237kg provide an aggregate factory-energy reference perkg,not operating losses. Potential factory/service overlap,forging details,lamination yield and actual coating remain gaps. AVR reference1kg contains0.05m2 unmountedPWB at assumed3.08kg/m2,6glassdiodes at0.596g,50gchoke,30gfilmcapacitor,10gmetalfilmresistors,5gSMTtransistors,100gCu,400gAl,100gepoxy andremainingsteel. This is an explicit analog material budget,not validated excitation circuit or a universal zeroTa/PM claim. Wound-field generator excitation is represented by the winding material budget;no unsupported full-machine permanent magnets. Full7050kg generator goes once toWEEE;AVR has no extra disposal. Native WEEE treatment is a proxy,not recoveryshare analysis. Gross-minus-net680kg shipping-package composition unresolved and excluded from installed mass;do not assign it invented metals. Rewire six passenger-train perMJ copies and provenance with unchanged lifetime-energy denominator;source generator kg increases7050/4410. Traction converter,motor,engine,tank,chassis and track unchanged. Only existing rail/final-energy workbooks;no runtime or native edits.
+          <t xml:space="preserve">APPROVED RAIL ENGINE MASS REFERENCE, issue 114, 2026-10-19. Caterpillar LEHR0024-01 (12-19), C175-16 Locomotive Engine, EU Stage V, page 1: 3000 bkW at 1800 rpm; engine including flywheel approximately 12500 kg net dry, aftertreatment 1000 kg and dosing cabinet 115 kg separately. Manufacturer-authored sheet indexed at https://www.zeppelin.com/content/dam/zeppelin/power-systems/produkte/motoren/lok-motoren/LEHR0024-01_C175_RAIL_EU_V.pdf ; direct retrieval returned 404 on 2026-10-19, indexed specification preserved in the audit source record.
+Replace the unsupported truck extrapolation 9593.181818181818 kg = 2800/352*1206 by one 12500 kg dry locomotive engine reference. The selected published 3000 kW rail engine covers the retained 2800 kW duty; do not multiply its mass by 2800/3000. This is a documented engineering reference from a later rail configuration, not a measured mass of the original UKLight engine. In particular, neither the standalone Wolff 1140 kg engine BOM nor its truck assembly including exhaust can simply replace 1206 kg at an assumed common 352 kW reference.
+Keep the corrected per-kg truck engine composition as an explicit material analogue, not a rail manufacturer BOM. Actual large-engine alloy grades, electronic controls, machining yields, cooling and exhaust hardware remain coverage uncertainties. Net dry mass excludes fuel, lubricant and coolant; retain existing operating fuel consumption and generator, converter, motor and tank inventories. Separate Stage V aftertreatment/dosing equipment is not silently added to this older duty reference; the equipment/emissions-generation match remains a stated gap. Retain the existing one engine over 40 years convention as an engineering allocation; overhaul/replacement needs source data (sensitivity 1-2 complete engines and 10-15 tonnes dry mass).
+Update the six stored passenger-train per-MJ copies and their source records by the same mass ratio, preserving purchased energy and source-service denominators. No chassis, track, native database, runtime or primary/secondary-share changes.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED RAIL GENERATOR FUNCTION AND RATING, issue104,2026-10-18. ABB NMG catalogue9AKK2017109096:page10 continuous60Hz40C,pf0.8,NMG0500DD04 DAPI 3590kVA/2872kW at460V;page17 net7050kg,gross7730kg. OldNMG0450DD04 at460V60Hz is2072kW,not2.8MW. https://search.abb.com/library/Download.aspx?DocumentID=9AKK2017109096&amp;LanguageCode=en&amp;DocumentPartId=&amp;Action=Launch . Material analogue:ABB AMG0900 5125kVA11kV EPD2000 pages2-3,https://library.e.abb.com/public/2bb39d909d618031c1256d63003c5c76/EPD%20for%20AMG%20900.pdf . Use kg/product column; kg/kVA column is visibly misaligned. Existing locomotive buys4410kg of unspecified passive electronics as a generator proxy; native mixture assigns153.468kg tantalum-capacitor packages,NOT elementalTa. Replace with7050kg of a dedicated synchronous powertrain-generator engineering reference. Selected industrial model rated2872kW is sufficient for the stated2800kW duty at460V/60Hz/pf0.8. This is not a rail-qualified UKlight generator or proof of compatible BORDLINE DC-link voltage:actual rail speed/voltage,rectification,EMC,cooling and mass require project-specific verification. Source mass is not scaled linearly fromkVA. Keep original40year generator allocation as a service assumption; EPD25year operation is not transferred as measured rail life. Test mass4410/7050/9000kg and20-40year service; keep operating diesel demand unchanged. Material composition is transferred PERkg from the much heavier,11kV medium-speed AMG0900,not claimed a published NMG BOM:kg/product={'electricalsteel': 7120.0, 'steel': 10900.0, 'forgedsteel': 5323.0, 'Al': 13.0, 'Cu': 2461.0, 'insulation': 155.0, 'resin': 225.0, 'paint': 40.0},installed total26237kg excluding800kg wood. Reserve1kg of the7050kg budget for an explicit analog excitation/AVR material reference; scale the remaining7049kg by these normalized fractions. The1kg AVR partition is an engineering allocation,not manufacturer traceability. Electricalsteel uses the existing3.2%Si reference;other/forgedsteel generic lowalloy feed,insulation glassfibre,impregnation epoxy,paint alkyd are stated material proxies. Existing electricalsteel rolling stays in its supplier;do not add a second generic metalworking energy package. EPD manufacturing40122kWh electricity and9659kWh heat per26237kg provide an aggregate factory-energy reference perkg,not operating losses. Potential factory/service overlap,forging details,lamination yield and actual coating remain gaps. AVR reference1kg contains0.05m2 unmountedPWB at assumed3.08kg/m2,6glassdiodes at0.596g,50gchoke,30gfilmcapacitor,10gmetalfilmresistors,5gSMTtransistors,100gCu,400gAl,100gepoxy andremainingsteel. This is an explicit analog material budget,not validated excitation circuit or a universal zeroTa/PM claim. Wound-field generator excitation is represented by the winding material budget;no unsupported full-machine permanent magnets. Full7050kg generator goes once toWEEE;AVR has no extra disposal. Native WEEE treatment is a proxy,not recoveryshare analysis. Gross-minus-net680kg shipping-package composition unresolved and excluded from installed mass;do not assign it invented metals. Rewire six passenger-train perMJ copies and provenance with unchanged lifetime-energy denominator;source generator kg increases7050/4410. Traction converter,motor,engine,tank,chassis and track unchanged. Only existing rail/final-energy workbooks;no runtime or native edits.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED RAIL CONVERTER ENGINEERING REFERENCE, item25, 2026-10-18. ABB2024 ACS6080 PEP ABBG-00712-V01.01-EN, marked Draft/Public, page7, https://library.e.abb.com/public/f0dd73990f0242ab9a0e88dbf6090edd/PEP_EPD_ACS6080_33AXD10002395301_RevA_EN_05122024.pdf; ABB BORDLINE masses/power retained from existing rail sources. Infineon FZ1500R33HE3 datasheet construction reference https://www.infineon.com/assets/row/public/documents/60/49/infineon-fz1500r33he3-datasheet-en.pdf. Replace the mass-scaled4.5kg car battery-voltage converter with an explicit medium-voltage AC-drive-based reference, not a measured BORDLINE BOM. ABB2024 draft PEP gives14583kg including packaging:steel43.4%,Cu20.4%,Al2.25%,GFRP1.7%,otherplastics0.4%,electroniccomponents12.9%,wood13.7%,other5.25%. Percentages sum100. Treat wood as packaging and exclude it from installed reference mass:hardware fraction0.863. Perkg installed converter divide other category fractions by0.863; purchase packaging wood0.137/0.863kg additionally. Source is an18MW industrial AC drive, not a rail-qualified product: composition transfer to BORDLINE is an explicit engineering analogue, with source installed masses and power/lifetime counts unchanged. Assume electronic component mass70%film capacitors,25%power semiconductor modules,5%populated control boards. These fractions are design assumptions; sensitivity capacitor50-80%, module10-40%, board2-10%, constrained to100%. Generic Pb-free through-hole board retains upstream precious metals; no zero-gold assumption. Illustrative power module retained recipe:Cu50%,Al10%,alumina20%,PPS10%,silicone8%,silicon die2%. Represent die fabrication by existing fabricated-IC-wafer service using300um silicon thickness and2330kg/m3 density:0.02/(2330*0.0003)m2/kgmodule. This wafer and power-module composition are engineering proxies, not Infineon material declarations or verified rail die technology. Module assembly1kWh/kg assumed. Film capacitor proxy includes its own constituent materials once. Other5.25%/0.863=6.08343% installed hardware mass remains compositionally UNRESOLVED and is not silently converted into zero metal or an arbitrary PCB. Known retained material coverage93.91657%; trace-metal completeness is not claimed.100%retention reference plus generic metal-working/1kWh final assembly perkg; yields, cooling coolant, additional cabling, end-of-life and rail qualification remain gaps. Do not infer corrected system gold totals before rebuilding and sensitivity analysis. No passenger/freight service denominator change in this commit.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -1495,7 +1500,10 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>APPROVED RAIL GENERATOR FUNCTION AND RATING, issue104,2026-10-18. ABB NMG catalogue9AKK2017109096:page10 continuous60Hz40C,pf0.8,NMG0500DD04 DAPI 3590kVA/2872kW at460V;page17 net7050kg,gross7730kg. OldNMG0450DD04 at460V60Hz is2072kW,not2.8MW. https://search.abb.com/library/Download.aspx?DocumentID=9AKK2017109096&amp;LanguageCode=en&amp;DocumentPartId=&amp;Action=Launch . Material analogue:ABB AMG0900 5125kVA11kV EPD2000 pages2-3,https://library.e.abb.com/public/2bb39d909d618031c1256d63003c5c76/EPD%20for%20AMG%20900.pdf . Use kg/product column; kg/kVA column is visibly misaligned. Existing locomotive buys4410kg of unspecified passive electronics as a generator proxy; native mixture assigns153.468kg tantalum-capacitor packages,NOT elementalTa. Replace with7050kg of a dedicated synchronous powertrain-generator engineering reference. Selected industrial model rated2872kW is sufficient for the stated2800kW duty at460V/60Hz/pf0.8. This is not a rail-qualified UKlight generator or proof of compatible BORDLINE DC-link voltage:actual rail speed/voltage,rectification,EMC,cooling and mass require project-specific verification. Source mass is not scaled linearly fromkVA. Keep original40year generator allocation as a service assumption; EPD25year operation is not transferred as measured rail life. Test mass4410/7050/9000kg and20-40year service; keep operating diesel demand unchanged. Material composition is transferred PERkg from the much heavier,11kV medium-speed AMG0900,not claimed a published NMG BOM:kg/product={'electricalsteel': 7120.0, 'steel': 10900.0, 'forgedsteel': 5323.0, 'Al': 13.0, 'Cu': 2461.0, 'insulation': 155.0, 'resin': 225.0, 'paint': 40.0},installed total26237kg excluding800kg wood. Reserve1kg of the7050kg budget for an explicit analog excitation/AVR material reference; scale the remaining7049kg by these normalized fractions. The1kg AVR partition is an engineering allocation,not manufacturer traceability. Electricalsteel uses the existing3.2%Si reference;other/forgedsteel generic lowalloy feed,insulation glassfibre,impregnation epoxy,paint alkyd are stated material proxies. Existing electricalsteel rolling stays in its supplier;do not add a second generic metalworking energy package. EPD manufacturing40122kWh electricity and9659kWh heat per26237kg provide an aggregate factory-energy reference perkg,not operating losses. Potential factory/service overlap,forging details,lamination yield and actual coating remain gaps. AVR reference1kg contains0.05m2 unmountedPWB at assumed3.08kg/m2,6glassdiodes at0.596g,50gchoke,30gfilmcapacitor,10gmetalfilmresistors,5gSMTtransistors,100gCu,400gAl,100gepoxy andremainingsteel. This is an explicit analog material budget,not validated excitation circuit or a universal zeroTa/PM claim. Wound-field generator excitation is represented by the winding material budget;no unsupported full-machine permanent magnets. Full7050kg generator goes once toWEEE;AVR has no extra disposal. Native WEEE treatment is a proxy,not recoveryshare analysis. Gross-minus-net680kg shipping-package composition unresolved and excluded from installed mass;do not assign it invented metals. Rewire six passenger-train perMJ copies and provenance with unchanged lifetime-energy denominator;source generator kg increases7050/4410. Traction converter,motor,engine,tank,chassis and track unchanged. Only existing rail/final-energy workbooks;no runtime or native edits.</t>
+          <t>APPROVED RAIL ENGINE MASS REFERENCE, issue 114, 2026-10-19. Caterpillar LEHR0024-01 (12-19), C175-16 Locomotive Engine, EU Stage V, page 1: 3000 bkW at 1800 rpm; engine including flywheel approximately 12500 kg net dry, aftertreatment 1000 kg and dosing cabinet 115 kg separately. Manufacturer-authored sheet indexed at https://www.zeppelin.com/content/dam/zeppelin/power-systems/produkte/motoren/lok-motoren/LEHR0024-01_C175_RAIL_EU_V.pdf ; direct retrieval returned 404 on 2026-10-19, indexed specification preserved in the audit source record.
+Replace the unsupported truck extrapolation 9593.181818181818 kg = 2800/352*1206 by one 12500 kg dry locomotive engine reference. The selected published 3000 kW rail engine covers the retained 2800 kW duty; do not multiply its mass by 2800/3000. This is a documented engineering reference from a later rail configuration, not a measured mass of the original UKLight engine. In particular, neither the standalone Wolff 1140 kg engine BOM nor its truck assembly including exhaust can simply replace 1206 kg at an assumed common 352 kW reference.
+Keep the corrected per-kg truck engine composition as an explicit material analogue, not a rail manufacturer BOM. Actual large-engine alloy grades, electronic controls, machining yields, cooling and exhaust hardware remain coverage uncertainties. Net dry mass excludes fuel, lubricant and coolant; retain existing operating fuel consumption and generator, converter, motor and tank inventories. Separate Stage V aftertreatment/dosing equipment is not silently added to this older duty reference; the equipment/emissions-generation match remains a stated gap. Retain the existing one engine over 40 years convention as an engineering allocation; overhaul/replacement needs source data (sensitivity 1-2 complete engines and 10-15 tonnes dry mass).
+Update the six stored passenger-train per-MJ copies and their source records by the same mass ratio, preserving purchased energy and source-service denominators. No chassis, track, native database, runtime or primary/secondary-share changes.</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1535,7 @@
         <v>266</v>
       </c>
       <c r="B14">
-        <v>9593.181818181818</v>
+        <v>12500.0</v>
       </c>
       <c r="C14" t="s">
         <v>23</v>
@@ -1541,8 +1549,13 @@
       <c r="G14" t="s">
         <v>27</v>
       </c>
-      <c r="H14" t="s">
-        <v>28</v>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>APPROVED RAIL ENGINE MASS REFERENCE, issue 114, 2026-10-19. Caterpillar LEHR0024-01 (12-19), C175-16 Locomotive Engine, EU Stage V, page 1: 3000 bkW at 1800 rpm; engine including flywheel approximately 12500 kg net dry, aftertreatment 1000 kg and dosing cabinet 115 kg separately. Manufacturer-authored sheet indexed at https://www.zeppelin.com/content/dam/zeppelin/power-systems/produkte/motoren/lok-motoren/LEHR0024-01_C175_RAIL_EU_V.pdf ; direct retrieval returned 404 on 2026-10-19, indexed specification preserved in the audit source record.
+Replace the unsupported truck extrapolation 9593.181818181818 kg = 2800/352*1206 by one 12500 kg dry locomotive engine reference. The selected published 3000 kW rail engine covers the retained 2800 kW duty; do not multiply its mass by 2800/3000. This is a documented engineering reference from a later rail configuration, not a measured mass of the original UKLight engine. In particular, neither the standalone Wolff 1140 kg engine BOM nor its truck assembly including exhaust can simply replace 1206 kg at an assumed common 352 kW reference.
+Keep the corrected per-kg truck engine composition as an explicit material analogue, not a rail manufacturer BOM. Actual large-engine alloy grades, electronic controls, machining yields, cooling and exhaust hardware remain coverage uncertainties. Net dry mass excludes fuel, lubricant and coolant; retain existing operating fuel consumption and generator, converter, motor and tank inventories. Separate Stage V aftertreatment/dosing equipment is not silently added to this older duty reference; the equipment/emissions-generation match remains a stated gap. Retain the existing one engine over 40 years convention as an engineering allocation; overhaul/replacement needs source data (sensitivity 1-2 complete engines and 10-15 tonnes dry mass).
+Update the six stored passenger-train per-MJ copies and their source records by the same mass ratio, preserving purchased energy and source-service denominators. No chassis, track, native database, runtime or primary/secondary-share changes.</t>
+        </is>
       </c>
     </row>
     <row r="15" spans="1:8" ns3:dyDescent="0.2">
@@ -18186,7 +18199,12 @@
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>APPROVED RAIL ENGINE PLASTIC SOURCE DOSE, issue106,2026-10-18. Wolff et al.2020, DOI10.3390/su12135396, original supplementary Production/Components/Engine.xlsx and Diesel Tank.xlsx. https://mdpi-res.com/d_attachment/sustainability/sustainability-12-05396/article_deploy/sustainability-12-05396-s001.zip . Engine.xlsx B9/B3=51.3/1140=.045kg plastic/kg engine;separate railcopy retained.45kg/kg after truckcopy wasfixed in38b99e4d. Correctonlythisdose to.045kg/kg. Currentmaterialsum1.405 becomes1kg/kg exactly with its retained decimal coefficients. Keep previouslyapproved ordinarycastAl.15kg/kg;othermetal/rubberfeeds unchanged. Sourceplastic isgeneric;retainedphenolicresin is an unverified chemistryproxy,not sourcedphenolic grade. Preserve manufacturingenergy/services,9593.181818181818kg installedengine reference andalllifetimes/perMJ buyers. This doesnotvalidate rail-specificengineefficiency,mass,power/life ormanufacturing/emissionyield;no artificialrenormalizationofothermaterials,recoverycredit orprimary/secondaryshares. Supersedesissue105 pendingplasticwarning. Existingworkbookonly.
+          <t>APPROVED RAIL ENGINE MASS REFERENCE, issue 114, 2026-10-19. Caterpillar LEHR0024-01 (12-19), C175-16 Locomotive Engine, EU Stage V, page 1: 3000 bkW at 1800 rpm; engine including flywheel approximately 12500 kg net dry, aftertreatment 1000 kg and dosing cabinet 115 kg separately. Manufacturer-authored sheet indexed at https://www.zeppelin.com/content/dam/zeppelin/power-systems/produkte/motoren/lok-motoren/LEHR0024-01_C175_RAIL_EU_V.pdf ; direct retrieval returned 404 on 2026-10-19, indexed specification preserved in the audit source record.
+Replace the unsupported truck extrapolation 9593.181818181818 kg = 2800/352*1206 by one 12500 kg dry locomotive engine reference. The selected published 3000 kW rail engine covers the retained 2800 kW duty; do not multiply its mass by 2800/3000. This is a documented engineering reference from a later rail configuration, not a measured mass of the original UKLight engine. In particular, neither the standalone Wolff 1140 kg engine BOM nor its truck assembly including exhaust can simply replace 1206 kg at an assumed common 352 kW reference.
+Keep the corrected per-kg truck engine composition as an explicit material analogue, not a rail manufacturer BOM. Actual large-engine alloy grades, electronic controls, machining yields, cooling and exhaust hardware remain coverage uncertainties. Net dry mass excludes fuel, lubricant and coolant; retain existing operating fuel consumption and generator, converter, motor and tank inventories. Separate Stage V aftertreatment/dosing equipment is not silently added to this older duty reference; the equipment/emissions-generation match remains a stated gap. Retain the existing one engine over 40 years convention as an engineering allocation; overhaul/replacement needs source data (sensitivity 1-2 complete engines and 10-15 tonnes dry mass).
+Update the six stored passenger-train per-MJ copies and their source records by the same mass ratio, preserving purchased energy and source-service denominators. No chassis, track, native database, runtime or primary/secondary-share changes.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED RAIL ENGINE PLASTIC SOURCE DOSE, issue106,2026-10-18. Wolff et al.2020, DOI10.3390/su12135396, original supplementary Production/Components/Engine.xlsx and Diesel Tank.xlsx. https://mdpi-res.com/d_attachment/sustainability/sustainability-12-05396/article_deploy/sustainability-12-05396-s001.zip . Engine.xlsx B9/B3=51.3/1140=.045kg plastic/kg engine;separate railcopy retained.45kg/kg after truckcopy wasfixed in38b99e4d. Correctonlythisdose to.045kg/kg. Currentmaterialsum1.405 becomes1kg/kg exactly with its retained decimal coefficients. Keep previouslyapproved ordinarycastAl.15kg/kg;othermetal/rubberfeeds unchanged. Sourceplastic isgeneric;retainedphenolicresin is an unverified chemistryproxy,not sourcedphenolic grade. Preserve manufacturingenergy/services,9593.181818181818kg installedengine reference andalllifetimes/perMJ buyers. This doesnotvalidate rail-specificengineefficiency,mass,power/life ormanufacturing/emissionyield;no artificialrenormalizationofothermaterials,recoverycredit orprimary/secondaryshares. Supersedesissue105 pendingplasticwarning. Existingworkbookonly.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED RAIL ENGINE ALUMINIUM IDENTITY, issue105,2026-10-18. Wolff et al.2020, DOI10.3390/su12135396, original supplementary Production/Components/Engine.xlsx and Diesel Tank.xlsx. https://mdpi-res.com/d_attachment/sustainability/sustainability-12-05396/article_deploy/sustainability-12-05396-s001.zip . Source Engine.xlsx Sheet1 B8=171kg aluminium/B3=1140kg engine=.15kg/kg. Apply alreadyapproved truck correction ad6bb596 to this separately active rail copy. Replace unsupported specialtyAlLi by ordinary cast-alloy market at unchanged.15kg/kg;castalloy is an engineering material-class proxy,not sourcecertifiedAlSi grade or proofallpartsarecast. Native AlLi includes unsupported lithium/silver supply. Preserve engine mass9593.181818181818kg/locomotive,all buyer/perMJ coefficients,other ingredients,services andenergy. Source oldplastic.45kg/kg remains separate issue106;this identity correction alone does not close the1.405kg/kg material sum. Keep alloy uncertainty,purity,yields andfuturedesign gaps explicit;no elementarycomposition,primary/secondaryshare orrecoverycredit assumed. Existing workbookonly,no runtime/native edits.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -18259,7 +18277,10 @@
       </c>
       <c r="H905" t="inlineStr">
         <is>
-          <t>APPROVED RAIL ENGINE PLASTIC SOURCE DOSE, issue106,2026-10-18. Wolff et al.2020, DOI10.3390/su12135396, original supplementary Production/Components/Engine.xlsx and Diesel Tank.xlsx. https://mdpi-res.com/d_attachment/sustainability/sustainability-12-05396/article_deploy/sustainability-12-05396-s001.zip . Engine.xlsx B9/B3=51.3/1140=.045kg plastic/kg engine;separate railcopy retained.45kg/kg after truckcopy wasfixed in38b99e4d. Correctonlythisdose to.045kg/kg. Currentmaterialsum1.405 becomes1kg/kg exactly with its retained decimal coefficients. Keep previouslyapproved ordinarycastAl.15kg/kg;othermetal/rubberfeeds unchanged. Sourceplastic isgeneric;retainedphenolicresin is an unverified chemistryproxy,not sourcedphenolic grade. Preserve manufacturingenergy/services,9593.181818181818kg installedengine reference andalllifetimes/perMJ buyers. This doesnotvalidate rail-specificengineefficiency,mass,power/life ormanufacturing/emissionyield;no artificialrenormalizationofothermaterials,recoverycredit orprimary/secondaryshares. Supersedesissue105 pendingplasticwarning. Existingworkbookonly.</t>
+          <t>APPROVED RAIL ENGINE MASS REFERENCE, issue 114, 2026-10-19. Caterpillar LEHR0024-01 (12-19), C175-16 Locomotive Engine, EU Stage V, page 1: 3000 bkW at 1800 rpm; engine including flywheel approximately 12500 kg net dry, aftertreatment 1000 kg and dosing cabinet 115 kg separately. Manufacturer-authored sheet indexed at https://www.zeppelin.com/content/dam/zeppelin/power-systems/produkte/motoren/lok-motoren/LEHR0024-01_C175_RAIL_EU_V.pdf ; direct retrieval returned 404 on 2026-10-19, indexed specification preserved in the audit source record.
+Replace the unsupported truck extrapolation 9593.181818181818 kg = 2800/352*1206 by one 12500 kg dry locomotive engine reference. The selected published 3000 kW rail engine covers the retained 2800 kW duty; do not multiply its mass by 2800/3000. This is a documented engineering reference from a later rail configuration, not a measured mass of the original UKLight engine. In particular, neither the standalone Wolff 1140 kg engine BOM nor its truck assembly including exhaust can simply replace 1206 kg at an assumed common 352 kW reference.
+Keep the corrected per-kg truck engine composition as an explicit material analogue, not a rail manufacturer BOM. Actual large-engine alloy grades, electronic controls, machining yields, cooling and exhaust hardware remain coverage uncertainties. Net dry mass excludes fuel, lubricant and coolant; retain existing operating fuel consumption and generator, converter, motor and tank inventories. Separate Stage V aftertreatment/dosing equipment is not silently added to this older duty reference; the equipment/emissions-generation match remains a stated gap. Retain the existing one engine over 40 years convention as an engineering allocation; overhaul/replacement needs source data (sensitivity 1-2 complete engines and 10-15 tonnes dry mass).
+Update the six stored passenger-train per-MJ copies and their source records by the same mass ratio, preserving purchased energy and source-service denominators. No chassis, track, native database, runtime or primary/secondary-share changes.</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-rail-freight.xlsx
+++ b/premise/data/additional_inventories/lci-rail-freight.xlsx
@@ -1561,7 +1561,7 @@
     <row r="15" spans="1:8" ns3:dyDescent="0.2">
       <c r="A15" t="inlineStr">
         <is>
-          <t>rail powertrain generator, synchronous engineering reference</t>
+          <t xml:space="preserve">traction generator production, synchronous, rail</t>
         </is>
       </c>
       <c r="B15">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>rail powertrain generator, synchronous engineering reference</t>
+          <t xml:space="preserve">traction generator, synchronous, rail</t>
         </is>
       </c>
       <c r="H15" t="s">
@@ -1590,7 +1590,7 @@
     <row r="16" spans="1:8" ns3:dyDescent="0.2">
       <c r="A16" t="inlineStr">
         <is>
-          <t>electric motor, asynchronous traction, engineering reference</t>
+          <t xml:space="preserve">electric motor production, asynchronous, traction</t>
         </is>
       </c>
       <c r="B16">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>electric motor, asynchronous traction, engineering reference</t>
+          <t xml:space="preserve">electric motor, asynchronous, traction</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1625,7 +1625,7 @@
     <row r="17" spans="1:8" ns3:dyDescent="0.2">
       <c r="A17" t="inlineStr">
         <is>
-          <t>traction converter, medium-voltage rail engineering reference</t>
+          <t xml:space="preserve">traction converter production, rail, medium voltage</t>
         </is>
       </c>
       <c r="B17">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>traction converter, medium-voltage rail engineering reference</t>
+          <t xml:space="preserve">traction converter, rail, medium voltage</t>
         </is>
       </c>
       <c r="H17" t="s">
@@ -1815,7 +1815,7 @@
     <row r="31" spans="1:8" ns3:dyDescent="0.2">
       <c r="A31" t="inlineStr">
         <is>
-          <t>electric motor, asynchronous traction, engineering reference</t>
+          <t xml:space="preserve">electric motor production, asynchronous, traction</t>
         </is>
       </c>
       <c r="B31">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>electric motor, asynchronous traction, engineering reference</t>
+          <t xml:space="preserve">electric motor, asynchronous, traction</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1854,7 +1854,7 @@
     <row r="32" spans="1:8" ns3:dyDescent="0.2">
       <c r="A32" t="inlineStr">
         <is>
-          <t>traction converter, medium-voltage rail engineering reference</t>
+          <t xml:space="preserve">traction converter production, rail, medium voltage</t>
         </is>
       </c>
       <c r="B32">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>traction converter, medium-voltage rail engineering reference</t>
+          <t xml:space="preserve">traction converter, rail, medium voltage</t>
         </is>
       </c>
       <c r="H32" t="s">
@@ -2030,7 +2030,7 @@
     <row r="45" spans="1:8" ns3:dyDescent="0.2">
       <c r="A45" t="inlineStr">
         <is>
-          <t>electric motor, asynchronous traction, engineering reference</t>
+          <t xml:space="preserve">electric motor production, asynchronous, traction</t>
         </is>
       </c>
       <c r="B45">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>electric motor, asynchronous traction, engineering reference</t>
+          <t xml:space="preserve">electric motor, asynchronous, traction</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2065,7 +2065,7 @@
     <row r="46" spans="1:8" ns3:dyDescent="0.2">
       <c r="A46" t="inlineStr">
         <is>
-          <t>traction converter, medium-voltage rail engineering reference</t>
+          <t xml:space="preserve">traction converter production, rail, medium voltage</t>
         </is>
       </c>
       <c r="B46">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>traction converter, medium-voltage rail engineering reference</t>
+          <t xml:space="preserve">traction converter, rail, medium voltage</t>
         </is>
       </c>
       <c r="H46" t="s">
@@ -2093,7 +2093,7 @@
     <row r="47" spans="1:8" ns3:dyDescent="0.2">
       <c r="A47" t="inlineStr">
         <is>
-          <t>fuel cell system assembly, rail30kh stack engineering reference</t>
+          <t xml:space="preserve">fuel cell system assembly production, rail transport</t>
         </is>
       </c>
       <c r="B47">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>fuel cell system assembly, rail30kh stack engineering reference</t>
+          <t xml:space="preserve">fuel cell system assembly, rail transport</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2122,7 +2122,7 @@
     <row r="48" spans="1:8" ns3:dyDescent="0.2">
       <c r="A48" t="inlineStr">
         <is>
-          <t>hydrogen fuel tank system, rail700bar lifetime reference</t>
+          <t xml:space="preserve">hydrogen fuel tank system production, rail, 700 bar</t>
         </is>
       </c>
       <c r="B48">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>hydrogen fuel tank system, rail700bar lifetime reference</t>
+          <t xml:space="preserve">hydrogen fuel tank system, rail, 700 bar</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2155,7 +2155,7 @@
     <row r="49" spans="1:8" ns3:dyDescent="0.2">
       <c r="A49" t="inlineStr">
         <is>
-          <t>battery capacity, hydrogen rail, LFP engineering reference</t>
+          <t xml:space="preserve">market for electricity storage capacity, battery, Li-ion, LFP, hydrogen train</t>
         </is>
       </c>
       <c r="B49">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>battery capacity, hydrogen rail, LFP engineering reference</t>
+          <t xml:space="preserve">electricity storage capacity, Li-ion, LFP, hydrogen train</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -19500,7 +19500,7 @@
       </c>
       <c r="B968" t="inlineStr">
         <is>
-          <t>non-oriented electrical steel, engineering alloy reference</t>
+          <t xml:space="preserve">electrical steel production, non-oriented</t>
         </is>
       </c>
     </row>
@@ -19534,7 +19534,7 @@
       </c>
       <c r="B971" t="inlineStr">
         <is>
-          <t>non-oriented electrical steel, engineering alloy reference</t>
+          <t xml:space="preserve">electrical steel, non-oriented</t>
         </is>
       </c>
     </row>
@@ -19570,7 +19570,8 @@
       </c>
       <c r="B974" t="inlineStr">
         <is>
-          <t>APPROVED ASYNCHRONOUS TRACTION ENGINEERING REFERENCE, item19, 2026-10-18. Hsieh etal2026 DOI10.1007/s11367-026-02610-7, SI FigureS7 IM2 and TableS11; ABB2017 Re460 asynchronous traction https://library.e.abb.com/public/bfe91c518ff94330a3c591b4bbeb8b6a/65-69%201m6073_EN_72dpi.pdf. Use the IM2 Cu-stator/Al-rotor induction design: source FigureS7 rounded masspercent Al37.4, electricalsteel46.3, Cu10.0, lowalloysteel3.93, coating/insulation2.42 (sum100.05). Divide these full-composition shares by100.05 to resolve rounding. TableS11 individual masses differ somewhat from the figure (source62.9kg motor); this reference explicitly adopts the complete figure composition, not a claim that both tables close exactly. No permanent magnets or Nd/Dy magnet-processing inputs are included by design; this does not prove zero rare-earth flows in upstream supply. Represent electrical steel as a3.2percentSi engineering alloy, assuming75percentSi ferrosilicon plus low-alloy steel balance, with sheet rolling; source source-specific steel grade, lamination scrap and non-oriented processing remain proxies. Coating uses epoxy resin; source electrical insulation is not fully specified. Generic metal working plus1kWh/kg final assembly electricity are explicit engineering process assumptions (sensitivity.3-3kWh/kg), not measured rail-motor factory data. Retain original rail installed motor masses, service lifetimes and per-MJ allocations; replace only the permanent-magnet passenger-car manufacturing composition. IM2 is a100kW passenger-car study extrapolated perkg to rail, not a rail-rated thermal/mechanical design. Rail nameplate/mass, actual motor efficiency, bearings/rotor fabrication losses, maintenance and EOL coverage remain gaps. No train chassis/track added. Rewire three source locomotive motor inputs and all explicit train/tram final-energy motor inputs; road vehicle motors remain unchanged. Align existing service-to-locomotive input product labels to their actual supplier reference products so the real scoped normalization can resolve the source production links; amounts and lifetime allocation are unchanged.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: non-oriented electrical steel, engineering alloy reference. Former reference product: non-oriented electrical steel, engineering alloy reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED ASYNCHRONOUS TRACTION ENGINEERING REFERENCE, item19, 2026-10-18. Hsieh etal2026 DOI10.1007/s11367-026-02610-7, SI FigureS7 IM2 and TableS11; ABB2017 Re460 asynchronous traction https://library.e.abb.com/public/bfe91c518ff94330a3c591b4bbeb8b6a/65-69%201m6073_EN_72dpi.pdf. Use the IM2 Cu-stator/Al-rotor induction design: source FigureS7 rounded masspercent Al37.4, electricalsteel46.3, Cu10.0, lowalloysteel3.93, coating/insulation2.42 (sum100.05). Divide these full-composition shares by100.05 to resolve rounding. TableS11 individual masses differ somewhat from the figure (source62.9kg motor); this reference explicitly adopts the complete figure composition, not a claim that both tables close exactly. No permanent magnets or Nd/Dy magnet-processing inputs are included by design; this does not prove zero rare-earth flows in upstream supply. Represent electrical steel as a3.2percentSi engineering alloy, assuming75percentSi ferrosilicon plus low-alloy steel balance, with sheet rolling; source source-specific steel grade, lamination scrap and non-oriented processing remain proxies. Coating uses epoxy resin; source electrical insulation is not fully specified. Generic metal working plus1kWh/kg final assembly electricity are explicit engineering process assumptions (sensitivity.3-3kWh/kg), not measured rail-motor factory data. Retain original rail installed motor masses, service lifetimes and per-MJ allocations; replace only the permanent-magnet passenger-car manufacturing composition. IM2 is a100kW passenger-car study extrapolated perkg to rail, not a rail-rated thermal/mechanical design. Rail nameplate/mass, actual motor efficiency, bearings/rotor fabrication losses, maintenance and EOL coverage remain gaps. No train chassis/track added. Rewire three source locomotive motor inputs and all explicit train/tram final-energy motor inputs; road vehicle motors remain unchanged. Align existing service-to-locomotive input product labels to their actual supplier reference products so the real scoped normalization can resolve the source production links; amounts and lifetime allocation are unchanged.</t>
         </is>
       </c>
     </row>
@@ -19626,7 +19627,7 @@
     <row r="977">
       <c r="A977" t="inlineStr">
         <is>
-          <t>non-oriented electrical steel, engineering alloy reference</t>
+          <t xml:space="preserve">electrical steel production, non-oriented</t>
         </is>
       </c>
       <c r="B977">
@@ -19649,7 +19650,7 @@
       </c>
       <c r="G977" t="inlineStr">
         <is>
-          <t>non-oriented electrical steel, engineering alloy reference</t>
+          <t xml:space="preserve">electrical steel, non-oriented</t>
         </is>
       </c>
     </row>
@@ -19751,7 +19752,7 @@
       </c>
       <c r="B983" t="inlineStr">
         <is>
-          <t>electric motor, asynchronous traction, engineering reference</t>
+          <t xml:space="preserve">electric motor production, asynchronous, traction</t>
         </is>
       </c>
     </row>
@@ -19785,7 +19786,7 @@
       </c>
       <c r="B986" t="inlineStr">
         <is>
-          <t>electric motor, asynchronous traction, engineering reference</t>
+          <t xml:space="preserve">electric motor, asynchronous, traction</t>
         </is>
       </c>
     </row>
@@ -19821,7 +19822,8 @@
       </c>
       <c r="B989" t="inlineStr">
         <is>
-          <t>APPROVED ASYNCHRONOUS TRACTION ENGINEERING REFERENCE, item19, 2026-10-18. Hsieh etal2026 DOI10.1007/s11367-026-02610-7, SI FigureS7 IM2 and TableS11; ABB2017 Re460 asynchronous traction https://library.e.abb.com/public/bfe91c518ff94330a3c591b4bbeb8b6a/65-69%201m6073_EN_72dpi.pdf. Use the IM2 Cu-stator/Al-rotor induction design: source FigureS7 rounded masspercent Al37.4, electricalsteel46.3, Cu10.0, lowalloysteel3.93, coating/insulation2.42 (sum100.05). Divide these full-composition shares by100.05 to resolve rounding. TableS11 individual masses differ somewhat from the figure (source62.9kg motor); this reference explicitly adopts the complete figure composition, not a claim that both tables close exactly. No permanent magnets or Nd/Dy magnet-processing inputs are included by design; this does not prove zero rare-earth flows in upstream supply. Represent electrical steel as a3.2percentSi engineering alloy, assuming75percentSi ferrosilicon plus low-alloy steel balance, with sheet rolling; source source-specific steel grade, lamination scrap and non-oriented processing remain proxies. Coating uses epoxy resin; source electrical insulation is not fully specified. Generic metal working plus1kWh/kg final assembly electricity are explicit engineering process assumptions (sensitivity.3-3kWh/kg), not measured rail-motor factory data. Retain original rail installed motor masses, service lifetimes and per-MJ allocations; replace only the permanent-magnet passenger-car manufacturing composition. IM2 is a100kW passenger-car study extrapolated perkg to rail, not a rail-rated thermal/mechanical design. Rail nameplate/mass, actual motor efficiency, bearings/rotor fabrication losses, maintenance and EOL coverage remain gaps. No train chassis/track added. Rewire three source locomotive motor inputs and all explicit train/tram final-energy motor inputs; road vehicle motors remain unchanged. Align existing service-to-locomotive input product labels to their actual supplier reference products so the real scoped normalization can resolve the source production links; amounts and lifetime allocation are unchanged.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: electric motor, asynchronous traction, engineering reference. Former reference product: electric motor, asynchronous traction, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED ASYNCHRONOUS TRACTION ENGINEERING REFERENCE, item19, 2026-10-18. Hsieh etal2026 DOI10.1007/s11367-026-02610-7, SI FigureS7 IM2 and TableS11; ABB2017 Re460 asynchronous traction https://library.e.abb.com/public/bfe91c518ff94330a3c591b4bbeb8b6a/65-69%201m6073_EN_72dpi.pdf. Use the IM2 Cu-stator/Al-rotor induction design: source FigureS7 rounded masspercent Al37.4, electricalsteel46.3, Cu10.0, lowalloysteel3.93, coating/insulation2.42 (sum100.05). Divide these full-composition shares by100.05 to resolve rounding. TableS11 individual masses differ somewhat from the figure (source62.9kg motor); this reference explicitly adopts the complete figure composition, not a claim that both tables close exactly. No permanent magnets or Nd/Dy magnet-processing inputs are included by design; this does not prove zero rare-earth flows in upstream supply. Represent electrical steel as a3.2percentSi engineering alloy, assuming75percentSi ferrosilicon plus low-alloy steel balance, with sheet rolling; source source-specific steel grade, lamination scrap and non-oriented processing remain proxies. Coating uses epoxy resin; source electrical insulation is not fully specified. Generic metal working plus1kWh/kg final assembly electricity are explicit engineering process assumptions (sensitivity.3-3kWh/kg), not measured rail-motor factory data. Retain original rail installed motor masses, service lifetimes and per-MJ allocations; replace only the permanent-magnet passenger-car manufacturing composition. IM2 is a100kW passenger-car study extrapolated perkg to rail, not a rail-rated thermal/mechanical design. Rail nameplate/mass, actual motor efficiency, bearings/rotor fabrication losses, maintenance and EOL coverage remain gaps. No train chassis/track added. Rewire three source locomotive motor inputs and all explicit train/tram final-energy motor inputs; road vehicle motors remain unchanged. Align existing service-to-locomotive input product labels to their actual supplier reference products so the real scoped normalization can resolve the source production links; amounts and lifetime allocation are unchanged.</t>
         </is>
       </c>
     </row>
@@ -19877,7 +19879,7 @@
     <row r="992">
       <c r="A992" t="inlineStr">
         <is>
-          <t>electric motor, asynchronous traction, engineering reference</t>
+          <t xml:space="preserve">electric motor production, asynchronous, traction</t>
         </is>
       </c>
       <c r="B992">
@@ -19900,7 +19902,7 @@
       </c>
       <c r="G992" t="inlineStr">
         <is>
-          <t>electric motor, asynchronous traction, engineering reference</t>
+          <t xml:space="preserve">electric motor, asynchronous, traction</t>
         </is>
       </c>
     </row>
@@ -19937,7 +19939,7 @@
     <row r="994">
       <c r="A994" t="inlineStr">
         <is>
-          <t>non-oriented electrical steel, engineering alloy reference</t>
+          <t xml:space="preserve">electrical steel production, non-oriented</t>
         </is>
       </c>
       <c r="B994">
@@ -19960,7 +19962,7 @@
       </c>
       <c r="G994" t="inlineStr">
         <is>
-          <t>non-oriented electrical steel, engineering alloy reference</t>
+          <t xml:space="preserve">electrical steel, non-oriented</t>
         </is>
       </c>
     </row>
@@ -20182,7 +20184,7 @@
       </c>
       <c r="B1004" t="inlineStr">
         <is>
-          <t>power semiconductor module, rail converter engineering reference</t>
+          <t xml:space="preserve">power semiconductor module production, rail converter</t>
         </is>
       </c>
     </row>
@@ -20216,7 +20218,7 @@
       </c>
       <c r="B1007" t="inlineStr">
         <is>
-          <t>power semiconductor module, rail converter engineering reference</t>
+          <t xml:space="preserve">power semiconductor module, rail converter</t>
         </is>
       </c>
     </row>
@@ -20252,7 +20254,8 @@
       </c>
       <c r="B1010" t="inlineStr">
         <is>
-          <t>APPROVED RAIL CONVERTER ENGINEERING REFERENCE, item25, 2026-10-18. ABB2024 ACS6080 PEP ABBG-00712-V01.01-EN, marked Draft/Public, page7, https://library.e.abb.com/public/f0dd73990f0242ab9a0e88dbf6090edd/PEP_EPD_ACS6080_33AXD10002395301_RevA_EN_05122024.pdf; ABB BORDLINE masses/power retained from existing rail sources. Infineon FZ1500R33HE3 datasheet construction reference https://www.infineon.com/assets/row/public/documents/60/49/infineon-fz1500r33he3-datasheet-en.pdf. Replace the mass-scaled4.5kg car battery-voltage converter with an explicit medium-voltage AC-drive-based reference, not a measured BORDLINE BOM. ABB2024 draft PEP gives14583kg including packaging:steel43.4%,Cu20.4%,Al2.25%,GFRP1.7%,otherplastics0.4%,electroniccomponents12.9%,wood13.7%,other5.25%. Percentages sum100. Treat wood as packaging and exclude it from installed reference mass:hardware fraction0.863. Perkg installed converter divide other category fractions by0.863; purchase packaging wood0.137/0.863kg additionally. Source is an18MW industrial AC drive, not a rail-qualified product: composition transfer to BORDLINE is an explicit engineering analogue, with source installed masses and power/lifetime counts unchanged. Assume electronic component mass70%film capacitors,25%power semiconductor modules,5%populated control boards. These fractions are design assumptions; sensitivity capacitor50-80%, module10-40%, board2-10%, constrained to100%. Generic Pb-free through-hole board retains upstream precious metals; no zero-gold assumption. Illustrative power module retained recipe:Cu50%,Al10%,alumina20%,PPS10%,silicone8%,silicon die2%. Represent die fabrication by existing fabricated-IC-wafer service using300um silicon thickness and2330kg/m3 density:0.02/(2330*0.0003)m2/kgmodule. This wafer and power-module composition are engineering proxies, not Infineon material declarations or verified rail die technology. Module assembly1kWh/kg assumed. Film capacitor proxy includes its own constituent materials once. Other5.25%/0.863=6.08343% installed hardware mass remains compositionally UNRESOLVED and is not silently converted into zero metal or an arbitrary PCB. Known retained material coverage93.91657%; trace-metal completeness is not claimed.100%retention reference plus generic metal-working/1kWh final assembly perkg; yields, cooling coolant, additional cabling, end-of-life and rail qualification remain gaps. Do not infer corrected system gold totals before rebuilding and sensitivity analysis. No passenger/freight service denominator change in this commit.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: power semiconductor module, rail converter engineering reference. Former reference product: power semiconductor module, rail converter engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED RAIL CONVERTER ENGINEERING REFERENCE, item25, 2026-10-18. ABB2024 ACS6080 PEP ABBG-00712-V01.01-EN, marked Draft/Public, page7, https://library.e.abb.com/public/f0dd73990f0242ab9a0e88dbf6090edd/PEP_EPD_ACS6080_33AXD10002395301_RevA_EN_05122024.pdf; ABB BORDLINE masses/power retained from existing rail sources. Infineon FZ1500R33HE3 datasheet construction reference https://www.infineon.com/assets/row/public/documents/60/49/infineon-fz1500r33he3-datasheet-en.pdf. Replace the mass-scaled4.5kg car battery-voltage converter with an explicit medium-voltage AC-drive-based reference, not a measured BORDLINE BOM. ABB2024 draft PEP gives14583kg including packaging:steel43.4%,Cu20.4%,Al2.25%,GFRP1.7%,otherplastics0.4%,electroniccomponents12.9%,wood13.7%,other5.25%. Percentages sum100. Treat wood as packaging and exclude it from installed reference mass:hardware fraction0.863. Perkg installed converter divide other category fractions by0.863; purchase packaging wood0.137/0.863kg additionally. Source is an18MW industrial AC drive, not a rail-qualified product: composition transfer to BORDLINE is an explicit engineering analogue, with source installed masses and power/lifetime counts unchanged. Assume electronic component mass70%film capacitors,25%power semiconductor modules,5%populated control boards. These fractions are design assumptions; sensitivity capacitor50-80%, module10-40%, board2-10%, constrained to100%. Generic Pb-free through-hole board retains upstream precious metals; no zero-gold assumption. Illustrative power module retained recipe:Cu50%,Al10%,alumina20%,PPS10%,silicone8%,silicon die2%. Represent die fabrication by existing fabricated-IC-wafer service using300um silicon thickness and2330kg/m3 density:0.02/(2330*0.0003)m2/kgmodule. This wafer and power-module composition are engineering proxies, not Infineon material declarations or verified rail die technology. Module assembly1kWh/kg assumed. Film capacitor proxy includes its own constituent materials once. Other5.25%/0.863=6.08343% installed hardware mass remains compositionally UNRESOLVED and is not silently converted into zero metal or an arbitrary PCB. Known retained material coverage93.91657%; trace-metal completeness is not claimed.100%retention reference plus generic metal-working/1kWh final assembly perkg; yields, cooling coolant, additional cabling, end-of-life and rail qualification remain gaps. Do not infer corrected system gold totals before rebuilding and sensitivity analysis. No passenger/freight service denominator change in this commit.</t>
         </is>
       </c>
     </row>
@@ -20308,7 +20311,7 @@
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>power semiconductor module, rail converter engineering reference</t>
+          <t xml:space="preserve">power semiconductor module production, rail converter</t>
         </is>
       </c>
       <c r="B1013">
@@ -20331,7 +20334,7 @@
       </c>
       <c r="G1013" t="inlineStr">
         <is>
-          <t>power semiconductor module, rail converter engineering reference</t>
+          <t xml:space="preserve">power semiconductor module, rail converter</t>
         </is>
       </c>
     </row>
@@ -20553,7 +20556,7 @@
       </c>
       <c r="B1023" t="inlineStr">
         <is>
-          <t>traction converter, medium-voltage rail engineering reference</t>
+          <t xml:space="preserve">traction converter production, rail, medium voltage</t>
         </is>
       </c>
     </row>
@@ -20587,7 +20590,7 @@
       </c>
       <c r="B1026" t="inlineStr">
         <is>
-          <t>traction converter, medium-voltage rail engineering reference</t>
+          <t xml:space="preserve">traction converter, rail, medium voltage</t>
         </is>
       </c>
     </row>
@@ -20623,7 +20626,8 @@
       </c>
       <c r="B1029" t="inlineStr">
         <is>
-          <t>APPROVED RAIL CONVERTER ENGINEERING REFERENCE, item25, 2026-10-18. ABB2024 ACS6080 PEP ABBG-00712-V01.01-EN, marked Draft/Public, page7, https://library.e.abb.com/public/f0dd73990f0242ab9a0e88dbf6090edd/PEP_EPD_ACS6080_33AXD10002395301_RevA_EN_05122024.pdf; ABB BORDLINE masses/power retained from existing rail sources. Infineon FZ1500R33HE3 datasheet construction reference https://www.infineon.com/assets/row/public/documents/60/49/infineon-fz1500r33he3-datasheet-en.pdf. Replace the mass-scaled4.5kg car battery-voltage converter with an explicit medium-voltage AC-drive-based reference, not a measured BORDLINE BOM. ABB2024 draft PEP gives14583kg including packaging:steel43.4%,Cu20.4%,Al2.25%,GFRP1.7%,otherplastics0.4%,electroniccomponents12.9%,wood13.7%,other5.25%. Percentages sum100. Treat wood as packaging and exclude it from installed reference mass:hardware fraction0.863. Perkg installed converter divide other category fractions by0.863; purchase packaging wood0.137/0.863kg additionally. Source is an18MW industrial AC drive, not a rail-qualified product: composition transfer to BORDLINE is an explicit engineering analogue, with source installed masses and power/lifetime counts unchanged. Assume electronic component mass70%film capacitors,25%power semiconductor modules,5%populated control boards. These fractions are design assumptions; sensitivity capacitor50-80%, module10-40%, board2-10%, constrained to100%. Generic Pb-free through-hole board retains upstream precious metals; no zero-gold assumption. Illustrative power module retained recipe:Cu50%,Al10%,alumina20%,PPS10%,silicone8%,silicon die2%. Represent die fabrication by existing fabricated-IC-wafer service using300um silicon thickness and2330kg/m3 density:0.02/(2330*0.0003)m2/kgmodule. This wafer and power-module composition are engineering proxies, not Infineon material declarations or verified rail die technology. Module assembly1kWh/kg assumed. Film capacitor proxy includes its own constituent materials once. Other5.25%/0.863=6.08343% installed hardware mass remains compositionally UNRESOLVED and is not silently converted into zero metal or an arbitrary PCB. Known retained material coverage93.91657%; trace-metal completeness is not claimed.100%retention reference plus generic metal-working/1kWh final assembly perkg; yields, cooling coolant, additional cabling, end-of-life and rail qualification remain gaps. Do not infer corrected system gold totals before rebuilding and sensitivity analysis. No passenger/freight service denominator change in this commit.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: traction converter, medium-voltage rail engineering reference. Former reference product: traction converter, medium-voltage rail engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED RAIL CONVERTER ENGINEERING REFERENCE, item25, 2026-10-18. ABB2024 ACS6080 PEP ABBG-00712-V01.01-EN, marked Draft/Public, page7, https://library.e.abb.com/public/f0dd73990f0242ab9a0e88dbf6090edd/PEP_EPD_ACS6080_33AXD10002395301_RevA_EN_05122024.pdf; ABB BORDLINE masses/power retained from existing rail sources. Infineon FZ1500R33HE3 datasheet construction reference https://www.infineon.com/assets/row/public/documents/60/49/infineon-fz1500r33he3-datasheet-en.pdf. Replace the mass-scaled4.5kg car battery-voltage converter with an explicit medium-voltage AC-drive-based reference, not a measured BORDLINE BOM. ABB2024 draft PEP gives14583kg including packaging:steel43.4%,Cu20.4%,Al2.25%,GFRP1.7%,otherplastics0.4%,electroniccomponents12.9%,wood13.7%,other5.25%. Percentages sum100. Treat wood as packaging and exclude it from installed reference mass:hardware fraction0.863. Perkg installed converter divide other category fractions by0.863; purchase packaging wood0.137/0.863kg additionally. Source is an18MW industrial AC drive, not a rail-qualified product: composition transfer to BORDLINE is an explicit engineering analogue, with source installed masses and power/lifetime counts unchanged. Assume electronic component mass70%film capacitors,25%power semiconductor modules,5%populated control boards. These fractions are design assumptions; sensitivity capacitor50-80%, module10-40%, board2-10%, constrained to100%. Generic Pb-free through-hole board retains upstream precious metals; no zero-gold assumption. Illustrative power module retained recipe:Cu50%,Al10%,alumina20%,PPS10%,silicone8%,silicon die2%. Represent die fabrication by existing fabricated-IC-wafer service using300um silicon thickness and2330kg/m3 density:0.02/(2330*0.0003)m2/kgmodule. This wafer and power-module composition are engineering proxies, not Infineon material declarations or verified rail die technology. Module assembly1kWh/kg assumed. Film capacitor proxy includes its own constituent materials once. Other5.25%/0.863=6.08343% installed hardware mass remains compositionally UNRESOLVED and is not silently converted into zero metal or an arbitrary PCB. Known retained material coverage93.91657%; trace-metal completeness is not claimed.100%retention reference plus generic metal-working/1kWh final assembly perkg; yields, cooling coolant, additional cabling, end-of-life and rail qualification remain gaps. Do not infer corrected system gold totals before rebuilding and sensitivity analysis. No passenger/freight service denominator change in this commit.</t>
         </is>
       </c>
     </row>
@@ -20679,7 +20683,7 @@
     <row r="1032">
       <c r="A1032" t="inlineStr">
         <is>
-          <t>traction converter, medium-voltage rail engineering reference</t>
+          <t xml:space="preserve">traction converter production, rail, medium voltage</t>
         </is>
       </c>
       <c r="B1032">
@@ -20702,7 +20706,7 @@
       </c>
       <c r="G1032" t="inlineStr">
         <is>
-          <t>traction converter, medium-voltage rail engineering reference</t>
+          <t xml:space="preserve">traction converter, rail, medium voltage</t>
         </is>
       </c>
     </row>
@@ -20889,7 +20893,7 @@
     <row r="1039">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>power semiconductor module, rail converter engineering reference</t>
+          <t xml:space="preserve">power semiconductor module production, rail converter</t>
         </is>
       </c>
       <c r="B1039">
@@ -20912,7 +20916,7 @@
       </c>
       <c r="G1039" t="inlineStr">
         <is>
-          <t>power semiconductor module, rail converter engineering reference</t>
+          <t xml:space="preserve">power semiconductor module, rail converter</t>
         </is>
       </c>
     </row>
@@ -21104,7 +21108,7 @@
       </c>
       <c r="B1048" t="inlineStr">
         <is>
-          <t>hydrogen fuel tank, rail700bar TypeIII cylinder, engineering reference</t>
+          <t xml:space="preserve">hydrogen fuel tank production, rail, type III cylinder, 700 bar</t>
         </is>
       </c>
     </row>
@@ -21138,7 +21142,7 @@
       </c>
       <c r="B1051" t="inlineStr">
         <is>
-          <t>hydrogen fuel tank, rail700bar TypeIII cylinder, engineering reference</t>
+          <t xml:space="preserve">hydrogen fuel tank, rail, type III cylinder, 700 bar</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21178,8 @@
       </c>
       <c r="B1054" t="inlineStr">
         <is>
-          <t>APPROVED RAIL-SPECIFIC700BAR STORAGE/LIFE REFERENCE, issue69,2026-10-18. FCH2RAIL D1.5 railstorage investigation,DLR2021,AnnexBTable20, https://elib.dlr.de/145010/1/FCH2RAIL_D1.5.pdf :TypeIII70MPaTPED surveyreference8.3kgH2,2048x455mm,333Loutervolume,179kgINCLUDINGgas =&gt;170.7kgdry. Supplier surveyreference is not a certifiedcompleteheavyhaullocomotive design. Preserve current700barworkingpressure and40yearrailmanufacturinghorizon; do not forcepassenger350barorroadbus/truckvessels intoheavyhaul. Existing30323.845714kg cumulativecar-TypeIIIproxy was4sets over40years,with93kgdry/5.6kgH2. Its impliedinstalledgas=oldmass/4*5.6/93=456.488kg. Retain thisimpliedenergy budget as explicitengineeringreference because no route-specificrefuellingrange is documented; not infergasinventory fromlifetimefuelthroughput. Select55surveycylinders*8.3=456.5kgH2capacity,roundingup only0.012kg. Sourcepreserved860kW/.06185kgH2perkWhe implies8.582hfullpower before reserve; actualroute/peakduty,reserveandrefilling range remainunvalidated. Keep10yearvessellife/foursets as existing conservativeassumption,NOT manufacturerlifecertificate;test10-20years ratherthan invent a lifetime saving. Cylinder dry170.7 excludes8.3kgfuel. MaterialBOMunpublished:6mmAl linerat2700kg/m3 overcapsulearea2*pi*outerradius*length,2kgstainlessbosses,2kgPAprotection,remainingCF/epoxy at60/40vol%(1800/1200kg/m3),69.2308wt%fiber. Outerdiametergeometry,linerthickness,actualalloy/fiber andpressurequalification areengineeringassumptions,not a certifiedpressurevessel design.95%materialretention withmatchingprocesswaste and1kWh/kgforming/curing reference; wovenfiber is filamentwindingmanufacturingproxy. Installedvesseldrymass9388.5kg. Dedicatedsharedrack500kg(one40yearset,80%ordinary steel/20%Al) and100kgvalve/manifold/controls(two20yearsets:50stainless,5Cu,5brass,10PA,29.5Al,0.5auxinterfaceboard) are explicitmountingassumptions; no wholelocomotive,tenderchassis ortrack added. Lifetimevesselmanufacture220units,one rack,twoBoPsets are inside oneunit oflifetimeenergy-equipmentreference. Qtyone atlocomotiveproduction,not count220again in perMJadapter. Nominalinstalledstorageenvelope55*.333=18.315m3beforemounting; availablelocomotive/tenderpackaging is unresolved and not asserted tofit. Preserveexistingroad/railoperatingfuel andcompression path;700barpressureunchanged,no unsubstantiatedcompressionenergy saving. Originalrangeandbodyenergy notresimulated. EOL remainswholevehicleboundary,pressurespecificcylinderrecovery gap,no credits. Refreshstoredhydrogenpassengerrailcoefficients andindependentlynormalizefreightrailservices.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: hydrogen fuel tank, rail700bar TypeIII cylinder, engineering reference. Former reference product: hydrogen fuel tank, rail700bar TypeIII cylinder, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED RAIL-SPECIFIC700BAR STORAGE/LIFE REFERENCE, issue69,2026-10-18. FCH2RAIL D1.5 railstorage investigation,DLR2021,AnnexBTable20, https://elib.dlr.de/145010/1/FCH2RAIL_D1.5.pdf :TypeIII70MPaTPED surveyreference8.3kgH2,2048x455mm,333Loutervolume,179kgINCLUDINGgas =&gt;170.7kgdry. Supplier surveyreference is not a certifiedcompleteheavyhaullocomotive design. Preserve current700barworkingpressure and40yearrailmanufacturinghorizon; do not forcepassenger350barorroadbus/truckvessels intoheavyhaul. Existing30323.845714kg cumulativecar-TypeIIIproxy was4sets over40years,with93kgdry/5.6kgH2. Its impliedinstalledgas=oldmass/4*5.6/93=456.488kg. Retain thisimpliedenergy budget as explicitengineeringreference because no route-specificrefuellingrange is documented; not infergasinventory fromlifetimefuelthroughput. Select55surveycylinders*8.3=456.5kgH2capacity,roundingup only0.012kg. Sourcepreserved860kW/.06185kgH2perkWhe implies8.582hfullpower before reserve; actualroute/peakduty,reserveandrefilling range remainunvalidated. Keep10yearvessellife/foursets as existing conservativeassumption,NOT manufacturerlifecertificate;test10-20years ratherthan invent a lifetime saving. Cylinder dry170.7 excludes8.3kgfuel. MaterialBOMunpublished:6mmAl linerat2700kg/m3 overcapsulearea2*pi*outerradius*length,2kgstainlessbosses,2kgPAprotection,remainingCF/epoxy at60/40vol%(1800/1200kg/m3),69.2308wt%fiber. Outerdiametergeometry,linerthickness,actualalloy/fiber andpressurequalification areengineeringassumptions,not a certifiedpressurevessel design.95%materialretention withmatchingprocesswaste and1kWh/kgforming/curing reference; wovenfiber is filamentwindingmanufacturingproxy. Installedvesseldrymass9388.5kg. Dedicatedsharedrack500kg(one40yearset,80%ordinary steel/20%Al) and100kgvalve/manifold/controls(two20yearsets:50stainless,5Cu,5brass,10PA,29.5Al,0.5auxinterfaceboard) are explicitmountingassumptions; no wholelocomotive,tenderchassis ortrack added. Lifetimevesselmanufacture220units,one rack,twoBoPsets are inside oneunit oflifetimeenergy-equipmentreference. Qtyone atlocomotiveproduction,not count220again in perMJadapter. Nominalinstalledstorageenvelope55*.333=18.315m3beforemounting; availablelocomotive/tenderpackaging is unresolved and not asserted tofit. Preserveexistingroad/railoperatingfuel andcompression path;700barpressureunchanged,no unsubstantiatedcompressionenergy saving. Originalrangeandbodyenergy notresimulated. EOL remainswholevehicleboundary,pressurespecificcylinderrecovery gap,no credits. Refreshstoredhydrogenpassengerrailcoefficients andindependentlynormalizefreightrailservices.</t>
         </is>
       </c>
     </row>
@@ -21235,7 +21240,7 @@
     <row r="1057">
       <c r="A1057" t="inlineStr">
         <is>
-          <t>hydrogen fuel tank, rail700bar TypeIII cylinder, engineering reference</t>
+          <t xml:space="preserve">hydrogen fuel tank production, rail, type III cylinder, 700 bar</t>
         </is>
       </c>
       <c r="B1057">
@@ -21258,12 +21263,12 @@
       </c>
       <c r="G1057" t="inlineStr">
         <is>
-          <t>hydrogen fuel tank, rail700bar TypeIII cylinder, engineering reference</t>
+          <t xml:space="preserve">hydrogen fuel tank, rail, type III cylinder, 700 bar</t>
         </is>
       </c>
       <c r="I1057" t="inlineStr">
         <is>
-          <t>hydrogen fuel tank, rail700bar TypeIII cylinder, engineering reference</t>
+          <t xml:space="preserve">hydrogen fuel tank, rail, type III cylinder, 700 bar</t>
         </is>
       </c>
     </row>
@@ -21520,7 +21525,7 @@
       </c>
       <c r="B1067" t="inlineStr">
         <is>
-          <t>hydrogen fuel tank, rail mounting rack, engineering reference</t>
+          <t xml:space="preserve">hydrogen fuel tank mounting rack production, rail</t>
         </is>
       </c>
     </row>
@@ -21554,7 +21559,7 @@
       </c>
       <c r="B1070" t="inlineStr">
         <is>
-          <t>hydrogen fuel tank, rail mounting rack, engineering reference</t>
+          <t xml:space="preserve">hydrogen fuel tank mounting rack, rail</t>
         </is>
       </c>
     </row>
@@ -21590,7 +21595,8 @@
       </c>
       <c r="B1073" t="inlineStr">
         <is>
-          <t>APPROVED RAIL-SPECIFIC700BAR STORAGE/LIFE REFERENCE, issue69,2026-10-18. FCH2RAIL D1.5 railstorage investigation,DLR2021,AnnexBTable20, https://elib.dlr.de/145010/1/FCH2RAIL_D1.5.pdf :TypeIII70MPaTPED surveyreference8.3kgH2,2048x455mm,333Loutervolume,179kgINCLUDINGgas =&gt;170.7kgdry. Supplier surveyreference is not a certifiedcompleteheavyhaullocomotive design. Preserve current700barworkingpressure and40yearrailmanufacturinghorizon; do not forcepassenger350barorroadbus/truckvessels intoheavyhaul. Existing30323.845714kg cumulativecar-TypeIIIproxy was4sets over40years,with93kgdry/5.6kgH2. Its impliedinstalledgas=oldmass/4*5.6/93=456.488kg. Retain thisimpliedenergy budget as explicitengineeringreference because no route-specificrefuellingrange is documented; not infergasinventory fromlifetimefuelthroughput. Select55surveycylinders*8.3=456.5kgH2capacity,roundingup only0.012kg. Sourcepreserved860kW/.06185kgH2perkWhe implies8.582hfullpower before reserve; actualroute/peakduty,reserveandrefilling range remainunvalidated. Keep10yearvessellife/foursets as existing conservativeassumption,NOT manufacturerlifecertificate;test10-20years ratherthan invent a lifetime saving. Cylinder dry170.7 excludes8.3kgfuel. MaterialBOMunpublished:6mmAl linerat2700kg/m3 overcapsulearea2*pi*outerradius*length,2kgstainlessbosses,2kgPAprotection,remainingCF/epoxy at60/40vol%(1800/1200kg/m3),69.2308wt%fiber. Outerdiametergeometry,linerthickness,actualalloy/fiber andpressurequalification areengineeringassumptions,not a certifiedpressurevessel design.95%materialretention withmatchingprocesswaste and1kWh/kgforming/curing reference; wovenfiber is filamentwindingmanufacturingproxy. Installedvesseldrymass9388.5kg. Dedicatedsharedrack500kg(one40yearset,80%ordinary steel/20%Al) and100kgvalve/manifold/controls(two20yearsets:50stainless,5Cu,5brass,10PA,29.5Al,0.5auxinterfaceboard) are explicitmountingassumptions; no wholelocomotive,tenderchassis ortrack added. Lifetimevesselmanufacture220units,one rack,twoBoPsets are inside oneunit oflifetimeenergy-equipmentreference. Qtyone atlocomotiveproduction,not count220again in perMJadapter. Nominalinstalledstorageenvelope55*.333=18.315m3beforemounting; availablelocomotive/tenderpackaging is unresolved and not asserted tofit. Preserveexistingroad/railoperatingfuel andcompression path;700barpressureunchanged,no unsubstantiatedcompressionenergy saving. Originalrangeandbodyenergy notresimulated. EOL remainswholevehicleboundary,pressurespecificcylinderrecovery gap,no credits. Refreshstoredhydrogenpassengerrailcoefficients andindependentlynormalizefreightrailservices.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: hydrogen fuel tank, rail mounting rack, engineering reference. Former reference product: hydrogen fuel tank, rail mounting rack, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED RAIL-SPECIFIC700BAR STORAGE/LIFE REFERENCE, issue69,2026-10-18. FCH2RAIL D1.5 railstorage investigation,DLR2021,AnnexBTable20, https://elib.dlr.de/145010/1/FCH2RAIL_D1.5.pdf :TypeIII70MPaTPED surveyreference8.3kgH2,2048x455mm,333Loutervolume,179kgINCLUDINGgas =&gt;170.7kgdry. Supplier surveyreference is not a certifiedcompleteheavyhaullocomotive design. Preserve current700barworkingpressure and40yearrailmanufacturinghorizon; do not forcepassenger350barorroadbus/truckvessels intoheavyhaul. Existing30323.845714kg cumulativecar-TypeIIIproxy was4sets over40years,with93kgdry/5.6kgH2. Its impliedinstalledgas=oldmass/4*5.6/93=456.488kg. Retain thisimpliedenergy budget as explicitengineeringreference because no route-specificrefuellingrange is documented; not infergasinventory fromlifetimefuelthroughput. Select55surveycylinders*8.3=456.5kgH2capacity,roundingup only0.012kg. Sourcepreserved860kW/.06185kgH2perkWhe implies8.582hfullpower before reserve; actualroute/peakduty,reserveandrefilling range remainunvalidated. Keep10yearvessellife/foursets as existing conservativeassumption,NOT manufacturerlifecertificate;test10-20years ratherthan invent a lifetime saving. Cylinder dry170.7 excludes8.3kgfuel. MaterialBOMunpublished:6mmAl linerat2700kg/m3 overcapsulearea2*pi*outerradius*length,2kgstainlessbosses,2kgPAprotection,remainingCF/epoxy at60/40vol%(1800/1200kg/m3),69.2308wt%fiber. Outerdiametergeometry,linerthickness,actualalloy/fiber andpressurequalification areengineeringassumptions,not a certifiedpressurevessel design.95%materialretention withmatchingprocesswaste and1kWh/kgforming/curing reference; wovenfiber is filamentwindingmanufacturingproxy. Installedvesseldrymass9388.5kg. Dedicatedsharedrack500kg(one40yearset,80%ordinary steel/20%Al) and100kgvalve/manifold/controls(two20yearsets:50stainless,5Cu,5brass,10PA,29.5Al,0.5auxinterfaceboard) are explicitmountingassumptions; no wholelocomotive,tenderchassis ortrack added. Lifetimevesselmanufacture220units,one rack,twoBoPsets are inside oneunit oflifetimeenergy-equipmentreference. Qtyone atlocomotiveproduction,not count220again in perMJadapter. Nominalinstalledstorageenvelope55*.333=18.315m3beforemounting; availablelocomotive/tenderpackaging is unresolved and not asserted tofit. Preserveexistingroad/railoperatingfuel andcompression path;700barpressureunchanged,no unsubstantiatedcompressionenergy saving. Originalrangeandbodyenergy notresimulated. EOL remainswholevehicleboundary,pressurespecificcylinderrecovery gap,no credits. Refreshstoredhydrogenpassengerrailcoefficients andindependentlynormalizefreightrailservices.</t>
         </is>
       </c>
     </row>
@@ -21651,7 +21657,7 @@
     <row r="1076">
       <c r="A1076" t="inlineStr">
         <is>
-          <t>hydrogen fuel tank, rail mounting rack, engineering reference</t>
+          <t xml:space="preserve">hydrogen fuel tank mounting rack production, rail</t>
         </is>
       </c>
       <c r="B1076">
@@ -21674,12 +21680,12 @@
       </c>
       <c r="G1076" t="inlineStr">
         <is>
-          <t>hydrogen fuel tank, rail mounting rack, engineering reference</t>
+          <t xml:space="preserve">hydrogen fuel tank mounting rack, rail</t>
         </is>
       </c>
       <c r="I1076" t="inlineStr">
         <is>
-          <t>hydrogen fuel tank, rail mounting rack, engineering reference</t>
+          <t xml:space="preserve">hydrogen fuel tank mounting rack, rail</t>
         </is>
       </c>
     </row>
@@ -21761,7 +21767,7 @@
       </c>
       <c r="B1081" t="inlineStr">
         <is>
-          <t>hydrogen fuel tank, rail shared valves and controls, engineering reference</t>
+          <t xml:space="preserve">hydrogen fuel tank valve and control system production, rail</t>
         </is>
       </c>
     </row>
@@ -21795,7 +21801,7 @@
       </c>
       <c r="B1084" t="inlineStr">
         <is>
-          <t>hydrogen fuel tank, rail shared valves and controls, engineering reference</t>
+          <t xml:space="preserve">hydrogen fuel tank valve and control system, rail</t>
         </is>
       </c>
     </row>
@@ -21831,7 +21837,8 @@
       </c>
       <c r="B1087" t="inlineStr">
         <is>
-          <t>APPROVED RAIL-SPECIFIC700BAR STORAGE/LIFE REFERENCE, issue69,2026-10-18. FCH2RAIL D1.5 railstorage investigation,DLR2021,AnnexBTable20, https://elib.dlr.de/145010/1/FCH2RAIL_D1.5.pdf :TypeIII70MPaTPED surveyreference8.3kgH2,2048x455mm,333Loutervolume,179kgINCLUDINGgas =&gt;170.7kgdry. Supplier surveyreference is not a certifiedcompleteheavyhaullocomotive design. Preserve current700barworkingpressure and40yearrailmanufacturinghorizon; do not forcepassenger350barorroadbus/truckvessels intoheavyhaul. Existing30323.845714kg cumulativecar-TypeIIIproxy was4sets over40years,with93kgdry/5.6kgH2. Its impliedinstalledgas=oldmass/4*5.6/93=456.488kg. Retain thisimpliedenergy budget as explicitengineeringreference because no route-specificrefuellingrange is documented; not infergasinventory fromlifetimefuelthroughput. Select55surveycylinders*8.3=456.5kgH2capacity,roundingup only0.012kg. Sourcepreserved860kW/.06185kgH2perkWhe implies8.582hfullpower before reserve; actualroute/peakduty,reserveandrefilling range remainunvalidated. Keep10yearvessellife/foursets as existing conservativeassumption,NOT manufacturerlifecertificate;test10-20years ratherthan invent a lifetime saving. Cylinder dry170.7 excludes8.3kgfuel. MaterialBOMunpublished:6mmAl linerat2700kg/m3 overcapsulearea2*pi*outerradius*length,2kgstainlessbosses,2kgPAprotection,remainingCF/epoxy at60/40vol%(1800/1200kg/m3),69.2308wt%fiber. Outerdiametergeometry,linerthickness,actualalloy/fiber andpressurequalification areengineeringassumptions,not a certifiedpressurevessel design.95%materialretention withmatchingprocesswaste and1kWh/kgforming/curing reference; wovenfiber is filamentwindingmanufacturingproxy. Installedvesseldrymass9388.5kg. Dedicatedsharedrack500kg(one40yearset,80%ordinary steel/20%Al) and100kgvalve/manifold/controls(two20yearsets:50stainless,5Cu,5brass,10PA,29.5Al,0.5auxinterfaceboard) are explicitmountingassumptions; no wholelocomotive,tenderchassis ortrack added. Lifetimevesselmanufacture220units,one rack,twoBoPsets are inside oneunit oflifetimeenergy-equipmentreference. Qtyone atlocomotiveproduction,not count220again in perMJadapter. Nominalinstalledstorageenvelope55*.333=18.315m3beforemounting; availablelocomotive/tenderpackaging is unresolved and not asserted tofit. Preserveexistingroad/railoperatingfuel andcompression path;700barpressureunchanged,no unsubstantiatedcompressionenergy saving. Originalrangeandbodyenergy notresimulated. EOL remainswholevehicleboundary,pressurespecificcylinderrecovery gap,no credits. Refreshstoredhydrogenpassengerrailcoefficients andindependentlynormalizefreightrailservices.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: hydrogen fuel tank, rail shared valves and controls, engineering reference. Former reference product: hydrogen fuel tank, rail shared valves and controls, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED RAIL-SPECIFIC700BAR STORAGE/LIFE REFERENCE, issue69,2026-10-18. FCH2RAIL D1.5 railstorage investigation,DLR2021,AnnexBTable20, https://elib.dlr.de/145010/1/FCH2RAIL_D1.5.pdf :TypeIII70MPaTPED surveyreference8.3kgH2,2048x455mm,333Loutervolume,179kgINCLUDINGgas =&gt;170.7kgdry. Supplier surveyreference is not a certifiedcompleteheavyhaullocomotive design. Preserve current700barworkingpressure and40yearrailmanufacturinghorizon; do not forcepassenger350barorroadbus/truckvessels intoheavyhaul. Existing30323.845714kg cumulativecar-TypeIIIproxy was4sets over40years,with93kgdry/5.6kgH2. Its impliedinstalledgas=oldmass/4*5.6/93=456.488kg. Retain thisimpliedenergy budget as explicitengineeringreference because no route-specificrefuellingrange is documented; not infergasinventory fromlifetimefuelthroughput. Select55surveycylinders*8.3=456.5kgH2capacity,roundingup only0.012kg. Sourcepreserved860kW/.06185kgH2perkWhe implies8.582hfullpower before reserve; actualroute/peakduty,reserveandrefilling range remainunvalidated. Keep10yearvessellife/foursets as existing conservativeassumption,NOT manufacturerlifecertificate;test10-20years ratherthan invent a lifetime saving. Cylinder dry170.7 excludes8.3kgfuel. MaterialBOMunpublished:6mmAl linerat2700kg/m3 overcapsulearea2*pi*outerradius*length,2kgstainlessbosses,2kgPAprotection,remainingCF/epoxy at60/40vol%(1800/1200kg/m3),69.2308wt%fiber. Outerdiametergeometry,linerthickness,actualalloy/fiber andpressurequalification areengineeringassumptions,not a certifiedpressurevessel design.95%materialretention withmatchingprocesswaste and1kWh/kgforming/curing reference; wovenfiber is filamentwindingmanufacturingproxy. Installedvesseldrymass9388.5kg. Dedicatedsharedrack500kg(one40yearset,80%ordinary steel/20%Al) and100kgvalve/manifold/controls(two20yearsets:50stainless,5Cu,5brass,10PA,29.5Al,0.5auxinterfaceboard) are explicitmountingassumptions; no wholelocomotive,tenderchassis ortrack added. Lifetimevesselmanufacture220units,one rack,twoBoPsets are inside oneunit oflifetimeenergy-equipmentreference. Qtyone atlocomotiveproduction,not count220again in perMJadapter. Nominalinstalledstorageenvelope55*.333=18.315m3beforemounting; availablelocomotive/tenderpackaging is unresolved and not asserted tofit. Preserveexistingroad/railoperatingfuel andcompression path;700barpressureunchanged,no unsubstantiatedcompressionenergy saving. Originalrangeandbodyenergy notresimulated. EOL remainswholevehicleboundary,pressurespecificcylinderrecovery gap,no credits. Refreshstoredhydrogenpassengerrailcoefficients andindependentlynormalizefreightrailservices.</t>
         </is>
       </c>
     </row>
@@ -21892,7 +21899,7 @@
     <row r="1090">
       <c r="A1090" t="inlineStr">
         <is>
-          <t>hydrogen fuel tank, rail shared valves and controls, engineering reference</t>
+          <t xml:space="preserve">hydrogen fuel tank valve and control system production, rail</t>
         </is>
       </c>
       <c r="B1090">
@@ -21915,12 +21922,12 @@
       </c>
       <c r="G1090" t="inlineStr">
         <is>
-          <t>hydrogen fuel tank, rail shared valves and controls, engineering reference</t>
+          <t xml:space="preserve">hydrogen fuel tank valve and control system, rail</t>
         </is>
       </c>
       <c r="I1090" t="inlineStr">
         <is>
-          <t>hydrogen fuel tank, rail shared valves and controls, engineering reference</t>
+          <t xml:space="preserve">hydrogen fuel tank valve and control system, rail</t>
         </is>
       </c>
     </row>
@@ -22102,7 +22109,7 @@
     <row r="1096">
       <c r="A1096" t="inlineStr">
         <is>
-          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit production</t>
         </is>
       </c>
       <c r="B1096">
@@ -22125,12 +22132,12 @@
       </c>
       <c r="G1096" t="inlineStr">
         <is>
-          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit</t>
         </is>
       </c>
       <c r="I1096" t="inlineStr">
         <is>
-          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit</t>
         </is>
       </c>
     </row>
@@ -22142,7 +22149,7 @@
       </c>
       <c r="B1099" t="inlineStr">
         <is>
-          <t>hydrogen fuel tank system, rail700bar lifetime reference</t>
+          <t xml:space="preserve">hydrogen fuel tank system production, rail, 700 bar</t>
         </is>
       </c>
     </row>
@@ -22176,7 +22183,7 @@
       </c>
       <c r="B1102" t="inlineStr">
         <is>
-          <t>hydrogen fuel tank system, rail700bar lifetime reference</t>
+          <t xml:space="preserve">hydrogen fuel tank system, rail, 700 bar</t>
         </is>
       </c>
     </row>
@@ -22212,7 +22219,8 @@
       </c>
       <c r="B1105" t="inlineStr">
         <is>
-          <t>APPROVED RAIL-SPECIFIC700BAR STORAGE/LIFE REFERENCE, issue69,2026-10-18. FCH2RAIL D1.5 railstorage investigation,DLR2021,AnnexBTable20, https://elib.dlr.de/145010/1/FCH2RAIL_D1.5.pdf :TypeIII70MPaTPED surveyreference8.3kgH2,2048x455mm,333Loutervolume,179kgINCLUDINGgas =&gt;170.7kgdry. Supplier surveyreference is not a certifiedcompleteheavyhaullocomotive design. Preserve current700barworkingpressure and40yearrailmanufacturinghorizon; do not forcepassenger350barorroadbus/truckvessels intoheavyhaul. Existing30323.845714kg cumulativecar-TypeIIIproxy was4sets over40years,with93kgdry/5.6kgH2. Its impliedinstalledgas=oldmass/4*5.6/93=456.488kg. Retain thisimpliedenergy budget as explicitengineeringreference because no route-specificrefuellingrange is documented; not infergasinventory fromlifetimefuelthroughput. Select55surveycylinders*8.3=456.5kgH2capacity,roundingup only0.012kg. Sourcepreserved860kW/.06185kgH2perkWhe implies8.582hfullpower before reserve; actualroute/peakduty,reserveandrefilling range remainunvalidated. Keep10yearvessellife/foursets as existing conservativeassumption,NOT manufacturerlifecertificate;test10-20years ratherthan invent a lifetime saving. Cylinder dry170.7 excludes8.3kgfuel. MaterialBOMunpublished:6mmAl linerat2700kg/m3 overcapsulearea2*pi*outerradius*length,2kgstainlessbosses,2kgPAprotection,remainingCF/epoxy at60/40vol%(1800/1200kg/m3),69.2308wt%fiber. Outerdiametergeometry,linerthickness,actualalloy/fiber andpressurequalification areengineeringassumptions,not a certifiedpressurevessel design.95%materialretention withmatchingprocesswaste and1kWh/kgforming/curing reference; wovenfiber is filamentwindingmanufacturingproxy. Installedvesseldrymass9388.5kg. Dedicatedsharedrack500kg(one40yearset,80%ordinary steel/20%Al) and100kgvalve/manifold/controls(two20yearsets:50stainless,5Cu,5brass,10PA,29.5Al,0.5auxinterfaceboard) are explicitmountingassumptions; no wholelocomotive,tenderchassis ortrack added. Lifetimevesselmanufacture220units,one rack,twoBoPsets are inside oneunit oflifetimeenergy-equipmentreference. Qtyone atlocomotiveproduction,not count220again in perMJadapter. Nominalinstalledstorageenvelope55*.333=18.315m3beforemounting; availablelocomotive/tenderpackaging is unresolved and not asserted tofit. Preserveexistingroad/railoperatingfuel andcompression path;700barpressureunchanged,no unsubstantiatedcompressionenergy saving. Originalrangeandbodyenergy notresimulated. EOL remainswholevehicleboundary,pressurespecificcylinderrecovery gap,no credits. Refreshstoredhydrogenpassengerrailcoefficients andindependentlynormalizefreightrailservices.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: hydrogen fuel tank system, rail700bar lifetime reference. Former reference product: hydrogen fuel tank system, rail700bar lifetime reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED RAIL-SPECIFIC700BAR STORAGE/LIFE REFERENCE, issue69,2026-10-18. FCH2RAIL D1.5 railstorage investigation,DLR2021,AnnexBTable20, https://elib.dlr.de/145010/1/FCH2RAIL_D1.5.pdf :TypeIII70MPaTPED surveyreference8.3kgH2,2048x455mm,333Loutervolume,179kgINCLUDINGgas =&gt;170.7kgdry. Supplier surveyreference is not a certifiedcompleteheavyhaullocomotive design. Preserve current700barworkingpressure and40yearrailmanufacturinghorizon; do not forcepassenger350barorroadbus/truckvessels intoheavyhaul. Existing30323.845714kg cumulativecar-TypeIIIproxy was4sets over40years,with93kgdry/5.6kgH2. Its impliedinstalledgas=oldmass/4*5.6/93=456.488kg. Retain thisimpliedenergy budget as explicitengineeringreference because no route-specificrefuellingrange is documented; not infergasinventory fromlifetimefuelthroughput. Select55surveycylinders*8.3=456.5kgH2capacity,roundingup only0.012kg. Sourcepreserved860kW/.06185kgH2perkWhe implies8.582hfullpower before reserve; actualroute/peakduty,reserveandrefilling range remainunvalidated. Keep10yearvessellife/foursets as existing conservativeassumption,NOT manufacturerlifecertificate;test10-20years ratherthan invent a lifetime saving. Cylinder dry170.7 excludes8.3kgfuel. MaterialBOMunpublished:6mmAl linerat2700kg/m3 overcapsulearea2*pi*outerradius*length,2kgstainlessbosses,2kgPAprotection,remainingCF/epoxy at60/40vol%(1800/1200kg/m3),69.2308wt%fiber. Outerdiametergeometry,linerthickness,actualalloy/fiber andpressurequalification areengineeringassumptions,not a certifiedpressurevessel design.95%materialretention withmatchingprocesswaste and1kWh/kgforming/curing reference; wovenfiber is filamentwindingmanufacturingproxy. Installedvesseldrymass9388.5kg. Dedicatedsharedrack500kg(one40yearset,80%ordinary steel/20%Al) and100kgvalve/manifold/controls(two20yearsets:50stainless,5Cu,5brass,10PA,29.5Al,0.5auxinterfaceboard) are explicitmountingassumptions; no wholelocomotive,tenderchassis ortrack added. Lifetimevesselmanufacture220units,one rack,twoBoPsets are inside oneunit oflifetimeenergy-equipmentreference. Qtyone atlocomotiveproduction,not count220again in perMJadapter. Nominalinstalledstorageenvelope55*.333=18.315m3beforemounting; availablelocomotive/tenderpackaging is unresolved and not asserted tofit. Preserveexistingroad/railoperatingfuel andcompression path;700barpressureunchanged,no unsubstantiatedcompressionenergy saving. Originalrangeandbodyenergy notresimulated. EOL remainswholevehicleboundary,pressurespecificcylinderrecovery gap,no credits. Refreshstoredhydrogenpassengerrailcoefficients andindependentlynormalizefreightrailservices.</t>
         </is>
       </c>
     </row>
@@ -22273,7 +22281,7 @@
     <row r="1108">
       <c r="A1108" t="inlineStr">
         <is>
-          <t>hydrogen fuel tank system, rail700bar lifetime reference</t>
+          <t xml:space="preserve">hydrogen fuel tank system production, rail, 700 bar</t>
         </is>
       </c>
       <c r="B1108">
@@ -22296,19 +22304,19 @@
       </c>
       <c r="G1108" t="inlineStr">
         <is>
-          <t>hydrogen fuel tank system, rail700bar lifetime reference</t>
+          <t xml:space="preserve">hydrogen fuel tank system, rail, 700 bar</t>
         </is>
       </c>
       <c r="I1108" t="inlineStr">
         <is>
-          <t>hydrogen fuel tank system, rail700bar lifetime reference</t>
+          <t xml:space="preserve">hydrogen fuel tank system, rail, 700 bar</t>
         </is>
       </c>
     </row>
     <row r="1109">
       <c r="A1109" t="inlineStr">
         <is>
-          <t>hydrogen fuel tank, rail700bar TypeIII cylinder, engineering reference</t>
+          <t xml:space="preserve">hydrogen fuel tank production, rail, type III cylinder, 700 bar</t>
         </is>
       </c>
       <c r="B1109">
@@ -22331,19 +22339,19 @@
       </c>
       <c r="G1109" t="inlineStr">
         <is>
-          <t>hydrogen fuel tank, rail700bar TypeIII cylinder, engineering reference</t>
+          <t xml:space="preserve">hydrogen fuel tank, rail, type III cylinder, 700 bar</t>
         </is>
       </c>
       <c r="I1109" t="inlineStr">
         <is>
-          <t>hydrogen fuel tank, rail700bar TypeIII cylinder, engineering reference</t>
+          <t xml:space="preserve">hydrogen fuel tank, rail, type III cylinder, 700 bar</t>
         </is>
       </c>
     </row>
     <row r="1110">
       <c r="A1110" t="inlineStr">
         <is>
-          <t>hydrogen fuel tank, rail mounting rack, engineering reference</t>
+          <t xml:space="preserve">hydrogen fuel tank mounting rack production, rail</t>
         </is>
       </c>
       <c r="B1110">
@@ -22366,19 +22374,19 @@
       </c>
       <c r="G1110" t="inlineStr">
         <is>
-          <t>hydrogen fuel tank, rail mounting rack, engineering reference</t>
+          <t xml:space="preserve">hydrogen fuel tank mounting rack, rail</t>
         </is>
       </c>
       <c r="I1110" t="inlineStr">
         <is>
-          <t>hydrogen fuel tank, rail mounting rack, engineering reference</t>
+          <t xml:space="preserve">hydrogen fuel tank mounting rack, rail</t>
         </is>
       </c>
     </row>
     <row r="1111">
       <c r="A1111" t="inlineStr">
         <is>
-          <t>hydrogen fuel tank, rail shared valves and controls, engineering reference</t>
+          <t xml:space="preserve">hydrogen fuel tank valve and control system production, rail</t>
         </is>
       </c>
       <c r="B1111">
@@ -22401,12 +22409,12 @@
       </c>
       <c r="G1111" t="inlineStr">
         <is>
-          <t>hydrogen fuel tank, rail shared valves and controls, engineering reference</t>
+          <t xml:space="preserve">hydrogen fuel tank valve and control system, rail</t>
         </is>
       </c>
       <c r="I1111" t="inlineStr">
         <is>
-          <t>hydrogen fuel tank, rail shared valves and controls, engineering reference</t>
+          <t xml:space="preserve">hydrogen fuel tank valve and control system, rail</t>
         </is>
       </c>
     </row>
@@ -22418,7 +22426,7 @@
       </c>
       <c r="B1114" t="inlineStr">
         <is>
-          <t>rail generator analog excitation controller, engineering material reference</t>
+          <t xml:space="preserve">excitation controller production, rail generator, analog</t>
         </is>
       </c>
     </row>
@@ -22452,7 +22460,7 @@
       </c>
       <c r="B1117" t="inlineStr">
         <is>
-          <t>rail generator analog excitation controller, engineering material reference</t>
+          <t xml:space="preserve">excitation controller, rail generator, analog</t>
         </is>
       </c>
     </row>
@@ -22488,7 +22496,8 @@
       </c>
       <c r="B1120" t="inlineStr">
         <is>
-          <t>APPROVED RAIL GENERATOR FUNCTION AND RATING, issue104,2026-10-18. ABB NMG catalogue9AKK2017109096:page10 continuous60Hz40C,pf0.8,NMG0500DD04 DAPI 3590kVA/2872kW at460V;page17 net7050kg,gross7730kg. OldNMG0450DD04 at460V60Hz is2072kW,not2.8MW. https://search.abb.com/library/Download.aspx?DocumentID=9AKK2017109096&amp;LanguageCode=en&amp;DocumentPartId=&amp;Action=Launch . Material analogue:ABB AMG0900 5125kVA11kV EPD2000 pages2-3,https://library.e.abb.com/public/2bb39d909d618031c1256d63003c5c76/EPD%20for%20AMG%20900.pdf . Use kg/product column; kg/kVA column is visibly misaligned. Existing locomotive buys4410kg of unspecified passive electronics as a generator proxy; native mixture assigns153.468kg tantalum-capacitor packages,NOT elementalTa. Replace with7050kg of a dedicated synchronous powertrain-generator engineering reference. Selected industrial model rated2872kW is sufficient for the stated2800kW duty at460V/60Hz/pf0.8. This is not a rail-qualified UKlight generator or proof of compatible BORDLINE DC-link voltage:actual rail speed/voltage,rectification,EMC,cooling and mass require project-specific verification. Source mass is not scaled linearly fromkVA. Keep original40year generator allocation as a service assumption; EPD25year operation is not transferred as measured rail life. Test mass4410/7050/9000kg and20-40year service; keep operating diesel demand unchanged. Material composition is transferred PERkg from the much heavier,11kV medium-speed AMG0900,not claimed a published NMG BOM:kg/product={'electricalsteel': 7120.0, 'steel': 10900.0, 'forgedsteel': 5323.0, 'Al': 13.0, 'Cu': 2461.0, 'insulation': 155.0, 'resin': 225.0, 'paint': 40.0},installed total26237kg excluding800kg wood. Reserve1kg of the7050kg budget for an explicit analog excitation/AVR material reference; scale the remaining7049kg by these normalized fractions. The1kg AVR partition is an engineering allocation,not manufacturer traceability. Electricalsteel uses the existing3.2%Si reference;other/forgedsteel generic lowalloy feed,insulation glassfibre,impregnation epoxy,paint alkyd are stated material proxies. Existing electricalsteel rolling stays in its supplier;do not add a second generic metalworking energy package. EPD manufacturing40122kWh electricity and9659kWh heat per26237kg provide an aggregate factory-energy reference perkg,not operating losses. Potential factory/service overlap,forging details,lamination yield and actual coating remain gaps. AVR reference1kg contains0.05m2 unmountedPWB at assumed3.08kg/m2,6glassdiodes at0.596g,50gchoke,30gfilmcapacitor,10gmetalfilmresistors,5gSMTtransistors,100gCu,400gAl,100gepoxy andremainingsteel. This is an explicit analog material budget,not validated excitation circuit or a universal zeroTa/PM claim. Wound-field generator excitation is represented by the winding material budget;no unsupported full-machine permanent magnets. Full7050kg generator goes once toWEEE;AVR has no extra disposal. Native WEEE treatment is a proxy,not recoveryshare analysis. Gross-minus-net680kg shipping-package composition unresolved and excluded from installed mass;do not assign it invented metals. Rewire six passenger-train perMJ copies and provenance with unchanged lifetime-energy denominator;source generator kg increases7050/4410. Traction converter,motor,engine,tank,chassis and track unchanged. Only existing rail/final-energy workbooks;no runtime or native edits.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: rail generator analog excitation controller, engineering material reference. Former reference product: rail generator analog excitation controller, engineering material reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED RAIL GENERATOR FUNCTION AND RATING, issue104,2026-10-18. ABB NMG catalogue9AKK2017109096:page10 continuous60Hz40C,pf0.8,NMG0500DD04 DAPI 3590kVA/2872kW at460V;page17 net7050kg,gross7730kg. OldNMG0450DD04 at460V60Hz is2072kW,not2.8MW. https://search.abb.com/library/Download.aspx?DocumentID=9AKK2017109096&amp;LanguageCode=en&amp;DocumentPartId=&amp;Action=Launch . Material analogue:ABB AMG0900 5125kVA11kV EPD2000 pages2-3,https://library.e.abb.com/public/2bb39d909d618031c1256d63003c5c76/EPD%20for%20AMG%20900.pdf . Use kg/product column; kg/kVA column is visibly misaligned. Existing locomotive buys4410kg of unspecified passive electronics as a generator proxy; native mixture assigns153.468kg tantalum-capacitor packages,NOT elementalTa. Replace with7050kg of a dedicated synchronous powertrain-generator engineering reference. Selected industrial model rated2872kW is sufficient for the stated2800kW duty at460V/60Hz/pf0.8. This is not a rail-qualified UKlight generator or proof of compatible BORDLINE DC-link voltage:actual rail speed/voltage,rectification,EMC,cooling and mass require project-specific verification. Source mass is not scaled linearly fromkVA. Keep original40year generator allocation as a service assumption; EPD25year operation is not transferred as measured rail life. Test mass4410/7050/9000kg and20-40year service; keep operating diesel demand unchanged. Material composition is transferred PERkg from the much heavier,11kV medium-speed AMG0900,not claimed a published NMG BOM:kg/product={'electricalsteel': 7120.0, 'steel': 10900.0, 'forgedsteel': 5323.0, 'Al': 13.0, 'Cu': 2461.0, 'insulation': 155.0, 'resin': 225.0, 'paint': 40.0},installed total26237kg excluding800kg wood. Reserve1kg of the7050kg budget for an explicit analog excitation/AVR material reference; scale the remaining7049kg by these normalized fractions. The1kg AVR partition is an engineering allocation,not manufacturer traceability. Electricalsteel uses the existing3.2%Si reference;other/forgedsteel generic lowalloy feed,insulation glassfibre,impregnation epoxy,paint alkyd are stated material proxies. Existing electricalsteel rolling stays in its supplier;do not add a second generic metalworking energy package. EPD manufacturing40122kWh electricity and9659kWh heat per26237kg provide an aggregate factory-energy reference perkg,not operating losses. Potential factory/service overlap,forging details,lamination yield and actual coating remain gaps. AVR reference1kg contains0.05m2 unmountedPWB at assumed3.08kg/m2,6glassdiodes at0.596g,50gchoke,30gfilmcapacitor,10gmetalfilmresistors,5gSMTtransistors,100gCu,400gAl,100gepoxy andremainingsteel. This is an explicit analog material budget,not validated excitation circuit or a universal zeroTa/PM claim. Wound-field generator excitation is represented by the winding material budget;no unsupported full-machine permanent magnets. Full7050kg generator goes once toWEEE;AVR has no extra disposal. Native WEEE treatment is a proxy,not recoveryshare analysis. Gross-minus-net680kg shipping-package composition unresolved and excluded from installed mass;do not assign it invented metals. Rewire six passenger-train perMJ copies and provenance with unchanged lifetime-energy denominator;source generator kg increases7050/4410. Traction converter,motor,engine,tank,chassis and track unchanged. Only existing rail/final-energy workbooks;no runtime or native edits.</t>
         </is>
       </c>
     </row>
@@ -22549,7 +22558,7 @@
     <row r="1123">
       <c r="A1123" t="inlineStr">
         <is>
-          <t>rail generator analog excitation controller, engineering material reference</t>
+          <t xml:space="preserve">excitation controller production, rail generator, analog</t>
         </is>
       </c>
       <c r="B1123">
@@ -22572,12 +22581,12 @@
       </c>
       <c r="G1123" t="inlineStr">
         <is>
-          <t>rail generator analog excitation controller, engineering material reference</t>
+          <t xml:space="preserve">excitation controller, rail generator, analog</t>
         </is>
       </c>
       <c r="I1123" t="inlineStr">
         <is>
-          <t>rail generator analog excitation controller, engineering material reference</t>
+          <t xml:space="preserve">excitation controller, rail generator, analog</t>
         </is>
       </c>
     </row>
@@ -22974,7 +22983,7 @@
       </c>
       <c r="B1137" t="inlineStr">
         <is>
-          <t>rail powertrain generator, synchronous engineering reference</t>
+          <t xml:space="preserve">traction generator production, synchronous, rail</t>
         </is>
       </c>
     </row>
@@ -23008,7 +23017,7 @@
       </c>
       <c r="B1140" t="inlineStr">
         <is>
-          <t>rail powertrain generator, synchronous engineering reference</t>
+          <t xml:space="preserve">traction generator, synchronous, rail</t>
         </is>
       </c>
     </row>
@@ -23044,7 +23053,8 @@
       </c>
       <c r="B1143" t="inlineStr">
         <is>
-          <t>APPROVED RAIL GENERATOR FUNCTION AND RATING, issue104,2026-10-18. ABB NMG catalogue9AKK2017109096:page10 continuous60Hz40C,pf0.8,NMG0500DD04 DAPI 3590kVA/2872kW at460V;page17 net7050kg,gross7730kg. OldNMG0450DD04 at460V60Hz is2072kW,not2.8MW. https://search.abb.com/library/Download.aspx?DocumentID=9AKK2017109096&amp;LanguageCode=en&amp;DocumentPartId=&amp;Action=Launch . Material analogue:ABB AMG0900 5125kVA11kV EPD2000 pages2-3,https://library.e.abb.com/public/2bb39d909d618031c1256d63003c5c76/EPD%20for%20AMG%20900.pdf . Use kg/product column; kg/kVA column is visibly misaligned. Existing locomotive buys4410kg of unspecified passive electronics as a generator proxy; native mixture assigns153.468kg tantalum-capacitor packages,NOT elementalTa. Replace with7050kg of a dedicated synchronous powertrain-generator engineering reference. Selected industrial model rated2872kW is sufficient for the stated2800kW duty at460V/60Hz/pf0.8. This is not a rail-qualified UKlight generator or proof of compatible BORDLINE DC-link voltage:actual rail speed/voltage,rectification,EMC,cooling and mass require project-specific verification. Source mass is not scaled linearly fromkVA. Keep original40year generator allocation as a service assumption; EPD25year operation is not transferred as measured rail life. Test mass4410/7050/9000kg and20-40year service; keep operating diesel demand unchanged. Material composition is transferred PERkg from the much heavier,11kV medium-speed AMG0900,not claimed a published NMG BOM:kg/product={'electricalsteel': 7120.0, 'steel': 10900.0, 'forgedsteel': 5323.0, 'Al': 13.0, 'Cu': 2461.0, 'insulation': 155.0, 'resin': 225.0, 'paint': 40.0},installed total26237kg excluding800kg wood. Reserve1kg of the7050kg budget for an explicit analog excitation/AVR material reference; scale the remaining7049kg by these normalized fractions. The1kg AVR partition is an engineering allocation,not manufacturer traceability. Electricalsteel uses the existing3.2%Si reference;other/forgedsteel generic lowalloy feed,insulation glassfibre,impregnation epoxy,paint alkyd are stated material proxies. Existing electricalsteel rolling stays in its supplier;do not add a second generic metalworking energy package. EPD manufacturing40122kWh electricity and9659kWh heat per26237kg provide an aggregate factory-energy reference perkg,not operating losses. Potential factory/service overlap,forging details,lamination yield and actual coating remain gaps. AVR reference1kg contains0.05m2 unmountedPWB at assumed3.08kg/m2,6glassdiodes at0.596g,50gchoke,30gfilmcapacitor,10gmetalfilmresistors,5gSMTtransistors,100gCu,400gAl,100gepoxy andremainingsteel. This is an explicit analog material budget,not validated excitation circuit or a universal zeroTa/PM claim. Wound-field generator excitation is represented by the winding material budget;no unsupported full-machine permanent magnets. Full7050kg generator goes once toWEEE;AVR has no extra disposal. Native WEEE treatment is a proxy,not recoveryshare analysis. Gross-minus-net680kg shipping-package composition unresolved and excluded from installed mass;do not assign it invented metals. Rewire six passenger-train perMJ copies and provenance with unchanged lifetime-energy denominator;source generator kg increases7050/4410. Traction converter,motor,engine,tank,chassis and track unchanged. Only existing rail/final-energy workbooks;no runtime or native edits.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: rail powertrain generator, synchronous engineering reference. Former reference product: rail powertrain generator, synchronous engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED RAIL GENERATOR FUNCTION AND RATING, issue104,2026-10-18. ABB NMG catalogue9AKK2017109096:page10 continuous60Hz40C,pf0.8,NMG0500DD04 DAPI 3590kVA/2872kW at460V;page17 net7050kg,gross7730kg. OldNMG0450DD04 at460V60Hz is2072kW,not2.8MW. https://search.abb.com/library/Download.aspx?DocumentID=9AKK2017109096&amp;LanguageCode=en&amp;DocumentPartId=&amp;Action=Launch . Material analogue:ABB AMG0900 5125kVA11kV EPD2000 pages2-3,https://library.e.abb.com/public/2bb39d909d618031c1256d63003c5c76/EPD%20for%20AMG%20900.pdf . Use kg/product column; kg/kVA column is visibly misaligned. Existing locomotive buys4410kg of unspecified passive electronics as a generator proxy; native mixture assigns153.468kg tantalum-capacitor packages,NOT elementalTa. Replace with7050kg of a dedicated synchronous powertrain-generator engineering reference. Selected industrial model rated2872kW is sufficient for the stated2800kW duty at460V/60Hz/pf0.8. This is not a rail-qualified UKlight generator or proof of compatible BORDLINE DC-link voltage:actual rail speed/voltage,rectification,EMC,cooling and mass require project-specific verification. Source mass is not scaled linearly fromkVA. Keep original40year generator allocation as a service assumption; EPD25year operation is not transferred as measured rail life. Test mass4410/7050/9000kg and20-40year service; keep operating diesel demand unchanged. Material composition is transferred PERkg from the much heavier,11kV medium-speed AMG0900,not claimed a published NMG BOM:kg/product={'electricalsteel': 7120.0, 'steel': 10900.0, 'forgedsteel': 5323.0, 'Al': 13.0, 'Cu': 2461.0, 'insulation': 155.0, 'resin': 225.0, 'paint': 40.0},installed total26237kg excluding800kg wood. Reserve1kg of the7050kg budget for an explicit analog excitation/AVR material reference; scale the remaining7049kg by these normalized fractions. The1kg AVR partition is an engineering allocation,not manufacturer traceability. Electricalsteel uses the existing3.2%Si reference;other/forgedsteel generic lowalloy feed,insulation glassfibre,impregnation epoxy,paint alkyd are stated material proxies. Existing electricalsteel rolling stays in its supplier;do not add a second generic metalworking energy package. EPD manufacturing40122kWh electricity and9659kWh heat per26237kg provide an aggregate factory-energy reference perkg,not operating losses. Potential factory/service overlap,forging details,lamination yield and actual coating remain gaps. AVR reference1kg contains0.05m2 unmountedPWB at assumed3.08kg/m2,6glassdiodes at0.596g,50gchoke,30gfilmcapacitor,10gmetalfilmresistors,5gSMTtransistors,100gCu,400gAl,100gepoxy andremainingsteel. This is an explicit analog material budget,not validated excitation circuit or a universal zeroTa/PM claim. Wound-field generator excitation is represented by the winding material budget;no unsupported full-machine permanent magnets. Full7050kg generator goes once toWEEE;AVR has no extra disposal. Native WEEE treatment is a proxy,not recoveryshare analysis. Gross-minus-net680kg shipping-package composition unresolved and excluded from installed mass;do not assign it invented metals. Rewire six passenger-train perMJ copies and provenance with unchanged lifetime-energy denominator;source generator kg increases7050/4410. Traction converter,motor,engine,tank,chassis and track unchanged. Only existing rail/final-energy workbooks;no runtime or native edits.</t>
         </is>
       </c>
     </row>
@@ -23105,7 +23115,7 @@
     <row r="1146">
       <c r="A1146" t="inlineStr">
         <is>
-          <t>rail powertrain generator, synchronous engineering reference</t>
+          <t xml:space="preserve">traction generator production, synchronous, rail</t>
         </is>
       </c>
       <c r="B1146">
@@ -23128,19 +23138,19 @@
       </c>
       <c r="G1146" t="inlineStr">
         <is>
-          <t>rail powertrain generator, synchronous engineering reference</t>
+          <t xml:space="preserve">traction generator, synchronous, rail</t>
         </is>
       </c>
       <c r="I1146" t="inlineStr">
         <is>
-          <t>rail powertrain generator, synchronous engineering reference</t>
+          <t xml:space="preserve">traction generator, synchronous, rail</t>
         </is>
       </c>
     </row>
     <row r="1147">
       <c r="A1147" t="inlineStr">
         <is>
-          <t>non-oriented electrical steel, engineering alloy reference</t>
+          <t xml:space="preserve">electrical steel production, non-oriented</t>
         </is>
       </c>
       <c r="B1147">
@@ -23163,12 +23173,12 @@
       </c>
       <c r="G1147" t="inlineStr">
         <is>
-          <t>non-oriented electrical steel, engineering alloy reference</t>
+          <t xml:space="preserve">electrical steel, non-oriented</t>
         </is>
       </c>
       <c r="I1147" t="inlineStr">
         <is>
-          <t>non-oriented electrical steel, engineering alloy reference</t>
+          <t xml:space="preserve">electrical steel, non-oriented</t>
         </is>
       </c>
     </row>
@@ -23385,7 +23395,7 @@
     <row r="1154">
       <c r="A1154" t="inlineStr">
         <is>
-          <t>rail generator analog excitation controller, engineering material reference</t>
+          <t xml:space="preserve">excitation controller production, rail generator, analog</t>
         </is>
       </c>
       <c r="B1154">
@@ -23408,12 +23418,12 @@
       </c>
       <c r="G1154" t="inlineStr">
         <is>
-          <t>rail generator analog excitation controller, engineering material reference</t>
+          <t xml:space="preserve">excitation controller, rail generator, analog</t>
         </is>
       </c>
       <c r="I1154" t="inlineStr">
         <is>
-          <t>rail generator analog excitation controller, engineering material reference</t>
+          <t xml:space="preserve">excitation controller, rail generator, analog</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-rail-freight.xlsx
+++ b/premise/data/additional_inventories/lci-rail-freight.xlsx
@@ -2093,11 +2093,11 @@
     <row r="47" spans="1:8" ns3:dyDescent="0.2">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuel cell system assembly production, rail transport</t>
+          <t xml:space="preserve">fuel cell system assembly production, rail transport, 860 kWe</t>
         </is>
       </c>
       <c r="B47">
-        <v>6880</v>
+        <v>8.0</v>
       </c>
       <c r="C47" t="s">
         <v>3</v>
@@ -2110,12 +2110,13 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuel cell system assembly, rail transport</t>
+          <t xml:space="preserve">fuel cell system assembly, rail transport, 860 kWe</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>APPROVED SINGLE RAIL FUEL-CELL REPLACEMENT BUDGET, item29, 2026-10-18. Knibbe2023 DOI10.1016/j.est.2023.108090, owner rail reference860kW/30000hstack and240000hoperation; Stropnik2022 DOI10.1016/j.ijhydene.2022.04.011 BoP20000h. Existing owner buys860kW*240000/30000=6880kW-equivalent system sets. Generic assembly additionally buys20000/3800=5.2631579stacks, yielding42.105stack sets over owner life. Introduce rail-specific assembly per1kWe owner set:one existing generic manufactured stack (not generic lifetime assembly) and30000/20000=1.5genericBoP units. Therefore owner lifetime has8stacksets and12BoPsets, each budget applied once.30000h railstack life is the existing heavy-haul engineering assumption, not a demonstrated lightvehicle stack endurance; retain it explicitly rather than silently importing3800h. BoP20000h is a source-based engineering durability proxy; fractional1.5 is expected lifetime attribution, not an instantaneous1.5BoP installation. Stack and BoP manufacture/source grades/size proxies remain unchanged; generic stack remains eligible for existing future catalyst updates. No new platinum loading or primary/secondary curve. Heavy-haul power/duty/passenger representativeness, storage and battery design remain separate gaps. Existing860kW and6880owner quantity retained; the explicit final-energy hydrogen passenger-rail purchase relinked; other rail service inherits its locomotive supplier so old cached assembly identity cannot persist.</t>
+          <t xml:space="preserve">APPROVED REFERENCE-UNIT CORRECTION, 2026-10-19. Current reference: One complete 860 kWe rail fuel-cell system, retaining the existing stack/BoP replacement attribution. Unit field: unit. Former reference: 1 unit = 0.0011627906976744186 unit on the current basis. All supplier/product references and direct purchasers are updated together. Recipes are divided by this conversion factor and consumer doses multiplied by it; physical inputs, emissions and waste per original functional unit are preserved. One complete 860 kWe system uses 860 one-kWe stack references and 1290 one-kWe BoP references over the existing 30000 h stack interval. The locomotive buys eight lifetime system sets, preserving eight full-power stack sets and twelve full-power BoP sets. Its per-MJ purchase and structured allocation provenance are divided by 860. Fractional BoP remains expected lifetime attribution. No new unit vocabulary, design, lifetime, manufacturing yield, recycling credit, primary/secondary share or runtime code change. Earlier source notes below retain their historical normalization; the current reference and amounts above supersede that normalization.
+APPROVED SINGLE RAIL FUEL-CELL REPLACEMENT BUDGET, item29, 2026-10-18. Knibbe2023 DOI10.1016/j.est.2023.108090, owner rail reference860kW/30000hstack and240000hoperation; Stropnik2022 DOI10.1016/j.ijhydene.2022.04.011 BoP20000h. Existing owner buys860kW*240000/30000=6880kW-equivalent system sets. Generic assembly additionally buys20000/3800=5.2631579stacks, yielding42.105stack sets over owner life. Introduce rail-specific assembly per1kWe owner set:one existing generic manufactured stack (not generic lifetime assembly) and30000/20000=1.5genericBoP units. Therefore owner lifetime has8stacksets and12BoPsets, each budget applied once.30000h railstack life is the existing heavy-haul engineering assumption, not a demonstrated lightvehicle stack endurance; retain it explicitly rather than silently importing3800h. BoP20000h is a source-based engineering durability proxy; fractional1.5 is expected lifetime attribution, not an instantaneous1.5BoP installation. Stack and BoP manufacture/source grades/size proxies remain unchanged; generic stack remains eligible for existing future catalyst updates. No new platinum loading or primary/secondary curve. Heavy-haul power/duty/passenger representativeness, storage and battery design remain separate gaps. Existing860kW and6880owner quantity retained; the explicit final-energy hydrogen passenger-rail purchase relinked; other rail service inherits its locomotive supplier so old cached assembly identity cannot persist.</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-rail-freight.xlsx
+++ b/premise/data/additional_inventories/lci-rail-freight.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$983</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$984</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1359,7 +1359,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{2A08E695-FC79-4DF0-ACCB-3B3F78317B74}">
-  <dimension ref="A1:Z1157"/>
+  <dimension ref="A1:Z1167"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="61.83203125" customWidth="1"/>
@@ -2093,7 +2093,7 @@
     <row r="47" spans="1:8" ns3:dyDescent="0.2">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuel cell system assembly production, rail transport, 860 kWe</t>
+          <t xml:space="preserve">fuel cell system assembly production, rail transport, 860 kwe</t>
         </is>
       </c>
       <c r="B47">
@@ -2156,7 +2156,7 @@
     <row r="49" spans="1:8" ns3:dyDescent="0.2">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">market for electricity storage capacity, battery, Li-ion, LFP, hydrogen train</t>
+          <t xml:space="preserve">market for electricity storage capacity, battery, lithium-ion, lfp, hydrogen train</t>
         </is>
       </c>
       <c r="B49">
@@ -19579,90 +19579,72 @@
     <row r="975">
       <c r="A975" t="inlineStr">
         <is>
-          <t>Exchanges</t>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t xml:space="preserve">processwithreferenceproduct</t>
         </is>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="inlineStr">
         <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B976" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C976" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D976" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E976" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F976" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G976" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H976" t="inlineStr">
-        <is>
-          <t>comment</t>
+          <t>Exchanges</t>
         </is>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="inlineStr">
         <is>
-          <t xml:space="preserve">electrical steel production, non-oriented</t>
-        </is>
-      </c>
-      <c r="B977">
-        <v>1</v>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
       </c>
       <c r="C977" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>location</t>
         </is>
       </c>
       <c r="D977" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E977" t="inlineStr">
+        <is>
+          <t>categories</t>
         </is>
       </c>
       <c r="F977" t="inlineStr">
         <is>
-          <t>production</t>
+          <t>type</t>
         </is>
       </c>
       <c r="G977" t="inlineStr">
         <is>
-          <t xml:space="preserve">electrical steel, non-oriented</t>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H977" t="inlineStr">
+        <is>
+          <t>comment</t>
         </is>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="inlineStr">
         <is>
-          <t>market for steel, low-alloyed</t>
+          <t xml:space="preserve">electrical steel production, non-oriented</t>
         </is>
       </c>
       <c r="B978">
-        <v>0.9573333333333334</v>
+        <v>1</v>
       </c>
       <c r="C978" t="inlineStr">
         <is>
@@ -19676,23 +19658,23 @@
       </c>
       <c r="F978" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>production</t>
         </is>
       </c>
       <c r="G978" t="inlineStr">
         <is>
-          <t>steel, low-alloyed</t>
+          <t xml:space="preserve">electrical steel, non-oriented</t>
         </is>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="inlineStr">
         <is>
-          <t>market for ferrosilicon</t>
+          <t>market for steel, low-alloyed</t>
         </is>
       </c>
       <c r="B979">
-        <v>0.042666666666666665</v>
+        <v>0.9573333333333334</v>
       </c>
       <c r="C979" t="inlineStr">
         <is>
@@ -19711,240 +19693,222 @@
       </c>
       <c r="G979" t="inlineStr">
         <is>
-          <t>ferrosilicon</t>
+          <t>steel, low-alloyed</t>
         </is>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="inlineStr">
         <is>
+          <t>market for ferrosilicon</t>
+        </is>
+      </c>
+      <c r="B980">
+        <v>0.042666666666666665</v>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F980" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G980" t="inlineStr">
+        <is>
+          <t>ferrosilicon</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
           <t>sheet rolling, steel</t>
         </is>
       </c>
-      <c r="B980">
+      <c r="B981">
         <v>1</v>
       </c>
-      <c r="C980" t="inlineStr">
+      <c r="C981" t="inlineStr">
         <is>
           <t>RER</t>
         </is>
       </c>
-      <c r="D980" t="inlineStr">
+      <c r="D981" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F980" t="inlineStr">
+      <c r="F981" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G980" t="inlineStr">
+      <c r="G981" t="inlineStr">
         <is>
           <t>sheet rolling, steel</t>
-        </is>
-      </c>
-    </row>
-    <row r="983">
-      <c r="A983" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B983" t="inlineStr">
-        <is>
-          <t xml:space="preserve">electric motor production, asynchronous, traction</t>
         </is>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B984" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t xml:space="preserve">electric motor production, asynchronous, traction</t>
         </is>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="inlineStr">
         <is>
-          <t>production amount</t>
-        </is>
-      </c>
-      <c r="B985">
-        <v>1</v>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="inlineStr">
         <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="B986" t="inlineStr">
-        <is>
-          <t xml:space="preserve">electric motor, asynchronous, traction</t>
-        </is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B986">
+        <v>1</v>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>reference product</t>
         </is>
       </c>
       <c r="B987" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t xml:space="preserve">electric motor, asynchronous, traction</t>
         </is>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="B988" t="inlineStr">
         <is>
-          <t>Hsieh etal2026 DOI10.1007/s11367-026-02610-7, SI FigureS7 IM2 and TableS11; ABB2017 Re460 asynchronous traction https://library.e.abb.com/public/bfe91c518ff94330a3c591b4bbeb8b6a/65-69%201m6073_EN_72dpi.pdf</t>
+          <t>kilogram</t>
         </is>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="inlineStr">
         <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>Hsieh etal2026 DOI10.1007/s11367-026-02610-7, SI FigureS7 IM2 and TableS11; ABB2017 Re460 asynchronous traction https://library.e.abb.com/public/bfe91c518ff94330a3c591b4bbeb8b6a/65-69%201m6073_EN_72dpi.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B989" t="inlineStr">
+      <c r="B990" t="inlineStr">
         <is>
           <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: electric motor, asynchronous traction, engineering reference. Former reference product: electric motor, asynchronous traction, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED ASYNCHRONOUS TRACTION ENGINEERING REFERENCE, item19, 2026-10-18. Hsieh etal2026 DOI10.1007/s11367-026-02610-7, SI FigureS7 IM2 and TableS11; ABB2017 Re460 asynchronous traction https://library.e.abb.com/public/bfe91c518ff94330a3c591b4bbeb8b6a/65-69%201m6073_EN_72dpi.pdf. Use the IM2 Cu-stator/Al-rotor induction design: source FigureS7 rounded masspercent Al37.4, electricalsteel46.3, Cu10.0, lowalloysteel3.93, coating/insulation2.42 (sum100.05). Divide these full-composition shares by100.05 to resolve rounding. TableS11 individual masses differ somewhat from the figure (source62.9kg motor); this reference explicitly adopts the complete figure composition, not a claim that both tables close exactly. No permanent magnets or Nd/Dy magnet-processing inputs are included by design; this does not prove zero rare-earth flows in upstream supply. Represent electrical steel as a3.2percentSi engineering alloy, assuming75percentSi ferrosilicon plus low-alloy steel balance, with sheet rolling; source source-specific steel grade, lamination scrap and non-oriented processing remain proxies. Coating uses epoxy resin; source electrical insulation is not fully specified. Generic metal working plus1kWh/kg final assembly electricity are explicit engineering process assumptions (sensitivity.3-3kWh/kg), not measured rail-motor factory data. Retain original rail installed motor masses, service lifetimes and per-MJ allocations; replace only the permanent-magnet passenger-car manufacturing composition. IM2 is a100kW passenger-car study extrapolated perkg to rail, not a rail-rated thermal/mechanical design. Rail nameplate/mass, actual motor efficiency, bearings/rotor fabrication losses, maintenance and EOL coverage remain gaps. No train chassis/track added. Rewire three source locomotive motor inputs and all explicit train/tram final-energy motor inputs; road vehicle motors remain unchanged. Align existing service-to-locomotive input product labels to their actual supplier reference products so the real scoped normalization can resolve the source production links; amounts and lifetime allocation are unchanged.</t>
         </is>
       </c>
     </row>
-    <row r="990">
-      <c r="A990" t="inlineStr">
-        <is>
-          <t>Exchanges</t>
-        </is>
-      </c>
-    </row>
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t>name</t>
+          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="B991" t="inlineStr">
         <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C991" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D991" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E991" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F991" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G991" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H991" t="inlineStr">
-        <is>
-          <t>comment</t>
+          <t xml:space="preserve">processwithreferenceproduct</t>
         </is>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="inlineStr">
         <is>
-          <t xml:space="preserve">electric motor production, asynchronous, traction</t>
-        </is>
-      </c>
-      <c r="B992">
-        <v>1</v>
-      </c>
-      <c r="C992" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D992" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F992" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="G992" t="inlineStr">
-        <is>
-          <t xml:space="preserve">electric motor, asynchronous, traction</t>
+          <t>Exchanges</t>
         </is>
       </c>
     </row>
     <row r="993">
       <c r="A993" t="inlineStr">
         <is>
-          <t>market for aluminium, wrought alloy</t>
-        </is>
-      </c>
-      <c r="B993">
-        <v>0.37381309345327335</v>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
       </c>
       <c r="C993" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>location</t>
         </is>
       </c>
       <c r="D993" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E993" t="inlineStr">
+        <is>
+          <t>categories</t>
         </is>
       </c>
       <c r="F993" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>type</t>
         </is>
       </c>
       <c r="G993" t="inlineStr">
         <is>
-          <t>aluminium, wrought alloy</t>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H993" t="inlineStr">
+        <is>
+          <t>comment</t>
         </is>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="inlineStr">
         <is>
-          <t xml:space="preserve">electrical steel production, non-oriented</t>
+          <t xml:space="preserve">electric motor production, asynchronous, traction</t>
         </is>
       </c>
       <c r="B994">
-        <v>0.4627686156921539</v>
+        <v>1</v>
       </c>
       <c r="C994" t="inlineStr">
         <is>
@@ -19958,23 +19922,23 @@
       </c>
       <c r="F994" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>production</t>
         </is>
       </c>
       <c r="G994" t="inlineStr">
         <is>
-          <t xml:space="preserve">electrical steel, non-oriented</t>
+          <t xml:space="preserve">electric motor, asynchronous, traction</t>
         </is>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="inlineStr">
         <is>
-          <t>market for copper, cathode</t>
+          <t>market for aluminium, wrought alloy</t>
         </is>
       </c>
       <c r="B995">
-        <v>0.09995002498750626</v>
+        <v>0.37381309345327335</v>
       </c>
       <c r="C995" t="inlineStr">
         <is>
@@ -19993,18 +19957,18 @@
       </c>
       <c r="G995" t="inlineStr">
         <is>
-          <t>copper, cathode</t>
+          <t>aluminium, wrought alloy</t>
         </is>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="inlineStr">
         <is>
-          <t>market for steel, low-alloyed</t>
+          <t xml:space="preserve">electrical steel production, non-oriented</t>
         </is>
       </c>
       <c r="B996">
-        <v>0.039280359820089955</v>
+        <v>0.4627686156921539</v>
       </c>
       <c r="C996" t="inlineStr">
         <is>
@@ -20023,22 +19987,22 @@
       </c>
       <c r="G996" t="inlineStr">
         <is>
-          <t>steel, low-alloyed</t>
+          <t xml:space="preserve">electrical steel, non-oriented</t>
         </is>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t>market for epoxy resin, liquid</t>
+          <t>market for copper, cathode</t>
         </is>
       </c>
       <c r="B997">
-        <v>0.02418790604697651</v>
+        <v>0.09995002498750626</v>
       </c>
       <c r="C997" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D997" t="inlineStr">
@@ -20053,22 +20017,22 @@
       </c>
       <c r="G997" t="inlineStr">
         <is>
-          <t>epoxy resin, liquid</t>
+          <t>copper, cathode</t>
         </is>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="inlineStr">
         <is>
-          <t>metal working, average for aluminium product manufacturing</t>
+          <t>market for steel, low-alloyed</t>
         </is>
       </c>
       <c r="B998">
-        <v>0.37381309345327335</v>
+        <v>0.039280359820089955</v>
       </c>
       <c r="C998" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D998" t="inlineStr">
@@ -20083,18 +20047,18 @@
       </c>
       <c r="G998" t="inlineStr">
         <is>
-          <t>metal working, average for aluminium product manufacturing</t>
+          <t>steel, low-alloyed</t>
         </is>
       </c>
     </row>
     <row r="999">
       <c r="A999" t="inlineStr">
         <is>
-          <t>metal working, average for copper product manufacturing</t>
+          <t>market for epoxy resin, liquid</t>
         </is>
       </c>
       <c r="B999">
-        <v>0.09995002498750626</v>
+        <v>0.02418790604697651</v>
       </c>
       <c r="C999" t="inlineStr">
         <is>
@@ -20113,18 +20077,18 @@
       </c>
       <c r="G999" t="inlineStr">
         <is>
-          <t>metal working, average for copper product manufacturing</t>
+          <t>epoxy resin, liquid</t>
         </is>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>metal working, average for steel product manufacturing</t>
+          <t>metal working, average for aluminium product manufacturing</t>
         </is>
       </c>
       <c r="B1000">
-        <v>0.5020489755122438</v>
+        <v>0.37381309345327335</v>
       </c>
       <c r="C1000" t="inlineStr">
         <is>
@@ -20143,274 +20107,256 @@
       </c>
       <c r="G1000" t="inlineStr">
         <is>
-          <t>metal working, average for steel product manufacturing</t>
+          <t>metal working, average for aluminium product manufacturing</t>
         </is>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="inlineStr">
         <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="B1001">
+        <v>0.09995002498750626</v>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1001" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1001" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="B1002">
+        <v>0.5020489755122438</v>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1002" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1002" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1002" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
           <t>market group for electricity, medium voltage</t>
         </is>
       </c>
-      <c r="B1001">
+      <c r="B1003">
         <v>1</v>
       </c>
-      <c r="C1001" t="inlineStr">
+      <c r="C1003" t="inlineStr">
         <is>
           <t>Europe without Switzerland</t>
         </is>
       </c>
-      <c r="D1001" t="inlineStr">
+      <c r="D1003" t="inlineStr">
         <is>
           <t>kilowatt hour</t>
         </is>
       </c>
-      <c r="F1001" t="inlineStr">
+      <c r="F1003" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G1001" t="inlineStr">
+      <c r="G1003" t="inlineStr">
         <is>
           <t>electricity, medium voltage</t>
-        </is>
-      </c>
-    </row>
-    <row r="1004">
-      <c r="A1004" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B1004" t="inlineStr">
-        <is>
-          <t xml:space="preserve">power semiconductor module production, rail converter</t>
-        </is>
-      </c>
-    </row>
-    <row r="1005">
-      <c r="A1005" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="B1005" t="inlineStr">
-        <is>
-          <t>GLO</t>
         </is>
       </c>
     </row>
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>production amount</t>
-        </is>
-      </c>
-      <c r="B1006">
-        <v>1</v>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t xml:space="preserve">power semiconductor module production, rail converter</t>
+        </is>
       </c>
     </row>
     <row r="1007">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>reference product</t>
+          <t>location</t>
         </is>
       </c>
       <c r="B1007" t="inlineStr">
         <is>
-          <t xml:space="preserve">power semiconductor module, rail converter</t>
+          <t>GLO</t>
         </is>
       </c>
     </row>
     <row r="1008">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="B1008" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1008">
+        <v>1</v>
       </c>
     </row>
     <row r="1009">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>reference product</t>
         </is>
       </c>
       <c r="B1009" t="inlineStr">
         <is>
-          <t>ABB2024 ACS6080 PEP ABBG-00712-V01.01-EN, marked Draft/Public, page7, https://library.e.abb.com/public/f0dd73990f0242ab9a0e88dbf6090edd/PEP_EPD_ACS6080_33AXD10002395301_RevA_EN_05122024.pdf; ABB BORDLINE masses/power retained from existing rail sources. Infineon FZ1500R33HE3 datasheet construction reference https://www.infineon.com/assets/row/public/documents/60/49/infineon-fz1500r33he3-datasheet-en.pdf.</t>
+          <t xml:space="preserve">power semiconductor module, rail converter</t>
         </is>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" t="inlineStr">
         <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>ABB2024 ACS6080 PEP ABBG-00712-V01.01-EN, marked Draft/Public, page7, https://library.e.abb.com/public/f0dd73990f0242ab9a0e88dbf6090edd/PEP_EPD_ACS6080_33AXD10002395301_RevA_EN_05122024.pdf; ABB BORDLINE masses/power retained from existing rail sources. Infineon FZ1500R33HE3 datasheet construction reference https://www.infineon.com/assets/row/public/documents/60/49/infineon-fz1500r33he3-datasheet-en.pdf.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B1010" t="inlineStr">
+      <c r="B1012" t="inlineStr">
         <is>
           <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: power semiconductor module, rail converter engineering reference. Former reference product: power semiconductor module, rail converter engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED RAIL CONVERTER ENGINEERING REFERENCE, item25, 2026-10-18. ABB2024 ACS6080 PEP ABBG-00712-V01.01-EN, marked Draft/Public, page7, https://library.e.abb.com/public/f0dd73990f0242ab9a0e88dbf6090edd/PEP_EPD_ACS6080_33AXD10002395301_RevA_EN_05122024.pdf; ABB BORDLINE masses/power retained from existing rail sources. Infineon FZ1500R33HE3 datasheet construction reference https://www.infineon.com/assets/row/public/documents/60/49/infineon-fz1500r33he3-datasheet-en.pdf. Replace the mass-scaled4.5kg car battery-voltage converter with an explicit medium-voltage AC-drive-based reference, not a measured BORDLINE BOM. ABB2024 draft PEP gives14583kg including packaging:steel43.4%,Cu20.4%,Al2.25%,GFRP1.7%,otherplastics0.4%,electroniccomponents12.9%,wood13.7%,other5.25%. Percentages sum100. Treat wood as packaging and exclude it from installed reference mass:hardware fraction0.863. Perkg installed converter divide other category fractions by0.863; purchase packaging wood0.137/0.863kg additionally. Source is an18MW industrial AC drive, not a rail-qualified product: composition transfer to BORDLINE is an explicit engineering analogue, with source installed masses and power/lifetime counts unchanged. Assume electronic component mass70%film capacitors,25%power semiconductor modules,5%populated control boards. These fractions are design assumptions; sensitivity capacitor50-80%, module10-40%, board2-10%, constrained to100%. Generic Pb-free through-hole board retains upstream precious metals; no zero-gold assumption. Illustrative power module retained recipe:Cu50%,Al10%,alumina20%,PPS10%,silicone8%,silicon die2%. Represent die fabrication by existing fabricated-IC-wafer service using300um silicon thickness and2330kg/m3 density:0.02/(2330*0.0003)m2/kgmodule. This wafer and power-module composition are engineering proxies, not Infineon material declarations or verified rail die technology. Module assembly1kWh/kg assumed. Film capacitor proxy includes its own constituent materials once. Other5.25%/0.863=6.08343% installed hardware mass remains compositionally UNRESOLVED and is not silently converted into zero metal or an arbitrary PCB. Known retained material coverage93.91657%; trace-metal completeness is not claimed.100%retention reference plus generic metal-working/1kWh final assembly perkg; yields, cooling coolant, additional cabling, end-of-life and rail qualification remain gaps. Do not infer corrected system gold totals before rebuilding and sensitivity analysis. No passenger/freight service denominator change in this commit.</t>
         </is>
       </c>
     </row>
-    <row r="1011">
-      <c r="A1011" t="inlineStr">
-        <is>
-          <t>Exchanges</t>
-        </is>
-      </c>
-    </row>
-    <row r="1012">
-      <c r="A1012" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B1012" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C1012" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D1012" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E1012" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F1012" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G1012" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H1012" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-    </row>
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t xml:space="preserve">power semiconductor module production, rail converter</t>
-        </is>
-      </c>
-      <c r="B1013">
-        <v>1</v>
-      </c>
-      <c r="C1013" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D1013" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F1013" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="G1013" t="inlineStr">
-        <is>
-          <t xml:space="preserve">power semiconductor module, rail converter</t>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t xml:space="preserve">processwithreferenceproduct</t>
         </is>
       </c>
     </row>
     <row r="1014">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>market for copper, cathode</t>
-        </is>
-      </c>
-      <c r="B1014">
-        <v>0.5</v>
-      </c>
-      <c r="C1014" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D1014" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F1014" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G1014" t="inlineStr">
-        <is>
-          <t>copper, cathode</t>
+          <t>Exchanges</t>
         </is>
       </c>
     </row>
     <row r="1015">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>market for aluminium, wrought alloy</t>
-        </is>
-      </c>
-      <c r="B1015">
-        <v>0.1</v>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
       </c>
       <c r="C1015" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>location</t>
         </is>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1015" t="inlineStr">
+        <is>
+          <t>categories</t>
         </is>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>type</t>
         </is>
       </c>
       <c r="G1015" t="inlineStr">
         <is>
-          <t>aluminium, wrought alloy</t>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1015" t="inlineStr">
+        <is>
+          <t>comment</t>
         </is>
       </c>
     </row>
     <row r="1016">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>market for aluminium oxide, non-metallurgical</t>
+          <t xml:space="preserve">power semiconductor module production, rail converter</t>
         </is>
       </c>
       <c r="B1016">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="C1016" t="inlineStr">
         <is>
-          <t>RoW</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D1016" t="inlineStr">
@@ -20420,23 +20366,23 @@
       </c>
       <c r="F1016" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>production</t>
         </is>
       </c>
       <c r="G1016" t="inlineStr">
         <is>
-          <t>aluminium oxide, non-metallurgical</t>
+          <t xml:space="preserve">power semiconductor module, rail converter</t>
         </is>
       </c>
     </row>
     <row r="1017">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>market for polyphenylene sulfide</t>
+          <t>market for copper, cathode</t>
         </is>
       </c>
       <c r="B1017">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="C1017" t="inlineStr">
         <is>
@@ -20455,22 +20401,22 @@
       </c>
       <c r="G1017" t="inlineStr">
         <is>
-          <t>polyphenylene sulfide</t>
+          <t>copper, cathode</t>
         </is>
       </c>
     </row>
     <row r="1018">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>market for silicone product</t>
+          <t>market for aluminium, wrought alloy</t>
         </is>
       </c>
       <c r="B1018">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="C1018" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D1018" t="inlineStr">
@@ -20485,27 +20431,27 @@
       </c>
       <c r="G1018" t="inlineStr">
         <is>
-          <t>silicone product</t>
+          <t>aluminium, wrought alloy</t>
         </is>
       </c>
     </row>
     <row r="1019">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>market for wafer, fabricated, for integrated circuit</t>
+          <t>market for aluminium oxide, non-metallurgical</t>
         </is>
       </c>
       <c r="B1019">
-        <v>0.028612303290414882</v>
+        <v>0.2</v>
       </c>
       <c r="C1019" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>RoW</t>
         </is>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
-          <t>square meter</t>
+          <t>kilogram</t>
         </is>
       </c>
       <c r="F1019" t="inlineStr">
@@ -20515,18 +20461,18 @@
       </c>
       <c r="G1019" t="inlineStr">
         <is>
-          <t>wafer, fabricated, for integrated circuit</t>
+          <t>aluminium oxide, non-metallurgical</t>
         </is>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>market group for electricity, medium voltage</t>
+          <t>market for polyphenylene sulfide</t>
         </is>
       </c>
       <c r="B1020">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="C1020" t="inlineStr">
         <is>
@@ -20535,7 +20481,7 @@
       </c>
       <c r="D1020" t="inlineStr">
         <is>
-          <t>kilowatt hour</t>
+          <t>kilogram</t>
         </is>
       </c>
       <c r="F1020" t="inlineStr">
@@ -20545,270 +20491,252 @@
       </c>
       <c r="G1020" t="inlineStr">
         <is>
-          <t>electricity, medium voltage</t>
+          <t>polyphenylene sulfide</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>market for silicone product</t>
+        </is>
+      </c>
+      <c r="B1021">
+        <v>0.08</v>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1021" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1021" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1021" t="inlineStr">
+        <is>
+          <t>silicone product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>market for wafer, fabricated, for integrated circuit</t>
+        </is>
+      </c>
+      <c r="B1022">
+        <v>0.028612303290414882</v>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>square meter</t>
+        </is>
+      </c>
+      <c r="F1022" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1022" t="inlineStr">
+        <is>
+          <t>wafer, fabricated, for integrated circuit</t>
         </is>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B1023" t="inlineStr">
-        <is>
-          <t xml:space="preserve">traction converter production, rail, medium voltage</t>
-        </is>
-      </c>
-    </row>
-    <row r="1024">
-      <c r="A1024" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="B1024" t="inlineStr">
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1023">
+        <v>1</v>
+      </c>
+      <c r="C1023" t="inlineStr">
         <is>
           <t>GLO</t>
         </is>
       </c>
-    </row>
-    <row r="1025">
-      <c r="A1025" t="inlineStr">
-        <is>
-          <t>production amount</t>
-        </is>
-      </c>
-      <c r="B1025">
-        <v>1</v>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1023" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1023" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
       </c>
     </row>
     <row r="1026">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>reference product</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B1026" t="inlineStr">
         <is>
-          <t xml:space="preserve">traction converter, rail, medium voltage</t>
+          <t xml:space="preserve">traction converter production, rail, medium voltage</t>
         </is>
       </c>
     </row>
     <row r="1027">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>location</t>
         </is>
       </c>
       <c r="B1027" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>GLO</t>
         </is>
       </c>
     </row>
     <row r="1028">
       <c r="A1028" t="inlineStr">
         <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="B1028" t="inlineStr">
-        <is>
-          <t>ABB2024 ACS6080 PEP ABBG-00712-V01.01-EN, marked Draft/Public, page7, https://library.e.abb.com/public/f0dd73990f0242ab9a0e88dbf6090edd/PEP_EPD_ACS6080_33AXD10002395301_RevA_EN_05122024.pdf; ABB BORDLINE masses/power retained from existing rail sources. Infineon FZ1500R33HE3 datasheet construction reference https://www.infineon.com/assets/row/public/documents/60/49/infineon-fz1500r33he3-datasheet-en.pdf.</t>
-        </is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1028">
+        <v>1</v>
       </c>
     </row>
     <row r="1029">
       <c r="A1029" t="inlineStr">
         <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t xml:space="preserve">traction converter, rail, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>ABB2024 ACS6080 PEP ABBG-00712-V01.01-EN, marked Draft/Public, page7, https://library.e.abb.com/public/f0dd73990f0242ab9a0e88dbf6090edd/PEP_EPD_ACS6080_33AXD10002395301_RevA_EN_05122024.pdf; ABB BORDLINE masses/power retained from existing rail sources. Infineon FZ1500R33HE3 datasheet construction reference https://www.infineon.com/assets/row/public/documents/60/49/infineon-fz1500r33he3-datasheet-en.pdf.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B1029" t="inlineStr">
+      <c r="B1032" t="inlineStr">
         <is>
           <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: traction converter, medium-voltage rail engineering reference. Former reference product: traction converter, medium-voltage rail engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED RAIL CONVERTER ENGINEERING REFERENCE, item25, 2026-10-18. ABB2024 ACS6080 PEP ABBG-00712-V01.01-EN, marked Draft/Public, page7, https://library.e.abb.com/public/f0dd73990f0242ab9a0e88dbf6090edd/PEP_EPD_ACS6080_33AXD10002395301_RevA_EN_05122024.pdf; ABB BORDLINE masses/power retained from existing rail sources. Infineon FZ1500R33HE3 datasheet construction reference https://www.infineon.com/assets/row/public/documents/60/49/infineon-fz1500r33he3-datasheet-en.pdf. Replace the mass-scaled4.5kg car battery-voltage converter with an explicit medium-voltage AC-drive-based reference, not a measured BORDLINE BOM. ABB2024 draft PEP gives14583kg including packaging:steel43.4%,Cu20.4%,Al2.25%,GFRP1.7%,otherplastics0.4%,electroniccomponents12.9%,wood13.7%,other5.25%. Percentages sum100. Treat wood as packaging and exclude it from installed reference mass:hardware fraction0.863. Perkg installed converter divide other category fractions by0.863; purchase packaging wood0.137/0.863kg additionally. Source is an18MW industrial AC drive, not a rail-qualified product: composition transfer to BORDLINE is an explicit engineering analogue, with source installed masses and power/lifetime counts unchanged. Assume electronic component mass70%film capacitors,25%power semiconductor modules,5%populated control boards. These fractions are design assumptions; sensitivity capacitor50-80%, module10-40%, board2-10%, constrained to100%. Generic Pb-free through-hole board retains upstream precious metals; no zero-gold assumption. Illustrative power module retained recipe:Cu50%,Al10%,alumina20%,PPS10%,silicone8%,silicon die2%. Represent die fabrication by existing fabricated-IC-wafer service using300um silicon thickness and2330kg/m3 density:0.02/(2330*0.0003)m2/kgmodule. This wafer and power-module composition are engineering proxies, not Infineon material declarations or verified rail die technology. Module assembly1kWh/kg assumed. Film capacitor proxy includes its own constituent materials once. Other5.25%/0.863=6.08343% installed hardware mass remains compositionally UNRESOLVED and is not silently converted into zero metal or an arbitrary PCB. Known retained material coverage93.91657%; trace-metal completeness is not claimed.100%retention reference plus generic metal-working/1kWh final assembly perkg; yields, cooling coolant, additional cabling, end-of-life and rail qualification remain gaps. Do not infer corrected system gold totals before rebuilding and sensitivity analysis. No passenger/freight service denominator change in this commit.</t>
         </is>
       </c>
     </row>
-    <row r="1030">
-      <c r="A1030" t="inlineStr">
-        <is>
-          <t>Exchanges</t>
-        </is>
-      </c>
-    </row>
-    <row r="1031">
-      <c r="A1031" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B1031" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C1031" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D1031" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E1031" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F1031" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G1031" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H1031" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-    </row>
-    <row r="1032">
-      <c r="A1032" t="inlineStr">
-        <is>
-          <t xml:space="preserve">traction converter production, rail, medium voltage</t>
-        </is>
-      </c>
-      <c r="B1032">
-        <v>1</v>
-      </c>
-      <c r="C1032" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D1032" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F1032" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="G1032" t="inlineStr">
-        <is>
-          <t xml:space="preserve">traction converter, rail, medium voltage</t>
-        </is>
-      </c>
-    </row>
     <row r="1033">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>market for steel, low-alloyed</t>
-        </is>
-      </c>
-      <c r="B1033">
-        <v>0.5028968713789108</v>
-      </c>
-      <c r="C1033" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D1033" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F1033" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G1033" t="inlineStr">
-        <is>
-          <t>steel, low-alloyed</t>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t xml:space="preserve">processwithreferenceproduct</t>
         </is>
       </c>
     </row>
     <row r="1034">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>market for copper, cathode</t>
-        </is>
-      </c>
-      <c r="B1034">
-        <v>0.23638470451911933</v>
-      </c>
-      <c r="C1034" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D1034" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F1034" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G1034" t="inlineStr">
-        <is>
-          <t>copper, cathode</t>
+          <t>Exchanges</t>
         </is>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="inlineStr">
         <is>
-          <t>market for aluminium, wrought alloy</t>
-        </is>
-      </c>
-      <c r="B1035">
-        <v>0.026071842410196985</v>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
       </c>
       <c r="C1035" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>location</t>
         </is>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1035" t="inlineStr">
+        <is>
+          <t>categories</t>
         </is>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>type</t>
         </is>
       </c>
       <c r="G1035" t="inlineStr">
         <is>
-          <t>aluminium, wrought alloy</t>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1035" t="inlineStr">
+        <is>
+          <t>comment</t>
         </is>
       </c>
     </row>
     <row r="1036">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>market for glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+          <t xml:space="preserve">traction converter production, rail, medium voltage</t>
         </is>
       </c>
       <c r="B1036">
-        <v>0.01969872537659328</v>
+        <v>1</v>
       </c>
       <c r="C1036" t="inlineStr">
         <is>
@@ -20822,23 +20750,23 @@
       </c>
       <c r="F1036" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>production</t>
         </is>
       </c>
       <c r="G1036" t="inlineStr">
         <is>
-          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+          <t xml:space="preserve">traction converter, rail, medium voltage</t>
         </is>
       </c>
     </row>
     <row r="1037">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>market for polyethylene, high density, granulate</t>
+          <t>market for steel, low-alloyed</t>
         </is>
       </c>
       <c r="B1037">
-        <v>0.004634994206257242</v>
+        <v>0.5028968713789108</v>
       </c>
       <c r="C1037" t="inlineStr">
         <is>
@@ -20857,18 +20785,18 @@
       </c>
       <c r="G1037" t="inlineStr">
         <is>
-          <t>polyethylene, high density, granulate</t>
+          <t>steel, low-alloyed</t>
         </is>
       </c>
     </row>
     <row r="1038">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>market for capacitor, film type, for through-hole mounting</t>
+          <t>market for copper, cathode</t>
         </is>
       </c>
       <c r="B1038">
-        <v>0.10463499420625723</v>
+        <v>0.23638470451911933</v>
       </c>
       <c r="C1038" t="inlineStr">
         <is>
@@ -20887,18 +20815,18 @@
       </c>
       <c r="G1038" t="inlineStr">
         <is>
-          <t>capacitor, film type, for through-hole mounting</t>
+          <t>copper, cathode</t>
         </is>
       </c>
     </row>
     <row r="1039">
       <c r="A1039" t="inlineStr">
         <is>
-          <t xml:space="preserve">power semiconductor module production, rail converter</t>
+          <t>market for aluminium, wrought alloy</t>
         </is>
       </c>
       <c r="B1039">
-        <v>0.037369640787949014</v>
+        <v>0.026071842410196985</v>
       </c>
       <c r="C1039" t="inlineStr">
         <is>
@@ -20917,18 +20845,18 @@
       </c>
       <c r="G1039" t="inlineStr">
         <is>
-          <t xml:space="preserve">power semiconductor module, rail converter</t>
+          <t>aluminium, wrought alloy</t>
         </is>
       </c>
     </row>
     <row r="1040">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>market for printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>market for glass fibre reinforced plastic, polyester resin, hand lay-up</t>
         </is>
       </c>
       <c r="B1040">
-        <v>0.0074739281575898035</v>
+        <v>0.01969872537659328</v>
       </c>
       <c r="C1040" t="inlineStr">
         <is>
@@ -20947,27 +20875,27 @@
       </c>
       <c r="G1040" t="inlineStr">
         <is>
-          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
         </is>
       </c>
     </row>
     <row r="1041">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>market for sawnwood, board, softwood, raw, dried (u=10%)</t>
+          <t>market for polyethylene, high density, granulate</t>
         </is>
       </c>
       <c r="B1041">
-        <v>0.0003174971031286211</v>
+        <v>0.004634994206257242</v>
       </c>
       <c r="C1041" t="inlineStr">
         <is>
-          <t>Europe without Switzerland</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
-          <t>cubic meter</t>
+          <t>kilogram</t>
         </is>
       </c>
       <c r="F1041" t="inlineStr">
@@ -20977,18 +20905,18 @@
       </c>
       <c r="G1041" t="inlineStr">
         <is>
-          <t>sawnwood, board, softwood, raw, dried (u=10%)</t>
+          <t>polyethylene, high density, granulate</t>
         </is>
       </c>
     </row>
     <row r="1042">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>market group for electricity, medium voltage</t>
+          <t>market for capacitor, film type, for through-hole mounting</t>
         </is>
       </c>
       <c r="B1042">
-        <v>1</v>
+        <v>0.10463499420625723</v>
       </c>
       <c r="C1042" t="inlineStr">
         <is>
@@ -20997,7 +20925,7 @@
       </c>
       <c r="D1042" t="inlineStr">
         <is>
-          <t>kilowatt hour</t>
+          <t>kilogram</t>
         </is>
       </c>
       <c r="F1042" t="inlineStr">
@@ -21007,22 +20935,22 @@
       </c>
       <c r="G1042" t="inlineStr">
         <is>
-          <t>electricity, medium voltage</t>
+          <t>capacitor, film type, for through-hole mounting</t>
         </is>
       </c>
     </row>
     <row r="1043">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>metal working, average for steel product manufacturing</t>
+          <t xml:space="preserve">power semiconductor module production, rail converter</t>
         </is>
       </c>
       <c r="B1043">
-        <v>0.5028968713789108</v>
+        <v>0.037369640787949014</v>
       </c>
       <c r="C1043" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D1043" t="inlineStr">
@@ -21037,22 +20965,22 @@
       </c>
       <c r="G1043" t="inlineStr">
         <is>
-          <t>metal working, average for steel product manufacturing</t>
+          <t xml:space="preserve">power semiconductor module, rail converter</t>
         </is>
       </c>
     </row>
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>metal working, average for copper product manufacturing</t>
+          <t>market for printed wiring board, through-hole mounted, unspecified, Pb free</t>
         </is>
       </c>
       <c r="B1044">
-        <v>0.23638470451911933</v>
+        <v>0.0074739281575898035</v>
       </c>
       <c r="C1044" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D1044" t="inlineStr">
@@ -21067,399 +20995,356 @@
       </c>
       <c r="G1044" t="inlineStr">
         <is>
-          <t>metal working, average for copper product manufacturing</t>
+          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
         </is>
       </c>
     </row>
     <row r="1045">
       <c r="A1045" t="inlineStr">
         <is>
-          <t>metal working, average for aluminium product manufacturing</t>
+          <t>market for sawnwood, board, softwood, raw, dried (u=10%)</t>
         </is>
       </c>
       <c r="B1045">
-        <v>0.026071842410196985</v>
+        <v>0.0003174971031286211</v>
       </c>
       <c r="C1045" t="inlineStr">
         <is>
+          <t>Europe without Switzerland</t>
+        </is>
+      </c>
+      <c r="D1045" t="inlineStr">
+        <is>
+          <t>cubic meter</t>
+        </is>
+      </c>
+      <c r="F1045" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1045" t="inlineStr">
+        <is>
+          <t>sawnwood, board, softwood, raw, dried (u=10%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1046">
+        <v>1</v>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1046" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1046" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1046" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="B1047">
+        <v>0.5028968713789108</v>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
           <t>RER</t>
         </is>
       </c>
-      <c r="D1045" t="inlineStr">
+      <c r="D1047" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F1045" t="inlineStr">
+      <c r="F1047" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G1045" t="inlineStr">
-        <is>
-          <t>metal working, average for aluminium product manufacturing</t>
+      <c r="G1047" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
         </is>
       </c>
     </row>
     <row r="1048">
       <c r="A1048" t="inlineStr">
         <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B1048" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hydrogen fuel tank production, rail, type III cylinder, 700 bar</t>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="B1048">
+        <v>0.23638470451911933</v>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1048" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1048" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1048" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
         </is>
       </c>
     </row>
     <row r="1049">
       <c r="A1049" t="inlineStr">
         <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="B1049" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-    </row>
-    <row r="1050">
-      <c r="A1050" t="inlineStr">
-        <is>
-          <t>production amount</t>
-        </is>
-      </c>
-      <c r="B1050">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="1051">
-      <c r="A1051" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="B1051" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hydrogen fuel tank, rail, type III cylinder, 700 bar</t>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="B1049">
+        <v>0.026071842410196985</v>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1049" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1049" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1049" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
         </is>
       </c>
     </row>
     <row r="1052">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B1052" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">hydrogen fuel tank production, rail, type 3 cylinder, 700 bar</t>
         </is>
       </c>
     </row>
     <row r="1053">
       <c r="A1053" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>location</t>
         </is>
       </c>
       <c r="B1053" t="inlineStr">
         <is>
-          <t>FCH2RAIL D1.5 railstorage investigation,DLR2021,AnnexBTable20, https://elib.dlr.de/145010/1/FCH2RAIL_D1.5.pdf :TypeIII70MPaTPED surveyreference8.3kgH2,2048x455mm,333Loutervolume,179kgINCLUDINGgas =&gt;170.7kgdry. Supplier surveyreference is not a certifiedcompleteheavyhaullocomotive design.</t>
+          <t>GLO</t>
         </is>
       </c>
     </row>
     <row r="1054">
       <c r="A1054" t="inlineStr">
         <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1054">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hydrogen fuel tank, rail, type III cylinder, 700 bar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>FCH2RAIL D1.5 railstorage investigation,DLR2021,AnnexBTable20, https://elib.dlr.de/145010/1/FCH2RAIL_D1.5.pdf :TypeIII70MPaTPED surveyreference8.3kgH2,2048x455mm,333Loutervolume,179kgINCLUDINGgas =&gt;170.7kgdry. Supplier surveyreference is not a certifiedcompleteheavyhaullocomotive design.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B1054" t="inlineStr">
+      <c r="B1058" t="inlineStr">
         <is>
           <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: hydrogen fuel tank, rail700bar TypeIII cylinder, engineering reference. Former reference product: hydrogen fuel tank, rail700bar TypeIII cylinder, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED RAIL-SPECIFIC700BAR STORAGE/LIFE REFERENCE, issue69,2026-10-18. FCH2RAIL D1.5 railstorage investigation,DLR2021,AnnexBTable20, https://elib.dlr.de/145010/1/FCH2RAIL_D1.5.pdf :TypeIII70MPaTPED surveyreference8.3kgH2,2048x455mm,333Loutervolume,179kgINCLUDINGgas =&gt;170.7kgdry. Supplier surveyreference is not a certifiedcompleteheavyhaullocomotive design. Preserve current700barworkingpressure and40yearrailmanufacturinghorizon; do not forcepassenger350barorroadbus/truckvessels intoheavyhaul. Existing30323.845714kg cumulativecar-TypeIIIproxy was4sets over40years,with93kgdry/5.6kgH2. Its impliedinstalledgas=oldmass/4*5.6/93=456.488kg. Retain thisimpliedenergy budget as explicitengineeringreference because no route-specificrefuellingrange is documented; not infergasinventory fromlifetimefuelthroughput. Select55surveycylinders*8.3=456.5kgH2capacity,roundingup only0.012kg. Sourcepreserved860kW/.06185kgH2perkWhe implies8.582hfullpower before reserve; actualroute/peakduty,reserveandrefilling range remainunvalidated. Keep10yearvessellife/foursets as existing conservativeassumption,NOT manufacturerlifecertificate;test10-20years ratherthan invent a lifetime saving. Cylinder dry170.7 excludes8.3kgfuel. MaterialBOMunpublished:6mmAl linerat2700kg/m3 overcapsulearea2*pi*outerradius*length,2kgstainlessbosses,2kgPAprotection,remainingCF/epoxy at60/40vol%(1800/1200kg/m3),69.2308wt%fiber. Outerdiametergeometry,linerthickness,actualalloy/fiber andpressurequalification areengineeringassumptions,not a certifiedpressurevessel design.95%materialretention withmatchingprocesswaste and1kWh/kgforming/curing reference; wovenfiber is filamentwindingmanufacturingproxy. Installedvesseldrymass9388.5kg. Dedicatedsharedrack500kg(one40yearset,80%ordinary steel/20%Al) and100kgvalve/manifold/controls(two20yearsets:50stainless,5Cu,5brass,10PA,29.5Al,0.5auxinterfaceboard) are explicitmountingassumptions; no wholelocomotive,tenderchassis ortrack added. Lifetimevesselmanufacture220units,one rack,twoBoPsets are inside oneunit oflifetimeenergy-equipmentreference. Qtyone atlocomotiveproduction,not count220again in perMJadapter. Nominalinstalledstorageenvelope55*.333=18.315m3beforemounting; availablelocomotive/tenderpackaging is unresolved and not asserted tofit. Preserveexistingroad/railoperatingfuel andcompression path;700barpressureunchanged,no unsubstantiatedcompressionenergy saving. Originalrangeandbodyenergy notresimulated. EOL remainswholevehicleboundary,pressurespecificcylinderrecovery gap,no credits. Refreshstoredhydrogenpassengerrailcoefficients andindependentlynormalizefreightrailservices.</t>
         </is>
       </c>
     </row>
-    <row r="1055">
-      <c r="A1055" t="inlineStr">
-        <is>
-          <t>Exchanges</t>
-        </is>
-      </c>
-    </row>
-    <row r="1056">
-      <c r="A1056" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B1056" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C1056" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D1056" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E1056" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F1056" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G1056" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H1056" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="I1056" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-    </row>
-    <row r="1057">
-      <c r="A1057" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hydrogen fuel tank production, rail, type III cylinder, 700 bar</t>
-        </is>
-      </c>
-      <c r="B1057">
-        <v>1</v>
-      </c>
-      <c r="C1057" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D1057" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="F1057" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="G1057" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hydrogen fuel tank, rail, type III cylinder, 700 bar</t>
-        </is>
-      </c>
-      <c r="I1057" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hydrogen fuel tank, rail, type III cylinder, 700 bar</t>
-        </is>
-      </c>
-    </row>
-    <row r="1058">
-      <c r="A1058" t="inlineStr">
-        <is>
-          <t>market for aluminium, wrought alloy</t>
-        </is>
-      </c>
-      <c r="B1058">
-        <v>49.92092580294951</v>
-      </c>
-      <c r="C1058" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D1058" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F1058" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G1058" t="inlineStr">
-        <is>
-          <t>aluminium, wrought alloy</t>
-        </is>
-      </c>
-      <c r="I1058" t="inlineStr">
-        <is>
-          <t>aluminium, wrought alloy</t>
-        </is>
-      </c>
-    </row>
     <row r="1059">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>carbon fiber production, weaved, at factory</t>
-        </is>
-      </c>
-      <c r="B1059">
-        <v>86.92114043601472</v>
-      </c>
-      <c r="C1059" t="inlineStr">
-        <is>
-          <t>RER</t>
-        </is>
-      </c>
-      <c r="D1059" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F1059" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G1059" t="inlineStr">
-        <is>
-          <t>carbon fiber, weaved</t>
-        </is>
-      </c>
-      <c r="I1059" t="inlineStr">
-        <is>
-          <t>carbon fiber, weaved</t>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t xml:space="preserve">processwithreferenceproduct</t>
         </is>
       </c>
     </row>
     <row r="1060">
       <c r="A1060" t="inlineStr">
         <is>
-          <t>market for epoxy resin, liquid</t>
-        </is>
-      </c>
-      <c r="B1060">
-        <v>38.63161797156208</v>
-      </c>
-      <c r="C1060" t="inlineStr">
-        <is>
-          <t>RER</t>
-        </is>
-      </c>
-      <c r="D1060" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F1060" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G1060" t="inlineStr">
-        <is>
-          <t>epoxy resin, liquid</t>
-        </is>
-      </c>
-      <c r="I1060" t="inlineStr">
-        <is>
-          <t>epoxy resin, liquid</t>
+          <t>Exchanges</t>
         </is>
       </c>
     </row>
     <row r="1061">
       <c r="A1061" t="inlineStr">
         <is>
-          <t>market for steel, chromium steel 18/8</t>
-        </is>
-      </c>
-      <c r="B1061">
-        <v>2.1052631578947367</v>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
       </c>
       <c r="C1061" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>location</t>
         </is>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1061" t="inlineStr">
+        <is>
+          <t>categories</t>
         </is>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>type</t>
         </is>
       </c>
       <c r="G1061" t="inlineStr">
         <is>
-          <t>steel, chromium steel 18/8</t>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1061" t="inlineStr">
+        <is>
+          <t>comment</t>
         </is>
       </c>
       <c r="I1061" t="inlineStr">
         <is>
-          <t>steel, chromium steel 18/8</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="1062">
       <c r="A1062" t="inlineStr">
         <is>
-          <t>market for nylon 6</t>
+          <t xml:space="preserve">hydrogen fuel tank production, rail, type 3 cylinder, 700 bar</t>
         </is>
       </c>
       <c r="B1062">
-        <v>2.1052631578947367</v>
+        <v>1</v>
       </c>
       <c r="C1062" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>production</t>
         </is>
       </c>
       <c r="G1062" t="inlineStr">
         <is>
-          <t>nylon 6</t>
+          <t xml:space="preserve">hydrogen fuel tank, rail, type III cylinder, 700 bar</t>
         </is>
       </c>
       <c r="I1062" t="inlineStr">
         <is>
-          <t>nylon 6</t>
+          <t xml:space="preserve">hydrogen fuel tank, rail, type III cylinder, 700 bar</t>
         </is>
       </c>
     </row>
     <row r="1063">
       <c r="A1063" t="inlineStr">
         <is>
-          <t>market for hazardous waste, for incineration</t>
+          <t>market for aluminium, wrought alloy</t>
         </is>
       </c>
       <c r="B1063">
-        <v>-8.98421052631578</v>
+        <v>49.92092580294951</v>
       </c>
       <c r="C1063" t="inlineStr">
         <is>
-          <t>RoW</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D1063" t="inlineStr">
@@ -21474,1446 +21359,1354 @@
       </c>
       <c r="G1063" t="inlineStr">
         <is>
-          <t>hazardous waste, for incineration</t>
+          <t>aluminium, wrought alloy</t>
         </is>
       </c>
       <c r="I1063" t="inlineStr">
         <is>
-          <t>hazardous waste, for incineration</t>
+          <t>aluminium, wrought alloy</t>
         </is>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" t="inlineStr">
         <is>
-          <t>market group for electricity, medium voltage</t>
+          <t>carbon fiber production, weaved, at factory</t>
         </is>
       </c>
       <c r="B1064">
-        <v>170.7</v>
+        <v>86.92114043601472</v>
       </c>
       <c r="C1064" t="inlineStr">
         <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1064" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1064" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1064" t="inlineStr">
+        <is>
+          <t>carbon fiber, weaved</t>
+        </is>
+      </c>
+      <c r="I1064" t="inlineStr">
+        <is>
+          <t>carbon fiber, weaved</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>market for epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="B1065">
+        <v>38.63161797156208</v>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1065" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1065" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1065" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="I1065" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>market for steel, chromium steel 18/8</t>
+        </is>
+      </c>
+      <c r="B1066">
+        <v>2.1052631578947367</v>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
           <t>GLO</t>
         </is>
       </c>
-      <c r="D1064" t="inlineStr">
-        <is>
-          <t>kilowatt hour</t>
-        </is>
-      </c>
-      <c r="F1064" t="inlineStr">
+      <c r="D1066" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1066" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G1064" t="inlineStr">
-        <is>
-          <t>electricity, medium voltage</t>
-        </is>
-      </c>
-      <c r="I1064" t="inlineStr">
-        <is>
-          <t>electricity, medium voltage</t>
+      <c r="G1066" t="inlineStr">
+        <is>
+          <t>steel, chromium steel 18/8</t>
+        </is>
+      </c>
+      <c r="I1066" t="inlineStr">
+        <is>
+          <t>steel, chromium steel 18/8</t>
         </is>
       </c>
     </row>
     <row r="1067">
       <c r="A1067" t="inlineStr">
         <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B1067" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hydrogen fuel tank mounting rack production, rail</t>
+          <t>market for nylon 6</t>
+        </is>
+      </c>
+      <c r="B1067">
+        <v>2.1052631578947367</v>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1067" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1067" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1067" t="inlineStr">
+        <is>
+          <t>nylon 6</t>
+        </is>
+      </c>
+      <c r="I1067" t="inlineStr">
+        <is>
+          <t>nylon 6</t>
         </is>
       </c>
     </row>
     <row r="1068">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="B1068" t="inlineStr">
-        <is>
-          <t>GLO</t>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B1068">
+        <v>-8.98421052631578</v>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1068" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1068" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I1068" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
         </is>
       </c>
     </row>
     <row r="1069">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>production amount</t>
+          <t>market group for electricity, medium voltage</t>
         </is>
       </c>
       <c r="B1069">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="1070">
-      <c r="A1070" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="B1070" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hydrogen fuel tank mounting rack, rail</t>
-        </is>
-      </c>
-    </row>
-    <row r="1071">
-      <c r="A1071" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="B1071" t="inlineStr">
-        <is>
-          <t>unit</t>
+        <v>170.7</v>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1069" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1069" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I1069" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
         </is>
       </c>
     </row>
     <row r="1072">
       <c r="A1072" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B1072" t="inlineStr">
         <is>
-          <t>FCH2RAIL D1.5 railstorage investigation,DLR2021,AnnexBTable20, https://elib.dlr.de/145010/1/FCH2RAIL_D1.5.pdf :TypeIII70MPaTPED surveyreference8.3kgH2,2048x455mm,333Loutervolume,179kgINCLUDINGgas =&gt;170.7kgdry. Supplier surveyreference is not a certifiedcompleteheavyhaullocomotive design.</t>
+          <t xml:space="preserve">hydrogen fuel tank mounting rack production, rail</t>
         </is>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" t="inlineStr">
         <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1074">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hydrogen fuel tank mounting rack, rail</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>FCH2RAIL D1.5 railstorage investigation,DLR2021,AnnexBTable20, https://elib.dlr.de/145010/1/FCH2RAIL_D1.5.pdf :TypeIII70MPaTPED surveyreference8.3kgH2,2048x455mm,333Loutervolume,179kgINCLUDINGgas =&gt;170.7kgdry. Supplier surveyreference is not a certifiedcompleteheavyhaullocomotive design.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B1073" t="inlineStr">
+      <c r="B1078" t="inlineStr">
         <is>
           <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: hydrogen fuel tank, rail mounting rack, engineering reference. Former reference product: hydrogen fuel tank, rail mounting rack, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED RAIL-SPECIFIC700BAR STORAGE/LIFE REFERENCE, issue69,2026-10-18. FCH2RAIL D1.5 railstorage investigation,DLR2021,AnnexBTable20, https://elib.dlr.de/145010/1/FCH2RAIL_D1.5.pdf :TypeIII70MPaTPED surveyreference8.3kgH2,2048x455mm,333Loutervolume,179kgINCLUDINGgas =&gt;170.7kgdry. Supplier surveyreference is not a certifiedcompleteheavyhaullocomotive design. Preserve current700barworkingpressure and40yearrailmanufacturinghorizon; do not forcepassenger350barorroadbus/truckvessels intoheavyhaul. Existing30323.845714kg cumulativecar-TypeIIIproxy was4sets over40years,with93kgdry/5.6kgH2. Its impliedinstalledgas=oldmass/4*5.6/93=456.488kg. Retain thisimpliedenergy budget as explicitengineeringreference because no route-specificrefuellingrange is documented; not infergasinventory fromlifetimefuelthroughput. Select55surveycylinders*8.3=456.5kgH2capacity,roundingup only0.012kg. Sourcepreserved860kW/.06185kgH2perkWhe implies8.582hfullpower before reserve; actualroute/peakduty,reserveandrefilling range remainunvalidated. Keep10yearvessellife/foursets as existing conservativeassumption,NOT manufacturerlifecertificate;test10-20years ratherthan invent a lifetime saving. Cylinder dry170.7 excludes8.3kgfuel. MaterialBOMunpublished:6mmAl linerat2700kg/m3 overcapsulearea2*pi*outerradius*length,2kgstainlessbosses,2kgPAprotection,remainingCF/epoxy at60/40vol%(1800/1200kg/m3),69.2308wt%fiber. Outerdiametergeometry,linerthickness,actualalloy/fiber andpressurequalification areengineeringassumptions,not a certifiedpressurevessel design.95%materialretention withmatchingprocesswaste and1kWh/kgforming/curing reference; wovenfiber is filamentwindingmanufacturingproxy. Installedvesseldrymass9388.5kg. Dedicatedsharedrack500kg(one40yearset,80%ordinary steel/20%Al) and100kgvalve/manifold/controls(two20yearsets:50stainless,5Cu,5brass,10PA,29.5Al,0.5auxinterfaceboard) are explicitmountingassumptions; no wholelocomotive,tenderchassis ortrack added. Lifetimevesselmanufacture220units,one rack,twoBoPsets are inside oneunit oflifetimeenergy-equipmentreference. Qtyone atlocomotiveproduction,not count220again in perMJadapter. Nominalinstalledstorageenvelope55*.333=18.315m3beforemounting; availablelocomotive/tenderpackaging is unresolved and not asserted tofit. Preserveexistingroad/railoperatingfuel andcompression path;700barpressureunchanged,no unsubstantiatedcompressionenergy saving. Originalrangeandbodyenergy notresimulated. EOL remainswholevehicleboundary,pressurespecificcylinderrecovery gap,no credits. Refreshstoredhydrogenpassengerrailcoefficients andindependentlynormalizefreightrailservices.</t>
         </is>
       </c>
     </row>
-    <row r="1074">
-      <c r="A1074" t="inlineStr">
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t xml:space="preserve">processwithreferenceproduct</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
         <is>
           <t>Exchanges</t>
-        </is>
-      </c>
-    </row>
-    <row r="1075">
-      <c r="A1075" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B1075" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C1075" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D1075" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E1075" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F1075" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G1075" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H1075" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="I1075" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-    </row>
-    <row r="1076">
-      <c r="A1076" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hydrogen fuel tank mounting rack production, rail</t>
-        </is>
-      </c>
-      <c r="B1076">
-        <v>1</v>
-      </c>
-      <c r="C1076" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D1076" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="F1076" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="G1076" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hydrogen fuel tank mounting rack, rail</t>
-        </is>
-      </c>
-      <c r="I1076" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hydrogen fuel tank mounting rack, rail</t>
-        </is>
-      </c>
-    </row>
-    <row r="1077">
-      <c r="A1077" t="inlineStr">
-        <is>
-          <t>market for steel, low-alloyed</t>
-        </is>
-      </c>
-      <c r="B1077">
-        <v>400</v>
-      </c>
-      <c r="C1077" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D1077" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F1077" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G1077" t="inlineStr">
-        <is>
-          <t>steel, low-alloyed</t>
-        </is>
-      </c>
-      <c r="I1077" t="inlineStr">
-        <is>
-          <t>steel, low-alloyed</t>
-        </is>
-      </c>
-    </row>
-    <row r="1078">
-      <c r="A1078" t="inlineStr">
-        <is>
-          <t>market for aluminium, wrought alloy</t>
-        </is>
-      </c>
-      <c r="B1078">
-        <v>100</v>
-      </c>
-      <c r="C1078" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D1078" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F1078" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G1078" t="inlineStr">
-        <is>
-          <t>aluminium, wrought alloy</t>
-        </is>
-      </c>
-      <c r="I1078" t="inlineStr">
-        <is>
-          <t>aluminium, wrought alloy</t>
         </is>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>name</t>
         </is>
       </c>
       <c r="B1081" t="inlineStr">
         <is>
-          <t xml:space="preserve">hydrogen fuel tank valve and control system production, rail</t>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1081" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1081" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1081" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1081" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1081" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1081" t="inlineStr">
+        <is>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="inlineStr">
         <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="B1082" t="inlineStr">
+          <t xml:space="preserve">hydrogen fuel tank mounting rack production, rail</t>
+        </is>
+      </c>
+      <c r="B1082">
+        <v>1</v>
+      </c>
+      <c r="C1082" t="inlineStr">
         <is>
           <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1082" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1082" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1082" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hydrogen fuel tank mounting rack, rail</t>
+        </is>
+      </c>
+      <c r="I1082" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hydrogen fuel tank mounting rack, rail</t>
         </is>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" t="inlineStr">
         <is>
-          <t>production amount</t>
+          <t>market for steel, low-alloyed</t>
         </is>
       </c>
       <c r="B1083">
-        <v>1</v>
+        <v>400</v>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1083" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1083" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1083" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I1083" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" t="inlineStr">
         <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="B1084" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hydrogen fuel tank valve and control system, rail</t>
-        </is>
-      </c>
-    </row>
-    <row r="1085">
-      <c r="A1085" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="B1085" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-    </row>
-    <row r="1086">
-      <c r="A1086" t="inlineStr">
-        <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="B1086" t="inlineStr">
-        <is>
-          <t>FCH2RAIL D1.5 railstorage investigation,DLR2021,AnnexBTable20, https://elib.dlr.de/145010/1/FCH2RAIL_D1.5.pdf :TypeIII70MPaTPED surveyreference8.3kgH2,2048x455mm,333Loutervolume,179kgINCLUDINGgas =&gt;170.7kgdry. Supplier surveyreference is not a certifiedcompleteheavyhaullocomotive design.</t>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B1084">
+        <v>100</v>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1084" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1084" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1084" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I1084" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
         </is>
       </c>
     </row>
     <row r="1087">
       <c r="A1087" t="inlineStr">
         <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hydrogen fuel tank valve and control system production, rail</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1089">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hydrogen fuel tank valve and control system, rail</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>FCH2RAIL D1.5 railstorage investigation,DLR2021,AnnexBTable20, https://elib.dlr.de/145010/1/FCH2RAIL_D1.5.pdf :TypeIII70MPaTPED surveyreference8.3kgH2,2048x455mm,333Loutervolume,179kgINCLUDINGgas =&gt;170.7kgdry. Supplier surveyreference is not a certifiedcompleteheavyhaullocomotive design.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B1087" t="inlineStr">
+      <c r="B1093" t="inlineStr">
         <is>
           <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: hydrogen fuel tank, rail shared valves and controls, engineering reference. Former reference product: hydrogen fuel tank, rail shared valves and controls, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED RAIL-SPECIFIC700BAR STORAGE/LIFE REFERENCE, issue69,2026-10-18. FCH2RAIL D1.5 railstorage investigation,DLR2021,AnnexBTable20, https://elib.dlr.de/145010/1/FCH2RAIL_D1.5.pdf :TypeIII70MPaTPED surveyreference8.3kgH2,2048x455mm,333Loutervolume,179kgINCLUDINGgas =&gt;170.7kgdry. Supplier surveyreference is not a certifiedcompleteheavyhaullocomotive design. Preserve current700barworkingpressure and40yearrailmanufacturinghorizon; do not forcepassenger350barorroadbus/truckvessels intoheavyhaul. Existing30323.845714kg cumulativecar-TypeIIIproxy was4sets over40years,with93kgdry/5.6kgH2. Its impliedinstalledgas=oldmass/4*5.6/93=456.488kg. Retain thisimpliedenergy budget as explicitengineeringreference because no route-specificrefuellingrange is documented; not infergasinventory fromlifetimefuelthroughput. Select55surveycylinders*8.3=456.5kgH2capacity,roundingup only0.012kg. Sourcepreserved860kW/.06185kgH2perkWhe implies8.582hfullpower before reserve; actualroute/peakduty,reserveandrefilling range remainunvalidated. Keep10yearvessellife/foursets as existing conservativeassumption,NOT manufacturerlifecertificate;test10-20years ratherthan invent a lifetime saving. Cylinder dry170.7 excludes8.3kgfuel. MaterialBOMunpublished:6mmAl linerat2700kg/m3 overcapsulearea2*pi*outerradius*length,2kgstainlessbosses,2kgPAprotection,remainingCF/epoxy at60/40vol%(1800/1200kg/m3),69.2308wt%fiber. Outerdiametergeometry,linerthickness,actualalloy/fiber andpressurequalification areengineeringassumptions,not a certifiedpressurevessel design.95%materialretention withmatchingprocesswaste and1kWh/kgforming/curing reference; wovenfiber is filamentwindingmanufacturingproxy. Installedvesseldrymass9388.5kg. Dedicatedsharedrack500kg(one40yearset,80%ordinary steel/20%Al) and100kgvalve/manifold/controls(two20yearsets:50stainless,5Cu,5brass,10PA,29.5Al,0.5auxinterfaceboard) are explicitmountingassumptions; no wholelocomotive,tenderchassis ortrack added. Lifetimevesselmanufacture220units,one rack,twoBoPsets are inside oneunit oflifetimeenergy-equipmentreference. Qtyone atlocomotiveproduction,not count220again in perMJadapter. Nominalinstalledstorageenvelope55*.333=18.315m3beforemounting; availablelocomotive/tenderpackaging is unresolved and not asserted tofit. Preserveexistingroad/railoperatingfuel andcompression path;700barpressureunchanged,no unsubstantiatedcompressionenergy saving. Originalrangeandbodyenergy notresimulated. EOL remainswholevehicleboundary,pressurespecificcylinderrecovery gap,no credits. Refreshstoredhydrogenpassengerrailcoefficients andindependentlynormalizefreightrailservices.</t>
         </is>
       </c>
     </row>
-    <row r="1088">
-      <c r="A1088" t="inlineStr">
-        <is>
-          <t>Exchanges</t>
-        </is>
-      </c>
-    </row>
-    <row r="1089">
-      <c r="A1089" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B1089" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C1089" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D1089" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E1089" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F1089" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G1089" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H1089" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="I1089" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-    </row>
-    <row r="1090">
-      <c r="A1090" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hydrogen fuel tank valve and control system production, rail</t>
-        </is>
-      </c>
-      <c r="B1090">
-        <v>1</v>
-      </c>
-      <c r="C1090" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D1090" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="F1090" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="G1090" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hydrogen fuel tank valve and control system, rail</t>
-        </is>
-      </c>
-      <c r="I1090" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hydrogen fuel tank valve and control system, rail</t>
-        </is>
-      </c>
-    </row>
-    <row r="1091">
-      <c r="A1091" t="inlineStr">
-        <is>
-          <t>market for steel, chromium steel 18/8</t>
-        </is>
-      </c>
-      <c r="B1091">
-        <v>50</v>
-      </c>
-      <c r="C1091" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D1091" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F1091" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G1091" t="inlineStr">
-        <is>
-          <t>steel, chromium steel 18/8</t>
-        </is>
-      </c>
-      <c r="I1091" t="inlineStr">
-        <is>
-          <t>steel, chromium steel 18/8</t>
-        </is>
-      </c>
-    </row>
-    <row r="1092">
-      <c r="A1092" t="inlineStr">
-        <is>
-          <t>market for copper, cathode</t>
-        </is>
-      </c>
-      <c r="B1092">
-        <v>5</v>
-      </c>
-      <c r="C1092" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D1092" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F1092" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G1092" t="inlineStr">
-        <is>
-          <t>copper, cathode</t>
-        </is>
-      </c>
-      <c r="I1092" t="inlineStr">
-        <is>
-          <t>copper, cathode</t>
-        </is>
-      </c>
-    </row>
-    <row r="1093">
-      <c r="A1093" t="inlineStr">
-        <is>
-          <t>market for brass</t>
-        </is>
-      </c>
-      <c r="B1093">
-        <v>5</v>
-      </c>
-      <c r="C1093" t="inlineStr">
-        <is>
-          <t>RoW</t>
-        </is>
-      </c>
-      <c r="D1093" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F1093" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G1093" t="inlineStr">
-        <is>
-          <t>brass</t>
-        </is>
-      </c>
-      <c r="I1093" t="inlineStr">
-        <is>
-          <t>brass</t>
-        </is>
-      </c>
-    </row>
     <row r="1094">
       <c r="A1094" t="inlineStr">
         <is>
-          <t>market for nylon 6</t>
-        </is>
-      </c>
-      <c r="B1094">
-        <v>10</v>
-      </c>
-      <c r="C1094" t="inlineStr">
-        <is>
-          <t>RER</t>
-        </is>
-      </c>
-      <c r="D1094" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F1094" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G1094" t="inlineStr">
-        <is>
-          <t>nylon 6</t>
-        </is>
-      </c>
-      <c r="I1094" t="inlineStr">
-        <is>
-          <t>nylon 6</t>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t xml:space="preserve">processwithreferenceproduct</t>
         </is>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" t="inlineStr">
         <is>
-          <t>market for aluminium, wrought alloy</t>
-        </is>
-      </c>
-      <c r="B1095">
-        <v>29.5</v>
-      </c>
-      <c r="C1095" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D1095" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F1095" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G1095" t="inlineStr">
-        <is>
-          <t>aluminium, wrought alloy</t>
-        </is>
-      </c>
-      <c r="I1095" t="inlineStr">
-        <is>
-          <t>aluminium, wrought alloy</t>
+          <t>Exchanges</t>
         </is>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery auxiliary interface and power conditioning unit production</t>
-        </is>
-      </c>
-      <c r="B1096">
-        <v>0.5</v>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
       </c>
       <c r="C1096" t="inlineStr">
         <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1096" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1096" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1096" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1096" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1096" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hydrogen fuel tank valve and control system production, rail</t>
+        </is>
+      </c>
+      <c r="B1097">
+        <v>1</v>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
           <t>GLO</t>
         </is>
       </c>
-      <c r="D1096" t="inlineStr">
+      <c r="D1097" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1097" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1097" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hydrogen fuel tank valve and control system, rail</t>
+        </is>
+      </c>
+      <c r="I1097" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hydrogen fuel tank valve and control system, rail</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>market for steel, chromium steel 18/8</t>
+        </is>
+      </c>
+      <c r="B1098">
+        <v>50</v>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1098" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F1096" t="inlineStr">
+      <c r="F1098" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G1096" t="inlineStr">
-        <is>
-          <t xml:space="preserve">battery auxiliary interface and power conditioning unit</t>
-        </is>
-      </c>
-      <c r="I1096" t="inlineStr">
-        <is>
-          <t xml:space="preserve">battery auxiliary interface and power conditioning unit</t>
+      <c r="G1098" t="inlineStr">
+        <is>
+          <t>steel, chromium steel 18/8</t>
+        </is>
+      </c>
+      <c r="I1098" t="inlineStr">
+        <is>
+          <t>steel, chromium steel 18/8</t>
         </is>
       </c>
     </row>
     <row r="1099">
       <c r="A1099" t="inlineStr">
         <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B1099" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hydrogen fuel tank system production, rail, 700 bar</t>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B1099">
+        <v>5</v>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1099" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1099" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1099" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I1099" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
         </is>
       </c>
     </row>
     <row r="1100">
       <c r="A1100" t="inlineStr">
         <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="B1100" t="inlineStr">
-        <is>
-          <t>GLO</t>
+          <t>market for brass</t>
+        </is>
+      </c>
+      <c r="B1100">
+        <v>5</v>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1100" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1100" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1100" t="inlineStr">
+        <is>
+          <t>brass</t>
+        </is>
+      </c>
+      <c r="I1100" t="inlineStr">
+        <is>
+          <t>brass</t>
         </is>
       </c>
     </row>
     <row r="1101">
       <c r="A1101" t="inlineStr">
         <is>
-          <t>production amount</t>
+          <t>market for nylon 6</t>
         </is>
       </c>
       <c r="B1101">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1101" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1101" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1101" t="inlineStr">
+        <is>
+          <t>nylon 6</t>
+        </is>
+      </c>
+      <c r="I1101" t="inlineStr">
+        <is>
+          <t>nylon 6</t>
+        </is>
       </c>
     </row>
     <row r="1102">
       <c r="A1102" t="inlineStr">
         <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="B1102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hydrogen fuel tank system, rail, 700 bar</t>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B1102">
+        <v>29.5</v>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1102" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1102" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1102" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I1102" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
         </is>
       </c>
     </row>
     <row r="1103">
       <c r="A1103" t="inlineStr">
         <is>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit production</t>
+        </is>
+      </c>
+      <c r="B1103">
+        <v>0.5</v>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1103" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1103" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit</t>
+        </is>
+      </c>
+      <c r="I1103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hydrogen fuel tank system production, rail, 700 bar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hydrogen fuel tank system, rail, 700 bar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="B1103" t="inlineStr">
+      <c r="B1110" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
     </row>
-    <row r="1104">
-      <c r="A1104" t="inlineStr">
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="B1104" t="inlineStr">
+      <c r="B1111" t="inlineStr">
         <is>
           <t>FCH2RAIL D1.5 railstorage investigation,DLR2021,AnnexBTable20, https://elib.dlr.de/145010/1/FCH2RAIL_D1.5.pdf :TypeIII70MPaTPED surveyreference8.3kgH2,2048x455mm,333Loutervolume,179kgINCLUDINGgas =&gt;170.7kgdry. Supplier surveyreference is not a certifiedcompleteheavyhaullocomotive design.</t>
         </is>
       </c>
     </row>
-    <row r="1105">
-      <c r="A1105" t="inlineStr">
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B1105" t="inlineStr">
+      <c r="B1112" t="inlineStr">
         <is>
           <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: hydrogen fuel tank system, rail700bar lifetime reference. Former reference product: hydrogen fuel tank system, rail700bar lifetime reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED RAIL-SPECIFIC700BAR STORAGE/LIFE REFERENCE, issue69,2026-10-18. FCH2RAIL D1.5 railstorage investigation,DLR2021,AnnexBTable20, https://elib.dlr.de/145010/1/FCH2RAIL_D1.5.pdf :TypeIII70MPaTPED surveyreference8.3kgH2,2048x455mm,333Loutervolume,179kgINCLUDINGgas =&gt;170.7kgdry. Supplier surveyreference is not a certifiedcompleteheavyhaullocomotive design. Preserve current700barworkingpressure and40yearrailmanufacturinghorizon; do not forcepassenger350barorroadbus/truckvessels intoheavyhaul. Existing30323.845714kg cumulativecar-TypeIIIproxy was4sets over40years,with93kgdry/5.6kgH2. Its impliedinstalledgas=oldmass/4*5.6/93=456.488kg. Retain thisimpliedenergy budget as explicitengineeringreference because no route-specificrefuellingrange is documented; not infergasinventory fromlifetimefuelthroughput. Select55surveycylinders*8.3=456.5kgH2capacity,roundingup only0.012kg. Sourcepreserved860kW/.06185kgH2perkWhe implies8.582hfullpower before reserve; actualroute/peakduty,reserveandrefilling range remainunvalidated. Keep10yearvessellife/foursets as existing conservativeassumption,NOT manufacturerlifecertificate;test10-20years ratherthan invent a lifetime saving. Cylinder dry170.7 excludes8.3kgfuel. MaterialBOMunpublished:6mmAl linerat2700kg/m3 overcapsulearea2*pi*outerradius*length,2kgstainlessbosses,2kgPAprotection,remainingCF/epoxy at60/40vol%(1800/1200kg/m3),69.2308wt%fiber. Outerdiametergeometry,linerthickness,actualalloy/fiber andpressurequalification areengineeringassumptions,not a certifiedpressurevessel design.95%materialretention withmatchingprocesswaste and1kWh/kgforming/curing reference; wovenfiber is filamentwindingmanufacturingproxy. Installedvesseldrymass9388.5kg. Dedicatedsharedrack500kg(one40yearset,80%ordinary steel/20%Al) and100kgvalve/manifold/controls(two20yearsets:50stainless,5Cu,5brass,10PA,29.5Al,0.5auxinterfaceboard) are explicitmountingassumptions; no wholelocomotive,tenderchassis ortrack added. Lifetimevesselmanufacture220units,one rack,twoBoPsets are inside oneunit oflifetimeenergy-equipmentreference. Qtyone atlocomotiveproduction,not count220again in perMJadapter. Nominalinstalledstorageenvelope55*.333=18.315m3beforemounting; availablelocomotive/tenderpackaging is unresolved and not asserted tofit. Preserveexistingroad/railoperatingfuel andcompression path;700barpressureunchanged,no unsubstantiatedcompressionenergy saving. Originalrangeandbodyenergy notresimulated. EOL remainswholevehicleboundary,pressurespecificcylinderrecovery gap,no credits. Refreshstoredhydrogenpassengerrailcoefficients andindependentlynormalizefreightrailservices.</t>
         </is>
       </c>
     </row>
-    <row r="1106">
-      <c r="A1106" t="inlineStr">
-        <is>
-          <t>Exchanges</t>
-        </is>
-      </c>
-    </row>
-    <row r="1107">
-      <c r="A1107" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B1107" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C1107" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D1107" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E1107" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F1107" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G1107" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H1107" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="I1107" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-    </row>
-    <row r="1108">
-      <c r="A1108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hydrogen fuel tank system production, rail, 700 bar</t>
-        </is>
-      </c>
-      <c r="B1108">
-        <v>1</v>
-      </c>
-      <c r="C1108" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D1108" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="F1108" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="G1108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hydrogen fuel tank system, rail, 700 bar</t>
-        </is>
-      </c>
-      <c r="I1108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hydrogen fuel tank system, rail, 700 bar</t>
-        </is>
-      </c>
-    </row>
-    <row r="1109">
-      <c r="A1109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hydrogen fuel tank production, rail, type III cylinder, 700 bar</t>
-        </is>
-      </c>
-      <c r="B1109">
-        <v>220</v>
-      </c>
-      <c r="C1109" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D1109" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="F1109" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G1109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hydrogen fuel tank, rail, type III cylinder, 700 bar</t>
-        </is>
-      </c>
-      <c r="I1109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hydrogen fuel tank, rail, type III cylinder, 700 bar</t>
-        </is>
-      </c>
-    </row>
-    <row r="1110">
-      <c r="A1110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hydrogen fuel tank mounting rack production, rail</t>
-        </is>
-      </c>
-      <c r="B1110">
-        <v>1</v>
-      </c>
-      <c r="C1110" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D1110" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="F1110" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G1110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hydrogen fuel tank mounting rack, rail</t>
-        </is>
-      </c>
-      <c r="I1110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hydrogen fuel tank mounting rack, rail</t>
-        </is>
-      </c>
-    </row>
-    <row r="1111">
-      <c r="A1111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hydrogen fuel tank valve and control system production, rail</t>
-        </is>
-      </c>
-      <c r="B1111">
-        <v>2</v>
-      </c>
-      <c r="C1111" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D1111" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="F1111" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G1111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hydrogen fuel tank valve and control system, rail</t>
-        </is>
-      </c>
-      <c r="I1111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hydrogen fuel tank valve and control system, rail</t>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">processwithreferenceproduct</t>
         </is>
       </c>
     </row>
     <row r="1114">
       <c r="A1114" t="inlineStr">
         <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B1114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">excitation controller production, rail generator, analog</t>
+          <t>Exchanges</t>
         </is>
       </c>
     </row>
     <row r="1115">
       <c r="A1115" t="inlineStr">
         <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
           <t>location</t>
         </is>
       </c>
-      <c r="B1115" t="inlineStr">
-        <is>
-          <t>GLO</t>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1115" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1115" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1115" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1115" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1115" t="inlineStr">
+        <is>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="1116">
       <c r="A1116" t="inlineStr">
         <is>
-          <t>production amount</t>
+          <t xml:space="preserve">hydrogen fuel tank system production, rail, 700 bar</t>
         </is>
       </c>
       <c r="B1116">
         <v>1</v>
       </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1116" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hydrogen fuel tank system, rail, 700 bar</t>
+        </is>
+      </c>
+      <c r="I1116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hydrogen fuel tank system, rail, 700 bar</t>
+        </is>
+      </c>
     </row>
     <row r="1117">
       <c r="A1117" t="inlineStr">
         <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="B1117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">excitation controller, rail generator, analog</t>
+          <t xml:space="preserve">hydrogen fuel tank production, rail, type 3 cylinder, 700 bar</t>
+        </is>
+      </c>
+      <c r="B1117">
+        <v>220</v>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1117" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hydrogen fuel tank, rail, type III cylinder, 700 bar</t>
+        </is>
+      </c>
+      <c r="I1117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hydrogen fuel tank, rail, type III cylinder, 700 bar</t>
         </is>
       </c>
     </row>
     <row r="1118">
       <c r="A1118" t="inlineStr">
         <is>
+          <t xml:space="preserve">hydrogen fuel tank mounting rack production, rail</t>
+        </is>
+      </c>
+      <c r="B1118">
+        <v>1</v>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1118" t="inlineStr">
+        <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="B1118" t="inlineStr">
-        <is>
-          <t>unit</t>
+      <c r="F1118" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hydrogen fuel tank mounting rack, rail</t>
+        </is>
+      </c>
+      <c r="I1118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hydrogen fuel tank mounting rack, rail</t>
         </is>
       </c>
     </row>
     <row r="1119">
       <c r="A1119" t="inlineStr">
         <is>
+          <t xml:space="preserve">hydrogen fuel tank valve and control system production, rail</t>
+        </is>
+      </c>
+      <c r="B1119">
+        <v>2</v>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1119" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hydrogen fuel tank valve and control system, rail</t>
+        </is>
+      </c>
+      <c r="I1119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hydrogen fuel tank valve and control system, rail</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">excitation controller production, rail generator, analog</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">excitation controller, rail generator, analog</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
           <t>source</t>
         </is>
       </c>
-      <c r="B1119" t="inlineStr">
+      <c r="B1127" t="inlineStr">
         <is>
           <t>ABB NMG catalogue9AKK2017109096:page10 continuous60Hz40C,pf0.8,NMG0500DD04 DAPI 3590kVA/2872kW at460V;page17 net7050kg,gross7730kg. OldNMG0450DD04 at460V60Hz is2072kW,not2.8MW. https://search.abb.com/library/Download.aspx?DocumentID=9AKK2017109096&amp;LanguageCode=en&amp;DocumentPartId=&amp;Action=Launch . Material analogue:ABB AMG0900 5125kVA11kV EPD2000 pages2-3,https://library.e.abb.com/public/2bb39d909d618031c1256d63003c5c76/EPD%20for%20AMG%20900.pdf . Use kg/product column; kg/kVA column is visibly misaligned.</t>
         </is>
       </c>
     </row>
-    <row r="1120">
-      <c r="A1120" t="inlineStr">
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B1120" t="inlineStr">
+      <c r="B1128" t="inlineStr">
         <is>
           <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: rail generator analog excitation controller, engineering material reference. Former reference product: rail generator analog excitation controller, engineering material reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED RAIL GENERATOR FUNCTION AND RATING, issue104,2026-10-18. ABB NMG catalogue9AKK2017109096:page10 continuous60Hz40C,pf0.8,NMG0500DD04 DAPI 3590kVA/2872kW at460V;page17 net7050kg,gross7730kg. OldNMG0450DD04 at460V60Hz is2072kW,not2.8MW. https://search.abb.com/library/Download.aspx?DocumentID=9AKK2017109096&amp;LanguageCode=en&amp;DocumentPartId=&amp;Action=Launch . Material analogue:ABB AMG0900 5125kVA11kV EPD2000 pages2-3,https://library.e.abb.com/public/2bb39d909d618031c1256d63003c5c76/EPD%20for%20AMG%20900.pdf . Use kg/product column; kg/kVA column is visibly misaligned. Existing locomotive buys4410kg of unspecified passive electronics as a generator proxy; native mixture assigns153.468kg tantalum-capacitor packages,NOT elementalTa. Replace with7050kg of a dedicated synchronous powertrain-generator engineering reference. Selected industrial model rated2872kW is sufficient for the stated2800kW duty at460V/60Hz/pf0.8. This is not a rail-qualified UKlight generator or proof of compatible BORDLINE DC-link voltage:actual rail speed/voltage,rectification,EMC,cooling and mass require project-specific verification. Source mass is not scaled linearly fromkVA. Keep original40year generator allocation as a service assumption; EPD25year operation is not transferred as measured rail life. Test mass4410/7050/9000kg and20-40year service; keep operating diesel demand unchanged. Material composition is transferred PERkg from the much heavier,11kV medium-speed AMG0900,not claimed a published NMG BOM:kg/product={'electricalsteel': 7120.0, 'steel': 10900.0, 'forgedsteel': 5323.0, 'Al': 13.0, 'Cu': 2461.0, 'insulation': 155.0, 'resin': 225.0, 'paint': 40.0},installed total26237kg excluding800kg wood. Reserve1kg of the7050kg budget for an explicit analog excitation/AVR material reference; scale the remaining7049kg by these normalized fractions. The1kg AVR partition is an engineering allocation,not manufacturer traceability. Electricalsteel uses the existing3.2%Si reference;other/forgedsteel generic lowalloy feed,insulation glassfibre,impregnation epoxy,paint alkyd are stated material proxies. Existing electricalsteel rolling stays in its supplier;do not add a second generic metalworking energy package. EPD manufacturing40122kWh electricity and9659kWh heat per26237kg provide an aggregate factory-energy reference perkg,not operating losses. Potential factory/service overlap,forging details,lamination yield and actual coating remain gaps. AVR reference1kg contains0.05m2 unmountedPWB at assumed3.08kg/m2,6glassdiodes at0.596g,50gchoke,30gfilmcapacitor,10gmetalfilmresistors,5gSMTtransistors,100gCu,400gAl,100gepoxy andremainingsteel. This is an explicit analog material budget,not validated excitation circuit or a universal zeroTa/PM claim. Wound-field generator excitation is represented by the winding material budget;no unsupported full-machine permanent magnets. Full7050kg generator goes once toWEEE;AVR has no extra disposal. Native WEEE treatment is a proxy,not recoveryshare analysis. Gross-minus-net680kg shipping-package composition unresolved and excluded from installed mass;do not assign it invented metals. Rewire six passenger-train perMJ copies and provenance with unchanged lifetime-energy denominator;source generator kg increases7050/4410. Traction converter,motor,engine,tank,chassis and track unchanged. Only existing rail/final-energy workbooks;no runtime or native edits.</t>
         </is>
       </c>
     </row>
-    <row r="1121">
-      <c r="A1121" t="inlineStr">
-        <is>
-          <t>Exchanges</t>
-        </is>
-      </c>
-    </row>
-    <row r="1122">
-      <c r="A1122" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B1122" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C1122" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D1122" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E1122" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F1122" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G1122" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H1122" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="I1122" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-    </row>
-    <row r="1123">
-      <c r="A1123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">excitation controller production, rail generator, analog</t>
-        </is>
-      </c>
-      <c r="B1123">
-        <v>1</v>
-      </c>
-      <c r="C1123" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D1123" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="F1123" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="G1123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">excitation controller, rail generator, analog</t>
-        </is>
-      </c>
-      <c r="I1123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">excitation controller, rail generator, analog</t>
-        </is>
-      </c>
-    </row>
-    <row r="1124">
-      <c r="A1124" t="inlineStr">
-        <is>
-          <t>market for printed wiring board, for surface mounting, Pb free surface</t>
-        </is>
-      </c>
-      <c r="B1124">
-        <v>0.05</v>
-      </c>
-      <c r="C1124" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D1124" t="inlineStr">
-        <is>
-          <t>square meter</t>
-        </is>
-      </c>
-      <c r="F1124" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G1124" t="inlineStr">
-        <is>
-          <t>printed wiring board, for surface mounting, Pb free surface</t>
-        </is>
-      </c>
-      <c r="I1124" t="inlineStr">
-        <is>
-          <t>printed wiring board, for surface mounting, Pb free surface</t>
-        </is>
-      </c>
-    </row>
-    <row r="1125">
-      <c r="A1125" t="inlineStr">
-        <is>
-          <t>market for diode, glass-, for through-hole mounting</t>
-        </is>
-      </c>
-      <c r="B1125">
-        <v>0.0035759999999999998</v>
-      </c>
-      <c r="C1125" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D1125" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F1125" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G1125" t="inlineStr">
-        <is>
-          <t>diode, glass-, for through-hole mounting</t>
-        </is>
-      </c>
-      <c r="I1125" t="inlineStr">
-        <is>
-          <t>diode, glass-, for through-hole mounting</t>
-        </is>
-      </c>
-    </row>
-    <row r="1126">
-      <c r="A1126" t="inlineStr">
-        <is>
-          <t>market for inductor, ring core choke type</t>
-        </is>
-      </c>
-      <c r="B1126">
-        <v>0.05</v>
-      </c>
-      <c r="C1126" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D1126" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F1126" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G1126" t="inlineStr">
-        <is>
-          <t>inductor, ring core choke type</t>
-        </is>
-      </c>
-      <c r="I1126" t="inlineStr">
-        <is>
-          <t>inductor, ring core choke type</t>
-        </is>
-      </c>
-    </row>
-    <row r="1127">
-      <c r="A1127" t="inlineStr">
-        <is>
-          <t>market for capacitor, film type, for through-hole mounting</t>
-        </is>
-      </c>
-      <c r="B1127">
-        <v>0.03</v>
-      </c>
-      <c r="C1127" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D1127" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F1127" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G1127" t="inlineStr">
-        <is>
-          <t>capacitor, film type, for through-hole mounting</t>
-        </is>
-      </c>
-      <c r="I1127" t="inlineStr">
-        <is>
-          <t>capacitor, film type, for through-hole mounting</t>
-        </is>
-      </c>
-    </row>
-    <row r="1128">
-      <c r="A1128" t="inlineStr">
-        <is>
-          <t>market for resistor, metal film type, through-hole mounting</t>
-        </is>
-      </c>
-      <c r="B1128">
-        <v>0.01</v>
-      </c>
-      <c r="C1128" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D1128" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F1128" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G1128" t="inlineStr">
-        <is>
-          <t>resistor, metal film type, through-hole mounting</t>
-        </is>
-      </c>
-      <c r="I1128" t="inlineStr">
-        <is>
-          <t>resistor, metal film type, through-hole mounting</t>
-        </is>
-      </c>
-    </row>
     <row r="1129">
       <c r="A1129" t="inlineStr">
         <is>
-          <t>market for transistor, surface-mounted</t>
-        </is>
-      </c>
-      <c r="B1129">
-        <v>0.005</v>
-      </c>
-      <c r="C1129" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D1129" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F1129" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G1129" t="inlineStr">
-        <is>
-          <t>transistor, surface-mounted</t>
-        </is>
-      </c>
-      <c r="I1129" t="inlineStr">
-        <is>
-          <t>transistor, surface-mounted</t>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">processwithreferenceproduct</t>
         </is>
       </c>
     </row>
     <row r="1130">
       <c r="A1130" t="inlineStr">
         <is>
-          <t>market for copper, cathode</t>
-        </is>
-      </c>
-      <c r="B1130">
-        <v>0.1</v>
-      </c>
-      <c r="C1130" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D1130" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F1130" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G1130" t="inlineStr">
-        <is>
-          <t>copper, cathode</t>
-        </is>
-      </c>
-      <c r="I1130" t="inlineStr">
-        <is>
-          <t>copper, cathode</t>
+          <t>Exchanges</t>
         </is>
       </c>
     </row>
     <row r="1131">
       <c r="A1131" t="inlineStr">
         <is>
-          <t>market for aluminium, wrought alloy</t>
-        </is>
-      </c>
-      <c r="B1131">
-        <v>0.4</v>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
       </c>
       <c r="C1131" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>location</t>
         </is>
       </c>
       <c r="D1131" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1131" t="inlineStr">
+        <is>
+          <t>categories</t>
         </is>
       </c>
       <c r="F1131" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>type</t>
         </is>
       </c>
       <c r="G1131" t="inlineStr">
         <is>
-          <t>aluminium, wrought alloy</t>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1131" t="inlineStr">
+        <is>
+          <t>comment</t>
         </is>
       </c>
       <c r="I1131" t="inlineStr">
         <is>
-          <t>aluminium, wrought alloy</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" t="inlineStr">
         <is>
-          <t>market for epoxy resin, liquid</t>
+          <t xml:space="preserve">excitation controller production, rail generator, analog</t>
         </is>
       </c>
       <c r="B1132">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="C1132" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D1132" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="F1132" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>production</t>
         </is>
       </c>
       <c r="G1132" t="inlineStr">
         <is>
-          <t>epoxy resin, liquid</t>
+          <t xml:space="preserve">excitation controller, rail generator, analog</t>
         </is>
       </c>
       <c r="I1132" t="inlineStr">
         <is>
-          <t>epoxy resin, liquid</t>
+          <t xml:space="preserve">excitation controller, rail generator, analog</t>
         </is>
       </c>
     </row>
     <row r="1133">
       <c r="A1133" t="inlineStr">
         <is>
-          <t>market for steel, low-alloyed</t>
+          <t>market for printed wiring board, for surface mounting, Pb free surface</t>
         </is>
       </c>
       <c r="B1133">
-        <v>0.14742399999999986</v>
+        <v>0.05</v>
       </c>
       <c r="C1133" t="inlineStr">
         <is>
@@ -22922,7 +22715,7 @@
       </c>
       <c r="D1133" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>square meter</t>
         </is>
       </c>
       <c r="F1133" t="inlineStr">
@@ -22932,23 +22725,23 @@
       </c>
       <c r="G1133" t="inlineStr">
         <is>
-          <t>steel, low-alloyed</t>
+          <t>printed wiring board, for surface mounting, Pb free surface</t>
         </is>
       </c>
       <c r="I1133" t="inlineStr">
         <is>
-          <t>steel, low-alloyed</t>
+          <t>printed wiring board, for surface mounting, Pb free surface</t>
         </is>
       </c>
     </row>
     <row r="1134">
       <c r="A1134" t="inlineStr">
         <is>
-          <t>market group for electricity, medium voltage</t>
+          <t>market for diode, glass-, for through-hole mounting</t>
         </is>
       </c>
       <c r="B1134">
-        <v>1</v>
+        <v>0.0035759999999999998</v>
       </c>
       <c r="C1134" t="inlineStr">
         <is>
@@ -22957,7 +22750,7 @@
       </c>
       <c r="D1134" t="inlineStr">
         <is>
-          <t>kilowatt hour</t>
+          <t>kilogram</t>
         </is>
       </c>
       <c r="F1134" t="inlineStr">
@@ -22967,574 +22760,901 @@
       </c>
       <c r="G1134" t="inlineStr">
         <is>
-          <t>electricity, medium voltage</t>
+          <t>diode, glass-, for through-hole mounting</t>
         </is>
       </c>
       <c r="I1134" t="inlineStr">
         <is>
-          <t>electricity, medium voltage</t>
+          <t>diode, glass-, for through-hole mounting</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>market for inductor, ring core choke type</t>
+        </is>
+      </c>
+      <c r="B1135">
+        <v>0.05</v>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1135" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1135" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1135" t="inlineStr">
+        <is>
+          <t>inductor, ring core choke type</t>
+        </is>
+      </c>
+      <c r="I1135" t="inlineStr">
+        <is>
+          <t>inductor, ring core choke type</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>market for capacitor, film type, for through-hole mounting</t>
+        </is>
+      </c>
+      <c r="B1136">
+        <v>0.03</v>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1136" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1136" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1136" t="inlineStr">
+        <is>
+          <t>capacitor, film type, for through-hole mounting</t>
+        </is>
+      </c>
+      <c r="I1136" t="inlineStr">
+        <is>
+          <t>capacitor, film type, for through-hole mounting</t>
         </is>
       </c>
     </row>
     <row r="1137">
       <c r="A1137" t="inlineStr">
         <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B1137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">traction generator production, synchronous, rail</t>
+          <t>market for resistor, metal film type, through-hole mounting</t>
+        </is>
+      </c>
+      <c r="B1137">
+        <v>0.01</v>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1137" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1137" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1137" t="inlineStr">
+        <is>
+          <t>resistor, metal film type, through-hole mounting</t>
+        </is>
+      </c>
+      <c r="I1137" t="inlineStr">
+        <is>
+          <t>resistor, metal film type, through-hole mounting</t>
         </is>
       </c>
     </row>
     <row r="1138">
       <c r="A1138" t="inlineStr">
         <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="B1138" t="inlineStr">
+          <t>market for transistor, surface-mounted</t>
+        </is>
+      </c>
+      <c r="B1138">
+        <v>0.005</v>
+      </c>
+      <c r="C1138" t="inlineStr">
         <is>
           <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1138" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1138" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1138" t="inlineStr">
+        <is>
+          <t>transistor, surface-mounted</t>
+        </is>
+      </c>
+      <c r="I1138" t="inlineStr">
+        <is>
+          <t>transistor, surface-mounted</t>
         </is>
       </c>
     </row>
     <row r="1139">
       <c r="A1139" t="inlineStr">
         <is>
-          <t>production amount</t>
+          <t>market for copper, cathode</t>
         </is>
       </c>
       <c r="B1139">
-        <v>1</v>
+        <v>0.1</v>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1139" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1139" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1139" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I1139" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
       </c>
     </row>
     <row r="1140">
       <c r="A1140" t="inlineStr">
         <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="B1140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">traction generator, synchronous, rail</t>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B1140">
+        <v>0.4</v>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1140" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1140" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1140" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I1140" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
         </is>
       </c>
     </row>
     <row r="1141">
       <c r="A1141" t="inlineStr">
         <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="B1141" t="inlineStr">
+          <t>market for epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="B1141">
+        <v>0.1</v>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1141" t="inlineStr">
         <is>
           <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1141" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1141" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="I1141" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
         </is>
       </c>
     </row>
     <row r="1142">
       <c r="A1142" t="inlineStr">
         <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="B1142" t="inlineStr">
-        <is>
-          <t>ABB NMG catalogue9AKK2017109096:page10 continuous60Hz40C,pf0.8,NMG0500DD04 DAPI 3590kVA/2872kW at460V;page17 net7050kg,gross7730kg. OldNMG0450DD04 at460V60Hz is2072kW,not2.8MW. https://search.abb.com/library/Download.aspx?DocumentID=9AKK2017109096&amp;LanguageCode=en&amp;DocumentPartId=&amp;Action=Launch . Material analogue:ABB AMG0900 5125kVA11kV EPD2000 pages2-3,https://library.e.abb.com/public/2bb39d909d618031c1256d63003c5c76/EPD%20for%20AMG%20900.pdf . Use kg/product column; kg/kVA column is visibly misaligned.</t>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B1142">
+        <v>0.14742399999999986</v>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1142" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1142" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1142" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I1142" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
         </is>
       </c>
     </row>
     <row r="1143">
       <c r="A1143" t="inlineStr">
         <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1143">
+        <v>1</v>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1143" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1143" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1143" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I1143" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">traction generator production, synchronous, rail</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1148">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">traction generator, synchronous, rail</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>ABB NMG catalogue9AKK2017109096:page10 continuous60Hz40C,pf0.8,NMG0500DD04 DAPI 3590kVA/2872kW at460V;page17 net7050kg,gross7730kg. OldNMG0450DD04 at460V60Hz is2072kW,not2.8MW. https://search.abb.com/library/Download.aspx?DocumentID=9AKK2017109096&amp;LanguageCode=en&amp;DocumentPartId=&amp;Action=Launch . Material analogue:ABB AMG0900 5125kVA11kV EPD2000 pages2-3,https://library.e.abb.com/public/2bb39d909d618031c1256d63003c5c76/EPD%20for%20AMG%20900.pdf . Use kg/product column; kg/kVA column is visibly misaligned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B1143" t="inlineStr">
+      <c r="B1152" t="inlineStr">
         <is>
           <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: rail powertrain generator, synchronous engineering reference. Former reference product: rail powertrain generator, synchronous engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED RAIL GENERATOR FUNCTION AND RATING, issue104,2026-10-18. ABB NMG catalogue9AKK2017109096:page10 continuous60Hz40C,pf0.8,NMG0500DD04 DAPI 3590kVA/2872kW at460V;page17 net7050kg,gross7730kg. OldNMG0450DD04 at460V60Hz is2072kW,not2.8MW. https://search.abb.com/library/Download.aspx?DocumentID=9AKK2017109096&amp;LanguageCode=en&amp;DocumentPartId=&amp;Action=Launch . Material analogue:ABB AMG0900 5125kVA11kV EPD2000 pages2-3,https://library.e.abb.com/public/2bb39d909d618031c1256d63003c5c76/EPD%20for%20AMG%20900.pdf . Use kg/product column; kg/kVA column is visibly misaligned. Existing locomotive buys4410kg of unspecified passive electronics as a generator proxy; native mixture assigns153.468kg tantalum-capacitor packages,NOT elementalTa. Replace with7050kg of a dedicated synchronous powertrain-generator engineering reference. Selected industrial model rated2872kW is sufficient for the stated2800kW duty at460V/60Hz/pf0.8. This is not a rail-qualified UKlight generator or proof of compatible BORDLINE DC-link voltage:actual rail speed/voltage,rectification,EMC,cooling and mass require project-specific verification. Source mass is not scaled linearly fromkVA. Keep original40year generator allocation as a service assumption; EPD25year operation is not transferred as measured rail life. Test mass4410/7050/9000kg and20-40year service; keep operating diesel demand unchanged. Material composition is transferred PERkg from the much heavier,11kV medium-speed AMG0900,not claimed a published NMG BOM:kg/product={'electricalsteel': 7120.0, 'steel': 10900.0, 'forgedsteel': 5323.0, 'Al': 13.0, 'Cu': 2461.0, 'insulation': 155.0, 'resin': 225.0, 'paint': 40.0},installed total26237kg excluding800kg wood. Reserve1kg of the7050kg budget for an explicit analog excitation/AVR material reference; scale the remaining7049kg by these normalized fractions. The1kg AVR partition is an engineering allocation,not manufacturer traceability. Electricalsteel uses the existing3.2%Si reference;other/forgedsteel generic lowalloy feed,insulation glassfibre,impregnation epoxy,paint alkyd are stated material proxies. Existing electricalsteel rolling stays in its supplier;do not add a second generic metalworking energy package. EPD manufacturing40122kWh electricity and9659kWh heat per26237kg provide an aggregate factory-energy reference perkg,not operating losses. Potential factory/service overlap,forging details,lamination yield and actual coating remain gaps. AVR reference1kg contains0.05m2 unmountedPWB at assumed3.08kg/m2,6glassdiodes at0.596g,50gchoke,30gfilmcapacitor,10gmetalfilmresistors,5gSMTtransistors,100gCu,400gAl,100gepoxy andremainingsteel. This is an explicit analog material budget,not validated excitation circuit or a universal zeroTa/PM claim. Wound-field generator excitation is represented by the winding material budget;no unsupported full-machine permanent magnets. Full7050kg generator goes once toWEEE;AVR has no extra disposal. Native WEEE treatment is a proxy,not recoveryshare analysis. Gross-minus-net680kg shipping-package composition unresolved and excluded from installed mass;do not assign it invented metals. Rewire six passenger-train perMJ copies and provenance with unchanged lifetime-energy denominator;source generator kg increases7050/4410. Traction converter,motor,engine,tank,chassis and track unchanged. Only existing rail/final-energy workbooks;no runtime or native edits.</t>
         </is>
       </c>
     </row>
-    <row r="1144">
-      <c r="A1144" t="inlineStr">
-        <is>
-          <t>Exchanges</t>
-        </is>
-      </c>
-    </row>
-    <row r="1145">
-      <c r="A1145" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B1145" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C1145" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D1145" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E1145" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F1145" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G1145" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H1145" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="I1145" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-    </row>
-    <row r="1146">
-      <c r="A1146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">traction generator production, synchronous, rail</t>
-        </is>
-      </c>
-      <c r="B1146">
-        <v>1</v>
-      </c>
-      <c r="C1146" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D1146" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F1146" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="G1146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">traction generator, synchronous, rail</t>
-        </is>
-      </c>
-      <c r="I1146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">traction generator, synchronous, rail</t>
-        </is>
-      </c>
-    </row>
-    <row r="1147">
-      <c r="A1147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">electrical steel production, non-oriented</t>
-        </is>
-      </c>
-      <c r="B1147">
-        <v>0.2713339966810987</v>
-      </c>
-      <c r="C1147" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D1147" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F1147" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G1147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">electrical steel, non-oriented</t>
-        </is>
-      </c>
-      <c r="I1147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">electrical steel, non-oriented</t>
-        </is>
-      </c>
-    </row>
-    <row r="1148">
-      <c r="A1148" t="inlineStr">
-        <is>
-          <t>market for steel, low-alloyed</t>
-        </is>
-      </c>
-      <c r="B1148">
-        <v>0.6182375601344753</v>
-      </c>
-      <c r="C1148" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D1148" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F1148" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G1148" t="inlineStr">
-        <is>
-          <t>steel, low-alloyed</t>
-        </is>
-      </c>
-      <c r="I1148" t="inlineStr">
-        <is>
-          <t>steel, low-alloyed</t>
-        </is>
-      </c>
-    </row>
-    <row r="1149">
-      <c r="A1149" t="inlineStr">
-        <is>
-          <t>market for aluminium, wrought alloy</t>
-        </is>
-      </c>
-      <c r="B1149">
-        <v>0.0004954131961873992</v>
-      </c>
-      <c r="C1149" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D1149" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F1149" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G1149" t="inlineStr">
-        <is>
-          <t>aluminium, wrought alloy</t>
-        </is>
-      </c>
-      <c r="I1149" t="inlineStr">
-        <is>
-          <t>aluminium, wrought alloy</t>
-        </is>
-      </c>
-    </row>
-    <row r="1150">
-      <c r="A1150" t="inlineStr">
-        <is>
-          <t>market for copper, cathode</t>
-        </is>
-      </c>
-      <c r="B1150">
-        <v>0.09378552890901458</v>
-      </c>
-      <c r="C1150" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D1150" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F1150" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G1150" t="inlineStr">
-        <is>
-          <t>copper, cathode</t>
-        </is>
-      </c>
-      <c r="I1150" t="inlineStr">
-        <is>
-          <t>copper, cathode</t>
-        </is>
-      </c>
-    </row>
-    <row r="1151">
-      <c r="A1151" t="inlineStr">
-        <is>
-          <t>market for glass fibre</t>
-        </is>
-      </c>
-      <c r="B1151">
-        <v>0.00590684964684976</v>
-      </c>
-      <c r="C1151" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D1151" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F1151" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G1151" t="inlineStr">
-        <is>
-          <t>glass fibre</t>
-        </is>
-      </c>
-      <c r="I1151" t="inlineStr">
-        <is>
-          <t>glass fibre</t>
-        </is>
-      </c>
-    </row>
-    <row r="1152">
-      <c r="A1152" t="inlineStr">
-        <is>
-          <t>market for epoxy resin, liquid</t>
-        </is>
-      </c>
-      <c r="B1152">
-        <v>0.00857445916478191</v>
-      </c>
-      <c r="C1152" t="inlineStr">
-        <is>
-          <t>RER</t>
-        </is>
-      </c>
-      <c r="D1152" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F1152" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G1152" t="inlineStr">
-        <is>
-          <t>epoxy resin, liquid</t>
-        </is>
-      </c>
-      <c r="I1152" t="inlineStr">
-        <is>
-          <t>epoxy resin, liquid</t>
-        </is>
-      </c>
-    </row>
     <row r="1153">
       <c r="A1153" t="inlineStr">
         <is>
-          <t>market for alkyd paint, white, without solvent, in 60% solution state</t>
-        </is>
-      </c>
-      <c r="B1153">
-        <v>0.0015243482959612284</v>
-      </c>
-      <c r="C1153" t="inlineStr">
-        <is>
-          <t>RER</t>
-        </is>
-      </c>
-      <c r="D1153" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F1153" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G1153" t="inlineStr">
-        <is>
-          <t>alkyd paint, white, without solvent, in 60% solution state</t>
-        </is>
-      </c>
-      <c r="I1153" t="inlineStr">
-        <is>
-          <t>alkyd paint, white, without solvent, in 60% solution state</t>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">processwithreferenceproduct</t>
         </is>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" t="inlineStr">
         <is>
-          <t xml:space="preserve">excitation controller production, rail generator, analog</t>
-        </is>
-      </c>
-      <c r="B1154">
-        <v>0.00014184397163120567</v>
-      </c>
-      <c r="C1154" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D1154" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="F1154" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G1154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">excitation controller, rail generator, analog</t>
-        </is>
-      </c>
-      <c r="I1154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">excitation controller, rail generator, analog</t>
+          <t>Exchanges</t>
         </is>
       </c>
     </row>
     <row r="1155">
       <c r="A1155" t="inlineStr">
         <is>
-          <t>market group for electricity, medium voltage</t>
-        </is>
-      </c>
-      <c r="B1155">
-        <v>1.529214468117544</v>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
       </c>
       <c r="C1155" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>location</t>
         </is>
       </c>
       <c r="D1155" t="inlineStr">
         <is>
-          <t>kilowatt hour</t>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1155" t="inlineStr">
+        <is>
+          <t>categories</t>
         </is>
       </c>
       <c r="F1155" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>type</t>
         </is>
       </c>
       <c r="G1155" t="inlineStr">
         <is>
-          <t>electricity, medium voltage</t>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1155" t="inlineStr">
+        <is>
+          <t>comment</t>
         </is>
       </c>
       <c r="I1155" t="inlineStr">
         <is>
-          <t>electricity, medium voltage</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="1156">
       <c r="A1156" t="inlineStr">
         <is>
-          <t>market for heat, district or industrial, natural gas</t>
+          <t xml:space="preserve">traction generator production, synchronous, rail</t>
         </is>
       </c>
       <c r="B1156">
-        <v>1.3253192057018715</v>
+        <v>1</v>
       </c>
       <c r="C1156" t="inlineStr">
         <is>
-          <t>RoW</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D1156" t="inlineStr">
         <is>
-          <t>megajoule</t>
+          <t>kilogram</t>
         </is>
       </c>
       <c r="F1156" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>production</t>
         </is>
       </c>
       <c r="G1156" t="inlineStr">
         <is>
-          <t>heat, district or industrial, natural gas</t>
+          <t xml:space="preserve">traction generator, synchronous, rail</t>
         </is>
       </c>
       <c r="I1156" t="inlineStr">
         <is>
-          <t>heat, district or industrial, natural gas</t>
+          <t xml:space="preserve">traction generator, synchronous, rail</t>
         </is>
       </c>
     </row>
     <row r="1157">
       <c r="A1157" t="inlineStr">
         <is>
+          <t xml:space="preserve">electrical steel production, non-oriented</t>
+        </is>
+      </c>
+      <c r="B1157">
+        <v>0.2713339966810987</v>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1157" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1157" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">electrical steel, non-oriented</t>
+        </is>
+      </c>
+      <c r="I1157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">electrical steel, non-oriented</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B1158">
+        <v>0.6182375601344753</v>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1158" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1158" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1158" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I1158" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B1159">
+        <v>0.0004954131961873992</v>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1159" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1159" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1159" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I1159" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B1160">
+        <v>0.09378552890901458</v>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1160" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1160" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1160" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I1160" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>market for glass fibre</t>
+        </is>
+      </c>
+      <c r="B1161">
+        <v>0.00590684964684976</v>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1161" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1161" t="inlineStr">
+        <is>
+          <t>glass fibre</t>
+        </is>
+      </c>
+      <c r="I1161" t="inlineStr">
+        <is>
+          <t>glass fibre</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>market for epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="B1162">
+        <v>0.00857445916478191</v>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1162" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1162" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="I1162" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>market for alkyd paint, white, without solvent, in 60% solution state</t>
+        </is>
+      </c>
+      <c r="B1163">
+        <v>0.0015243482959612284</v>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1163" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1163" t="inlineStr">
+        <is>
+          <t>alkyd paint, white, without solvent, in 60% solution state</t>
+        </is>
+      </c>
+      <c r="I1163" t="inlineStr">
+        <is>
+          <t>alkyd paint, white, without solvent, in 60% solution state</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">excitation controller production, rail generator, analog</t>
+        </is>
+      </c>
+      <c r="B1164">
+        <v>0.00014184397163120567</v>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1164" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">excitation controller, rail generator, analog</t>
+        </is>
+      </c>
+      <c r="I1164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">excitation controller, rail generator, analog</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1165">
+        <v>1.529214468117544</v>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1165" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1165" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I1165" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B1166">
+        <v>1.3253192057018715</v>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1166" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F1166" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1166" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I1166" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
           <t>market for waste electric and electronic equipment</t>
         </is>
       </c>
-      <c r="B1157">
+      <c r="B1167">
         <v>-1</v>
       </c>
-      <c r="C1157" t="inlineStr">
+      <c r="C1167" t="inlineStr">
         <is>
           <t>GLO</t>
         </is>
       </c>
-      <c r="D1157" t="inlineStr">
+      <c r="D1167" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F1157" t="inlineStr">
+      <c r="F1167" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G1157" t="inlineStr">
+      <c r="G1167" t="inlineStr">
         <is>
           <t>waste electric and electronic equipment</t>
         </is>
       </c>
-      <c r="I1157" t="inlineStr">
+      <c r="I1167" t="inlineStr">
         <is>
           <t>waste electric and electronic equipment</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H983" ns2:uid="{2A08E695-FC79-4DF0-ACCB-3B3F78317B74}"/>
+  <autoFilter ref="A1:H984" ns2:uid="{2A08E695-FC79-4DF0-ACCB-3B3F78317B74}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
